--- a/shared_uploads/vsventas.xlsx
+++ b/shared_uploads/vsventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C960806\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF94D14-2EB5-4D33-8044-434726D1C8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D39515C-D785-40A2-B6EA-54709F3921E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8884" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9727" uniqueCount="117">
   <si>
     <t># Mes</t>
   </si>
@@ -387,7 +387,7 @@
     <t>Octubre</t>
   </si>
   <si>
-    <t>Mas Barata Neuquén - 3608</t>
+    <t>Coronel Díaz</t>
   </si>
 </sst>
 </file>
@@ -410,6 +410,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -80129,7 +80130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE92DB44-9108-48C0-9E4D-CDD7D4A1EECC}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K379"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.90625" style="5"/>
@@ -83110,6 +83111,8005 @@
         <v>3</v>
       </c>
     </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>115</v>
+      </c>
+      <c r="B99" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C99" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99">
+        <v>1002</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="4">
+        <v>71649690.109999999</v>
+      </c>
+      <c r="G99" s="4">
+        <v>4247554.88</v>
+      </c>
+      <c r="H99" s="4">
+        <v>56056659.450000003</v>
+      </c>
+      <c r="I99" s="4">
+        <v>3300929.11</v>
+      </c>
+      <c r="J99">
+        <v>1343.82</v>
+      </c>
+      <c r="K99">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>115</v>
+      </c>
+      <c r="B100" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C100" t="s">
+        <v>106</v>
+      </c>
+      <c r="D100">
+        <v>1003</v>
+      </c>
+      <c r="E100" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="4">
+        <v>97713067.370000005</v>
+      </c>
+      <c r="G100" s="4">
+        <v>4106829.05</v>
+      </c>
+      <c r="H100" s="4">
+        <v>76814519.180000007</v>
+      </c>
+      <c r="I100" s="4">
+        <v>3201034.29</v>
+      </c>
+      <c r="J100">
+        <v>1463.443</v>
+      </c>
+      <c r="K100">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>115</v>
+      </c>
+      <c r="B101" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101">
+        <v>1004</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="4">
+        <v>97885830.430000007</v>
+      </c>
+      <c r="G101" s="4">
+        <v>7351848.4400000004</v>
+      </c>
+      <c r="H101" s="4">
+        <v>76933855.730000004</v>
+      </c>
+      <c r="I101" s="4">
+        <v>5734233.4299999997</v>
+      </c>
+      <c r="J101">
+        <v>2209.6019999999999</v>
+      </c>
+      <c r="K101">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C102" t="s">
+        <v>106</v>
+      </c>
+      <c r="D102">
+        <v>1005</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="4">
+        <v>60034497.020000003</v>
+      </c>
+      <c r="H102" s="4">
+        <v>47235833.859999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>115</v>
+      </c>
+      <c r="B103" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103">
+        <v>1006</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="4">
+        <v>67662689.189999998</v>
+      </c>
+      <c r="G103" s="4">
+        <v>3903052.63</v>
+      </c>
+      <c r="H103" s="4">
+        <v>53349058.490000002</v>
+      </c>
+      <c r="I103" s="4">
+        <v>3067096.89</v>
+      </c>
+      <c r="J103">
+        <v>868.17100000000005</v>
+      </c>
+      <c r="K103">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>115</v>
+      </c>
+      <c r="B104" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C104" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104">
+        <v>1007</v>
+      </c>
+      <c r="E104" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="4">
+        <v>120759806.33</v>
+      </c>
+      <c r="G104" s="4">
+        <v>1104229.95</v>
+      </c>
+      <c r="H104" s="4">
+        <v>95444873.75</v>
+      </c>
+      <c r="I104" s="4">
+        <v>849782.92</v>
+      </c>
+      <c r="J104">
+        <v>125.075</v>
+      </c>
+      <c r="K104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>115</v>
+      </c>
+      <c r="B105" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C105" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105">
+        <v>1008</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" s="4">
+        <v>84725815.930000007</v>
+      </c>
+      <c r="G105" s="4">
+        <v>4147738.65</v>
+      </c>
+      <c r="H105" s="4">
+        <v>66564114.289999999</v>
+      </c>
+      <c r="I105" s="4">
+        <v>3237809.47</v>
+      </c>
+      <c r="J105">
+        <v>1681.09</v>
+      </c>
+      <c r="K105">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C106" t="s">
+        <v>106</v>
+      </c>
+      <c r="D106">
+        <v>1010</v>
+      </c>
+      <c r="E106" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="4">
+        <v>46926815.259999998</v>
+      </c>
+      <c r="H106" s="4">
+        <v>36862038.369999997</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C107" t="s">
+        <v>106</v>
+      </c>
+      <c r="D107">
+        <v>1011</v>
+      </c>
+      <c r="E107" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" s="4">
+        <v>62336669.890000001</v>
+      </c>
+      <c r="G107" s="4">
+        <v>849895.09</v>
+      </c>
+      <c r="H107" s="4">
+        <v>49106409.869999997</v>
+      </c>
+      <c r="I107" s="4">
+        <v>674133.78</v>
+      </c>
+      <c r="J107">
+        <v>282.012</v>
+      </c>
+      <c r="K107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C108" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108">
+        <v>1012</v>
+      </c>
+      <c r="E108" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="4">
+        <v>67903159.060000002</v>
+      </c>
+      <c r="G108" s="4">
+        <v>1269775.29</v>
+      </c>
+      <c r="H108" s="4">
+        <v>53091581.460000001</v>
+      </c>
+      <c r="I108" s="4">
+        <v>984083.05</v>
+      </c>
+      <c r="J108">
+        <v>125</v>
+      </c>
+      <c r="K108">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C109" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109">
+        <v>1013</v>
+      </c>
+      <c r="E109" t="s">
+        <v>20</v>
+      </c>
+      <c r="F109" s="4">
+        <v>60600702.520000003</v>
+      </c>
+      <c r="H109" s="4">
+        <v>47586159.859999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C110" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110">
+        <v>1014</v>
+      </c>
+      <c r="E110" t="s">
+        <v>21</v>
+      </c>
+      <c r="F110" s="4">
+        <v>61438982.799999997</v>
+      </c>
+      <c r="H110" s="4">
+        <v>48081892.119999997</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C111" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111">
+        <v>1015</v>
+      </c>
+      <c r="E111" t="s">
+        <v>22</v>
+      </c>
+      <c r="F111" s="4">
+        <v>56122343.960000001</v>
+      </c>
+      <c r="H111" s="4">
+        <v>44106204.329999998</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112">
+        <v>1016</v>
+      </c>
+      <c r="E112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112" s="4">
+        <v>63977037.719999999</v>
+      </c>
+      <c r="H112" s="4">
+        <v>50088362.359999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C113" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113">
+        <v>1017</v>
+      </c>
+      <c r="E113" t="s">
+        <v>24</v>
+      </c>
+      <c r="F113" s="4">
+        <v>57813739.850000001</v>
+      </c>
+      <c r="H113" s="4">
+        <v>45525760.630000003</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C114" t="s">
+        <v>106</v>
+      </c>
+      <c r="D114">
+        <v>1018</v>
+      </c>
+      <c r="E114" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" s="4">
+        <v>40914880.170000002</v>
+      </c>
+      <c r="G114" s="4">
+        <v>271103.46000000002</v>
+      </c>
+      <c r="H114" s="4">
+        <v>32070523.98</v>
+      </c>
+      <c r="I114" s="4">
+        <v>211760.45</v>
+      </c>
+      <c r="J114">
+        <v>111.58799999999999</v>
+      </c>
+      <c r="K114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115">
+        <v>1020</v>
+      </c>
+      <c r="E115" t="s">
+        <v>26</v>
+      </c>
+      <c r="F115" s="4">
+        <v>59966855.789999999</v>
+      </c>
+      <c r="G115" s="4">
+        <v>5795174.8499999996</v>
+      </c>
+      <c r="H115" s="4">
+        <v>47426133.299999997</v>
+      </c>
+      <c r="I115" s="4">
+        <v>4544667.67</v>
+      </c>
+      <c r="J115">
+        <v>1700.431</v>
+      </c>
+      <c r="K115">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C116" t="s">
+        <v>106</v>
+      </c>
+      <c r="D116">
+        <v>1021</v>
+      </c>
+      <c r="E116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116" s="4">
+        <v>87872854.409999996</v>
+      </c>
+      <c r="H116" s="4">
+        <v>68666383.530000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C117" t="s">
+        <v>106</v>
+      </c>
+      <c r="D117">
+        <v>1022</v>
+      </c>
+      <c r="E117" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="4">
+        <v>86363845.560000002</v>
+      </c>
+      <c r="G117" s="4">
+        <v>327168.02</v>
+      </c>
+      <c r="H117" s="4">
+        <v>68523118.909999996</v>
+      </c>
+      <c r="I117" s="4">
+        <v>254095.16</v>
+      </c>
+      <c r="J117">
+        <v>144.72300000000001</v>
+      </c>
+      <c r="K117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>115</v>
+      </c>
+      <c r="B118" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C118" t="s">
+        <v>106</v>
+      </c>
+      <c r="D118">
+        <v>1023</v>
+      </c>
+      <c r="E118" t="s">
+        <v>29</v>
+      </c>
+      <c r="F118" s="4">
+        <v>65989807.560000002</v>
+      </c>
+      <c r="G118" s="4">
+        <v>61190.61</v>
+      </c>
+      <c r="H118" s="4">
+        <v>51904229.18</v>
+      </c>
+      <c r="I118" s="4">
+        <v>47045.83</v>
+      </c>
+      <c r="J118">
+        <v>4.1660000000000004</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>115</v>
+      </c>
+      <c r="B119" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C119" t="s">
+        <v>106</v>
+      </c>
+      <c r="D119">
+        <v>1024</v>
+      </c>
+      <c r="E119" t="s">
+        <v>30</v>
+      </c>
+      <c r="F119" s="4">
+        <v>79943176.409999996</v>
+      </c>
+      <c r="G119" s="4">
+        <v>4245584.09</v>
+      </c>
+      <c r="H119" s="4">
+        <v>62628029.920000002</v>
+      </c>
+      <c r="I119" s="4">
+        <v>3344517.31</v>
+      </c>
+      <c r="J119">
+        <v>1882.509</v>
+      </c>
+      <c r="K119">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>115</v>
+      </c>
+      <c r="B120" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C120" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120">
+        <v>1026</v>
+      </c>
+      <c r="E120" t="s">
+        <v>31</v>
+      </c>
+      <c r="F120" s="4">
+        <v>58886340.189999998</v>
+      </c>
+      <c r="G120" s="4">
+        <v>117484.05</v>
+      </c>
+      <c r="H120" s="4">
+        <v>46638997.549999997</v>
+      </c>
+      <c r="I120" s="4">
+        <v>91025.91</v>
+      </c>
+      <c r="J120">
+        <v>58</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>115</v>
+      </c>
+      <c r="B121" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C121" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121">
+        <v>1027</v>
+      </c>
+      <c r="E121" t="s">
+        <v>32</v>
+      </c>
+      <c r="F121" s="4">
+        <v>16876318.969999999</v>
+      </c>
+      <c r="H121" s="4">
+        <v>13326192.800000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>115</v>
+      </c>
+      <c r="B122" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C122" t="s">
+        <v>106</v>
+      </c>
+      <c r="D122">
+        <v>1028</v>
+      </c>
+      <c r="E122" t="s">
+        <v>33</v>
+      </c>
+      <c r="F122" s="4">
+        <v>50758777.759999998</v>
+      </c>
+      <c r="H122" s="4">
+        <v>39853939.549999997</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>115</v>
+      </c>
+      <c r="B123" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C123" t="s">
+        <v>106</v>
+      </c>
+      <c r="D123">
+        <v>1029</v>
+      </c>
+      <c r="E123" t="s">
+        <v>34</v>
+      </c>
+      <c r="F123" s="4">
+        <v>34733017.030000001</v>
+      </c>
+      <c r="H123" s="4">
+        <v>27276964.57</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>115</v>
+      </c>
+      <c r="B124" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C124" t="s">
+        <v>106</v>
+      </c>
+      <c r="D124">
+        <v>1030</v>
+      </c>
+      <c r="E124" t="s">
+        <v>35</v>
+      </c>
+      <c r="F124" s="4">
+        <v>16864329.010000002</v>
+      </c>
+      <c r="H124" s="4">
+        <v>13330316.17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>115</v>
+      </c>
+      <c r="B125" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C125" t="s">
+        <v>106</v>
+      </c>
+      <c r="D125">
+        <v>1031</v>
+      </c>
+      <c r="E125" t="s">
+        <v>36</v>
+      </c>
+      <c r="F125" s="4">
+        <v>73367368.969999999</v>
+      </c>
+      <c r="G125" s="4">
+        <v>1166521.04</v>
+      </c>
+      <c r="H125" s="4">
+        <v>58407643.520000003</v>
+      </c>
+      <c r="I125" s="4">
+        <v>911505.99</v>
+      </c>
+      <c r="J125">
+        <v>405.77</v>
+      </c>
+      <c r="K125">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>115</v>
+      </c>
+      <c r="B126" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C126" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126">
+        <v>1032</v>
+      </c>
+      <c r="E126" t="s">
+        <v>37</v>
+      </c>
+      <c r="F126" s="4">
+        <v>54137881.859999999</v>
+      </c>
+      <c r="H126" s="4">
+        <v>42693551.810000002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>115</v>
+      </c>
+      <c r="B127" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C127" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127">
+        <v>1033</v>
+      </c>
+      <c r="E127" t="s">
+        <v>38</v>
+      </c>
+      <c r="F127" s="4">
+        <v>51086167.740000002</v>
+      </c>
+      <c r="G127" s="4">
+        <v>201188.37</v>
+      </c>
+      <c r="H127" s="4">
+        <v>40284814.020000003</v>
+      </c>
+      <c r="I127" s="4">
+        <v>155879.74</v>
+      </c>
+      <c r="J127">
+        <v>89</v>
+      </c>
+      <c r="K127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C128" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128">
+        <v>1035</v>
+      </c>
+      <c r="E128" t="s">
+        <v>39</v>
+      </c>
+      <c r="F128" s="4">
+        <v>34258983.630000003</v>
+      </c>
+      <c r="H128" s="4">
+        <v>27109164.129999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>115</v>
+      </c>
+      <c r="B129" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C129" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129">
+        <v>1036</v>
+      </c>
+      <c r="E129" t="s">
+        <v>40</v>
+      </c>
+      <c r="F129" s="4">
+        <v>20361731.98</v>
+      </c>
+      <c r="H129" s="4">
+        <v>16026245.17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>115</v>
+      </c>
+      <c r="B130" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C130" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130">
+        <v>1038</v>
+      </c>
+      <c r="E130" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" s="4">
+        <v>86053321.090000004</v>
+      </c>
+      <c r="G130" s="4">
+        <v>2222627.64</v>
+      </c>
+      <c r="H130" s="4">
+        <v>67476591.040000007</v>
+      </c>
+      <c r="I130" s="4">
+        <v>1729380.48</v>
+      </c>
+      <c r="J130">
+        <v>732.22400000000005</v>
+      </c>
+      <c r="K130">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>115</v>
+      </c>
+      <c r="B131" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131">
+        <v>1039</v>
+      </c>
+      <c r="E131" t="s">
+        <v>43</v>
+      </c>
+      <c r="F131" s="4">
+        <v>72498897.930000007</v>
+      </c>
+      <c r="G131" s="4">
+        <v>179994</v>
+      </c>
+      <c r="H131" s="4">
+        <v>56845786.600000001</v>
+      </c>
+      <c r="I131" s="4">
+        <v>139458.16</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>115</v>
+      </c>
+      <c r="B132" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C132" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132">
+        <v>1042</v>
+      </c>
+      <c r="E132" t="s">
+        <v>44</v>
+      </c>
+      <c r="F132" s="4">
+        <v>46649180.969999999</v>
+      </c>
+      <c r="G132" s="4">
+        <v>181226.98</v>
+      </c>
+      <c r="H132" s="4">
+        <v>36951275.630000003</v>
+      </c>
+      <c r="I132" s="4">
+        <v>134255.59</v>
+      </c>
+      <c r="J132">
+        <v>37.747999999999998</v>
+      </c>
+      <c r="K132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>115</v>
+      </c>
+      <c r="B133" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C133" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133">
+        <v>1043</v>
+      </c>
+      <c r="E133" t="s">
+        <v>45</v>
+      </c>
+      <c r="F133" s="4">
+        <v>41759972.659999996</v>
+      </c>
+      <c r="H133" s="4">
+        <v>32800622.43</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>115</v>
+      </c>
+      <c r="B134" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134">
+        <v>1044</v>
+      </c>
+      <c r="E134" t="s">
+        <v>46</v>
+      </c>
+      <c r="F134" s="4">
+        <v>16443576.26</v>
+      </c>
+      <c r="H134" s="4">
+        <v>12845323.58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>115</v>
+      </c>
+      <c r="B135" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135">
+        <v>1045</v>
+      </c>
+      <c r="E135" t="s">
+        <v>47</v>
+      </c>
+      <c r="F135" s="4">
+        <v>15500129.970000001</v>
+      </c>
+      <c r="H135" s="4">
+        <v>12213711.300000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>115</v>
+      </c>
+      <c r="B136" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C136" t="s">
+        <v>106</v>
+      </c>
+      <c r="D136">
+        <v>1046</v>
+      </c>
+      <c r="E136" t="s">
+        <v>48</v>
+      </c>
+      <c r="F136" s="4">
+        <v>21562892.609999999</v>
+      </c>
+      <c r="H136" s="4">
+        <v>16907145.760000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>115</v>
+      </c>
+      <c r="B137" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C137" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137">
+        <v>1050</v>
+      </c>
+      <c r="E137" t="s">
+        <v>49</v>
+      </c>
+      <c r="F137" s="4">
+        <v>41208674.890000001</v>
+      </c>
+      <c r="H137" s="4">
+        <v>32327940.280000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>115</v>
+      </c>
+      <c r="B138" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C138" t="s">
+        <v>106</v>
+      </c>
+      <c r="D138">
+        <v>1051</v>
+      </c>
+      <c r="E138" t="s">
+        <v>50</v>
+      </c>
+      <c r="F138" s="4">
+        <v>75844923.439999998</v>
+      </c>
+      <c r="G138" s="4">
+        <v>1423146.38</v>
+      </c>
+      <c r="H138" s="4">
+        <v>60594597.270000003</v>
+      </c>
+      <c r="I138" s="4">
+        <v>1087814.1200000001</v>
+      </c>
+      <c r="J138">
+        <v>180.048</v>
+      </c>
+      <c r="K138">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>115</v>
+      </c>
+      <c r="B139" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C139" t="s">
+        <v>106</v>
+      </c>
+      <c r="D139">
+        <v>1052</v>
+      </c>
+      <c r="E139" t="s">
+        <v>51</v>
+      </c>
+      <c r="F139" s="4">
+        <v>50272861.719999999</v>
+      </c>
+      <c r="G139" s="4">
+        <v>66745.8</v>
+      </c>
+      <c r="H139" s="4">
+        <v>39759396.039999999</v>
+      </c>
+      <c r="I139" s="4">
+        <v>51714.21</v>
+      </c>
+      <c r="J139">
+        <v>7</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>115</v>
+      </c>
+      <c r="B140" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C140" t="s">
+        <v>106</v>
+      </c>
+      <c r="D140">
+        <v>1053</v>
+      </c>
+      <c r="E140" t="s">
+        <v>52</v>
+      </c>
+      <c r="F140" s="4">
+        <v>62404086.409999996</v>
+      </c>
+      <c r="H140" s="4">
+        <v>49031391.770000003</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>115</v>
+      </c>
+      <c r="B141" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C141" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141">
+        <v>1054</v>
+      </c>
+      <c r="E141" t="s">
+        <v>53</v>
+      </c>
+      <c r="F141" s="4">
+        <v>54594631.659999996</v>
+      </c>
+      <c r="G141" s="4">
+        <v>3430482.92</v>
+      </c>
+      <c r="H141" s="4">
+        <v>42678518.479999997</v>
+      </c>
+      <c r="I141" s="4">
+        <v>2689313.74</v>
+      </c>
+      <c r="J141">
+        <v>1189.134</v>
+      </c>
+      <c r="K141">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>115</v>
+      </c>
+      <c r="B142" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C142" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142">
+        <v>1055</v>
+      </c>
+      <c r="E142" t="s">
+        <v>54</v>
+      </c>
+      <c r="F142" s="4">
+        <v>52367273.18</v>
+      </c>
+      <c r="G142" s="4">
+        <v>3622584.63</v>
+      </c>
+      <c r="H142" s="4">
+        <v>41182183.640000001</v>
+      </c>
+      <c r="I142" s="4">
+        <v>2806870.83</v>
+      </c>
+      <c r="J142">
+        <v>381.22300000000001</v>
+      </c>
+      <c r="K142">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>115</v>
+      </c>
+      <c r="B143" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C143" t="s">
+        <v>106</v>
+      </c>
+      <c r="D143">
+        <v>1056</v>
+      </c>
+      <c r="E143" t="s">
+        <v>55</v>
+      </c>
+      <c r="F143" s="4">
+        <v>34502308.719999999</v>
+      </c>
+      <c r="G143" s="4">
+        <v>304749.68</v>
+      </c>
+      <c r="H143" s="4">
+        <v>27266495.43</v>
+      </c>
+      <c r="I143" s="4">
+        <v>233327.72</v>
+      </c>
+      <c r="J143">
+        <v>47</v>
+      </c>
+      <c r="K143">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>115</v>
+      </c>
+      <c r="B144" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C144" t="s">
+        <v>106</v>
+      </c>
+      <c r="D144">
+        <v>1057</v>
+      </c>
+      <c r="E144" t="s">
+        <v>56</v>
+      </c>
+      <c r="F144" s="4">
+        <v>89117157.900000006</v>
+      </c>
+      <c r="G144" s="4">
+        <v>3478422.49</v>
+      </c>
+      <c r="H144" s="4">
+        <v>70353736.829999998</v>
+      </c>
+      <c r="I144" s="4">
+        <v>2743707.36</v>
+      </c>
+      <c r="J144">
+        <v>1299.146</v>
+      </c>
+      <c r="K144">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>115</v>
+      </c>
+      <c r="B145" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C145" t="s">
+        <v>106</v>
+      </c>
+      <c r="D145">
+        <v>1058</v>
+      </c>
+      <c r="E145" t="s">
+        <v>57</v>
+      </c>
+      <c r="F145" s="4">
+        <v>48876856.140000001</v>
+      </c>
+      <c r="G145" s="4">
+        <v>1112990.06</v>
+      </c>
+      <c r="H145" s="4">
+        <v>38321990.030000001</v>
+      </c>
+      <c r="I145" s="4">
+        <v>868355.99</v>
+      </c>
+      <c r="J145">
+        <v>348.1</v>
+      </c>
+      <c r="K145">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>115</v>
+      </c>
+      <c r="B146" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C146" t="s">
+        <v>106</v>
+      </c>
+      <c r="D146">
+        <v>1059</v>
+      </c>
+      <c r="E146" t="s">
+        <v>58</v>
+      </c>
+      <c r="F146" s="4">
+        <v>43739634.850000001</v>
+      </c>
+      <c r="H146" s="4">
+        <v>34160743.060000002</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>115</v>
+      </c>
+      <c r="B147" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C147" t="s">
+        <v>106</v>
+      </c>
+      <c r="D147">
+        <v>1060</v>
+      </c>
+      <c r="E147" t="s">
+        <v>59</v>
+      </c>
+      <c r="F147" s="4">
+        <v>38846609.659999996</v>
+      </c>
+      <c r="H147" s="4">
+        <v>30986576.800000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>115</v>
+      </c>
+      <c r="B148" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C148" t="s">
+        <v>106</v>
+      </c>
+      <c r="D148">
+        <v>1061</v>
+      </c>
+      <c r="E148" t="s">
+        <v>60</v>
+      </c>
+      <c r="F148" s="4">
+        <v>59661035.100000001</v>
+      </c>
+      <c r="G148" s="4">
+        <v>2367670.13</v>
+      </c>
+      <c r="H148" s="4">
+        <v>46499219.770000003</v>
+      </c>
+      <c r="I148" s="4">
+        <v>1831927.31</v>
+      </c>
+      <c r="J148">
+        <v>234.03</v>
+      </c>
+      <c r="K148">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>115</v>
+      </c>
+      <c r="B149" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C149" t="s">
+        <v>106</v>
+      </c>
+      <c r="D149">
+        <v>1066</v>
+      </c>
+      <c r="E149" t="s">
+        <v>111</v>
+      </c>
+      <c r="F149" s="4">
+        <v>2336714.15</v>
+      </c>
+      <c r="H149" s="4">
+        <v>1816906.93</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>115</v>
+      </c>
+      <c r="B150" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+      <c r="D150">
+        <v>1067</v>
+      </c>
+      <c r="E150" t="s">
+        <v>61</v>
+      </c>
+      <c r="F150" s="4">
+        <v>38636733.729999997</v>
+      </c>
+      <c r="G150" s="4">
+        <v>1023857.1</v>
+      </c>
+      <c r="H150" s="4">
+        <v>30587053.27</v>
+      </c>
+      <c r="I150" s="4">
+        <v>793095.19</v>
+      </c>
+      <c r="J150">
+        <v>23</v>
+      </c>
+      <c r="K150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>115</v>
+      </c>
+      <c r="B151" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C151" t="s">
+        <v>106</v>
+      </c>
+      <c r="D151">
+        <v>1068</v>
+      </c>
+      <c r="E151" t="s">
+        <v>62</v>
+      </c>
+      <c r="F151" s="4">
+        <v>67877468.890000001</v>
+      </c>
+      <c r="H151" s="4">
+        <v>53271243.18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>115</v>
+      </c>
+      <c r="B152" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C152" t="s">
+        <v>106</v>
+      </c>
+      <c r="D152">
+        <v>1074</v>
+      </c>
+      <c r="E152" t="s">
+        <v>63</v>
+      </c>
+      <c r="F152" s="4">
+        <v>23425032.09</v>
+      </c>
+      <c r="H152" s="4">
+        <v>18420844.73</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>115</v>
+      </c>
+      <c r="B153" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C153" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153">
+        <v>1075</v>
+      </c>
+      <c r="E153" t="s">
+        <v>64</v>
+      </c>
+      <c r="F153" s="4">
+        <v>50195805.090000004</v>
+      </c>
+      <c r="H153" s="4">
+        <v>39899236.950000003</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>115</v>
+      </c>
+      <c r="B154" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C154" t="s">
+        <v>106</v>
+      </c>
+      <c r="D154">
+        <v>1076</v>
+      </c>
+      <c r="E154" t="s">
+        <v>65</v>
+      </c>
+      <c r="F154" s="4">
+        <v>45635503.57</v>
+      </c>
+      <c r="H154" s="4">
+        <v>35891168.740000002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>115</v>
+      </c>
+      <c r="B155" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C155" t="s">
+        <v>106</v>
+      </c>
+      <c r="D155">
+        <v>1077</v>
+      </c>
+      <c r="E155" t="s">
+        <v>66</v>
+      </c>
+      <c r="F155" s="4">
+        <v>73122073.989999995</v>
+      </c>
+      <c r="G155" s="4">
+        <v>225096.19</v>
+      </c>
+      <c r="H155" s="4">
+        <v>57927283.049999997</v>
+      </c>
+      <c r="I155" s="4">
+        <v>173627.51</v>
+      </c>
+      <c r="J155">
+        <v>65.436000000000007</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>115</v>
+      </c>
+      <c r="B156" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C156" t="s">
+        <v>106</v>
+      </c>
+      <c r="D156">
+        <v>1078</v>
+      </c>
+      <c r="E156" t="s">
+        <v>67</v>
+      </c>
+      <c r="F156" s="4">
+        <v>55839206.719999999</v>
+      </c>
+      <c r="G156" s="4">
+        <v>25913.26</v>
+      </c>
+      <c r="H156" s="4">
+        <v>44114844.32</v>
+      </c>
+      <c r="I156" s="4">
+        <v>21337.53</v>
+      </c>
+      <c r="J156">
+        <v>17.163</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>115</v>
+      </c>
+      <c r="B157" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C157" t="s">
+        <v>106</v>
+      </c>
+      <c r="D157">
+        <v>1080</v>
+      </c>
+      <c r="E157" t="s">
+        <v>68</v>
+      </c>
+      <c r="F157" s="4">
+        <v>41058223.939999998</v>
+      </c>
+      <c r="G157" s="4">
+        <v>1419165.42</v>
+      </c>
+      <c r="H157" s="4">
+        <v>32000565.199999999</v>
+      </c>
+      <c r="I157" s="4">
+        <v>1117515.98</v>
+      </c>
+      <c r="J157">
+        <v>500.01499999999999</v>
+      </c>
+      <c r="K157">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>115</v>
+      </c>
+      <c r="B158" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C158" t="s">
+        <v>106</v>
+      </c>
+      <c r="D158">
+        <v>1081</v>
+      </c>
+      <c r="E158" t="s">
+        <v>69</v>
+      </c>
+      <c r="F158" s="4">
+        <v>32896909.59</v>
+      </c>
+      <c r="G158" s="4">
+        <v>-87999.45</v>
+      </c>
+      <c r="H158" s="4">
+        <v>25942277.52</v>
+      </c>
+      <c r="I158" s="4">
+        <v>-68181.39</v>
+      </c>
+      <c r="J158">
+        <v>-1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C159" t="s">
+        <v>106</v>
+      </c>
+      <c r="D159">
+        <v>1082</v>
+      </c>
+      <c r="E159" t="s">
+        <v>70</v>
+      </c>
+      <c r="F159" s="4">
+        <v>22588748.620000001</v>
+      </c>
+      <c r="G159" s="4">
+        <v>469999</v>
+      </c>
+      <c r="H159" s="4">
+        <v>18132669.43</v>
+      </c>
+      <c r="I159" s="4">
+        <v>364152.12</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>115</v>
+      </c>
+      <c r="B160" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C160" t="s">
+        <v>106</v>
+      </c>
+      <c r="D160">
+        <v>1084</v>
+      </c>
+      <c r="E160" t="s">
+        <v>71</v>
+      </c>
+      <c r="F160" s="4">
+        <v>16544663.640000001</v>
+      </c>
+      <c r="G160" s="4">
+        <v>43367.9</v>
+      </c>
+      <c r="H160" s="4">
+        <v>13033386.289999999</v>
+      </c>
+      <c r="I160" s="4">
+        <v>34771.99</v>
+      </c>
+      <c r="J160">
+        <v>21</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>115</v>
+      </c>
+      <c r="B161" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C161" t="s">
+        <v>106</v>
+      </c>
+      <c r="D161">
+        <v>1085</v>
+      </c>
+      <c r="E161" t="s">
+        <v>72</v>
+      </c>
+      <c r="F161" s="4">
+        <v>17928805.16</v>
+      </c>
+      <c r="H161" s="4">
+        <v>14179662.609999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>115</v>
+      </c>
+      <c r="B162" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C162" t="s">
+        <v>106</v>
+      </c>
+      <c r="D162">
+        <v>1086</v>
+      </c>
+      <c r="E162" t="s">
+        <v>73</v>
+      </c>
+      <c r="F162" s="4">
+        <v>56580198.880000003</v>
+      </c>
+      <c r="H162" s="4">
+        <v>44354031.829999998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>115</v>
+      </c>
+      <c r="B163" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C163" t="s">
+        <v>106</v>
+      </c>
+      <c r="D163">
+        <v>1087</v>
+      </c>
+      <c r="E163" t="s">
+        <v>74</v>
+      </c>
+      <c r="F163" s="4">
+        <v>74672000.090000004</v>
+      </c>
+      <c r="G163" s="4">
+        <v>5855640.7300000004</v>
+      </c>
+      <c r="H163" s="4">
+        <v>58803954.119999997</v>
+      </c>
+      <c r="I163" s="4">
+        <v>4530871.18</v>
+      </c>
+      <c r="J163">
+        <v>2393.5390000000002</v>
+      </c>
+      <c r="K163">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>115</v>
+      </c>
+      <c r="B164" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C164" t="s">
+        <v>106</v>
+      </c>
+      <c r="D164">
+        <v>1088</v>
+      </c>
+      <c r="E164" t="s">
+        <v>75</v>
+      </c>
+      <c r="F164" s="4">
+        <v>43298657.969999999</v>
+      </c>
+      <c r="G164" s="4">
+        <v>306594.09000000003</v>
+      </c>
+      <c r="H164" s="4">
+        <v>34917387.560000002</v>
+      </c>
+      <c r="I164" s="4">
+        <v>242164.73</v>
+      </c>
+      <c r="J164">
+        <v>58.164000000000001</v>
+      </c>
+      <c r="K164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>115</v>
+      </c>
+      <c r="B165" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C165" t="s">
+        <v>106</v>
+      </c>
+      <c r="D165">
+        <v>1092</v>
+      </c>
+      <c r="E165" t="s">
+        <v>76</v>
+      </c>
+      <c r="F165" s="4">
+        <v>53979561.579999998</v>
+      </c>
+      <c r="G165" s="4">
+        <v>560997.48</v>
+      </c>
+      <c r="H165" s="4">
+        <v>42171322.530000001</v>
+      </c>
+      <c r="I165" s="4">
+        <v>434657.13</v>
+      </c>
+      <c r="J165">
+        <v>3</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>115</v>
+      </c>
+      <c r="B166" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C166" t="s">
+        <v>106</v>
+      </c>
+      <c r="D166">
+        <v>1093</v>
+      </c>
+      <c r="E166" t="s">
+        <v>77</v>
+      </c>
+      <c r="F166" s="4">
+        <v>64823465.810000002</v>
+      </c>
+      <c r="H166" s="4">
+        <v>51124312.25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>115</v>
+      </c>
+      <c r="B167" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C167" t="s">
+        <v>106</v>
+      </c>
+      <c r="D167">
+        <v>1096</v>
+      </c>
+      <c r="E167" t="s">
+        <v>78</v>
+      </c>
+      <c r="F167" s="4">
+        <v>39772325.450000003</v>
+      </c>
+      <c r="H167" s="4">
+        <v>31353180.149999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>115</v>
+      </c>
+      <c r="B168" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C168" t="s">
+        <v>106</v>
+      </c>
+      <c r="D168">
+        <v>1097</v>
+      </c>
+      <c r="E168" t="s">
+        <v>79</v>
+      </c>
+      <c r="F168" s="4">
+        <v>37905173.079999998</v>
+      </c>
+      <c r="H168" s="4">
+        <v>29901975.960000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>115</v>
+      </c>
+      <c r="B169" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C169" t="s">
+        <v>106</v>
+      </c>
+      <c r="D169">
+        <v>1098</v>
+      </c>
+      <c r="E169" t="s">
+        <v>80</v>
+      </c>
+      <c r="F169" s="4">
+        <v>31353479.289999999</v>
+      </c>
+      <c r="G169" s="4">
+        <v>957197.84</v>
+      </c>
+      <c r="H169" s="4">
+        <v>24624562.640000001</v>
+      </c>
+      <c r="I169" s="4">
+        <v>747081.94</v>
+      </c>
+      <c r="J169">
+        <v>64.206999999999994</v>
+      </c>
+      <c r="K169">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>115</v>
+      </c>
+      <c r="B170" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C170" t="s">
+        <v>106</v>
+      </c>
+      <c r="D170">
+        <v>1099</v>
+      </c>
+      <c r="E170" t="s">
+        <v>81</v>
+      </c>
+      <c r="F170" s="4">
+        <v>48069266.590000004</v>
+      </c>
+      <c r="H170" s="4">
+        <v>38228406.210000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>115</v>
+      </c>
+      <c r="B171" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C171" t="s">
+        <v>106</v>
+      </c>
+      <c r="D171">
+        <v>1100</v>
+      </c>
+      <c r="E171" t="s">
+        <v>82</v>
+      </c>
+      <c r="F171" s="4">
+        <v>50188205.210000001</v>
+      </c>
+      <c r="H171" s="4">
+        <v>39590197.43</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>115</v>
+      </c>
+      <c r="B172" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C172" t="s">
+        <v>106</v>
+      </c>
+      <c r="D172">
+        <v>1102</v>
+      </c>
+      <c r="E172" t="s">
+        <v>112</v>
+      </c>
+      <c r="F172" s="4">
+        <v>3226580.13</v>
+      </c>
+      <c r="H172" s="4">
+        <v>2505771.5099999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>115</v>
+      </c>
+      <c r="B173" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C173" t="s">
+        <v>106</v>
+      </c>
+      <c r="D173">
+        <v>1103</v>
+      </c>
+      <c r="E173" t="s">
+        <v>113</v>
+      </c>
+      <c r="F173" s="4">
+        <v>2435851.02</v>
+      </c>
+      <c r="H173" s="4">
+        <v>1885454.92</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>115</v>
+      </c>
+      <c r="B174" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C174" t="s">
+        <v>106</v>
+      </c>
+      <c r="D174">
+        <v>1106</v>
+      </c>
+      <c r="E174" t="s">
+        <v>83</v>
+      </c>
+      <c r="F174" s="4">
+        <v>22968203.780000001</v>
+      </c>
+      <c r="H174" s="4">
+        <v>18091603.670000002</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>115</v>
+      </c>
+      <c r="B175" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C175" t="s">
+        <v>106</v>
+      </c>
+      <c r="D175">
+        <v>1108</v>
+      </c>
+      <c r="E175" t="s">
+        <v>84</v>
+      </c>
+      <c r="F175" s="4">
+        <v>60242705.369999997</v>
+      </c>
+      <c r="G175" s="4">
+        <v>22611.05</v>
+      </c>
+      <c r="H175" s="4">
+        <v>47657921.719999999</v>
+      </c>
+      <c r="I175" s="4">
+        <v>17623.71</v>
+      </c>
+      <c r="J175">
+        <v>10.597</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>115</v>
+      </c>
+      <c r="B176" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C176" t="s">
+        <v>106</v>
+      </c>
+      <c r="D176">
+        <v>1109</v>
+      </c>
+      <c r="E176" t="s">
+        <v>114</v>
+      </c>
+      <c r="F176" s="4">
+        <v>4398869.72</v>
+      </c>
+      <c r="H176" s="4">
+        <v>3457248.13</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>115</v>
+      </c>
+      <c r="B177" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C177" t="s">
+        <v>106</v>
+      </c>
+      <c r="D177">
+        <v>1110</v>
+      </c>
+      <c r="E177" t="s">
+        <v>85</v>
+      </c>
+      <c r="F177" s="4">
+        <v>30498194.899999999</v>
+      </c>
+      <c r="H177" s="4">
+        <v>23902802.379999999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>115</v>
+      </c>
+      <c r="B178" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C178" t="s">
+        <v>106</v>
+      </c>
+      <c r="D178">
+        <v>1111</v>
+      </c>
+      <c r="E178" t="s">
+        <v>86</v>
+      </c>
+      <c r="F178" s="4">
+        <v>41514629.770000003</v>
+      </c>
+      <c r="G178" s="4">
+        <v>2199987.2000000002</v>
+      </c>
+      <c r="H178" s="4">
+        <v>32991322.109999999</v>
+      </c>
+      <c r="I178" s="4">
+        <v>1704535.54</v>
+      </c>
+      <c r="J178">
+        <v>2</v>
+      </c>
+      <c r="K178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>115</v>
+      </c>
+      <c r="B179" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C179" t="s">
+        <v>106</v>
+      </c>
+      <c r="D179">
+        <v>1114</v>
+      </c>
+      <c r="E179" t="s">
+        <v>87</v>
+      </c>
+      <c r="F179" s="4">
+        <v>31380304.68</v>
+      </c>
+      <c r="H179" s="4">
+        <v>24731219.530000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>115</v>
+      </c>
+      <c r="B180" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C180" t="s">
+        <v>106</v>
+      </c>
+      <c r="D180">
+        <v>1115</v>
+      </c>
+      <c r="E180" t="s">
+        <v>88</v>
+      </c>
+      <c r="F180" s="4">
+        <v>52171989.530000001</v>
+      </c>
+      <c r="G180" s="4">
+        <v>492935.58</v>
+      </c>
+      <c r="H180" s="4">
+        <v>41360305.869999997</v>
+      </c>
+      <c r="I180" s="4">
+        <v>392473.11</v>
+      </c>
+      <c r="J180">
+        <v>127.178</v>
+      </c>
+      <c r="K180">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>115</v>
+      </c>
+      <c r="B181" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C181" t="s">
+        <v>106</v>
+      </c>
+      <c r="D181">
+        <v>1116</v>
+      </c>
+      <c r="E181" t="s">
+        <v>89</v>
+      </c>
+      <c r="F181" s="4">
+        <v>41034059.240000002</v>
+      </c>
+      <c r="H181" s="4">
+        <v>32259588.829999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>115</v>
+      </c>
+      <c r="B182" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C182" t="s">
+        <v>106</v>
+      </c>
+      <c r="D182">
+        <v>1119</v>
+      </c>
+      <c r="E182" t="s">
+        <v>90</v>
+      </c>
+      <c r="F182" s="4">
+        <v>33859995.030000001</v>
+      </c>
+      <c r="H182" s="4">
+        <v>26665302</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>115</v>
+      </c>
+      <c r="B183" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C183" t="s">
+        <v>106</v>
+      </c>
+      <c r="D183">
+        <v>2997</v>
+      </c>
+      <c r="E183" t="s">
+        <v>91</v>
+      </c>
+      <c r="F183" s="4">
+        <v>229058798.86000001</v>
+      </c>
+      <c r="G183" s="4">
+        <v>20423635.370000001</v>
+      </c>
+      <c r="H183" s="4">
+        <v>182639447.66</v>
+      </c>
+      <c r="I183" s="4">
+        <v>15710306.859999999</v>
+      </c>
+      <c r="J183">
+        <v>7205.38</v>
+      </c>
+      <c r="K183">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>115</v>
+      </c>
+      <c r="B184" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C184" t="s">
+        <v>106</v>
+      </c>
+      <c r="D184">
+        <v>2998</v>
+      </c>
+      <c r="E184" t="s">
+        <v>92</v>
+      </c>
+      <c r="F184" s="4">
+        <v>107246220.54000001</v>
+      </c>
+      <c r="G184" s="4">
+        <v>15103913.83</v>
+      </c>
+      <c r="H184" s="4">
+        <v>84106275.959999993</v>
+      </c>
+      <c r="I184" s="4">
+        <v>11739443.23</v>
+      </c>
+      <c r="J184">
+        <v>6671.8090000000002</v>
+      </c>
+      <c r="K184">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>115</v>
+      </c>
+      <c r="B185" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C185" t="s">
+        <v>106</v>
+      </c>
+      <c r="D185">
+        <v>2999</v>
+      </c>
+      <c r="E185" t="s">
+        <v>93</v>
+      </c>
+      <c r="F185" s="4">
+        <v>116113644.84</v>
+      </c>
+      <c r="G185" s="4">
+        <v>13971495.199999999</v>
+      </c>
+      <c r="H185" s="4">
+        <v>91147995.650000006</v>
+      </c>
+      <c r="I185" s="4">
+        <v>10858500</v>
+      </c>
+      <c r="J185">
+        <v>5058.7569999999996</v>
+      </c>
+      <c r="K185">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>115</v>
+      </c>
+      <c r="B186" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C186" t="s">
+        <v>106</v>
+      </c>
+      <c r="D186">
+        <v>3601</v>
+      </c>
+      <c r="E186" t="s">
+        <v>94</v>
+      </c>
+      <c r="F186" s="4">
+        <v>141060507.61000001</v>
+      </c>
+      <c r="G186" s="4">
+        <v>12300737.640000001</v>
+      </c>
+      <c r="H186" s="4">
+        <v>110573098.25</v>
+      </c>
+      <c r="I186" s="4">
+        <v>9526519.1799999997</v>
+      </c>
+      <c r="J186">
+        <v>4400.8490000000002</v>
+      </c>
+      <c r="K186">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>115</v>
+      </c>
+      <c r="B187" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C187" t="s">
+        <v>106</v>
+      </c>
+      <c r="D187">
+        <v>3602</v>
+      </c>
+      <c r="E187" t="s">
+        <v>95</v>
+      </c>
+      <c r="F187" s="4">
+        <v>113598022.52</v>
+      </c>
+      <c r="G187" s="4">
+        <v>8066974.7699999996</v>
+      </c>
+      <c r="H187" s="4">
+        <v>89125673.650000006</v>
+      </c>
+      <c r="I187" s="4">
+        <v>6218628.2300000004</v>
+      </c>
+      <c r="J187">
+        <v>2483.0520000000001</v>
+      </c>
+      <c r="K187">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>115</v>
+      </c>
+      <c r="B188" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C188" t="s">
+        <v>106</v>
+      </c>
+      <c r="D188">
+        <v>3603</v>
+      </c>
+      <c r="E188" t="s">
+        <v>96</v>
+      </c>
+      <c r="F188" s="4">
+        <v>100425179.03</v>
+      </c>
+      <c r="G188" s="4">
+        <v>6847051.6500000004</v>
+      </c>
+      <c r="H188" s="4">
+        <v>78561913.780000001</v>
+      </c>
+      <c r="I188" s="4">
+        <v>5328112.6100000003</v>
+      </c>
+      <c r="J188">
+        <v>2588.8159999999998</v>
+      </c>
+      <c r="K188">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>115</v>
+      </c>
+      <c r="B189" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C189" t="s">
+        <v>106</v>
+      </c>
+      <c r="D189">
+        <v>3604</v>
+      </c>
+      <c r="E189" t="s">
+        <v>97</v>
+      </c>
+      <c r="F189" s="4">
+        <v>83091966.090000004</v>
+      </c>
+      <c r="G189" s="4">
+        <v>6190735.6900000004</v>
+      </c>
+      <c r="H189" s="4">
+        <v>64872877.090000004</v>
+      </c>
+      <c r="I189" s="4">
+        <v>4813133.1399999997</v>
+      </c>
+      <c r="J189">
+        <v>2233.212</v>
+      </c>
+      <c r="K189">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>115</v>
+      </c>
+      <c r="B190" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C190" t="s">
+        <v>106</v>
+      </c>
+      <c r="D190">
+        <v>3605</v>
+      </c>
+      <c r="E190" t="s">
+        <v>98</v>
+      </c>
+      <c r="F190" s="4">
+        <v>184765498.13</v>
+      </c>
+      <c r="G190" s="4">
+        <v>18764954.460000001</v>
+      </c>
+      <c r="H190" s="4">
+        <v>145734274.81</v>
+      </c>
+      <c r="I190" s="4">
+        <v>14434716.119999999</v>
+      </c>
+      <c r="J190">
+        <v>6498.3919999999998</v>
+      </c>
+      <c r="K190">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>115</v>
+      </c>
+      <c r="B191" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C191" t="s">
+        <v>106</v>
+      </c>
+      <c r="D191">
+        <v>3606</v>
+      </c>
+      <c r="E191" t="s">
+        <v>99</v>
+      </c>
+      <c r="F191" s="4">
+        <v>90240340.560000002</v>
+      </c>
+      <c r="H191" s="4">
+        <v>71285402.450000003</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>115</v>
+      </c>
+      <c r="B192" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C192" t="s">
+        <v>106</v>
+      </c>
+      <c r="D192">
+        <v>3608</v>
+      </c>
+      <c r="E192" t="s">
+        <v>100</v>
+      </c>
+      <c r="F192" s="4">
+        <v>169053025.63</v>
+      </c>
+      <c r="G192" s="4">
+        <v>5436091.5700000003</v>
+      </c>
+      <c r="H192" s="4">
+        <v>132344451.47</v>
+      </c>
+      <c r="I192" s="4">
+        <v>4263240.99</v>
+      </c>
+      <c r="J192">
+        <v>1727.2529999999999</v>
+      </c>
+      <c r="K192">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>115</v>
+      </c>
+      <c r="B193" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C193" t="s">
+        <v>106</v>
+      </c>
+      <c r="D193">
+        <v>3613</v>
+      </c>
+      <c r="E193" t="s">
+        <v>101</v>
+      </c>
+      <c r="F193" s="4">
+        <v>107094064.84</v>
+      </c>
+      <c r="G193" s="4">
+        <v>12664309.32</v>
+      </c>
+      <c r="H193" s="4">
+        <v>84234991.840000004</v>
+      </c>
+      <c r="I193" s="4">
+        <v>9845512.2300000004</v>
+      </c>
+      <c r="J193">
+        <v>3785.9740000000002</v>
+      </c>
+      <c r="K193">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>115</v>
+      </c>
+      <c r="B194" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C194" t="s">
+        <v>106</v>
+      </c>
+      <c r="D194">
+        <v>4001</v>
+      </c>
+      <c r="E194" t="s">
+        <v>102</v>
+      </c>
+      <c r="F194" s="4">
+        <v>25925001.440000001</v>
+      </c>
+      <c r="G194" s="4">
+        <v>177624.1</v>
+      </c>
+      <c r="H194" s="4">
+        <v>20484626.879999999</v>
+      </c>
+      <c r="I194" s="4">
+        <v>140369.88</v>
+      </c>
+      <c r="J194">
+        <v>95</v>
+      </c>
+      <c r="K194">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>115</v>
+      </c>
+      <c r="B195" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C195" t="s">
+        <v>107</v>
+      </c>
+      <c r="D195">
+        <v>1002</v>
+      </c>
+      <c r="E195" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="4">
+        <v>117022483.81</v>
+      </c>
+      <c r="G195" s="4">
+        <v>2778675.66</v>
+      </c>
+      <c r="H195" s="4">
+        <v>91771671.090000004</v>
+      </c>
+      <c r="I195" s="4">
+        <v>2178761.6800000002</v>
+      </c>
+      <c r="J195">
+        <v>775.30200000000002</v>
+      </c>
+      <c r="K195">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>115</v>
+      </c>
+      <c r="B196" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C196" t="s">
+        <v>107</v>
+      </c>
+      <c r="D196">
+        <v>1003</v>
+      </c>
+      <c r="E196" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" s="4">
+        <v>123148648.3</v>
+      </c>
+      <c r="G196" s="4">
+        <v>2888958.22</v>
+      </c>
+      <c r="H196" s="4">
+        <v>96857112.920000002</v>
+      </c>
+      <c r="I196" s="4">
+        <v>2238165.7799999998</v>
+      </c>
+      <c r="J196">
+        <v>1277.9480000000001</v>
+      </c>
+      <c r="K196">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>115</v>
+      </c>
+      <c r="B197" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C197" t="s">
+        <v>107</v>
+      </c>
+      <c r="D197">
+        <v>1004</v>
+      </c>
+      <c r="E197" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="4">
+        <v>128519593.09999999</v>
+      </c>
+      <c r="G197" s="4">
+        <v>3860110.11</v>
+      </c>
+      <c r="H197" s="4">
+        <v>101540193.81</v>
+      </c>
+      <c r="I197" s="4">
+        <v>3043001.78</v>
+      </c>
+      <c r="J197">
+        <v>1091.8</v>
+      </c>
+      <c r="K197">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>115</v>
+      </c>
+      <c r="B198" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C198" t="s">
+        <v>107</v>
+      </c>
+      <c r="D198">
+        <v>1005</v>
+      </c>
+      <c r="E198" t="s">
+        <v>13</v>
+      </c>
+      <c r="F198" s="4">
+        <v>78192430.780000001</v>
+      </c>
+      <c r="H198" s="4">
+        <v>61542679.609999999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>115</v>
+      </c>
+      <c r="B199" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C199" t="s">
+        <v>107</v>
+      </c>
+      <c r="D199">
+        <v>1006</v>
+      </c>
+      <c r="E199" t="s">
+        <v>14</v>
+      </c>
+      <c r="F199" s="4">
+        <v>99010834.640000001</v>
+      </c>
+      <c r="G199" s="4">
+        <v>5135827.63</v>
+      </c>
+      <c r="H199" s="4">
+        <v>77523154.670000002</v>
+      </c>
+      <c r="I199" s="4">
+        <v>3983575.64</v>
+      </c>
+      <c r="J199">
+        <v>1457.423</v>
+      </c>
+      <c r="K199">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>115</v>
+      </c>
+      <c r="B200" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C200" t="s">
+        <v>107</v>
+      </c>
+      <c r="D200">
+        <v>1007</v>
+      </c>
+      <c r="E200" t="s">
+        <v>15</v>
+      </c>
+      <c r="F200" s="4">
+        <v>158357424.62</v>
+      </c>
+      <c r="G200" s="4">
+        <v>318449.36</v>
+      </c>
+      <c r="H200" s="4">
+        <v>124707259.59</v>
+      </c>
+      <c r="I200" s="4">
+        <v>246819.07</v>
+      </c>
+      <c r="J200">
+        <v>70</v>
+      </c>
+      <c r="K200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>115</v>
+      </c>
+      <c r="B201" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C201" t="s">
+        <v>107</v>
+      </c>
+      <c r="D201">
+        <v>1008</v>
+      </c>
+      <c r="E201" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201" s="4">
+        <v>105266296.97</v>
+      </c>
+      <c r="G201" s="4">
+        <v>3645312.74</v>
+      </c>
+      <c r="H201" s="4">
+        <v>82520526.879999995</v>
+      </c>
+      <c r="I201" s="4">
+        <v>2864642.12</v>
+      </c>
+      <c r="J201">
+        <v>651.74300000000005</v>
+      </c>
+      <c r="K201">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>115</v>
+      </c>
+      <c r="B202" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C202" t="s">
+        <v>107</v>
+      </c>
+      <c r="D202">
+        <v>1010</v>
+      </c>
+      <c r="E202" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="4">
+        <v>67101639.579999998</v>
+      </c>
+      <c r="H202" s="4">
+        <v>53003719.810000002</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>115</v>
+      </c>
+      <c r="B203" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C203" t="s">
+        <v>107</v>
+      </c>
+      <c r="D203">
+        <v>1011</v>
+      </c>
+      <c r="E203" t="s">
+        <v>18</v>
+      </c>
+      <c r="F203" s="4">
+        <v>80485252.290000007</v>
+      </c>
+      <c r="G203" s="4">
+        <v>1751121</v>
+      </c>
+      <c r="H203" s="4">
+        <v>63517074.439999998</v>
+      </c>
+      <c r="I203" s="4">
+        <v>1367804.05</v>
+      </c>
+      <c r="J203">
+        <v>593.23699999999997</v>
+      </c>
+      <c r="K203">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>115</v>
+      </c>
+      <c r="B204" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C204" t="s">
+        <v>107</v>
+      </c>
+      <c r="D204">
+        <v>1012</v>
+      </c>
+      <c r="E204" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="4">
+        <v>83157880.079999998</v>
+      </c>
+      <c r="G204" s="4">
+        <v>334253.40999999997</v>
+      </c>
+      <c r="H204" s="4">
+        <v>64970756.049999997</v>
+      </c>
+      <c r="I204" s="4">
+        <v>263243.98</v>
+      </c>
+      <c r="J204">
+        <v>85.185000000000002</v>
+      </c>
+      <c r="K204">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>115</v>
+      </c>
+      <c r="B205" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C205" t="s">
+        <v>107</v>
+      </c>
+      <c r="D205">
+        <v>1013</v>
+      </c>
+      <c r="E205" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" s="4">
+        <v>88509004.290000007</v>
+      </c>
+      <c r="H205" s="4">
+        <v>69588557.609999999</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>115</v>
+      </c>
+      <c r="B206" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C206" t="s">
+        <v>107</v>
+      </c>
+      <c r="D206">
+        <v>1014</v>
+      </c>
+      <c r="E206" t="s">
+        <v>21</v>
+      </c>
+      <c r="F206" s="4">
+        <v>55966259.280000001</v>
+      </c>
+      <c r="G206" s="4">
+        <v>314991</v>
+      </c>
+      <c r="H206" s="4">
+        <v>43748963.090000004</v>
+      </c>
+      <c r="I206" s="4">
+        <v>244052.95</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>115</v>
+      </c>
+      <c r="B207" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C207" t="s">
+        <v>107</v>
+      </c>
+      <c r="D207">
+        <v>1015</v>
+      </c>
+      <c r="E207" t="s">
+        <v>22</v>
+      </c>
+      <c r="F207" s="4">
+        <v>67153205.769999996</v>
+      </c>
+      <c r="H207" s="4">
+        <v>52635385</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>115</v>
+      </c>
+      <c r="B208" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C208" t="s">
+        <v>107</v>
+      </c>
+      <c r="D208">
+        <v>1016</v>
+      </c>
+      <c r="E208" t="s">
+        <v>23</v>
+      </c>
+      <c r="F208" s="4">
+        <v>138390183.13999999</v>
+      </c>
+      <c r="H208" s="4">
+        <v>108315470.05</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>115</v>
+      </c>
+      <c r="B209" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C209" t="s">
+        <v>107</v>
+      </c>
+      <c r="D209">
+        <v>1017</v>
+      </c>
+      <c r="E209" t="s">
+        <v>24</v>
+      </c>
+      <c r="F209" s="4">
+        <v>102977617.45999999</v>
+      </c>
+      <c r="H209" s="4">
+        <v>80820745.069999993</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>115</v>
+      </c>
+      <c r="B210" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C210" t="s">
+        <v>107</v>
+      </c>
+      <c r="D210">
+        <v>1018</v>
+      </c>
+      <c r="E210" t="s">
+        <v>25</v>
+      </c>
+      <c r="F210" s="4">
+        <v>69293942.189999998</v>
+      </c>
+      <c r="G210" s="4">
+        <v>114370.65</v>
+      </c>
+      <c r="H210" s="4">
+        <v>54367635.619999997</v>
+      </c>
+      <c r="I210" s="4">
+        <v>92399.61</v>
+      </c>
+      <c r="J210">
+        <v>37</v>
+      </c>
+      <c r="K210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>115</v>
+      </c>
+      <c r="B211" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C211" t="s">
+        <v>107</v>
+      </c>
+      <c r="D211">
+        <v>1020</v>
+      </c>
+      <c r="E211" t="s">
+        <v>26</v>
+      </c>
+      <c r="F211" s="4">
+        <v>71033912.319999993</v>
+      </c>
+      <c r="G211" s="4">
+        <v>2722164.53</v>
+      </c>
+      <c r="H211" s="4">
+        <v>56063152.409999996</v>
+      </c>
+      <c r="I211" s="4">
+        <v>2133238.73</v>
+      </c>
+      <c r="J211">
+        <v>778.58100000000002</v>
+      </c>
+      <c r="K211">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>115</v>
+      </c>
+      <c r="B212" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C212" t="s">
+        <v>107</v>
+      </c>
+      <c r="D212">
+        <v>1021</v>
+      </c>
+      <c r="E212" t="s">
+        <v>27</v>
+      </c>
+      <c r="F212" s="4">
+        <v>94883784.069999993</v>
+      </c>
+      <c r="H212" s="4">
+        <v>74726373.25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>115</v>
+      </c>
+      <c r="B213" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C213" t="s">
+        <v>107</v>
+      </c>
+      <c r="D213">
+        <v>1022</v>
+      </c>
+      <c r="E213" t="s">
+        <v>28</v>
+      </c>
+      <c r="F213" s="4">
+        <v>138782677.53</v>
+      </c>
+      <c r="G213" s="4">
+        <v>1280315.5900000001</v>
+      </c>
+      <c r="H213" s="4">
+        <v>110063525.11</v>
+      </c>
+      <c r="I213" s="4">
+        <v>1002695.52</v>
+      </c>
+      <c r="J213">
+        <v>296.88</v>
+      </c>
+      <c r="K213">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>115</v>
+      </c>
+      <c r="B214" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C214" t="s">
+        <v>107</v>
+      </c>
+      <c r="D214">
+        <v>1023</v>
+      </c>
+      <c r="E214" t="s">
+        <v>29</v>
+      </c>
+      <c r="F214" s="4">
+        <v>121367462.18000001</v>
+      </c>
+      <c r="H214" s="4">
+        <v>95455898.040000007</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>115</v>
+      </c>
+      <c r="B215" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C215" t="s">
+        <v>107</v>
+      </c>
+      <c r="D215">
+        <v>1024</v>
+      </c>
+      <c r="E215" t="s">
+        <v>30</v>
+      </c>
+      <c r="F215" s="4">
+        <v>109184581.19</v>
+      </c>
+      <c r="G215" s="4">
+        <v>5641979.0199999996</v>
+      </c>
+      <c r="H215" s="4">
+        <v>85532969.939999998</v>
+      </c>
+      <c r="I215" s="4">
+        <v>4448399.41</v>
+      </c>
+      <c r="J215">
+        <v>2085.7820000000002</v>
+      </c>
+      <c r="K215">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>115</v>
+      </c>
+      <c r="B216" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C216" t="s">
+        <v>107</v>
+      </c>
+      <c r="D216">
+        <v>1026</v>
+      </c>
+      <c r="E216" t="s">
+        <v>31</v>
+      </c>
+      <c r="F216" s="4">
+        <v>82025578.689999998</v>
+      </c>
+      <c r="H216" s="4">
+        <v>64263162.649999999</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>115</v>
+      </c>
+      <c r="B217" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C217" t="s">
+        <v>107</v>
+      </c>
+      <c r="D217">
+        <v>1027</v>
+      </c>
+      <c r="E217" t="s">
+        <v>32</v>
+      </c>
+      <c r="F217" s="4">
+        <v>23356118.800000001</v>
+      </c>
+      <c r="H217" s="4">
+        <v>18489201.469999999</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>115</v>
+      </c>
+      <c r="B218" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C218" t="s">
+        <v>107</v>
+      </c>
+      <c r="D218">
+        <v>1028</v>
+      </c>
+      <c r="E218" t="s">
+        <v>33</v>
+      </c>
+      <c r="F218" s="4">
+        <v>71622323.280000001</v>
+      </c>
+      <c r="G218" s="4">
+        <v>38849.25</v>
+      </c>
+      <c r="H218" s="4">
+        <v>56392511.5</v>
+      </c>
+      <c r="I218" s="4">
+        <v>30100.14</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>115</v>
+      </c>
+      <c r="B219" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C219" t="s">
+        <v>107</v>
+      </c>
+      <c r="D219">
+        <v>1029</v>
+      </c>
+      <c r="E219" t="s">
+        <v>34</v>
+      </c>
+      <c r="F219" s="4">
+        <v>65690813.5</v>
+      </c>
+      <c r="H219" s="4">
+        <v>51763497.969999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>115</v>
+      </c>
+      <c r="B220" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C220" t="s">
+        <v>107</v>
+      </c>
+      <c r="D220">
+        <v>1030</v>
+      </c>
+      <c r="E220" t="s">
+        <v>35</v>
+      </c>
+      <c r="F220" s="4">
+        <v>27032072.77</v>
+      </c>
+      <c r="H220" s="4">
+        <v>21390453.120000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>115</v>
+      </c>
+      <c r="B221" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C221" t="s">
+        <v>107</v>
+      </c>
+      <c r="D221">
+        <v>1031</v>
+      </c>
+      <c r="E221" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221" s="4">
+        <v>118383356.8</v>
+      </c>
+      <c r="G221" s="4">
+        <v>920704.65</v>
+      </c>
+      <c r="H221" s="4">
+        <v>93731603.140000001</v>
+      </c>
+      <c r="I221" s="4">
+        <v>733699.85</v>
+      </c>
+      <c r="J221">
+        <v>186.11500000000001</v>
+      </c>
+      <c r="K221">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>115</v>
+      </c>
+      <c r="B222" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C222" t="s">
+        <v>107</v>
+      </c>
+      <c r="D222">
+        <v>1032</v>
+      </c>
+      <c r="E222" t="s">
+        <v>37</v>
+      </c>
+      <c r="F222" s="4">
+        <v>88353724.75</v>
+      </c>
+      <c r="H222" s="4">
+        <v>69325625.310000002</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>115</v>
+      </c>
+      <c r="B223" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C223" t="s">
+        <v>107</v>
+      </c>
+      <c r="D223">
+        <v>1033</v>
+      </c>
+      <c r="E223" t="s">
+        <v>38</v>
+      </c>
+      <c r="F223" s="4">
+        <v>50694639.439999998</v>
+      </c>
+      <c r="G223" s="4">
+        <v>126352.21</v>
+      </c>
+      <c r="H223" s="4">
+        <v>40098761.700000003</v>
+      </c>
+      <c r="I223" s="4">
+        <v>98583.1</v>
+      </c>
+      <c r="J223">
+        <v>45</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>115</v>
+      </c>
+      <c r="B224" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C224" t="s">
+        <v>107</v>
+      </c>
+      <c r="D224">
+        <v>1035</v>
+      </c>
+      <c r="E224" t="s">
+        <v>39</v>
+      </c>
+      <c r="F224" s="4">
+        <v>57281261.170000002</v>
+      </c>
+      <c r="G224" s="4">
+        <v>91413.75</v>
+      </c>
+      <c r="H224" s="4">
+        <v>45011539.619999997</v>
+      </c>
+      <c r="I224" s="4">
+        <v>76951.820000000007</v>
+      </c>
+      <c r="J224">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>115</v>
+      </c>
+      <c r="B225" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C225" t="s">
+        <v>107</v>
+      </c>
+      <c r="D225">
+        <v>1036</v>
+      </c>
+      <c r="E225" t="s">
+        <v>40</v>
+      </c>
+      <c r="F225" s="4">
+        <v>23441428.149999999</v>
+      </c>
+      <c r="H225" s="4">
+        <v>18362832.02</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>115</v>
+      </c>
+      <c r="B226" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C226" t="s">
+        <v>107</v>
+      </c>
+      <c r="D226">
+        <v>1038</v>
+      </c>
+      <c r="E226" t="s">
+        <v>42</v>
+      </c>
+      <c r="F226" s="4">
+        <v>113063444.08</v>
+      </c>
+      <c r="G226" s="4">
+        <v>1372332.63</v>
+      </c>
+      <c r="H226" s="4">
+        <v>88669626.450000003</v>
+      </c>
+      <c r="I226" s="4">
+        <v>1090560.47</v>
+      </c>
+      <c r="J226">
+        <v>456.149</v>
+      </c>
+      <c r="K226">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>115</v>
+      </c>
+      <c r="B227" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C227" t="s">
+        <v>107</v>
+      </c>
+      <c r="D227">
+        <v>1039</v>
+      </c>
+      <c r="E227" t="s">
+        <v>43</v>
+      </c>
+      <c r="F227" s="4">
+        <v>93331073.579999998</v>
+      </c>
+      <c r="G227" s="4">
+        <v>1119999.25</v>
+      </c>
+      <c r="H227" s="4">
+        <v>73045671.590000004</v>
+      </c>
+      <c r="I227" s="4">
+        <v>867768.04</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>115</v>
+      </c>
+      <c r="B228" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C228" t="s">
+        <v>107</v>
+      </c>
+      <c r="D228">
+        <v>1042</v>
+      </c>
+      <c r="E228" t="s">
+        <v>44</v>
+      </c>
+      <c r="F228" s="4">
+        <v>82474426.769999996</v>
+      </c>
+      <c r="G228" s="4">
+        <v>335784.57</v>
+      </c>
+      <c r="H228" s="4">
+        <v>65096569.829999998</v>
+      </c>
+      <c r="I228" s="4">
+        <v>273439.26</v>
+      </c>
+      <c r="J228">
+        <v>89.805999999999997</v>
+      </c>
+      <c r="K228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>115</v>
+      </c>
+      <c r="B229" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C229" t="s">
+        <v>107</v>
+      </c>
+      <c r="D229">
+        <v>1043</v>
+      </c>
+      <c r="E229" t="s">
+        <v>45</v>
+      </c>
+      <c r="F229" s="4">
+        <v>75446146</v>
+      </c>
+      <c r="H229" s="4">
+        <v>58881296.909999996</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>115</v>
+      </c>
+      <c r="B230" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C230" t="s">
+        <v>107</v>
+      </c>
+      <c r="D230">
+        <v>1044</v>
+      </c>
+      <c r="E230" t="s">
+        <v>46</v>
+      </c>
+      <c r="F230" s="4">
+        <v>21249287.760000002</v>
+      </c>
+      <c r="H230" s="4">
+        <v>16713321.41</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>115</v>
+      </c>
+      <c r="B231" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C231" t="s">
+        <v>107</v>
+      </c>
+      <c r="D231">
+        <v>1045</v>
+      </c>
+      <c r="E231" t="s">
+        <v>47</v>
+      </c>
+      <c r="F231" s="4">
+        <v>19956082.989999998</v>
+      </c>
+      <c r="G231" s="4">
+        <v>159999.20000000001</v>
+      </c>
+      <c r="H231" s="4">
+        <v>15727114.58</v>
+      </c>
+      <c r="I231" s="4">
+        <v>123966.32</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>115</v>
+      </c>
+      <c r="B232" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C232" t="s">
+        <v>107</v>
+      </c>
+      <c r="D232">
+        <v>1046</v>
+      </c>
+      <c r="E232" t="s">
+        <v>48</v>
+      </c>
+      <c r="F232" s="4">
+        <v>36343293.280000001</v>
+      </c>
+      <c r="H232" s="4">
+        <v>28523704.989999998</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>115</v>
+      </c>
+      <c r="B233" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C233" t="s">
+        <v>107</v>
+      </c>
+      <c r="D233">
+        <v>1050</v>
+      </c>
+      <c r="E233" t="s">
+        <v>49</v>
+      </c>
+      <c r="F233" s="4">
+        <v>54172345.640000001</v>
+      </c>
+      <c r="G233" s="4">
+        <v>594999.31000000006</v>
+      </c>
+      <c r="H233" s="4">
+        <v>42640894.159999996</v>
+      </c>
+      <c r="I233" s="4">
+        <v>461001.54</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>115</v>
+      </c>
+      <c r="B234" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C234" t="s">
+        <v>107</v>
+      </c>
+      <c r="D234">
+        <v>1051</v>
+      </c>
+      <c r="E234" t="s">
+        <v>50</v>
+      </c>
+      <c r="F234" s="4">
+        <v>82293298.159999996</v>
+      </c>
+      <c r="G234" s="4">
+        <v>27640.400000000001</v>
+      </c>
+      <c r="H234" s="4">
+        <v>65710692.049999997</v>
+      </c>
+      <c r="I234" s="4">
+        <v>17541.66</v>
+      </c>
+      <c r="J234">
+        <v>6</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>115</v>
+      </c>
+      <c r="B235" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C235" t="s">
+        <v>107</v>
+      </c>
+      <c r="D235">
+        <v>1052</v>
+      </c>
+      <c r="E235" t="s">
+        <v>51</v>
+      </c>
+      <c r="F235" s="4">
+        <v>63713535.57</v>
+      </c>
+      <c r="G235" s="4">
+        <v>1587996.19</v>
+      </c>
+      <c r="H235" s="4">
+        <v>50545631.689999998</v>
+      </c>
+      <c r="I235" s="4">
+        <v>1214873.1000000001</v>
+      </c>
+      <c r="J235">
+        <v>4</v>
+      </c>
+      <c r="K235">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>115</v>
+      </c>
+      <c r="B236" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C236" t="s">
+        <v>107</v>
+      </c>
+      <c r="D236">
+        <v>1053</v>
+      </c>
+      <c r="E236" t="s">
+        <v>52</v>
+      </c>
+      <c r="F236" s="4">
+        <v>72907562.590000004</v>
+      </c>
+      <c r="G236" s="4">
+        <v>51242.02</v>
+      </c>
+      <c r="H236" s="4">
+        <v>57282892.990000002</v>
+      </c>
+      <c r="I236" s="4">
+        <v>39764.85</v>
+      </c>
+      <c r="J236">
+        <v>21</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>115</v>
+      </c>
+      <c r="B237" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C237" t="s">
+        <v>107</v>
+      </c>
+      <c r="D237">
+        <v>1054</v>
+      </c>
+      <c r="E237" t="s">
+        <v>53</v>
+      </c>
+      <c r="F237" s="4">
+        <v>97988399.969999999</v>
+      </c>
+      <c r="G237" s="4">
+        <v>2193814.04</v>
+      </c>
+      <c r="H237" s="4">
+        <v>76467859.370000005</v>
+      </c>
+      <c r="I237" s="4">
+        <v>1709206.75</v>
+      </c>
+      <c r="J237">
+        <v>873.89800000000002</v>
+      </c>
+      <c r="K237">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>115</v>
+      </c>
+      <c r="B238" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C238" t="s">
+        <v>107</v>
+      </c>
+      <c r="D238">
+        <v>1055</v>
+      </c>
+      <c r="E238" t="s">
+        <v>54</v>
+      </c>
+      <c r="F238" s="4">
+        <v>70775870.599999994</v>
+      </c>
+      <c r="G238" s="4">
+        <v>1392103.49</v>
+      </c>
+      <c r="H238" s="4">
+        <v>55759042.57</v>
+      </c>
+      <c r="I238" s="4">
+        <v>1099557.1299999999</v>
+      </c>
+      <c r="J238">
+        <v>317.02</v>
+      </c>
+      <c r="K238">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>115</v>
+      </c>
+      <c r="B239" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C239" t="s">
+        <v>107</v>
+      </c>
+      <c r="D239">
+        <v>1056</v>
+      </c>
+      <c r="E239" t="s">
+        <v>55</v>
+      </c>
+      <c r="F239" s="4">
+        <v>47277557.100000001</v>
+      </c>
+      <c r="G239" s="4">
+        <v>686508.39</v>
+      </c>
+      <c r="H239" s="4">
+        <v>37024510.159999996</v>
+      </c>
+      <c r="I239" s="4">
+        <v>531902.14</v>
+      </c>
+      <c r="J239">
+        <v>26</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>115</v>
+      </c>
+      <c r="B240" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C240" t="s">
+        <v>107</v>
+      </c>
+      <c r="D240">
+        <v>1057</v>
+      </c>
+      <c r="E240" t="s">
+        <v>56</v>
+      </c>
+      <c r="F240" s="4">
+        <v>139674044.00999999</v>
+      </c>
+      <c r="G240" s="4">
+        <v>4284403.6399999997</v>
+      </c>
+      <c r="H240" s="4">
+        <v>109486280.79000001</v>
+      </c>
+      <c r="I240" s="4">
+        <v>3336225.41</v>
+      </c>
+      <c r="J240">
+        <v>1361.3689999999999</v>
+      </c>
+      <c r="K240">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>115</v>
+      </c>
+      <c r="B241" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C241" t="s">
+        <v>107</v>
+      </c>
+      <c r="D241">
+        <v>1058</v>
+      </c>
+      <c r="E241" t="s">
+        <v>57</v>
+      </c>
+      <c r="F241" s="4">
+        <v>66549019.189999998</v>
+      </c>
+      <c r="G241" s="4">
+        <v>6833029.1500000004</v>
+      </c>
+      <c r="H241" s="4">
+        <v>52219749.07</v>
+      </c>
+      <c r="I241" s="4">
+        <v>5259550.25</v>
+      </c>
+      <c r="J241">
+        <v>2027.9860000000001</v>
+      </c>
+      <c r="K241">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>115</v>
+      </c>
+      <c r="B242" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C242" t="s">
+        <v>107</v>
+      </c>
+      <c r="D242">
+        <v>1059</v>
+      </c>
+      <c r="E242" t="s">
+        <v>58</v>
+      </c>
+      <c r="F242" s="4">
+        <v>73163430.25</v>
+      </c>
+      <c r="H242" s="4">
+        <v>57192773.509999998</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>115</v>
+      </c>
+      <c r="B243" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C243" t="s">
+        <v>107</v>
+      </c>
+      <c r="D243">
+        <v>1060</v>
+      </c>
+      <c r="E243" t="s">
+        <v>59</v>
+      </c>
+      <c r="F243" s="4">
+        <v>45941503.619999997</v>
+      </c>
+      <c r="H243" s="4">
+        <v>36246783.310000002</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>115</v>
+      </c>
+      <c r="B244" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C244" t="s">
+        <v>107</v>
+      </c>
+      <c r="D244">
+        <v>1061</v>
+      </c>
+      <c r="E244" t="s">
+        <v>60</v>
+      </c>
+      <c r="F244" s="4">
+        <v>103501054.84</v>
+      </c>
+      <c r="G244" s="4">
+        <v>216399.1</v>
+      </c>
+      <c r="H244" s="4">
+        <v>80693563.349999994</v>
+      </c>
+      <c r="I244" s="4">
+        <v>164952.92000000001</v>
+      </c>
+      <c r="J244">
+        <v>73</v>
+      </c>
+      <c r="K244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>115</v>
+      </c>
+      <c r="B245" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C245" t="s">
+        <v>107</v>
+      </c>
+      <c r="D245">
+        <v>1066</v>
+      </c>
+      <c r="E245" t="s">
+        <v>111</v>
+      </c>
+      <c r="F245" s="4">
+        <v>2051651.18</v>
+      </c>
+      <c r="H245" s="4">
+        <v>1595585.86</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>115</v>
+      </c>
+      <c r="B246" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C246" t="s">
+        <v>107</v>
+      </c>
+      <c r="D246">
+        <v>1067</v>
+      </c>
+      <c r="E246" t="s">
+        <v>61</v>
+      </c>
+      <c r="F246" s="4">
+        <v>41708740.450000003</v>
+      </c>
+      <c r="G246" s="4">
+        <v>122608.54</v>
+      </c>
+      <c r="H246" s="4">
+        <v>32887117.48</v>
+      </c>
+      <c r="I246" s="4">
+        <v>99293.9</v>
+      </c>
+      <c r="J246">
+        <v>58.097000000000001</v>
+      </c>
+      <c r="K246">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>115</v>
+      </c>
+      <c r="B247" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C247" t="s">
+        <v>107</v>
+      </c>
+      <c r="D247">
+        <v>1068</v>
+      </c>
+      <c r="E247" t="s">
+        <v>62</v>
+      </c>
+      <c r="F247" s="4">
+        <v>83018412.5</v>
+      </c>
+      <c r="H247" s="4">
+        <v>65373006.689999998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>115</v>
+      </c>
+      <c r="B248" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C248" t="s">
+        <v>107</v>
+      </c>
+      <c r="D248">
+        <v>1074</v>
+      </c>
+      <c r="E248" t="s">
+        <v>63</v>
+      </c>
+      <c r="F248" s="4">
+        <v>27625436.469999999</v>
+      </c>
+      <c r="G248" s="4">
+        <v>140497.15</v>
+      </c>
+      <c r="H248" s="4">
+        <v>21678603.870000001</v>
+      </c>
+      <c r="I248" s="4">
+        <v>109489.73</v>
+      </c>
+      <c r="J248">
+        <v>29.442</v>
+      </c>
+      <c r="K248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>115</v>
+      </c>
+      <c r="B249" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C249" t="s">
+        <v>107</v>
+      </c>
+      <c r="D249">
+        <v>1075</v>
+      </c>
+      <c r="E249" t="s">
+        <v>64</v>
+      </c>
+      <c r="F249" s="4">
+        <v>72517027.519999996</v>
+      </c>
+      <c r="G249" s="4">
+        <v>269999.09000000003</v>
+      </c>
+      <c r="H249" s="4">
+        <v>57839172.240000002</v>
+      </c>
+      <c r="I249" s="4">
+        <v>209193.5</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>115</v>
+      </c>
+      <c r="B250" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C250" t="s">
+        <v>107</v>
+      </c>
+      <c r="D250">
+        <v>1076</v>
+      </c>
+      <c r="E250" t="s">
+        <v>65</v>
+      </c>
+      <c r="F250" s="4">
+        <v>70181635.799999997</v>
+      </c>
+      <c r="G250" s="4">
+        <v>25799.25</v>
+      </c>
+      <c r="H250" s="4">
+        <v>55345411.259999998</v>
+      </c>
+      <c r="I250" s="4">
+        <v>21888.5</v>
+      </c>
+      <c r="J250">
+        <v>1</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>115</v>
+      </c>
+      <c r="B251" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C251" t="s">
+        <v>107</v>
+      </c>
+      <c r="D251">
+        <v>1077</v>
+      </c>
+      <c r="E251" t="s">
+        <v>66</v>
+      </c>
+      <c r="F251" s="4">
+        <v>129933190.87</v>
+      </c>
+      <c r="G251" s="4">
+        <v>2817730.85</v>
+      </c>
+      <c r="H251" s="4">
+        <v>102627399.45999999</v>
+      </c>
+      <c r="I251" s="4">
+        <v>2067294.33</v>
+      </c>
+      <c r="J251">
+        <v>64.173000000000002</v>
+      </c>
+      <c r="K251">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>115</v>
+      </c>
+      <c r="B252" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C252" t="s">
+        <v>107</v>
+      </c>
+      <c r="D252">
+        <v>1078</v>
+      </c>
+      <c r="E252" t="s">
+        <v>67</v>
+      </c>
+      <c r="F252" s="4">
+        <v>79154904.900000006</v>
+      </c>
+      <c r="G252" s="4">
+        <v>631999.19999999995</v>
+      </c>
+      <c r="H252" s="4">
+        <v>62695708.450000003</v>
+      </c>
+      <c r="I252" s="4">
+        <v>489668.8</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>115</v>
+      </c>
+      <c r="B253" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C253" t="s">
+        <v>107</v>
+      </c>
+      <c r="D253">
+        <v>1080</v>
+      </c>
+      <c r="E253" t="s">
+        <v>68</v>
+      </c>
+      <c r="F253" s="4">
+        <v>58283979.159999996</v>
+      </c>
+      <c r="G253" s="4">
+        <v>4461558.9800000004</v>
+      </c>
+      <c r="H253" s="4">
+        <v>45513863.399999999</v>
+      </c>
+      <c r="I253" s="4">
+        <v>3455341.69</v>
+      </c>
+      <c r="J253">
+        <v>1033.3530000000001</v>
+      </c>
+      <c r="K253">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>115</v>
+      </c>
+      <c r="B254" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C254" t="s">
+        <v>107</v>
+      </c>
+      <c r="D254">
+        <v>1081</v>
+      </c>
+      <c r="E254" t="s">
+        <v>69</v>
+      </c>
+      <c r="F254" s="4">
+        <v>54254723.32</v>
+      </c>
+      <c r="H254" s="4">
+        <v>42915281.100000001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>115</v>
+      </c>
+      <c r="B255" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C255" t="s">
+        <v>107</v>
+      </c>
+      <c r="D255">
+        <v>1082</v>
+      </c>
+      <c r="E255" t="s">
+        <v>70</v>
+      </c>
+      <c r="F255" s="4">
+        <v>26379268.489999998</v>
+      </c>
+      <c r="H255" s="4">
+        <v>20991361.559999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>115</v>
+      </c>
+      <c r="B256" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C256" t="s">
+        <v>107</v>
+      </c>
+      <c r="D256">
+        <v>1084</v>
+      </c>
+      <c r="E256" t="s">
+        <v>71</v>
+      </c>
+      <c r="F256" s="4">
+        <v>24173965.789999999</v>
+      </c>
+      <c r="G256" s="4">
+        <v>420518.41</v>
+      </c>
+      <c r="H256" s="4">
+        <v>19117222.530000001</v>
+      </c>
+      <c r="I256" s="4">
+        <v>329296.34000000003</v>
+      </c>
+      <c r="J256">
+        <v>100.334</v>
+      </c>
+      <c r="K256">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>115</v>
+      </c>
+      <c r="B257" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C257" t="s">
+        <v>107</v>
+      </c>
+      <c r="D257">
+        <v>1085</v>
+      </c>
+      <c r="E257" t="s">
+        <v>72</v>
+      </c>
+      <c r="F257" s="4">
+        <v>24419111.239999998</v>
+      </c>
+      <c r="H257" s="4">
+        <v>19313316.719999999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>115</v>
+      </c>
+      <c r="B258" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C258" t="s">
+        <v>107</v>
+      </c>
+      <c r="D258">
+        <v>1086</v>
+      </c>
+      <c r="E258" t="s">
+        <v>73</v>
+      </c>
+      <c r="F258" s="4">
+        <v>72160689.099999994</v>
+      </c>
+      <c r="H258" s="4">
+        <v>56472075.159999996</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>115</v>
+      </c>
+      <c r="B259" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C259" t="s">
+        <v>107</v>
+      </c>
+      <c r="D259">
+        <v>1087</v>
+      </c>
+      <c r="E259" t="s">
+        <v>74</v>
+      </c>
+      <c r="F259" s="4">
+        <v>109331542.63</v>
+      </c>
+      <c r="G259" s="4">
+        <v>4322736.96</v>
+      </c>
+      <c r="H259" s="4">
+        <v>86136464.780000001</v>
+      </c>
+      <c r="I259" s="4">
+        <v>3326064.94</v>
+      </c>
+      <c r="J259">
+        <v>1354.6110000000001</v>
+      </c>
+      <c r="K259">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>115</v>
+      </c>
+      <c r="B260" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C260" t="s">
+        <v>107</v>
+      </c>
+      <c r="D260">
+        <v>1088</v>
+      </c>
+      <c r="E260" t="s">
+        <v>75</v>
+      </c>
+      <c r="F260" s="4">
+        <v>49617386.689999998</v>
+      </c>
+      <c r="G260" s="4">
+        <v>1375141.1</v>
+      </c>
+      <c r="H260" s="4">
+        <v>39465632.060000002</v>
+      </c>
+      <c r="I260" s="4">
+        <v>1071952.02</v>
+      </c>
+      <c r="J260">
+        <v>26</v>
+      </c>
+      <c r="K260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>115</v>
+      </c>
+      <c r="B261" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C261" t="s">
+        <v>107</v>
+      </c>
+      <c r="D261">
+        <v>1092</v>
+      </c>
+      <c r="E261" t="s">
+        <v>76</v>
+      </c>
+      <c r="F261" s="4">
+        <v>63880097.310000002</v>
+      </c>
+      <c r="H261" s="4">
+        <v>49878651.159999996</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>115</v>
+      </c>
+      <c r="B262" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C262" t="s">
+        <v>107</v>
+      </c>
+      <c r="D262">
+        <v>1093</v>
+      </c>
+      <c r="E262" t="s">
+        <v>77</v>
+      </c>
+      <c r="F262" s="4">
+        <v>98158981.129999995</v>
+      </c>
+      <c r="H262" s="4">
+        <v>77395224.75</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>115</v>
+      </c>
+      <c r="B263" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C263" t="s">
+        <v>107</v>
+      </c>
+      <c r="D263">
+        <v>1096</v>
+      </c>
+      <c r="E263" t="s">
+        <v>78</v>
+      </c>
+      <c r="F263" s="4">
+        <v>78817118.450000003</v>
+      </c>
+      <c r="H263" s="4">
+        <v>61975747.439999998</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>115</v>
+      </c>
+      <c r="B264" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C264" t="s">
+        <v>107</v>
+      </c>
+      <c r="D264">
+        <v>1097</v>
+      </c>
+      <c r="E264" t="s">
+        <v>79</v>
+      </c>
+      <c r="F264" s="4">
+        <v>61704554.340000004</v>
+      </c>
+      <c r="H264" s="4">
+        <v>48461231.640000001</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>115</v>
+      </c>
+      <c r="B265" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C265" t="s">
+        <v>107</v>
+      </c>
+      <c r="D265">
+        <v>1098</v>
+      </c>
+      <c r="E265" t="s">
+        <v>80</v>
+      </c>
+      <c r="F265" s="4">
+        <v>48783819.68</v>
+      </c>
+      <c r="H265" s="4">
+        <v>38148522.369999997</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>115</v>
+      </c>
+      <c r="B266" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C266" t="s">
+        <v>107</v>
+      </c>
+      <c r="D266">
+        <v>1099</v>
+      </c>
+      <c r="E266" t="s">
+        <v>81</v>
+      </c>
+      <c r="F266" s="4">
+        <v>62811915.5</v>
+      </c>
+      <c r="H266" s="4">
+        <v>50106366.450000003</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>115</v>
+      </c>
+      <c r="B267" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C267" t="s">
+        <v>107</v>
+      </c>
+      <c r="D267">
+        <v>1100</v>
+      </c>
+      <c r="E267" t="s">
+        <v>82</v>
+      </c>
+      <c r="F267" s="4">
+        <v>80819039.560000002</v>
+      </c>
+      <c r="H267" s="4">
+        <v>63611948.32</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>115</v>
+      </c>
+      <c r="B268" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C268" t="s">
+        <v>107</v>
+      </c>
+      <c r="D268">
+        <v>1102</v>
+      </c>
+      <c r="E268" t="s">
+        <v>112</v>
+      </c>
+      <c r="F268" s="4">
+        <v>2729253.36</v>
+      </c>
+      <c r="H268" s="4">
+        <v>2133667.2799999998</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>115</v>
+      </c>
+      <c r="B269" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C269" t="s">
+        <v>107</v>
+      </c>
+      <c r="D269">
+        <v>1103</v>
+      </c>
+      <c r="E269" t="s">
+        <v>113</v>
+      </c>
+      <c r="F269" s="4">
+        <v>674576.11</v>
+      </c>
+      <c r="H269" s="4">
+        <v>522500.7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>115</v>
+      </c>
+      <c r="B270" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C270" t="s">
+        <v>107</v>
+      </c>
+      <c r="D270">
+        <v>1106</v>
+      </c>
+      <c r="E270" t="s">
+        <v>83</v>
+      </c>
+      <c r="F270" s="4">
+        <v>29420053.670000002</v>
+      </c>
+      <c r="H270" s="4">
+        <v>23273080.420000002</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>115</v>
+      </c>
+      <c r="B271" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C271" t="s">
+        <v>107</v>
+      </c>
+      <c r="D271">
+        <v>1108</v>
+      </c>
+      <c r="E271" t="s">
+        <v>84</v>
+      </c>
+      <c r="F271" s="4">
+        <v>76619212.650000006</v>
+      </c>
+      <c r="G271" s="4">
+        <v>539997</v>
+      </c>
+      <c r="H271" s="4">
+        <v>60315946.909999996</v>
+      </c>
+      <c r="I271" s="4">
+        <v>418386.12</v>
+      </c>
+      <c r="J271">
+        <v>4</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>115</v>
+      </c>
+      <c r="B272" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C272" t="s">
+        <v>107</v>
+      </c>
+      <c r="D272">
+        <v>1109</v>
+      </c>
+      <c r="E272" t="s">
+        <v>114</v>
+      </c>
+      <c r="F272" s="4">
+        <v>4867406.8</v>
+      </c>
+      <c r="H272" s="4">
+        <v>3815783.44</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>115</v>
+      </c>
+      <c r="B273" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C273" t="s">
+        <v>107</v>
+      </c>
+      <c r="D273">
+        <v>1110</v>
+      </c>
+      <c r="E273" t="s">
+        <v>85</v>
+      </c>
+      <c r="F273" s="4">
+        <v>49707128.170000002</v>
+      </c>
+      <c r="H273" s="4">
+        <v>39065736.380000003</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>115</v>
+      </c>
+      <c r="B274" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C274" t="s">
+        <v>107</v>
+      </c>
+      <c r="D274">
+        <v>1111</v>
+      </c>
+      <c r="E274" t="s">
+        <v>86</v>
+      </c>
+      <c r="F274" s="4">
+        <v>47685017.810000002</v>
+      </c>
+      <c r="H274" s="4">
+        <v>37893586.270000003</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>115</v>
+      </c>
+      <c r="B275" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C275" t="s">
+        <v>107</v>
+      </c>
+      <c r="D275">
+        <v>1114</v>
+      </c>
+      <c r="E275" t="s">
+        <v>87</v>
+      </c>
+      <c r="F275" s="4">
+        <v>34808096.560000002</v>
+      </c>
+      <c r="H275" s="4">
+        <v>27385850.120000001</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>115</v>
+      </c>
+      <c r="B276" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C276" t="s">
+        <v>107</v>
+      </c>
+      <c r="D276">
+        <v>1115</v>
+      </c>
+      <c r="E276" t="s">
+        <v>88</v>
+      </c>
+      <c r="F276" s="4">
+        <v>68054935.319999993</v>
+      </c>
+      <c r="G276" s="4">
+        <v>903872.64</v>
+      </c>
+      <c r="H276" s="4">
+        <v>53830409.960000001</v>
+      </c>
+      <c r="I276" s="4">
+        <v>721580.21</v>
+      </c>
+      <c r="J276">
+        <v>322.637</v>
+      </c>
+      <c r="K276">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>115</v>
+      </c>
+      <c r="B277" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C277" t="s">
+        <v>107</v>
+      </c>
+      <c r="D277">
+        <v>1116</v>
+      </c>
+      <c r="E277" t="s">
+        <v>89</v>
+      </c>
+      <c r="F277" s="4">
+        <v>59694482.350000001</v>
+      </c>
+      <c r="H277" s="4">
+        <v>46722720.159999996</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>115</v>
+      </c>
+      <c r="B278" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C278" t="s">
+        <v>107</v>
+      </c>
+      <c r="D278">
+        <v>1119</v>
+      </c>
+      <c r="E278" t="s">
+        <v>90</v>
+      </c>
+      <c r="F278" s="4">
+        <v>48102459.920000002</v>
+      </c>
+      <c r="H278" s="4">
+        <v>37829384.869999997</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>115</v>
+      </c>
+      <c r="B279" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C279" t="s">
+        <v>107</v>
+      </c>
+      <c r="D279">
+        <v>2997</v>
+      </c>
+      <c r="E279" t="s">
+        <v>91</v>
+      </c>
+      <c r="F279" s="4">
+        <v>353739521.47000003</v>
+      </c>
+      <c r="G279" s="4">
+        <v>25107902.460000001</v>
+      </c>
+      <c r="H279" s="4">
+        <v>280895183.18000001</v>
+      </c>
+      <c r="I279" s="4">
+        <v>19327704.710000001</v>
+      </c>
+      <c r="J279">
+        <v>6137.5129999999999</v>
+      </c>
+      <c r="K279">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>115</v>
+      </c>
+      <c r="B280" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C280" t="s">
+        <v>107</v>
+      </c>
+      <c r="D280">
+        <v>2998</v>
+      </c>
+      <c r="E280" t="s">
+        <v>92</v>
+      </c>
+      <c r="F280" s="4">
+        <v>194319692.40000001</v>
+      </c>
+      <c r="G280" s="4">
+        <v>13141775.5</v>
+      </c>
+      <c r="H280" s="4">
+        <v>152287467.65000001</v>
+      </c>
+      <c r="I280" s="4">
+        <v>10161305.84</v>
+      </c>
+      <c r="J280">
+        <v>3929.6860000000001</v>
+      </c>
+      <c r="K280">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>115</v>
+      </c>
+      <c r="B281" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C281" t="s">
+        <v>107</v>
+      </c>
+      <c r="D281">
+        <v>2999</v>
+      </c>
+      <c r="E281" t="s">
+        <v>93</v>
+      </c>
+      <c r="F281" s="4">
+        <v>203213620.56</v>
+      </c>
+      <c r="G281" s="4">
+        <v>12796960.52</v>
+      </c>
+      <c r="H281" s="4">
+        <v>159499309.84999999</v>
+      </c>
+      <c r="I281" s="4">
+        <v>9901876.9000000004</v>
+      </c>
+      <c r="J281">
+        <v>4485.768</v>
+      </c>
+      <c r="K281">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>115</v>
+      </c>
+      <c r="B282" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C282" t="s">
+        <v>107</v>
+      </c>
+      <c r="D282">
+        <v>3601</v>
+      </c>
+      <c r="E282" t="s">
+        <v>94</v>
+      </c>
+      <c r="F282" s="4">
+        <v>228107555.47999999</v>
+      </c>
+      <c r="G282" s="4">
+        <v>16481393.560000001</v>
+      </c>
+      <c r="H282" s="4">
+        <v>178986473.02000001</v>
+      </c>
+      <c r="I282" s="4">
+        <v>12808322.25</v>
+      </c>
+      <c r="J282">
+        <v>4986.8370000000004</v>
+      </c>
+      <c r="K282">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>115</v>
+      </c>
+      <c r="B283" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C283" t="s">
+        <v>107</v>
+      </c>
+      <c r="D283">
+        <v>3602</v>
+      </c>
+      <c r="E283" t="s">
+        <v>95</v>
+      </c>
+      <c r="F283" s="4">
+        <v>181050733.09</v>
+      </c>
+      <c r="G283" s="4">
+        <v>8790635.5899999999</v>
+      </c>
+      <c r="H283" s="4">
+        <v>141990761.08000001</v>
+      </c>
+      <c r="I283" s="4">
+        <v>6864352.7199999997</v>
+      </c>
+      <c r="J283">
+        <v>1798.6780000000001</v>
+      </c>
+      <c r="K283">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>115</v>
+      </c>
+      <c r="B284" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C284" t="s">
+        <v>107</v>
+      </c>
+      <c r="D284">
+        <v>3603</v>
+      </c>
+      <c r="E284" t="s">
+        <v>96</v>
+      </c>
+      <c r="F284" s="4">
+        <v>196180236.13</v>
+      </c>
+      <c r="G284" s="4">
+        <v>6542335.4400000004</v>
+      </c>
+      <c r="H284" s="4">
+        <v>153354560.59</v>
+      </c>
+      <c r="I284" s="4">
+        <v>5047170.9000000004</v>
+      </c>
+      <c r="J284">
+        <v>2315.5920000000001</v>
+      </c>
+      <c r="K284">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>115</v>
+      </c>
+      <c r="B285" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C285" t="s">
+        <v>107</v>
+      </c>
+      <c r="D285">
+        <v>3604</v>
+      </c>
+      <c r="E285" t="s">
+        <v>97</v>
+      </c>
+      <c r="F285" s="4">
+        <v>141846980.34</v>
+      </c>
+      <c r="G285" s="4">
+        <v>9012860.0399999991</v>
+      </c>
+      <c r="H285" s="4">
+        <v>111184671.02</v>
+      </c>
+      <c r="I285" s="4">
+        <v>6994437.5999999996</v>
+      </c>
+      <c r="J285">
+        <v>2804.308</v>
+      </c>
+      <c r="K285">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>115</v>
+      </c>
+      <c r="B286" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C286" t="s">
+        <v>107</v>
+      </c>
+      <c r="D286">
+        <v>3605</v>
+      </c>
+      <c r="E286" t="s">
+        <v>98</v>
+      </c>
+      <c r="F286" s="4">
+        <v>233984670.03999999</v>
+      </c>
+      <c r="G286" s="4">
+        <v>17459201.600000001</v>
+      </c>
+      <c r="H286" s="4">
+        <v>184671372.44</v>
+      </c>
+      <c r="I286" s="4">
+        <v>13379512.16</v>
+      </c>
+      <c r="J286">
+        <v>4908.2929999999997</v>
+      </c>
+      <c r="K286">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>115</v>
+      </c>
+      <c r="B287" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C287" t="s">
+        <v>107</v>
+      </c>
+      <c r="D287">
+        <v>3606</v>
+      </c>
+      <c r="E287" t="s">
+        <v>99</v>
+      </c>
+      <c r="F287" s="4">
+        <v>135889890.13999999</v>
+      </c>
+      <c r="H287" s="4">
+        <v>106934006.65000001</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>115</v>
+      </c>
+      <c r="B288" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C288" t="s">
+        <v>107</v>
+      </c>
+      <c r="D288">
+        <v>3608</v>
+      </c>
+      <c r="E288" t="s">
+        <v>100</v>
+      </c>
+      <c r="F288" s="4">
+        <v>233744805.13</v>
+      </c>
+      <c r="G288" s="4">
+        <v>5450659.0199999996</v>
+      </c>
+      <c r="H288" s="4">
+        <v>183670667.77000001</v>
+      </c>
+      <c r="I288" s="4">
+        <v>4238773.6500000004</v>
+      </c>
+      <c r="J288">
+        <v>1759.5889999999999</v>
+      </c>
+      <c r="K288">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>115</v>
+      </c>
+      <c r="B289" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C289" t="s">
+        <v>107</v>
+      </c>
+      <c r="D289">
+        <v>3613</v>
+      </c>
+      <c r="E289" t="s">
+        <v>101</v>
+      </c>
+      <c r="F289" s="4">
+        <v>129217578.8</v>
+      </c>
+      <c r="G289" s="4">
+        <v>5192261.37</v>
+      </c>
+      <c r="H289" s="4">
+        <v>101878363.3</v>
+      </c>
+      <c r="I289" s="4">
+        <v>4064361.73</v>
+      </c>
+      <c r="J289">
+        <v>1662.87</v>
+      </c>
+      <c r="K289">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>115</v>
+      </c>
+      <c r="B290" s="5">
+        <v>46298</v>
+      </c>
+      <c r="C290" t="s">
+        <v>107</v>
+      </c>
+      <c r="D290">
+        <v>4001</v>
+      </c>
+      <c r="E290" t="s">
+        <v>102</v>
+      </c>
+      <c r="F290" s="4">
+        <v>33060838.350000001</v>
+      </c>
+      <c r="G290" s="4">
+        <v>143820.39000000001</v>
+      </c>
+      <c r="H290" s="4">
+        <v>26094183.940000001</v>
+      </c>
+      <c r="I290" s="4">
+        <v>119639.92</v>
+      </c>
+      <c r="J290">
+        <v>21.222000000000001</v>
+      </c>
+      <c r="K290">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>115</v>
+      </c>
+      <c r="B291" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C291" t="s">
+        <v>108</v>
+      </c>
+      <c r="D291">
+        <v>1002</v>
+      </c>
+      <c r="E291" t="s">
+        <v>10</v>
+      </c>
+      <c r="F291" s="4">
+        <v>56814105.280000001</v>
+      </c>
+      <c r="G291" s="4">
+        <v>838783.9</v>
+      </c>
+      <c r="H291" s="4">
+        <v>44412514.939999998</v>
+      </c>
+      <c r="I291" s="4">
+        <v>636325.31000000006</v>
+      </c>
+      <c r="J291">
+        <v>114</v>
+      </c>
+      <c r="K291">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>115</v>
+      </c>
+      <c r="B292" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C292" t="s">
+        <v>108</v>
+      </c>
+      <c r="D292">
+        <v>1003</v>
+      </c>
+      <c r="E292" t="s">
+        <v>11</v>
+      </c>
+      <c r="F292" s="4">
+        <v>51309425.82</v>
+      </c>
+      <c r="H292" s="4">
+        <v>40167811.240000002</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>115</v>
+      </c>
+      <c r="B293" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C293" t="s">
+        <v>108</v>
+      </c>
+      <c r="D293">
+        <v>1004</v>
+      </c>
+      <c r="E293" t="s">
+        <v>12</v>
+      </c>
+      <c r="F293" s="4">
+        <v>53587224.149999999</v>
+      </c>
+      <c r="G293" s="4">
+        <v>1169657.06</v>
+      </c>
+      <c r="H293" s="4">
+        <v>42277267.229999997</v>
+      </c>
+      <c r="I293" s="4">
+        <v>918904.47</v>
+      </c>
+      <c r="J293">
+        <v>305.53199999999998</v>
+      </c>
+      <c r="K293">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>115</v>
+      </c>
+      <c r="B294" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C294" t="s">
+        <v>108</v>
+      </c>
+      <c r="D294">
+        <v>1005</v>
+      </c>
+      <c r="E294" t="s">
+        <v>13</v>
+      </c>
+      <c r="F294" s="4">
+        <v>44794424.859999999</v>
+      </c>
+      <c r="H294" s="4">
+        <v>35352710.649999999</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>115</v>
+      </c>
+      <c r="B295" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C295" t="s">
+        <v>108</v>
+      </c>
+      <c r="D295">
+        <v>1006</v>
+      </c>
+      <c r="E295" t="s">
+        <v>14</v>
+      </c>
+      <c r="F295" s="4">
+        <v>48738620.170000002</v>
+      </c>
+      <c r="H295" s="4">
+        <v>38150513.380000003</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>115</v>
+      </c>
+      <c r="B296" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C296" t="s">
+        <v>108</v>
+      </c>
+      <c r="D296">
+        <v>1008</v>
+      </c>
+      <c r="E296" t="s">
+        <v>16</v>
+      </c>
+      <c r="F296" s="4">
+        <v>69158414.689999998</v>
+      </c>
+      <c r="H296" s="4">
+        <v>54343172.049999997</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>115</v>
+      </c>
+      <c r="B297" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C297" t="s">
+        <v>108</v>
+      </c>
+      <c r="D297">
+        <v>1010</v>
+      </c>
+      <c r="E297" t="s">
+        <v>17</v>
+      </c>
+      <c r="F297" s="4">
+        <v>34705327.340000004</v>
+      </c>
+      <c r="H297" s="4">
+        <v>27212043.440000001</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>115</v>
+      </c>
+      <c r="B298" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C298" t="s">
+        <v>108</v>
+      </c>
+      <c r="D298">
+        <v>1011</v>
+      </c>
+      <c r="E298" t="s">
+        <v>18</v>
+      </c>
+      <c r="F298" s="4">
+        <v>45716472.630000003</v>
+      </c>
+      <c r="H298" s="4">
+        <v>36555814.740000002</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>115</v>
+      </c>
+      <c r="B299" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C299" t="s">
+        <v>108</v>
+      </c>
+      <c r="D299">
+        <v>1012</v>
+      </c>
+      <c r="E299" t="s">
+        <v>19</v>
+      </c>
+      <c r="F299" s="4">
+        <v>35131909.030000001</v>
+      </c>
+      <c r="H299" s="4">
+        <v>27533147.629999999</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>115</v>
+      </c>
+      <c r="B300" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C300" t="s">
+        <v>108</v>
+      </c>
+      <c r="D300">
+        <v>1013</v>
+      </c>
+      <c r="E300" t="s">
+        <v>20</v>
+      </c>
+      <c r="F300" s="4">
+        <v>42923910.039999999</v>
+      </c>
+      <c r="H300" s="4">
+        <v>33838330.719999999</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>115</v>
+      </c>
+      <c r="B301" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C301" t="s">
+        <v>108</v>
+      </c>
+      <c r="D301">
+        <v>1014</v>
+      </c>
+      <c r="E301" t="s">
+        <v>21</v>
+      </c>
+      <c r="F301" s="4">
+        <v>37800498.270000003</v>
+      </c>
+      <c r="H301" s="4">
+        <v>29650561.350000001</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>115</v>
+      </c>
+      <c r="B302" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C302" t="s">
+        <v>108</v>
+      </c>
+      <c r="D302">
+        <v>1015</v>
+      </c>
+      <c r="E302" t="s">
+        <v>22</v>
+      </c>
+      <c r="F302" s="4">
+        <v>35087569.219999999</v>
+      </c>
+      <c r="H302" s="4">
+        <v>27570687.260000002</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>115</v>
+      </c>
+      <c r="B303" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C303" t="s">
+        <v>108</v>
+      </c>
+      <c r="D303">
+        <v>1016</v>
+      </c>
+      <c r="E303" t="s">
+        <v>23</v>
+      </c>
+      <c r="F303" s="4">
+        <v>61908259.509999998</v>
+      </c>
+      <c r="H303" s="4">
+        <v>48501538.939999998</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>115</v>
+      </c>
+      <c r="B304" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C304" t="s">
+        <v>108</v>
+      </c>
+      <c r="D304">
+        <v>1017</v>
+      </c>
+      <c r="E304" t="s">
+        <v>24</v>
+      </c>
+      <c r="F304" s="4">
+        <v>57380799.770000003</v>
+      </c>
+      <c r="G304" s="4">
+        <v>699999</v>
+      </c>
+      <c r="H304" s="4">
+        <v>44827338.140000001</v>
+      </c>
+      <c r="I304" s="4">
+        <v>542354.63</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>115</v>
+      </c>
+      <c r="B305" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C305" t="s">
+        <v>108</v>
+      </c>
+      <c r="D305">
+        <v>1018</v>
+      </c>
+      <c r="E305" t="s">
+        <v>25</v>
+      </c>
+      <c r="F305" s="4">
+        <v>29992610.789999999</v>
+      </c>
+      <c r="G305" s="4">
+        <v>104105.05</v>
+      </c>
+      <c r="H305" s="4">
+        <v>23574669.57</v>
+      </c>
+      <c r="I305" s="4">
+        <v>80887.320000000007</v>
+      </c>
+      <c r="J305">
+        <v>77</v>
+      </c>
+      <c r="K305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>115</v>
+      </c>
+      <c r="B306" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C306" t="s">
+        <v>108</v>
+      </c>
+      <c r="D306">
+        <v>1020</v>
+      </c>
+      <c r="E306" t="s">
+        <v>26</v>
+      </c>
+      <c r="F306" s="4">
+        <v>41685684.840000004</v>
+      </c>
+      <c r="H306" s="4">
+        <v>32874598.09</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>115</v>
+      </c>
+      <c r="B307" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C307" t="s">
+        <v>108</v>
+      </c>
+      <c r="D307">
+        <v>1021</v>
+      </c>
+      <c r="E307" t="s">
+        <v>27</v>
+      </c>
+      <c r="F307" s="4">
+        <v>33124046.25</v>
+      </c>
+      <c r="H307" s="4">
+        <v>26085163.050000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>115</v>
+      </c>
+      <c r="B308" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C308" t="s">
+        <v>108</v>
+      </c>
+      <c r="D308">
+        <v>1022</v>
+      </c>
+      <c r="E308" t="s">
+        <v>28</v>
+      </c>
+      <c r="F308" s="4">
+        <v>65247870.490000002</v>
+      </c>
+      <c r="G308" s="4">
+        <v>91668.5</v>
+      </c>
+      <c r="H308" s="4">
+        <v>51623501.490000002</v>
+      </c>
+      <c r="I308" s="4">
+        <v>77773.06</v>
+      </c>
+      <c r="J308">
+        <v>5.6479999999999997</v>
+      </c>
+      <c r="K308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>115</v>
+      </c>
+      <c r="B309" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C309" t="s">
+        <v>108</v>
+      </c>
+      <c r="D309">
+        <v>1024</v>
+      </c>
+      <c r="E309" t="s">
+        <v>30</v>
+      </c>
+      <c r="F309" s="4">
+        <v>64622392.539999999</v>
+      </c>
+      <c r="G309" s="4">
+        <v>559301.42000000004</v>
+      </c>
+      <c r="H309" s="4">
+        <v>50636690.57</v>
+      </c>
+      <c r="I309" s="4">
+        <v>433825.97</v>
+      </c>
+      <c r="J309">
+        <v>156</v>
+      </c>
+      <c r="K309">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>115</v>
+      </c>
+      <c r="B310" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C310" t="s">
+        <v>108</v>
+      </c>
+      <c r="D310">
+        <v>1026</v>
+      </c>
+      <c r="E310" t="s">
+        <v>31</v>
+      </c>
+      <c r="F310" s="4">
+        <v>41591563.649999999</v>
+      </c>
+      <c r="H310" s="4">
+        <v>32859983.609999999</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>115</v>
+      </c>
+      <c r="B311" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C311" t="s">
+        <v>108</v>
+      </c>
+      <c r="D311">
+        <v>1027</v>
+      </c>
+      <c r="E311" t="s">
+        <v>32</v>
+      </c>
+      <c r="F311" s="4">
+        <v>12369537.91</v>
+      </c>
+      <c r="H311" s="4">
+        <v>9823496</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>115</v>
+      </c>
+      <c r="B312" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C312" t="s">
+        <v>108</v>
+      </c>
+      <c r="D312">
+        <v>1028</v>
+      </c>
+      <c r="E312" t="s">
+        <v>33</v>
+      </c>
+      <c r="F312" s="4">
+        <v>35378530.020000003</v>
+      </c>
+      <c r="H312" s="4">
+        <v>27862050.66</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>115</v>
+      </c>
+      <c r="B313" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C313" t="s">
+        <v>108</v>
+      </c>
+      <c r="D313">
+        <v>1029</v>
+      </c>
+      <c r="E313" t="s">
+        <v>34</v>
+      </c>
+      <c r="F313" s="4">
+        <v>30459227.34</v>
+      </c>
+      <c r="H313" s="4">
+        <v>24066289.16</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>115</v>
+      </c>
+      <c r="B314" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C314" t="s">
+        <v>108</v>
+      </c>
+      <c r="D314">
+        <v>1030</v>
+      </c>
+      <c r="E314" t="s">
+        <v>35</v>
+      </c>
+      <c r="F314" s="4">
+        <v>14788412.9</v>
+      </c>
+      <c r="H314" s="4">
+        <v>11752156.380000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>115</v>
+      </c>
+      <c r="B315" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C315" t="s">
+        <v>108</v>
+      </c>
+      <c r="D315">
+        <v>1031</v>
+      </c>
+      <c r="E315" t="s">
+        <v>36</v>
+      </c>
+      <c r="F315" s="4">
+        <v>60911503.920000002</v>
+      </c>
+      <c r="H315" s="4">
+        <v>48608347.170000002</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>115</v>
+      </c>
+      <c r="B316" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C316" t="s">
+        <v>108</v>
+      </c>
+      <c r="D316">
+        <v>1032</v>
+      </c>
+      <c r="E316" t="s">
+        <v>37</v>
+      </c>
+      <c r="F316" s="4">
+        <v>42173516.729999997</v>
+      </c>
+      <c r="H316" s="4">
+        <v>33203102.640000001</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>115</v>
+      </c>
+      <c r="B317" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C317" t="s">
+        <v>108</v>
+      </c>
+      <c r="D317">
+        <v>1033</v>
+      </c>
+      <c r="E317" t="s">
+        <v>38</v>
+      </c>
+      <c r="F317" s="4">
+        <v>37427368.789999999</v>
+      </c>
+      <c r="G317" s="4">
+        <v>1064539.1499999999</v>
+      </c>
+      <c r="H317" s="4">
+        <v>29545466.859999999</v>
+      </c>
+      <c r="I317" s="4">
+        <v>827490.12</v>
+      </c>
+      <c r="J317">
+        <v>24</v>
+      </c>
+      <c r="K317">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>115</v>
+      </c>
+      <c r="B318" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C318" t="s">
+        <v>108</v>
+      </c>
+      <c r="D318">
+        <v>1035</v>
+      </c>
+      <c r="E318" t="s">
+        <v>39</v>
+      </c>
+      <c r="F318" s="4">
+        <v>25514009.050000001</v>
+      </c>
+      <c r="G318" s="4">
+        <v>-91413.75</v>
+      </c>
+      <c r="H318" s="4">
+        <v>20067749.219999999</v>
+      </c>
+      <c r="I318" s="4">
+        <v>-76951.820000000007</v>
+      </c>
+      <c r="J318">
+        <v>-7.2039999999999997</v>
+      </c>
+      <c r="K318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>115</v>
+      </c>
+      <c r="B319" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C319" t="s">
+        <v>108</v>
+      </c>
+      <c r="D319">
+        <v>1036</v>
+      </c>
+      <c r="E319" t="s">
+        <v>40</v>
+      </c>
+      <c r="F319" s="4">
+        <v>7037528.0899999999</v>
+      </c>
+      <c r="H319" s="4">
+        <v>5541309</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>115</v>
+      </c>
+      <c r="B320" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C320" t="s">
+        <v>108</v>
+      </c>
+      <c r="D320">
+        <v>1039</v>
+      </c>
+      <c r="E320" t="s">
+        <v>43</v>
+      </c>
+      <c r="F320" s="4">
+        <v>45248968.32</v>
+      </c>
+      <c r="G320" s="4">
+        <v>2349998.19</v>
+      </c>
+      <c r="H320" s="4">
+        <v>35353148.369999997</v>
+      </c>
+      <c r="I320" s="4">
+        <v>1820763.07</v>
+      </c>
+      <c r="J320">
+        <v>2</v>
+      </c>
+      <c r="K320">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>115</v>
+      </c>
+      <c r="B321" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C321" t="s">
+        <v>108</v>
+      </c>
+      <c r="D321">
+        <v>1042</v>
+      </c>
+      <c r="E321" t="s">
+        <v>44</v>
+      </c>
+      <c r="F321" s="4">
+        <v>35231703.619999997</v>
+      </c>
+      <c r="G321" s="4">
+        <v>350483.85</v>
+      </c>
+      <c r="H321" s="4">
+        <v>27873864.949999999</v>
+      </c>
+      <c r="I321" s="4">
+        <v>272899.42</v>
+      </c>
+      <c r="J321">
+        <v>26</v>
+      </c>
+      <c r="K321">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>115</v>
+      </c>
+      <c r="B322" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C322" t="s">
+        <v>108</v>
+      </c>
+      <c r="D322">
+        <v>1043</v>
+      </c>
+      <c r="E322" t="s">
+        <v>45</v>
+      </c>
+      <c r="F322" s="4">
+        <v>35830746</v>
+      </c>
+      <c r="H322" s="4">
+        <v>28124638.07</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>115</v>
+      </c>
+      <c r="B323" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C323" t="s">
+        <v>108</v>
+      </c>
+      <c r="D323">
+        <v>1044</v>
+      </c>
+      <c r="E323" t="s">
+        <v>46</v>
+      </c>
+      <c r="F323" s="4">
+        <v>11122852.09</v>
+      </c>
+      <c r="H323" s="4">
+        <v>8747218.1799999997</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>115</v>
+      </c>
+      <c r="B324" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C324" t="s">
+        <v>108</v>
+      </c>
+      <c r="D324">
+        <v>1045</v>
+      </c>
+      <c r="E324" t="s">
+        <v>47</v>
+      </c>
+      <c r="F324" s="4">
+        <v>10040423.449999999</v>
+      </c>
+      <c r="H324" s="4">
+        <v>7943015.4100000001</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>115</v>
+      </c>
+      <c r="B325" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C325" t="s">
+        <v>108</v>
+      </c>
+      <c r="D325">
+        <v>1046</v>
+      </c>
+      <c r="E325" t="s">
+        <v>48</v>
+      </c>
+      <c r="F325" s="4">
+        <v>11010337.869999999</v>
+      </c>
+      <c r="G325" s="4">
+        <v>17760</v>
+      </c>
+      <c r="H325" s="4">
+        <v>8636093.3399999999</v>
+      </c>
+      <c r="I325" s="4">
+        <v>13760.32</v>
+      </c>
+      <c r="J325">
+        <v>8</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>115</v>
+      </c>
+      <c r="B326" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C326" t="s">
+        <v>108</v>
+      </c>
+      <c r="D326">
+        <v>1050</v>
+      </c>
+      <c r="E326" t="s">
+        <v>49</v>
+      </c>
+      <c r="F326" s="4">
+        <v>27527320.640000001</v>
+      </c>
+      <c r="H326" s="4">
+        <v>21481914.579999998</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>115</v>
+      </c>
+      <c r="B327" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C327" t="s">
+        <v>108</v>
+      </c>
+      <c r="D327">
+        <v>1051</v>
+      </c>
+      <c r="E327" t="s">
+        <v>50</v>
+      </c>
+      <c r="F327" s="4">
+        <v>52388130.969999999</v>
+      </c>
+      <c r="H327" s="4">
+        <v>41749547.799999997</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>115</v>
+      </c>
+      <c r="B328" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C328" t="s">
+        <v>108</v>
+      </c>
+      <c r="D328">
+        <v>1052</v>
+      </c>
+      <c r="E328" t="s">
+        <v>51</v>
+      </c>
+      <c r="F328" s="4">
+        <v>38850188.340000004</v>
+      </c>
+      <c r="G328" s="4">
+        <v>80790.5</v>
+      </c>
+      <c r="H328" s="4">
+        <v>31084626.989999998</v>
+      </c>
+      <c r="I328" s="4">
+        <v>68543.97</v>
+      </c>
+      <c r="J328">
+        <v>5.39</v>
+      </c>
+      <c r="K328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>115</v>
+      </c>
+      <c r="B329" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C329" t="s">
+        <v>108</v>
+      </c>
+      <c r="D329">
+        <v>1053</v>
+      </c>
+      <c r="E329" t="s">
+        <v>52</v>
+      </c>
+      <c r="F329" s="4">
+        <v>31005651.460000001</v>
+      </c>
+      <c r="H329" s="4">
+        <v>24312870.510000002</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>115</v>
+      </c>
+      <c r="B330" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C330" t="s">
+        <v>108</v>
+      </c>
+      <c r="D330">
+        <v>1054</v>
+      </c>
+      <c r="E330" t="s">
+        <v>53</v>
+      </c>
+      <c r="F330" s="4">
+        <v>32820384.309999999</v>
+      </c>
+      <c r="H330" s="4">
+        <v>25697133.859999999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>115</v>
+      </c>
+      <c r="B331" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C331" t="s">
+        <v>108</v>
+      </c>
+      <c r="D331">
+        <v>1055</v>
+      </c>
+      <c r="E331" t="s">
+        <v>54</v>
+      </c>
+      <c r="F331" s="4">
+        <v>28037072.550000001</v>
+      </c>
+      <c r="H331" s="4">
+        <v>22159882.57</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>115</v>
+      </c>
+      <c r="B332" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C332" t="s">
+        <v>108</v>
+      </c>
+      <c r="D332">
+        <v>1056</v>
+      </c>
+      <c r="E332" t="s">
+        <v>55</v>
+      </c>
+      <c r="F332" s="4">
+        <v>25255417.02</v>
+      </c>
+      <c r="H332" s="4">
+        <v>19906621.489999998</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>115</v>
+      </c>
+      <c r="B333" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C333" t="s">
+        <v>108</v>
+      </c>
+      <c r="D333">
+        <v>1057</v>
+      </c>
+      <c r="E333" t="s">
+        <v>56</v>
+      </c>
+      <c r="F333" s="4">
+        <v>59028340.719999999</v>
+      </c>
+      <c r="H333" s="4">
+        <v>46276457.460000001</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>115</v>
+      </c>
+      <c r="B334" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C334" t="s">
+        <v>108</v>
+      </c>
+      <c r="D334">
+        <v>1058</v>
+      </c>
+      <c r="E334" t="s">
+        <v>57</v>
+      </c>
+      <c r="F334" s="4">
+        <v>42515591.869999997</v>
+      </c>
+      <c r="H334" s="4">
+        <v>33450122.280000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>115</v>
+      </c>
+      <c r="B335" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C335" t="s">
+        <v>108</v>
+      </c>
+      <c r="D335">
+        <v>1059</v>
+      </c>
+      <c r="E335" t="s">
+        <v>58</v>
+      </c>
+      <c r="F335" s="4">
+        <v>35393171.619999997</v>
+      </c>
+      <c r="H335" s="4">
+        <v>27738379.699999999</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>115</v>
+      </c>
+      <c r="B336" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C336" t="s">
+        <v>108</v>
+      </c>
+      <c r="D336">
+        <v>1060</v>
+      </c>
+      <c r="E336" t="s">
+        <v>59</v>
+      </c>
+      <c r="F336" s="4">
+        <v>26836684.539999999</v>
+      </c>
+      <c r="H336" s="4">
+        <v>21387515.27</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>115</v>
+      </c>
+      <c r="B337" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C337" t="s">
+        <v>108</v>
+      </c>
+      <c r="D337">
+        <v>1061</v>
+      </c>
+      <c r="E337" t="s">
+        <v>60</v>
+      </c>
+      <c r="F337" s="4">
+        <v>31680730.289999999</v>
+      </c>
+      <c r="H337" s="4">
+        <v>24686024.780000001</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>115</v>
+      </c>
+      <c r="B338" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C338" t="s">
+        <v>108</v>
+      </c>
+      <c r="D338">
+        <v>1066</v>
+      </c>
+      <c r="E338" t="s">
+        <v>111</v>
+      </c>
+      <c r="F338" s="4">
+        <v>2188836.2599999998</v>
+      </c>
+      <c r="H338" s="4">
+        <v>1706732.36</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>115</v>
+      </c>
+      <c r="B339" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C339" t="s">
+        <v>108</v>
+      </c>
+      <c r="D339">
+        <v>1067</v>
+      </c>
+      <c r="E339" t="s">
+        <v>61</v>
+      </c>
+      <c r="F339" s="4">
+        <v>26443154.73</v>
+      </c>
+      <c r="G339" s="4">
+        <v>141823.20000000001</v>
+      </c>
+      <c r="H339" s="4">
+        <v>20763552</v>
+      </c>
+      <c r="I339" s="4">
+        <v>109883.52</v>
+      </c>
+      <c r="J339">
+        <v>48</v>
+      </c>
+      <c r="K339">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>115</v>
+      </c>
+      <c r="B340" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C340" t="s">
+        <v>108</v>
+      </c>
+      <c r="D340">
+        <v>1068</v>
+      </c>
+      <c r="E340" t="s">
+        <v>62</v>
+      </c>
+      <c r="F340" s="4">
+        <v>49461759.57</v>
+      </c>
+      <c r="H340" s="4">
+        <v>38915429.170000002</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>115</v>
+      </c>
+      <c r="B341" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C341" t="s">
+        <v>108</v>
+      </c>
+      <c r="D341">
+        <v>1074</v>
+      </c>
+      <c r="E341" t="s">
+        <v>63</v>
+      </c>
+      <c r="F341" s="4">
+        <v>19877881.280000001</v>
+      </c>
+      <c r="H341" s="4">
+        <v>15555791.380000001</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>115</v>
+      </c>
+      <c r="B342" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C342" t="s">
+        <v>108</v>
+      </c>
+      <c r="D342">
+        <v>1075</v>
+      </c>
+      <c r="E342" t="s">
+        <v>64</v>
+      </c>
+      <c r="F342" s="4">
+        <v>40937563.829999998</v>
+      </c>
+      <c r="H342" s="4">
+        <v>32592393.859999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>115</v>
+      </c>
+      <c r="B343" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C343" t="s">
+        <v>108</v>
+      </c>
+      <c r="D343">
+        <v>1076</v>
+      </c>
+      <c r="E343" t="s">
+        <v>65</v>
+      </c>
+      <c r="F343" s="4">
+        <v>36486712.670000002</v>
+      </c>
+      <c r="H343" s="4">
+        <v>28766577.93</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>115</v>
+      </c>
+      <c r="B344" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C344" t="s">
+        <v>108</v>
+      </c>
+      <c r="D344">
+        <v>1078</v>
+      </c>
+      <c r="E344" t="s">
+        <v>67</v>
+      </c>
+      <c r="F344" s="4">
+        <v>44401623.740000002</v>
+      </c>
+      <c r="G344" s="4">
+        <v>129382.78</v>
+      </c>
+      <c r="H344" s="4">
+        <v>35335077.259999998</v>
+      </c>
+      <c r="I344" s="4">
+        <v>96370.84</v>
+      </c>
+      <c r="J344">
+        <v>70</v>
+      </c>
+      <c r="K344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>115</v>
+      </c>
+      <c r="B345" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C345" t="s">
+        <v>108</v>
+      </c>
+      <c r="D345">
+        <v>1080</v>
+      </c>
+      <c r="E345" t="s">
+        <v>68</v>
+      </c>
+      <c r="F345" s="4">
+        <v>37740036.829999998</v>
+      </c>
+      <c r="H345" s="4">
+        <v>29560958.120000001</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>115</v>
+      </c>
+      <c r="B346" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C346" t="s">
+        <v>108</v>
+      </c>
+      <c r="D346">
+        <v>1081</v>
+      </c>
+      <c r="E346" t="s">
+        <v>69</v>
+      </c>
+      <c r="F346" s="4">
+        <v>26374265.920000002</v>
+      </c>
+      <c r="H346" s="4">
+        <v>20616714.949999999</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>115</v>
+      </c>
+      <c r="B347" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C347" t="s">
+        <v>108</v>
+      </c>
+      <c r="D347">
+        <v>1082</v>
+      </c>
+      <c r="E347" t="s">
+        <v>70</v>
+      </c>
+      <c r="F347" s="4">
+        <v>16240307.5</v>
+      </c>
+      <c r="H347" s="4">
+        <v>12906928.85</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>115</v>
+      </c>
+      <c r="B348" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C348" t="s">
+        <v>108</v>
+      </c>
+      <c r="D348">
+        <v>1084</v>
+      </c>
+      <c r="E348" t="s">
+        <v>71</v>
+      </c>
+      <c r="F348" s="4">
+        <v>11798441.529999999</v>
+      </c>
+      <c r="G348" s="4">
+        <v>348895.52</v>
+      </c>
+      <c r="H348" s="4">
+        <v>9375503.3900000006</v>
+      </c>
+      <c r="I348" s="4">
+        <v>271878.39</v>
+      </c>
+      <c r="J348">
+        <v>109.006</v>
+      </c>
+      <c r="K348">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>115</v>
+      </c>
+      <c r="B349" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C349" t="s">
+        <v>108</v>
+      </c>
+      <c r="D349">
+        <v>1085</v>
+      </c>
+      <c r="E349" t="s">
+        <v>72</v>
+      </c>
+      <c r="F349" s="4">
+        <v>24959945.800000001</v>
+      </c>
+      <c r="H349" s="4">
+        <v>19746182.57</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>115</v>
+      </c>
+      <c r="B350" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C350" t="s">
+        <v>108</v>
+      </c>
+      <c r="D350">
+        <v>1086</v>
+      </c>
+      <c r="E350" t="s">
+        <v>73</v>
+      </c>
+      <c r="F350" s="4">
+        <v>43502093.960000001</v>
+      </c>
+      <c r="H350" s="4">
+        <v>34040828.579999998</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>115</v>
+      </c>
+      <c r="B351" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C351" t="s">
+        <v>108</v>
+      </c>
+      <c r="D351">
+        <v>1087</v>
+      </c>
+      <c r="E351" t="s">
+        <v>74</v>
+      </c>
+      <c r="F351" s="4">
+        <v>39019238.280000001</v>
+      </c>
+      <c r="G351" s="4">
+        <v>-270736.64000000001</v>
+      </c>
+      <c r="H351" s="4">
+        <v>30807632.109999999</v>
+      </c>
+      <c r="I351" s="4">
+        <v>-212350.8</v>
+      </c>
+      <c r="J351">
+        <v>-113.946</v>
+      </c>
+      <c r="K351">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>115</v>
+      </c>
+      <c r="B352" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C352" t="s">
+        <v>108</v>
+      </c>
+      <c r="D352">
+        <v>1088</v>
+      </c>
+      <c r="E352" t="s">
+        <v>75</v>
+      </c>
+      <c r="F352" s="4">
+        <v>30834044.75</v>
+      </c>
+      <c r="H352" s="4">
+        <v>24094777.57</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>115</v>
+      </c>
+      <c r="B353" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C353" t="s">
+        <v>108</v>
+      </c>
+      <c r="D353">
+        <v>1092</v>
+      </c>
+      <c r="E353" t="s">
+        <v>76</v>
+      </c>
+      <c r="F353" s="4">
+        <v>35853797.229999997</v>
+      </c>
+      <c r="H353" s="4">
+        <v>28147303.640000001</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>115</v>
+      </c>
+      <c r="B354" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C354" t="s">
+        <v>108</v>
+      </c>
+      <c r="D354">
+        <v>1093</v>
+      </c>
+      <c r="E354" t="s">
+        <v>77</v>
+      </c>
+      <c r="F354" s="4">
+        <v>41159709.689999998</v>
+      </c>
+      <c r="H354" s="4">
+        <v>32381413.329999998</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>115</v>
+      </c>
+      <c r="B355" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C355" t="s">
+        <v>108</v>
+      </c>
+      <c r="D355">
+        <v>1096</v>
+      </c>
+      <c r="E355" t="s">
+        <v>78</v>
+      </c>
+      <c r="F355" s="4">
+        <v>42170899.229999997</v>
+      </c>
+      <c r="H355" s="4">
+        <v>33082289.34</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>115</v>
+      </c>
+      <c r="B356" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C356" t="s">
+        <v>108</v>
+      </c>
+      <c r="D356">
+        <v>1097</v>
+      </c>
+      <c r="E356" t="s">
+        <v>79</v>
+      </c>
+      <c r="F356" s="4">
+        <v>29832267.43</v>
+      </c>
+      <c r="H356" s="4">
+        <v>23495781.199999999</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>115</v>
+      </c>
+      <c r="B357" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C357" t="s">
+        <v>108</v>
+      </c>
+      <c r="D357">
+        <v>1099</v>
+      </c>
+      <c r="E357" t="s">
+        <v>81</v>
+      </c>
+      <c r="F357" s="4">
+        <v>55080034.060000002</v>
+      </c>
+      <c r="H357" s="4">
+        <v>43934659.759999998</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>115</v>
+      </c>
+      <c r="B358" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C358" t="s">
+        <v>108</v>
+      </c>
+      <c r="D358">
+        <v>1102</v>
+      </c>
+      <c r="E358" t="s">
+        <v>112</v>
+      </c>
+      <c r="F358" s="4">
+        <v>2225052.1</v>
+      </c>
+      <c r="H358" s="4">
+        <v>1746479.75</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>115</v>
+      </c>
+      <c r="B359" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C359" t="s">
+        <v>108</v>
+      </c>
+      <c r="D359">
+        <v>1106</v>
+      </c>
+      <c r="E359" t="s">
+        <v>83</v>
+      </c>
+      <c r="F359" s="4">
+        <v>21686687.32</v>
+      </c>
+      <c r="H359" s="4">
+        <v>17207597.199999999</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>115</v>
+      </c>
+      <c r="B360" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C360" t="s">
+        <v>108</v>
+      </c>
+      <c r="D360">
+        <v>1108</v>
+      </c>
+      <c r="E360" t="s">
+        <v>84</v>
+      </c>
+      <c r="F360" s="4">
+        <v>38512381.509999998</v>
+      </c>
+      <c r="H360" s="4">
+        <v>30229136.350000001</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>115</v>
+      </c>
+      <c r="B361" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C361" t="s">
+        <v>108</v>
+      </c>
+      <c r="D361">
+        <v>1109</v>
+      </c>
+      <c r="E361" t="s">
+        <v>114</v>
+      </c>
+      <c r="F361" s="4">
+        <v>3244168.22</v>
+      </c>
+      <c r="H361" s="4">
+        <v>2548086.41</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>115</v>
+      </c>
+      <c r="B362" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C362" t="s">
+        <v>108</v>
+      </c>
+      <c r="D362">
+        <v>1110</v>
+      </c>
+      <c r="E362" t="s">
+        <v>85</v>
+      </c>
+      <c r="F362" s="4">
+        <v>23524673.309999999</v>
+      </c>
+      <c r="H362" s="4">
+        <v>18553267.75</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>115</v>
+      </c>
+      <c r="B363" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C363" t="s">
+        <v>108</v>
+      </c>
+      <c r="D363">
+        <v>1111</v>
+      </c>
+      <c r="E363" t="s">
+        <v>86</v>
+      </c>
+      <c r="F363" s="4">
+        <v>29154198.280000001</v>
+      </c>
+      <c r="G363" s="4">
+        <v>1909997.38</v>
+      </c>
+      <c r="H363" s="4">
+        <v>23169010.52</v>
+      </c>
+      <c r="I363" s="4">
+        <v>1479853.35</v>
+      </c>
+      <c r="J363">
+        <v>3</v>
+      </c>
+      <c r="K363">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>115</v>
+      </c>
+      <c r="B364" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C364" t="s">
+        <v>108</v>
+      </c>
+      <c r="D364">
+        <v>1114</v>
+      </c>
+      <c r="E364" t="s">
+        <v>87</v>
+      </c>
+      <c r="F364" s="4">
+        <v>21747983.059999999</v>
+      </c>
+      <c r="H364" s="4">
+        <v>17118912.050000001</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>115</v>
+      </c>
+      <c r="B365" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C365" t="s">
+        <v>108</v>
+      </c>
+      <c r="D365">
+        <v>1115</v>
+      </c>
+      <c r="E365" t="s">
+        <v>88</v>
+      </c>
+      <c r="F365" s="4">
+        <v>30771703.93</v>
+      </c>
+      <c r="H365" s="4">
+        <v>24362370.09</v>
+      </c>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>115</v>
+      </c>
+      <c r="B366" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C366" t="s">
+        <v>108</v>
+      </c>
+      <c r="D366">
+        <v>1116</v>
+      </c>
+      <c r="E366" t="s">
+        <v>89</v>
+      </c>
+      <c r="F366" s="4">
+        <v>31659307.289999999</v>
+      </c>
+      <c r="H366" s="4">
+        <v>24922705.489999998</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>115</v>
+      </c>
+      <c r="B367" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C367" t="s">
+        <v>108</v>
+      </c>
+      <c r="D367">
+        <v>1119</v>
+      </c>
+      <c r="E367" t="s">
+        <v>90</v>
+      </c>
+      <c r="F367" s="4">
+        <v>30806777.260000002</v>
+      </c>
+      <c r="H367" s="4">
+        <v>24195790.579999998</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>115</v>
+      </c>
+      <c r="B368" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C368" t="s">
+        <v>108</v>
+      </c>
+      <c r="D368">
+        <v>2997</v>
+      </c>
+      <c r="E368" t="s">
+        <v>91</v>
+      </c>
+      <c r="F368" s="4">
+        <v>167121641.97</v>
+      </c>
+      <c r="G368" s="4">
+        <v>4623692.3</v>
+      </c>
+      <c r="H368" s="4">
+        <v>132927864.36</v>
+      </c>
+      <c r="I368" s="4">
+        <v>3595846.91</v>
+      </c>
+      <c r="J368">
+        <v>1674.242</v>
+      </c>
+      <c r="K368">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>115</v>
+      </c>
+      <c r="B369" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C369" t="s">
+        <v>108</v>
+      </c>
+      <c r="D369">
+        <v>2998</v>
+      </c>
+      <c r="E369" t="s">
+        <v>92</v>
+      </c>
+      <c r="F369" s="4">
+        <v>89086672.769999996</v>
+      </c>
+      <c r="G369" s="4">
+        <v>4549077.72</v>
+      </c>
+      <c r="H369" s="4">
+        <v>69796426.730000004</v>
+      </c>
+      <c r="I369" s="4">
+        <v>3495796.8</v>
+      </c>
+      <c r="J369">
+        <v>1680.7460000000001</v>
+      </c>
+      <c r="K369">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>115</v>
+      </c>
+      <c r="B370" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C370" t="s">
+        <v>108</v>
+      </c>
+      <c r="D370">
+        <v>2999</v>
+      </c>
+      <c r="E370" t="s">
+        <v>93</v>
+      </c>
+      <c r="F370" s="4">
+        <v>82927643.439999998</v>
+      </c>
+      <c r="G370" s="4">
+        <v>-62311.4</v>
+      </c>
+      <c r="H370" s="4">
+        <v>65118422.829999998</v>
+      </c>
+      <c r="I370" s="4">
+        <v>-48278.47</v>
+      </c>
+      <c r="J370">
+        <v>-12</v>
+      </c>
+      <c r="K370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>115</v>
+      </c>
+      <c r="B371" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C371" t="s">
+        <v>108</v>
+      </c>
+      <c r="D371">
+        <v>3601</v>
+      </c>
+      <c r="E371" t="s">
+        <v>94</v>
+      </c>
+      <c r="F371" s="4">
+        <v>82409222.659999996</v>
+      </c>
+      <c r="G371" s="4">
+        <v>2314932.9900000002</v>
+      </c>
+      <c r="H371" s="4">
+        <v>64350092.729999997</v>
+      </c>
+      <c r="I371" s="4">
+        <v>1789502.88</v>
+      </c>
+      <c r="J371">
+        <v>826.303</v>
+      </c>
+      <c r="K371">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>115</v>
+      </c>
+      <c r="B372" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C372" t="s">
+        <v>108</v>
+      </c>
+      <c r="D372">
+        <v>3602</v>
+      </c>
+      <c r="E372" t="s">
+        <v>95</v>
+      </c>
+      <c r="F372" s="4">
+        <v>66582009.799999997</v>
+      </c>
+      <c r="H372" s="4">
+        <v>52318261.649999999</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>115</v>
+      </c>
+      <c r="B373" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C373" t="s">
+        <v>108</v>
+      </c>
+      <c r="D373">
+        <v>3603</v>
+      </c>
+      <c r="E373" t="s">
+        <v>96</v>
+      </c>
+      <c r="F373" s="4">
+        <v>89083836.430000007</v>
+      </c>
+      <c r="H373" s="4">
+        <v>69683934.329999998</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>115</v>
+      </c>
+      <c r="B374" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C374" t="s">
+        <v>108</v>
+      </c>
+      <c r="D374">
+        <v>3604</v>
+      </c>
+      <c r="E374" t="s">
+        <v>97</v>
+      </c>
+      <c r="F374" s="4">
+        <v>61991084.530000001</v>
+      </c>
+      <c r="H374" s="4">
+        <v>48628458.939999998</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>115</v>
+      </c>
+      <c r="B375" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C375" t="s">
+        <v>108</v>
+      </c>
+      <c r="D375">
+        <v>3605</v>
+      </c>
+      <c r="E375" t="s">
+        <v>98</v>
+      </c>
+      <c r="F375" s="4">
+        <v>108259870.11</v>
+      </c>
+      <c r="H375" s="4">
+        <v>85499091.989999995</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>115</v>
+      </c>
+      <c r="B376" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C376" t="s">
+        <v>108</v>
+      </c>
+      <c r="D376">
+        <v>3606</v>
+      </c>
+      <c r="E376" t="s">
+        <v>99</v>
+      </c>
+      <c r="F376" s="4">
+        <v>75660184.219999999</v>
+      </c>
+      <c r="H376" s="4">
+        <v>59621704.700000003</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>115</v>
+      </c>
+      <c r="B377" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C377" t="s">
+        <v>108</v>
+      </c>
+      <c r="D377">
+        <v>3608</v>
+      </c>
+      <c r="E377" t="s">
+        <v>100</v>
+      </c>
+      <c r="F377" s="4">
+        <v>96443670.099999994</v>
+      </c>
+      <c r="G377" s="4">
+        <v>1016637.9</v>
+      </c>
+      <c r="H377" s="4">
+        <v>75691404.650000006</v>
+      </c>
+      <c r="I377" s="4">
+        <v>791361.49</v>
+      </c>
+      <c r="J377">
+        <v>363.69799999999998</v>
+      </c>
+      <c r="K377">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>115</v>
+      </c>
+      <c r="B378" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C378" t="s">
+        <v>108</v>
+      </c>
+      <c r="D378">
+        <v>3613</v>
+      </c>
+      <c r="E378" t="s">
+        <v>101</v>
+      </c>
+      <c r="F378" s="4">
+        <v>53152539.5</v>
+      </c>
+      <c r="H378" s="4">
+        <v>41882872.640000001</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>115</v>
+      </c>
+      <c r="B379" s="5">
+        <v>46299</v>
+      </c>
+      <c r="C379" t="s">
+        <v>108</v>
+      </c>
+      <c r="D379">
+        <v>4001</v>
+      </c>
+      <c r="E379" t="s">
+        <v>102</v>
+      </c>
+      <c r="F379" s="4">
+        <v>13226017.810000001</v>
+      </c>
+      <c r="H379" s="4">
+        <v>10473150.32</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{FE92DB44-9108-48C0-9E4D-CDD7D4A1EECC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shared_uploads/vsventas.xlsx
+++ b/shared_uploads/vsventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C960806\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D39515C-D785-40A2-B6EA-54709F3921E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EF19B9-2793-4DA3-9924-3EBE88E6EE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83115,7 +83115,7 @@
       <c r="A99" t="s">
         <v>115</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99" s="1">
         <v>46297</v>
       </c>
       <c r="C99" t="s">
@@ -83127,22 +83127,22 @@
       <c r="E99" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="2">
         <v>71649690.109999999</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="2">
         <v>4247554.88</v>
       </c>
-      <c r="H99" s="4">
+      <c r="H99" s="2">
         <v>56056659.450000003</v>
       </c>
-      <c r="I99" s="4">
+      <c r="I99" s="2">
         <v>3300929.11</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="3">
         <v>1343.82</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="3">
         <v>36</v>
       </c>
     </row>
@@ -83150,7 +83150,7 @@
       <c r="A100" t="s">
         <v>115</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100" s="1">
         <v>46297</v>
       </c>
       <c r="C100" t="s">
@@ -83162,22 +83162,22 @@
       <c r="E100" t="s">
         <v>11</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="2">
         <v>97713067.370000005</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="2">
         <v>4106829.05</v>
       </c>
-      <c r="H100" s="4">
+      <c r="H100" s="2">
         <v>76814519.180000007</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="2">
         <v>3201034.29</v>
       </c>
-      <c r="J100">
+      <c r="J100" s="3">
         <v>1463.443</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="3">
         <v>38</v>
       </c>
     </row>
@@ -83185,7 +83185,7 @@
       <c r="A101" t="s">
         <v>115</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101" s="1">
         <v>46297</v>
       </c>
       <c r="C101" t="s">
@@ -83197,22 +83197,22 @@
       <c r="E101" t="s">
         <v>12</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="2">
         <v>97885830.430000007</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="2">
         <v>7351848.4400000004</v>
       </c>
-      <c r="H101" s="4">
+      <c r="H101" s="2">
         <v>76933855.730000004</v>
       </c>
-      <c r="I101" s="4">
+      <c r="I101" s="2">
         <v>5734233.4299999997</v>
       </c>
-      <c r="J101">
+      <c r="J101" s="3">
         <v>2209.6019999999999</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="3">
         <v>53</v>
       </c>
     </row>
@@ -83220,7 +83220,7 @@
       <c r="A102" t="s">
         <v>115</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B102" s="1">
         <v>46297</v>
       </c>
       <c r="C102" t="s">
@@ -83232,18 +83232,20 @@
       <c r="E102" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="2">
         <v>60034497.020000003</v>
       </c>
-      <c r="H102" s="4">
+      <c r="G102"/>
+      <c r="H102" s="2">
         <v>47235833.859999999</v>
       </c>
+      <c r="I102"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
-      <c r="B103" s="5">
+      <c r="B103" s="1">
         <v>46297</v>
       </c>
       <c r="C103" t="s">
@@ -83255,22 +83257,22 @@
       <c r="E103" t="s">
         <v>14</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="2">
         <v>67662689.189999998</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="2">
         <v>3903052.63</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="2">
         <v>53349058.490000002</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="2">
         <v>3067096.89</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="3">
         <v>868.17100000000005</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="3">
         <v>37</v>
       </c>
     </row>
@@ -83278,7 +83280,7 @@
       <c r="A104" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="5">
+      <c r="B104" s="1">
         <v>46297</v>
       </c>
       <c r="C104" t="s">
@@ -83290,22 +83292,22 @@
       <c r="E104" t="s">
         <v>15</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>120759806.33</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="2">
         <v>1104229.95</v>
       </c>
-      <c r="H104" s="4">
+      <c r="H104" s="2">
         <v>95444873.75</v>
       </c>
-      <c r="I104" s="4">
+      <c r="I104" s="2">
         <v>849782.92</v>
       </c>
-      <c r="J104">
+      <c r="J104" s="3">
         <v>125.075</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="3">
         <v>5</v>
       </c>
     </row>
@@ -83313,7 +83315,7 @@
       <c r="A105" t="s">
         <v>115</v>
       </c>
-      <c r="B105" s="5">
+      <c r="B105" s="1">
         <v>46297</v>
       </c>
       <c r="C105" t="s">
@@ -83325,22 +83327,22 @@
       <c r="E105" t="s">
         <v>16</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>84725815.930000007</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="2">
         <v>4147738.65</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="2">
         <v>66564114.289999999</v>
       </c>
-      <c r="I105" s="4">
+      <c r="I105" s="2">
         <v>3237809.47</v>
       </c>
-      <c r="J105">
+      <c r="J105" s="3">
         <v>1681.09</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="3">
         <v>44</v>
       </c>
     </row>
@@ -83348,7 +83350,7 @@
       <c r="A106" t="s">
         <v>115</v>
       </c>
-      <c r="B106" s="5">
+      <c r="B106" s="1">
         <v>46297</v>
       </c>
       <c r="C106" t="s">
@@ -83360,18 +83362,20 @@
       <c r="E106" t="s">
         <v>17</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="2">
         <v>46926815.259999998</v>
       </c>
-      <c r="H106" s="4">
+      <c r="G106"/>
+      <c r="H106" s="2">
         <v>36862038.369999997</v>
       </c>
+      <c r="I106"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>115</v>
       </c>
-      <c r="B107" s="5">
+      <c r="B107" s="1">
         <v>46297</v>
       </c>
       <c r="C107" t="s">
@@ -83383,22 +83387,22 @@
       <c r="E107" t="s">
         <v>18</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="2">
         <v>62336669.890000001</v>
       </c>
-      <c r="G107" s="4">
+      <c r="G107" s="2">
         <v>849895.09</v>
       </c>
-      <c r="H107" s="4">
+      <c r="H107" s="2">
         <v>49106409.869999997</v>
       </c>
-      <c r="I107" s="4">
+      <c r="I107" s="2">
         <v>674133.78</v>
       </c>
-      <c r="J107">
+      <c r="J107" s="3">
         <v>282.012</v>
       </c>
-      <c r="K107">
+      <c r="K107" s="3">
         <v>18</v>
       </c>
     </row>
@@ -83406,7 +83410,7 @@
       <c r="A108" t="s">
         <v>115</v>
       </c>
-      <c r="B108" s="5">
+      <c r="B108" s="1">
         <v>46297</v>
       </c>
       <c r="C108" t="s">
@@ -83418,22 +83422,22 @@
       <c r="E108" t="s">
         <v>19</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="2">
         <v>67903159.060000002</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G108" s="2">
         <v>1269775.29</v>
       </c>
-      <c r="H108" s="4">
+      <c r="H108" s="2">
         <v>53091581.460000001</v>
       </c>
-      <c r="I108" s="4">
+      <c r="I108" s="2">
         <v>984083.05</v>
       </c>
-      <c r="J108">
+      <c r="J108" s="3">
         <v>125</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="3">
         <v>9</v>
       </c>
     </row>
@@ -83441,7 +83445,7 @@
       <c r="A109" t="s">
         <v>115</v>
       </c>
-      <c r="B109" s="5">
+      <c r="B109" s="1">
         <v>46297</v>
       </c>
       <c r="C109" t="s">
@@ -83453,18 +83457,20 @@
       <c r="E109" t="s">
         <v>20</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="2">
         <v>60600702.520000003</v>
       </c>
-      <c r="H109" s="4">
+      <c r="G109"/>
+      <c r="H109" s="2">
         <v>47586159.859999999</v>
       </c>
+      <c r="I109"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>115</v>
       </c>
-      <c r="B110" s="5">
+      <c r="B110" s="1">
         <v>46297</v>
       </c>
       <c r="C110" t="s">
@@ -83476,18 +83482,20 @@
       <c r="E110" t="s">
         <v>21</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="2">
         <v>61438982.799999997</v>
       </c>
-      <c r="H110" s="4">
+      <c r="G110"/>
+      <c r="H110" s="2">
         <v>48081892.119999997</v>
       </c>
+      <c r="I110"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>115</v>
       </c>
-      <c r="B111" s="5">
+      <c r="B111" s="1">
         <v>46297</v>
       </c>
       <c r="C111" t="s">
@@ -83499,18 +83507,20 @@
       <c r="E111" t="s">
         <v>22</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="2">
         <v>56122343.960000001</v>
       </c>
-      <c r="H111" s="4">
+      <c r="G111"/>
+      <c r="H111" s="2">
         <v>44106204.329999998</v>
       </c>
+      <c r="I111"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>115</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B112" s="1">
         <v>46297</v>
       </c>
       <c r="C112" t="s">
@@ -83522,18 +83532,20 @@
       <c r="E112" t="s">
         <v>23</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="2">
         <v>63977037.719999999</v>
       </c>
-      <c r="H112" s="4">
+      <c r="G112"/>
+      <c r="H112" s="2">
         <v>50088362.359999999</v>
       </c>
+      <c r="I112"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
-      <c r="B113" s="5">
+      <c r="B113" s="1">
         <v>46297</v>
       </c>
       <c r="C113" t="s">
@@ -83545,18 +83557,20 @@
       <c r="E113" t="s">
         <v>24</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="2">
         <v>57813739.850000001</v>
       </c>
-      <c r="H113" s="4">
+      <c r="G113"/>
+      <c r="H113" s="2">
         <v>45525760.630000003</v>
       </c>
+      <c r="I113"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
-      <c r="B114" s="5">
+      <c r="B114" s="1">
         <v>46297</v>
       </c>
       <c r="C114" t="s">
@@ -83568,22 +83582,22 @@
       <c r="E114" t="s">
         <v>25</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>40914880.170000002</v>
       </c>
-      <c r="G114" s="4">
+      <c r="G114" s="2">
         <v>271103.46000000002</v>
       </c>
-      <c r="H114" s="4">
+      <c r="H114" s="2">
         <v>32070523.98</v>
       </c>
-      <c r="I114" s="4">
+      <c r="I114" s="2">
         <v>211760.45</v>
       </c>
-      <c r="J114">
+      <c r="J114" s="3">
         <v>111.58799999999999</v>
       </c>
-      <c r="K114">
+      <c r="K114" s="3">
         <v>5</v>
       </c>
     </row>
@@ -83591,7 +83605,7 @@
       <c r="A115" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B115" s="1">
         <v>46297</v>
       </c>
       <c r="C115" t="s">
@@ -83603,22 +83617,22 @@
       <c r="E115" t="s">
         <v>26</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="2">
         <v>59966855.789999999</v>
       </c>
-      <c r="G115" s="4">
+      <c r="G115" s="2">
         <v>5795174.8499999996</v>
       </c>
-      <c r="H115" s="4">
+      <c r="H115" s="2">
         <v>47426133.299999997</v>
       </c>
-      <c r="I115" s="4">
+      <c r="I115" s="2">
         <v>4544667.67</v>
       </c>
-      <c r="J115">
+      <c r="J115" s="3">
         <v>1700.431</v>
       </c>
-      <c r="K115">
+      <c r="K115" s="3">
         <v>53</v>
       </c>
     </row>
@@ -83626,7 +83640,7 @@
       <c r="A116" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="5">
+      <c r="B116" s="1">
         <v>46297</v>
       </c>
       <c r="C116" t="s">
@@ -83638,18 +83652,20 @@
       <c r="E116" t="s">
         <v>27</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="2">
         <v>87872854.409999996</v>
       </c>
-      <c r="H116" s="4">
+      <c r="G116"/>
+      <c r="H116" s="2">
         <v>68666383.530000001</v>
       </c>
+      <c r="I116"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="5">
+      <c r="B117" s="1">
         <v>46297</v>
       </c>
       <c r="C117" t="s">
@@ -83661,22 +83677,22 @@
       <c r="E117" t="s">
         <v>28</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="2">
         <v>86363845.560000002</v>
       </c>
-      <c r="G117" s="4">
+      <c r="G117" s="2">
         <v>327168.02</v>
       </c>
-      <c r="H117" s="4">
+      <c r="H117" s="2">
         <v>68523118.909999996</v>
       </c>
-      <c r="I117" s="4">
+      <c r="I117" s="2">
         <v>254095.16</v>
       </c>
-      <c r="J117">
+      <c r="J117" s="3">
         <v>144.72300000000001</v>
       </c>
-      <c r="K117">
+      <c r="K117" s="3">
         <v>4</v>
       </c>
     </row>
@@ -83684,7 +83700,7 @@
       <c r="A118" t="s">
         <v>115</v>
       </c>
-      <c r="B118" s="5">
+      <c r="B118" s="1">
         <v>46297</v>
       </c>
       <c r="C118" t="s">
@@ -83696,22 +83712,22 @@
       <c r="E118" t="s">
         <v>29</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="2">
         <v>65989807.560000002</v>
       </c>
-      <c r="G118" s="4">
+      <c r="G118" s="2">
         <v>61190.61</v>
       </c>
-      <c r="H118" s="4">
+      <c r="H118" s="2">
         <v>51904229.18</v>
       </c>
-      <c r="I118" s="4">
+      <c r="I118" s="2">
         <v>47045.83</v>
       </c>
-      <c r="J118">
+      <c r="J118" s="3">
         <v>4.1660000000000004</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="3">
         <v>1</v>
       </c>
     </row>
@@ -83719,7 +83735,7 @@
       <c r="A119" t="s">
         <v>115</v>
       </c>
-      <c r="B119" s="5">
+      <c r="B119" s="1">
         <v>46297</v>
       </c>
       <c r="C119" t="s">
@@ -83731,22 +83747,22 @@
       <c r="E119" t="s">
         <v>30</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="2">
         <v>79943176.409999996</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="2">
         <v>4245584.09</v>
       </c>
-      <c r="H119" s="4">
+      <c r="H119" s="2">
         <v>62628029.920000002</v>
       </c>
-      <c r="I119" s="4">
+      <c r="I119" s="2">
         <v>3344517.31</v>
       </c>
-      <c r="J119">
+      <c r="J119" s="3">
         <v>1882.509</v>
       </c>
-      <c r="K119">
+      <c r="K119" s="3">
         <v>62</v>
       </c>
     </row>
@@ -83754,7 +83770,7 @@
       <c r="A120" t="s">
         <v>115</v>
       </c>
-      <c r="B120" s="5">
+      <c r="B120" s="1">
         <v>46297</v>
       </c>
       <c r="C120" t="s">
@@ -83766,22 +83782,22 @@
       <c r="E120" t="s">
         <v>31</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>58886340.189999998</v>
       </c>
-      <c r="G120" s="4">
+      <c r="G120" s="2">
         <v>117484.05</v>
       </c>
-      <c r="H120" s="4">
+      <c r="H120" s="2">
         <v>46638997.549999997</v>
       </c>
-      <c r="I120" s="4">
+      <c r="I120" s="2">
         <v>91025.91</v>
       </c>
-      <c r="J120">
+      <c r="J120" s="3">
         <v>58</v>
       </c>
-      <c r="K120">
+      <c r="K120" s="3">
         <v>1</v>
       </c>
     </row>
@@ -83789,7 +83805,7 @@
       <c r="A121" t="s">
         <v>115</v>
       </c>
-      <c r="B121" s="5">
+      <c r="B121" s="1">
         <v>46297</v>
       </c>
       <c r="C121" t="s">
@@ -83801,18 +83817,20 @@
       <c r="E121" t="s">
         <v>32</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="2">
         <v>16876318.969999999</v>
       </c>
-      <c r="H121" s="4">
+      <c r="G121"/>
+      <c r="H121" s="2">
         <v>13326192.800000001</v>
       </c>
+      <c r="I121"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>115</v>
       </c>
-      <c r="B122" s="5">
+      <c r="B122" s="1">
         <v>46297</v>
       </c>
       <c r="C122" t="s">
@@ -83824,18 +83842,20 @@
       <c r="E122" t="s">
         <v>33</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="2">
         <v>50758777.759999998</v>
       </c>
-      <c r="H122" s="4">
+      <c r="G122"/>
+      <c r="H122" s="2">
         <v>39853939.549999997</v>
       </c>
+      <c r="I122"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="5">
+      <c r="B123" s="1">
         <v>46297</v>
       </c>
       <c r="C123" t="s">
@@ -83847,18 +83867,20 @@
       <c r="E123" t="s">
         <v>34</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="2">
         <v>34733017.030000001</v>
       </c>
-      <c r="H123" s="4">
+      <c r="G123"/>
+      <c r="H123" s="2">
         <v>27276964.57</v>
       </c>
+      <c r="I123"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>115</v>
       </c>
-      <c r="B124" s="5">
+      <c r="B124" s="1">
         <v>46297</v>
       </c>
       <c r="C124" t="s">
@@ -83870,18 +83892,20 @@
       <c r="E124" t="s">
         <v>35</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>16864329.010000002</v>
       </c>
-      <c r="H124" s="4">
+      <c r="G124"/>
+      <c r="H124" s="2">
         <v>13330316.17</v>
       </c>
+      <c r="I124"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>115</v>
       </c>
-      <c r="B125" s="5">
+      <c r="B125" s="1">
         <v>46297</v>
       </c>
       <c r="C125" t="s">
@@ -83893,22 +83917,22 @@
       <c r="E125" t="s">
         <v>36</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="2">
         <v>73367368.969999999</v>
       </c>
-      <c r="G125" s="4">
+      <c r="G125" s="2">
         <v>1166521.04</v>
       </c>
-      <c r="H125" s="4">
+      <c r="H125" s="2">
         <v>58407643.520000003</v>
       </c>
-      <c r="I125" s="4">
+      <c r="I125" s="2">
         <v>911505.99</v>
       </c>
-      <c r="J125">
+      <c r="J125" s="3">
         <v>405.77</v>
       </c>
-      <c r="K125">
+      <c r="K125" s="3">
         <v>21</v>
       </c>
     </row>
@@ -83916,7 +83940,7 @@
       <c r="A126" t="s">
         <v>115</v>
       </c>
-      <c r="B126" s="5">
+      <c r="B126" s="1">
         <v>46297</v>
       </c>
       <c r="C126" t="s">
@@ -83928,18 +83952,20 @@
       <c r="E126" t="s">
         <v>37</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="2">
         <v>54137881.859999999</v>
       </c>
-      <c r="H126" s="4">
+      <c r="G126"/>
+      <c r="H126" s="2">
         <v>42693551.810000002</v>
       </c>
+      <c r="I126"/>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="5">
+      <c r="B127" s="1">
         <v>46297</v>
       </c>
       <c r="C127" t="s">
@@ -83951,22 +83977,22 @@
       <c r="E127" t="s">
         <v>38</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>51086167.740000002</v>
       </c>
-      <c r="G127" s="4">
+      <c r="G127" s="2">
         <v>201188.37</v>
       </c>
-      <c r="H127" s="4">
+      <c r="H127" s="2">
         <v>40284814.020000003</v>
       </c>
-      <c r="I127" s="4">
+      <c r="I127" s="2">
         <v>155879.74</v>
       </c>
-      <c r="J127">
+      <c r="J127" s="3">
         <v>89</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="3">
         <v>5</v>
       </c>
     </row>
@@ -83974,7 +84000,7 @@
       <c r="A128" t="s">
         <v>115</v>
       </c>
-      <c r="B128" s="5">
+      <c r="B128" s="1">
         <v>46297</v>
       </c>
       <c r="C128" t="s">
@@ -83986,18 +84012,20 @@
       <c r="E128" t="s">
         <v>39</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="2">
         <v>34258983.630000003</v>
       </c>
-      <c r="H128" s="4">
+      <c r="G128"/>
+      <c r="H128" s="2">
         <v>27109164.129999999</v>
       </c>
+      <c r="I128"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>115</v>
       </c>
-      <c r="B129" s="5">
+      <c r="B129" s="1">
         <v>46297</v>
       </c>
       <c r="C129" t="s">
@@ -84009,18 +84037,20 @@
       <c r="E129" t="s">
         <v>40</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>20361731.98</v>
       </c>
-      <c r="H129" s="4">
+      <c r="G129"/>
+      <c r="H129" s="2">
         <v>16026245.17</v>
       </c>
+      <c r="I129"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>115</v>
       </c>
-      <c r="B130" s="5">
+      <c r="B130" s="1">
         <v>46297</v>
       </c>
       <c r="C130" t="s">
@@ -84032,22 +84062,22 @@
       <c r="E130" t="s">
         <v>42</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>86053321.090000004</v>
       </c>
-      <c r="G130" s="4">
+      <c r="G130" s="2">
         <v>2222627.64</v>
       </c>
-      <c r="H130" s="4">
+      <c r="H130" s="2">
         <v>67476591.040000007</v>
       </c>
-      <c r="I130" s="4">
+      <c r="I130" s="2">
         <v>1729380.48</v>
       </c>
-      <c r="J130">
+      <c r="J130" s="3">
         <v>732.22400000000005</v>
       </c>
-      <c r="K130">
+      <c r="K130" s="3">
         <v>21</v>
       </c>
     </row>
@@ -84055,7 +84085,7 @@
       <c r="A131" t="s">
         <v>115</v>
       </c>
-      <c r="B131" s="5">
+      <c r="B131" s="1">
         <v>46297</v>
       </c>
       <c r="C131" t="s">
@@ -84067,22 +84097,22 @@
       <c r="E131" t="s">
         <v>43</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>72498897.930000007</v>
       </c>
-      <c r="G131" s="4">
+      <c r="G131" s="2">
         <v>179994</v>
       </c>
-      <c r="H131" s="4">
+      <c r="H131" s="2">
         <v>56845786.600000001</v>
       </c>
-      <c r="I131" s="4">
+      <c r="I131" s="2">
         <v>139458.16</v>
       </c>
-      <c r="J131">
+      <c r="J131" s="3">
         <v>1</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84090,7 +84120,7 @@
       <c r="A132" t="s">
         <v>115</v>
       </c>
-      <c r="B132" s="5">
+      <c r="B132" s="1">
         <v>46297</v>
       </c>
       <c r="C132" t="s">
@@ -84102,22 +84132,22 @@
       <c r="E132" t="s">
         <v>44</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="2">
         <v>46649180.969999999</v>
       </c>
-      <c r="G132" s="4">
+      <c r="G132" s="2">
         <v>181226.98</v>
       </c>
-      <c r="H132" s="4">
+      <c r="H132" s="2">
         <v>36951275.630000003</v>
       </c>
-      <c r="I132" s="4">
+      <c r="I132" s="2">
         <v>134255.59</v>
       </c>
-      <c r="J132">
+      <c r="J132" s="3">
         <v>37.747999999999998</v>
       </c>
-      <c r="K132">
+      <c r="K132" s="3">
         <v>6</v>
       </c>
     </row>
@@ -84125,7 +84155,7 @@
       <c r="A133" t="s">
         <v>115</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133" s="1">
         <v>46297</v>
       </c>
       <c r="C133" t="s">
@@ -84137,18 +84167,20 @@
       <c r="E133" t="s">
         <v>45</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="2">
         <v>41759972.659999996</v>
       </c>
-      <c r="H133" s="4">
+      <c r="G133"/>
+      <c r="H133" s="2">
         <v>32800622.43</v>
       </c>
+      <c r="I133"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>115</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="1">
         <v>46297</v>
       </c>
       <c r="C134" t="s">
@@ -84160,18 +84192,20 @@
       <c r="E134" t="s">
         <v>46</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>16443576.26</v>
       </c>
-      <c r="H134" s="4">
+      <c r="G134"/>
+      <c r="H134" s="2">
         <v>12845323.58</v>
       </c>
+      <c r="I134"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>115</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135" s="1">
         <v>46297</v>
       </c>
       <c r="C135" t="s">
@@ -84183,18 +84217,20 @@
       <c r="E135" t="s">
         <v>47</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="2">
         <v>15500129.970000001</v>
       </c>
-      <c r="H135" s="4">
+      <c r="G135"/>
+      <c r="H135" s="2">
         <v>12213711.300000001</v>
       </c>
+      <c r="I135"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>115</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136" s="1">
         <v>46297</v>
       </c>
       <c r="C136" t="s">
@@ -84206,18 +84242,20 @@
       <c r="E136" t="s">
         <v>48</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>21562892.609999999</v>
       </c>
-      <c r="H136" s="4">
+      <c r="G136"/>
+      <c r="H136" s="2">
         <v>16907145.760000002</v>
       </c>
+      <c r="I136"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>115</v>
       </c>
-      <c r="B137" s="5">
+      <c r="B137" s="1">
         <v>46297</v>
       </c>
       <c r="C137" t="s">
@@ -84229,18 +84267,20 @@
       <c r="E137" t="s">
         <v>49</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="2">
         <v>41208674.890000001</v>
       </c>
-      <c r="H137" s="4">
+      <c r="G137"/>
+      <c r="H137" s="2">
         <v>32327940.280000001</v>
       </c>
+      <c r="I137"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>115</v>
       </c>
-      <c r="B138" s="5">
+      <c r="B138" s="1">
         <v>46297</v>
       </c>
       <c r="C138" t="s">
@@ -84252,22 +84292,22 @@
       <c r="E138" t="s">
         <v>50</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="2">
         <v>75844923.439999998</v>
       </c>
-      <c r="G138" s="4">
+      <c r="G138" s="2">
         <v>1423146.38</v>
       </c>
-      <c r="H138" s="4">
+      <c r="H138" s="2">
         <v>60594597.270000003</v>
       </c>
-      <c r="I138" s="4">
+      <c r="I138" s="2">
         <v>1087814.1200000001</v>
       </c>
-      <c r="J138">
+      <c r="J138" s="3">
         <v>180.048</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="3">
         <v>7</v>
       </c>
     </row>
@@ -84275,7 +84315,7 @@
       <c r="A139" t="s">
         <v>115</v>
       </c>
-      <c r="B139" s="5">
+      <c r="B139" s="1">
         <v>46297</v>
       </c>
       <c r="C139" t="s">
@@ -84287,22 +84327,22 @@
       <c r="E139" t="s">
         <v>51</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>50272861.719999999</v>
       </c>
-      <c r="G139" s="4">
+      <c r="G139" s="2">
         <v>66745.8</v>
       </c>
-      <c r="H139" s="4">
+      <c r="H139" s="2">
         <v>39759396.039999999</v>
       </c>
-      <c r="I139" s="4">
+      <c r="I139" s="2">
         <v>51714.21</v>
       </c>
-      <c r="J139">
+      <c r="J139" s="3">
         <v>7</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84310,7 +84350,7 @@
       <c r="A140" t="s">
         <v>115</v>
       </c>
-      <c r="B140" s="5">
+      <c r="B140" s="1">
         <v>46297</v>
       </c>
       <c r="C140" t="s">
@@ -84322,18 +84362,20 @@
       <c r="E140" t="s">
         <v>52</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="2">
         <v>62404086.409999996</v>
       </c>
-      <c r="H140" s="4">
+      <c r="G140"/>
+      <c r="H140" s="2">
         <v>49031391.770000003</v>
       </c>
+      <c r="I140"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>115</v>
       </c>
-      <c r="B141" s="5">
+      <c r="B141" s="1">
         <v>46297</v>
       </c>
       <c r="C141" t="s">
@@ -84345,22 +84387,22 @@
       <c r="E141" t="s">
         <v>53</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="2">
         <v>54594631.659999996</v>
       </c>
-      <c r="G141" s="4">
+      <c r="G141" s="2">
         <v>3430482.92</v>
       </c>
-      <c r="H141" s="4">
+      <c r="H141" s="2">
         <v>42678518.479999997</v>
       </c>
-      <c r="I141" s="4">
+      <c r="I141" s="2">
         <v>2689313.74</v>
       </c>
-      <c r="J141">
+      <c r="J141" s="3">
         <v>1189.134</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="3">
         <v>40</v>
       </c>
     </row>
@@ -84368,7 +84410,7 @@
       <c r="A142" t="s">
         <v>115</v>
       </c>
-      <c r="B142" s="5">
+      <c r="B142" s="1">
         <v>46297</v>
       </c>
       <c r="C142" t="s">
@@ -84380,22 +84422,22 @@
       <c r="E142" t="s">
         <v>54</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="2">
         <v>52367273.18</v>
       </c>
-      <c r="G142" s="4">
+      <c r="G142" s="2">
         <v>3622584.63</v>
       </c>
-      <c r="H142" s="4">
+      <c r="H142" s="2">
         <v>41182183.640000001</v>
       </c>
-      <c r="I142" s="4">
+      <c r="I142" s="2">
         <v>2806870.83</v>
       </c>
-      <c r="J142">
+      <c r="J142" s="3">
         <v>381.22300000000001</v>
       </c>
-      <c r="K142">
+      <c r="K142" s="3">
         <v>18</v>
       </c>
     </row>
@@ -84403,7 +84445,7 @@
       <c r="A143" t="s">
         <v>115</v>
       </c>
-      <c r="B143" s="5">
+      <c r="B143" s="1">
         <v>46297</v>
       </c>
       <c r="C143" t="s">
@@ -84415,22 +84457,22 @@
       <c r="E143" t="s">
         <v>55</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="2">
         <v>34502308.719999999</v>
       </c>
-      <c r="G143" s="4">
+      <c r="G143" s="2">
         <v>304749.68</v>
       </c>
-      <c r="H143" s="4">
+      <c r="H143" s="2">
         <v>27266495.43</v>
       </c>
-      <c r="I143" s="4">
+      <c r="I143" s="2">
         <v>233327.72</v>
       </c>
-      <c r="J143">
+      <c r="J143" s="3">
         <v>47</v>
       </c>
-      <c r="K143">
+      <c r="K143" s="3">
         <v>4</v>
       </c>
     </row>
@@ -84438,7 +84480,7 @@
       <c r="A144" t="s">
         <v>115</v>
       </c>
-      <c r="B144" s="5">
+      <c r="B144" s="1">
         <v>46297</v>
       </c>
       <c r="C144" t="s">
@@ -84450,22 +84492,22 @@
       <c r="E144" t="s">
         <v>56</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="2">
         <v>89117157.900000006</v>
       </c>
-      <c r="G144" s="4">
+      <c r="G144" s="2">
         <v>3478422.49</v>
       </c>
-      <c r="H144" s="4">
+      <c r="H144" s="2">
         <v>70353736.829999998</v>
       </c>
-      <c r="I144" s="4">
+      <c r="I144" s="2">
         <v>2743707.36</v>
       </c>
-      <c r="J144">
+      <c r="J144" s="3">
         <v>1299.146</v>
       </c>
-      <c r="K144">
+      <c r="K144" s="3">
         <v>37</v>
       </c>
     </row>
@@ -84473,7 +84515,7 @@
       <c r="A145" t="s">
         <v>115</v>
       </c>
-      <c r="B145" s="5">
+      <c r="B145" s="1">
         <v>46297</v>
       </c>
       <c r="C145" t="s">
@@ -84485,22 +84527,22 @@
       <c r="E145" t="s">
         <v>57</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="2">
         <v>48876856.140000001</v>
       </c>
-      <c r="G145" s="4">
+      <c r="G145" s="2">
         <v>1112990.06</v>
       </c>
-      <c r="H145" s="4">
+      <c r="H145" s="2">
         <v>38321990.030000001</v>
       </c>
-      <c r="I145" s="4">
+      <c r="I145" s="2">
         <v>868355.99</v>
       </c>
-      <c r="J145">
+      <c r="J145" s="3">
         <v>348.1</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="3">
         <v>19</v>
       </c>
     </row>
@@ -84508,7 +84550,7 @@
       <c r="A146" t="s">
         <v>115</v>
       </c>
-      <c r="B146" s="5">
+      <c r="B146" s="1">
         <v>46297</v>
       </c>
       <c r="C146" t="s">
@@ -84520,18 +84562,20 @@
       <c r="E146" t="s">
         <v>58</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="2">
         <v>43739634.850000001</v>
       </c>
-      <c r="H146" s="4">
+      <c r="G146"/>
+      <c r="H146" s="2">
         <v>34160743.060000002</v>
       </c>
+      <c r="I146"/>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>115</v>
       </c>
-      <c r="B147" s="5">
+      <c r="B147" s="1">
         <v>46297</v>
       </c>
       <c r="C147" t="s">
@@ -84543,18 +84587,20 @@
       <c r="E147" t="s">
         <v>59</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="2">
         <v>38846609.659999996</v>
       </c>
-      <c r="H147" s="4">
+      <c r="G147"/>
+      <c r="H147" s="2">
         <v>30986576.800000001</v>
       </c>
+      <c r="I147"/>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="5">
+      <c r="B148" s="1">
         <v>46297</v>
       </c>
       <c r="C148" t="s">
@@ -84566,22 +84612,22 @@
       <c r="E148" t="s">
         <v>60</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="2">
         <v>59661035.100000001</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G148" s="2">
         <v>2367670.13</v>
       </c>
-      <c r="H148" s="4">
+      <c r="H148" s="2">
         <v>46499219.770000003</v>
       </c>
-      <c r="I148" s="4">
+      <c r="I148" s="2">
         <v>1831927.31</v>
       </c>
-      <c r="J148">
+      <c r="J148" s="3">
         <v>234.03</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="3">
         <v>11</v>
       </c>
     </row>
@@ -84589,7 +84635,7 @@
       <c r="A149" t="s">
         <v>115</v>
       </c>
-      <c r="B149" s="5">
+      <c r="B149" s="1">
         <v>46297</v>
       </c>
       <c r="C149" t="s">
@@ -84601,18 +84647,20 @@
       <c r="E149" t="s">
         <v>111</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="2">
         <v>2336714.15</v>
       </c>
-      <c r="H149" s="4">
+      <c r="G149"/>
+      <c r="H149" s="2">
         <v>1816906.93</v>
       </c>
+      <c r="I149"/>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>115</v>
       </c>
-      <c r="B150" s="5">
+      <c r="B150" s="1">
         <v>46297</v>
       </c>
       <c r="C150" t="s">
@@ -84624,22 +84672,22 @@
       <c r="E150" t="s">
         <v>61</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="2">
         <v>38636733.729999997</v>
       </c>
-      <c r="G150" s="4">
+      <c r="G150" s="2">
         <v>1023857.1</v>
       </c>
-      <c r="H150" s="4">
+      <c r="H150" s="2">
         <v>30587053.27</v>
       </c>
-      <c r="I150" s="4">
+      <c r="I150" s="2">
         <v>793095.19</v>
       </c>
-      <c r="J150">
+      <c r="J150" s="3">
         <v>23</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="3">
         <v>5</v>
       </c>
     </row>
@@ -84647,7 +84695,7 @@
       <c r="A151" t="s">
         <v>115</v>
       </c>
-      <c r="B151" s="5">
+      <c r="B151" s="1">
         <v>46297</v>
       </c>
       <c r="C151" t="s">
@@ -84659,18 +84707,20 @@
       <c r="E151" t="s">
         <v>62</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="2">
         <v>67877468.890000001</v>
       </c>
-      <c r="H151" s="4">
+      <c r="G151"/>
+      <c r="H151" s="2">
         <v>53271243.18</v>
       </c>
+      <c r="I151"/>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>115</v>
       </c>
-      <c r="B152" s="5">
+      <c r="B152" s="1">
         <v>46297</v>
       </c>
       <c r="C152" t="s">
@@ -84682,18 +84732,20 @@
       <c r="E152" t="s">
         <v>63</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="2">
         <v>23425032.09</v>
       </c>
-      <c r="H152" s="4">
+      <c r="G152"/>
+      <c r="H152" s="2">
         <v>18420844.73</v>
       </c>
+      <c r="I152"/>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>115</v>
       </c>
-      <c r="B153" s="5">
+      <c r="B153" s="1">
         <v>46297</v>
       </c>
       <c r="C153" t="s">
@@ -84705,18 +84757,20 @@
       <c r="E153" t="s">
         <v>64</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="2">
         <v>50195805.090000004</v>
       </c>
-      <c r="H153" s="4">
+      <c r="G153"/>
+      <c r="H153" s="2">
         <v>39899236.950000003</v>
       </c>
+      <c r="I153"/>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>115</v>
       </c>
-      <c r="B154" s="5">
+      <c r="B154" s="1">
         <v>46297</v>
       </c>
       <c r="C154" t="s">
@@ -84728,18 +84782,20 @@
       <c r="E154" t="s">
         <v>65</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="2">
         <v>45635503.57</v>
       </c>
-      <c r="H154" s="4">
+      <c r="G154"/>
+      <c r="H154" s="2">
         <v>35891168.740000002</v>
       </c>
+      <c r="I154"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>115</v>
       </c>
-      <c r="B155" s="5">
+      <c r="B155" s="1">
         <v>46297</v>
       </c>
       <c r="C155" t="s">
@@ -84751,22 +84807,22 @@
       <c r="E155" t="s">
         <v>66</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>73122073.989999995</v>
       </c>
-      <c r="G155" s="4">
+      <c r="G155" s="2">
         <v>225096.19</v>
       </c>
-      <c r="H155" s="4">
+      <c r="H155" s="2">
         <v>57927283.049999997</v>
       </c>
-      <c r="I155" s="4">
+      <c r="I155" s="2">
         <v>173627.51</v>
       </c>
-      <c r="J155">
+      <c r="J155" s="3">
         <v>65.436000000000007</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="3">
         <v>2</v>
       </c>
     </row>
@@ -84774,7 +84830,7 @@
       <c r="A156" t="s">
         <v>115</v>
       </c>
-      <c r="B156" s="5">
+      <c r="B156" s="1">
         <v>46297</v>
       </c>
       <c r="C156" t="s">
@@ -84786,22 +84842,22 @@
       <c r="E156" t="s">
         <v>67</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="2">
         <v>55839206.719999999</v>
       </c>
-      <c r="G156" s="4">
+      <c r="G156" s="2">
         <v>25913.26</v>
       </c>
-      <c r="H156" s="4">
+      <c r="H156" s="2">
         <v>44114844.32</v>
       </c>
-      <c r="I156" s="4">
+      <c r="I156" s="2">
         <v>21337.53</v>
       </c>
-      <c r="J156">
+      <c r="J156" s="3">
         <v>17.163</v>
       </c>
-      <c r="K156">
+      <c r="K156" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84809,7 +84865,7 @@
       <c r="A157" t="s">
         <v>115</v>
       </c>
-      <c r="B157" s="5">
+      <c r="B157" s="1">
         <v>46297</v>
       </c>
       <c r="C157" t="s">
@@ -84821,22 +84877,22 @@
       <c r="E157" t="s">
         <v>68</v>
       </c>
-      <c r="F157" s="4">
+      <c r="F157" s="2">
         <v>41058223.939999998</v>
       </c>
-      <c r="G157" s="4">
+      <c r="G157" s="2">
         <v>1419165.42</v>
       </c>
-      <c r="H157" s="4">
+      <c r="H157" s="2">
         <v>32000565.199999999</v>
       </c>
-      <c r="I157" s="4">
+      <c r="I157" s="2">
         <v>1117515.98</v>
       </c>
-      <c r="J157">
+      <c r="J157" s="3">
         <v>500.01499999999999</v>
       </c>
-      <c r="K157">
+      <c r="K157" s="3">
         <v>26</v>
       </c>
     </row>
@@ -84844,7 +84900,7 @@
       <c r="A158" t="s">
         <v>115</v>
       </c>
-      <c r="B158" s="5">
+      <c r="B158" s="1">
         <v>46297</v>
       </c>
       <c r="C158" t="s">
@@ -84856,22 +84912,22 @@
       <c r="E158" t="s">
         <v>69</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="2">
         <v>32896909.59</v>
       </c>
-      <c r="G158" s="4">
+      <c r="G158" s="2">
         <v>-87999.45</v>
       </c>
-      <c r="H158" s="4">
+      <c r="H158" s="2">
         <v>25942277.52</v>
       </c>
-      <c r="I158" s="4">
+      <c r="I158" s="2">
         <v>-68181.39</v>
       </c>
-      <c r="J158">
+      <c r="J158" s="3">
         <v>-1</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84879,7 +84935,7 @@
       <c r="A159" t="s">
         <v>115</v>
       </c>
-      <c r="B159" s="5">
+      <c r="B159" s="1">
         <v>46297</v>
       </c>
       <c r="C159" t="s">
@@ -84891,22 +84947,22 @@
       <c r="E159" t="s">
         <v>70</v>
       </c>
-      <c r="F159" s="4">
+      <c r="F159" s="2">
         <v>22588748.620000001</v>
       </c>
-      <c r="G159" s="4">
+      <c r="G159" s="2">
         <v>469999</v>
       </c>
-      <c r="H159" s="4">
+      <c r="H159" s="2">
         <v>18132669.43</v>
       </c>
-      <c r="I159" s="4">
+      <c r="I159" s="2">
         <v>364152.12</v>
       </c>
-      <c r="J159">
+      <c r="J159" s="3">
         <v>1</v>
       </c>
-      <c r="K159">
+      <c r="K159" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84914,7 +84970,7 @@
       <c r="A160" t="s">
         <v>115</v>
       </c>
-      <c r="B160" s="5">
+      <c r="B160" s="1">
         <v>46297</v>
       </c>
       <c r="C160" t="s">
@@ -84926,22 +84982,22 @@
       <c r="E160" t="s">
         <v>71</v>
       </c>
-      <c r="F160" s="4">
+      <c r="F160" s="2">
         <v>16544663.640000001</v>
       </c>
-      <c r="G160" s="4">
+      <c r="G160" s="2">
         <v>43367.9</v>
       </c>
-      <c r="H160" s="4">
+      <c r="H160" s="2">
         <v>13033386.289999999</v>
       </c>
-      <c r="I160" s="4">
+      <c r="I160" s="2">
         <v>34771.99</v>
       </c>
-      <c r="J160">
+      <c r="J160" s="3">
         <v>21</v>
       </c>
-      <c r="K160">
+      <c r="K160" s="3">
         <v>1</v>
       </c>
     </row>
@@ -84949,7 +85005,7 @@
       <c r="A161" t="s">
         <v>115</v>
       </c>
-      <c r="B161" s="5">
+      <c r="B161" s="1">
         <v>46297</v>
       </c>
       <c r="C161" t="s">
@@ -84961,18 +85017,20 @@
       <c r="E161" t="s">
         <v>72</v>
       </c>
-      <c r="F161" s="4">
+      <c r="F161" s="2">
         <v>17928805.16</v>
       </c>
-      <c r="H161" s="4">
+      <c r="G161"/>
+      <c r="H161" s="2">
         <v>14179662.609999999</v>
       </c>
+      <c r="I161"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>115</v>
       </c>
-      <c r="B162" s="5">
+      <c r="B162" s="1">
         <v>46297</v>
       </c>
       <c r="C162" t="s">
@@ -84984,18 +85042,20 @@
       <c r="E162" t="s">
         <v>73</v>
       </c>
-      <c r="F162" s="4">
+      <c r="F162" s="2">
         <v>56580198.880000003</v>
       </c>
-      <c r="H162" s="4">
+      <c r="G162"/>
+      <c r="H162" s="2">
         <v>44354031.829999998</v>
       </c>
+      <c r="I162"/>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>115</v>
       </c>
-      <c r="B163" s="5">
+      <c r="B163" s="1">
         <v>46297</v>
       </c>
       <c r="C163" t="s">
@@ -85007,22 +85067,22 @@
       <c r="E163" t="s">
         <v>74</v>
       </c>
-      <c r="F163" s="4">
+      <c r="F163" s="2">
         <v>74672000.090000004</v>
       </c>
-      <c r="G163" s="4">
+      <c r="G163" s="2">
         <v>5855640.7300000004</v>
       </c>
-      <c r="H163" s="4">
+      <c r="H163" s="2">
         <v>58803954.119999997</v>
       </c>
-      <c r="I163" s="4">
+      <c r="I163" s="2">
         <v>4530871.18</v>
       </c>
-      <c r="J163">
+      <c r="J163" s="3">
         <v>2393.5390000000002</v>
       </c>
-      <c r="K163">
+      <c r="K163" s="3">
         <v>60</v>
       </c>
     </row>
@@ -85030,7 +85090,7 @@
       <c r="A164" t="s">
         <v>115</v>
       </c>
-      <c r="B164" s="5">
+      <c r="B164" s="1">
         <v>46297</v>
       </c>
       <c r="C164" t="s">
@@ -85042,22 +85102,22 @@
       <c r="E164" t="s">
         <v>75</v>
       </c>
-      <c r="F164" s="4">
+      <c r="F164" s="2">
         <v>43298657.969999999</v>
       </c>
-      <c r="G164" s="4">
+      <c r="G164" s="2">
         <v>306594.09000000003</v>
       </c>
-      <c r="H164" s="4">
+      <c r="H164" s="2">
         <v>34917387.560000002</v>
       </c>
-      <c r="I164" s="4">
+      <c r="I164" s="2">
         <v>242164.73</v>
       </c>
-      <c r="J164">
+      <c r="J164" s="3">
         <v>58.164000000000001</v>
       </c>
-      <c r="K164">
+      <c r="K164" s="3">
         <v>2</v>
       </c>
     </row>
@@ -85065,7 +85125,7 @@
       <c r="A165" t="s">
         <v>115</v>
       </c>
-      <c r="B165" s="5">
+      <c r="B165" s="1">
         <v>46297</v>
       </c>
       <c r="C165" t="s">
@@ -85077,22 +85137,22 @@
       <c r="E165" t="s">
         <v>76</v>
       </c>
-      <c r="F165" s="4">
+      <c r="F165" s="2">
         <v>53979561.579999998</v>
       </c>
-      <c r="G165" s="4">
+      <c r="G165" s="2">
         <v>560997.48</v>
       </c>
-      <c r="H165" s="4">
+      <c r="H165" s="2">
         <v>42171322.530000001</v>
       </c>
-      <c r="I165" s="4">
+      <c r="I165" s="2">
         <v>434657.13</v>
       </c>
-      <c r="J165">
+      <c r="J165" s="3">
         <v>3</v>
       </c>
-      <c r="K165">
+      <c r="K165" s="3">
         <v>1</v>
       </c>
     </row>
@@ -85100,7 +85160,7 @@
       <c r="A166" t="s">
         <v>115</v>
       </c>
-      <c r="B166" s="5">
+      <c r="B166" s="1">
         <v>46297</v>
       </c>
       <c r="C166" t="s">
@@ -85112,18 +85172,20 @@
       <c r="E166" t="s">
         <v>77</v>
       </c>
-      <c r="F166" s="4">
+      <c r="F166" s="2">
         <v>64823465.810000002</v>
       </c>
-      <c r="H166" s="4">
+      <c r="G166"/>
+      <c r="H166" s="2">
         <v>51124312.25</v>
       </c>
+      <c r="I166"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>115</v>
       </c>
-      <c r="B167" s="5">
+      <c r="B167" s="1">
         <v>46297</v>
       </c>
       <c r="C167" t="s">
@@ -85135,18 +85197,20 @@
       <c r="E167" t="s">
         <v>78</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="2">
         <v>39772325.450000003</v>
       </c>
-      <c r="H167" s="4">
+      <c r="G167"/>
+      <c r="H167" s="2">
         <v>31353180.149999999</v>
       </c>
+      <c r="I167"/>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>115</v>
       </c>
-      <c r="B168" s="5">
+      <c r="B168" s="1">
         <v>46297</v>
       </c>
       <c r="C168" t="s">
@@ -85158,18 +85222,20 @@
       <c r="E168" t="s">
         <v>79</v>
       </c>
-      <c r="F168" s="4">
+      <c r="F168" s="2">
         <v>37905173.079999998</v>
       </c>
-      <c r="H168" s="4">
+      <c r="G168"/>
+      <c r="H168" s="2">
         <v>29901975.960000001</v>
       </c>
+      <c r="I168"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>115</v>
       </c>
-      <c r="B169" s="5">
+      <c r="B169" s="1">
         <v>46297</v>
       </c>
       <c r="C169" t="s">
@@ -85181,22 +85247,22 @@
       <c r="E169" t="s">
         <v>80</v>
       </c>
-      <c r="F169" s="4">
+      <c r="F169" s="2">
         <v>31353479.289999999</v>
       </c>
-      <c r="G169" s="4">
+      <c r="G169" s="2">
         <v>957197.84</v>
       </c>
-      <c r="H169" s="4">
+      <c r="H169" s="2">
         <v>24624562.640000001</v>
       </c>
-      <c r="I169" s="4">
+      <c r="I169" s="2">
         <v>747081.94</v>
       </c>
-      <c r="J169">
+      <c r="J169" s="3">
         <v>64.206999999999994</v>
       </c>
-      <c r="K169">
+      <c r="K169" s="3">
         <v>4</v>
       </c>
     </row>
@@ -85204,7 +85270,7 @@
       <c r="A170" t="s">
         <v>115</v>
       </c>
-      <c r="B170" s="5">
+      <c r="B170" s="1">
         <v>46297</v>
       </c>
       <c r="C170" t="s">
@@ -85216,18 +85282,20 @@
       <c r="E170" t="s">
         <v>81</v>
       </c>
-      <c r="F170" s="4">
+      <c r="F170" s="2">
         <v>48069266.590000004</v>
       </c>
-      <c r="H170" s="4">
+      <c r="G170"/>
+      <c r="H170" s="2">
         <v>38228406.210000001</v>
       </c>
+      <c r="I170"/>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>115</v>
       </c>
-      <c r="B171" s="5">
+      <c r="B171" s="1">
         <v>46297</v>
       </c>
       <c r="C171" t="s">
@@ -85239,18 +85307,20 @@
       <c r="E171" t="s">
         <v>82</v>
       </c>
-      <c r="F171" s="4">
+      <c r="F171" s="2">
         <v>50188205.210000001</v>
       </c>
-      <c r="H171" s="4">
+      <c r="G171"/>
+      <c r="H171" s="2">
         <v>39590197.43</v>
       </c>
+      <c r="I171"/>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>115</v>
       </c>
-      <c r="B172" s="5">
+      <c r="B172" s="1">
         <v>46297</v>
       </c>
       <c r="C172" t="s">
@@ -85262,18 +85332,20 @@
       <c r="E172" t="s">
         <v>112</v>
       </c>
-      <c r="F172" s="4">
+      <c r="F172" s="2">
         <v>3226580.13</v>
       </c>
-      <c r="H172" s="4">
+      <c r="G172"/>
+      <c r="H172" s="2">
         <v>2505771.5099999998</v>
       </c>
+      <c r="I172"/>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>115</v>
       </c>
-      <c r="B173" s="5">
+      <c r="B173" s="1">
         <v>46297</v>
       </c>
       <c r="C173" t="s">
@@ -85285,18 +85357,20 @@
       <c r="E173" t="s">
         <v>113</v>
       </c>
-      <c r="F173" s="4">
+      <c r="F173" s="2">
         <v>2435851.02</v>
       </c>
-      <c r="H173" s="4">
+      <c r="G173"/>
+      <c r="H173" s="2">
         <v>1885454.92</v>
       </c>
+      <c r="I173"/>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>115</v>
       </c>
-      <c r="B174" s="5">
+      <c r="B174" s="1">
         <v>46297</v>
       </c>
       <c r="C174" t="s">
@@ -85308,18 +85382,20 @@
       <c r="E174" t="s">
         <v>83</v>
       </c>
-      <c r="F174" s="4">
+      <c r="F174" s="2">
         <v>22968203.780000001</v>
       </c>
-      <c r="H174" s="4">
+      <c r="G174"/>
+      <c r="H174" s="2">
         <v>18091603.670000002</v>
       </c>
+      <c r="I174"/>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>115</v>
       </c>
-      <c r="B175" s="5">
+      <c r="B175" s="1">
         <v>46297</v>
       </c>
       <c r="C175" t="s">
@@ -85331,22 +85407,22 @@
       <c r="E175" t="s">
         <v>84</v>
       </c>
-      <c r="F175" s="4">
+      <c r="F175" s="2">
         <v>60242705.369999997</v>
       </c>
-      <c r="G175" s="4">
+      <c r="G175" s="2">
         <v>22611.05</v>
       </c>
-      <c r="H175" s="4">
+      <c r="H175" s="2">
         <v>47657921.719999999</v>
       </c>
-      <c r="I175" s="4">
+      <c r="I175" s="2">
         <v>17623.71</v>
       </c>
-      <c r="J175">
+      <c r="J175" s="3">
         <v>10.597</v>
       </c>
-      <c r="K175">
+      <c r="K175" s="3">
         <v>1</v>
       </c>
     </row>
@@ -85354,7 +85430,7 @@
       <c r="A176" t="s">
         <v>115</v>
       </c>
-      <c r="B176" s="5">
+      <c r="B176" s="1">
         <v>46297</v>
       </c>
       <c r="C176" t="s">
@@ -85366,18 +85442,20 @@
       <c r="E176" t="s">
         <v>114</v>
       </c>
-      <c r="F176" s="4">
+      <c r="F176" s="2">
         <v>4398869.72</v>
       </c>
-      <c r="H176" s="4">
+      <c r="G176"/>
+      <c r="H176" s="2">
         <v>3457248.13</v>
       </c>
+      <c r="I176"/>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>115</v>
       </c>
-      <c r="B177" s="5">
+      <c r="B177" s="1">
         <v>46297</v>
       </c>
       <c r="C177" t="s">
@@ -85389,18 +85467,20 @@
       <c r="E177" t="s">
         <v>85</v>
       </c>
-      <c r="F177" s="4">
+      <c r="F177" s="2">
         <v>30498194.899999999</v>
       </c>
-      <c r="H177" s="4">
+      <c r="G177"/>
+      <c r="H177" s="2">
         <v>23902802.379999999</v>
       </c>
+      <c r="I177"/>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>115</v>
       </c>
-      <c r="B178" s="5">
+      <c r="B178" s="1">
         <v>46297</v>
       </c>
       <c r="C178" t="s">
@@ -85412,22 +85492,22 @@
       <c r="E178" t="s">
         <v>86</v>
       </c>
-      <c r="F178" s="4">
+      <c r="F178" s="2">
         <v>41514629.770000003</v>
       </c>
-      <c r="G178" s="4">
+      <c r="G178" s="2">
         <v>2199987.2000000002</v>
       </c>
-      <c r="H178" s="4">
+      <c r="H178" s="2">
         <v>32991322.109999999</v>
       </c>
-      <c r="I178" s="4">
+      <c r="I178" s="2">
         <v>1704535.54</v>
       </c>
-      <c r="J178">
+      <c r="J178" s="3">
         <v>2</v>
       </c>
-      <c r="K178">
+      <c r="K178" s="3">
         <v>2</v>
       </c>
     </row>
@@ -85435,7 +85515,7 @@
       <c r="A179" t="s">
         <v>115</v>
       </c>
-      <c r="B179" s="5">
+      <c r="B179" s="1">
         <v>46297</v>
       </c>
       <c r="C179" t="s">
@@ -85447,18 +85527,20 @@
       <c r="E179" t="s">
         <v>87</v>
       </c>
-      <c r="F179" s="4">
+      <c r="F179" s="2">
         <v>31380304.68</v>
       </c>
-      <c r="H179" s="4">
+      <c r="G179"/>
+      <c r="H179" s="2">
         <v>24731219.530000001</v>
       </c>
+      <c r="I179"/>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>115</v>
       </c>
-      <c r="B180" s="5">
+      <c r="B180" s="1">
         <v>46297</v>
       </c>
       <c r="C180" t="s">
@@ -85470,22 +85552,22 @@
       <c r="E180" t="s">
         <v>88</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="2">
         <v>52171989.530000001</v>
       </c>
-      <c r="G180" s="4">
+      <c r="G180" s="2">
         <v>492935.58</v>
       </c>
-      <c r="H180" s="4">
+      <c r="H180" s="2">
         <v>41360305.869999997</v>
       </c>
-      <c r="I180" s="4">
+      <c r="I180" s="2">
         <v>392473.11</v>
       </c>
-      <c r="J180">
+      <c r="J180" s="3">
         <v>127.178</v>
       </c>
-      <c r="K180">
+      <c r="K180" s="3">
         <v>9</v>
       </c>
     </row>
@@ -85493,7 +85575,7 @@
       <c r="A181" t="s">
         <v>115</v>
       </c>
-      <c r="B181" s="5">
+      <c r="B181" s="1">
         <v>46297</v>
       </c>
       <c r="C181" t="s">
@@ -85505,18 +85587,20 @@
       <c r="E181" t="s">
         <v>89</v>
       </c>
-      <c r="F181" s="4">
+      <c r="F181" s="2">
         <v>41034059.240000002</v>
       </c>
-      <c r="H181" s="4">
+      <c r="G181"/>
+      <c r="H181" s="2">
         <v>32259588.829999998</v>
       </c>
+      <c r="I181"/>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>115</v>
       </c>
-      <c r="B182" s="5">
+      <c r="B182" s="1">
         <v>46297</v>
       </c>
       <c r="C182" t="s">
@@ -85528,18 +85612,20 @@
       <c r="E182" t="s">
         <v>90</v>
       </c>
-      <c r="F182" s="4">
+      <c r="F182" s="2">
         <v>33859995.030000001</v>
       </c>
-      <c r="H182" s="4">
+      <c r="G182"/>
+      <c r="H182" s="2">
         <v>26665302</v>
       </c>
+      <c r="I182"/>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>115</v>
       </c>
-      <c r="B183" s="5">
+      <c r="B183" s="1">
         <v>46297</v>
       </c>
       <c r="C183" t="s">
@@ -85551,22 +85637,22 @@
       <c r="E183" t="s">
         <v>91</v>
       </c>
-      <c r="F183" s="4">
+      <c r="F183" s="2">
         <v>229058798.86000001</v>
       </c>
-      <c r="G183" s="4">
+      <c r="G183" s="2">
         <v>20423635.370000001</v>
       </c>
-      <c r="H183" s="4">
+      <c r="H183" s="2">
         <v>182639447.66</v>
       </c>
-      <c r="I183" s="4">
+      <c r="I183" s="2">
         <v>15710306.859999999</v>
       </c>
-      <c r="J183">
+      <c r="J183" s="3">
         <v>7205.38</v>
       </c>
-      <c r="K183">
+      <c r="K183" s="3">
         <v>231</v>
       </c>
     </row>
@@ -85574,7 +85660,7 @@
       <c r="A184" t="s">
         <v>115</v>
       </c>
-      <c r="B184" s="5">
+      <c r="B184" s="1">
         <v>46297</v>
       </c>
       <c r="C184" t="s">
@@ -85586,22 +85672,22 @@
       <c r="E184" t="s">
         <v>92</v>
       </c>
-      <c r="F184" s="4">
+      <c r="F184" s="2">
         <v>107246220.54000001</v>
       </c>
-      <c r="G184" s="4">
+      <c r="G184" s="2">
         <v>15103913.83</v>
       </c>
-      <c r="H184" s="4">
+      <c r="H184" s="2">
         <v>84106275.959999993</v>
       </c>
-      <c r="I184" s="4">
+      <c r="I184" s="2">
         <v>11739443.23</v>
       </c>
-      <c r="J184">
+      <c r="J184" s="3">
         <v>6671.8090000000002</v>
       </c>
-      <c r="K184">
+      <c r="K184" s="3">
         <v>170</v>
       </c>
     </row>
@@ -85609,7 +85695,7 @@
       <c r="A185" t="s">
         <v>115</v>
       </c>
-      <c r="B185" s="5">
+      <c r="B185" s="1">
         <v>46297</v>
       </c>
       <c r="C185" t="s">
@@ -85621,22 +85707,22 @@
       <c r="E185" t="s">
         <v>93</v>
       </c>
-      <c r="F185" s="4">
+      <c r="F185" s="2">
         <v>116113644.84</v>
       </c>
-      <c r="G185" s="4">
+      <c r="G185" s="2">
         <v>13971495.199999999</v>
       </c>
-      <c r="H185" s="4">
+      <c r="H185" s="2">
         <v>91147995.650000006</v>
       </c>
-      <c r="I185" s="4">
+      <c r="I185" s="2">
         <v>10858500</v>
       </c>
-      <c r="J185">
+      <c r="J185" s="3">
         <v>5058.7569999999996</v>
       </c>
-      <c r="K185">
+      <c r="K185" s="3">
         <v>163</v>
       </c>
     </row>
@@ -85644,7 +85730,7 @@
       <c r="A186" t="s">
         <v>115</v>
       </c>
-      <c r="B186" s="5">
+      <c r="B186" s="1">
         <v>46297</v>
       </c>
       <c r="C186" t="s">
@@ -85656,22 +85742,22 @@
       <c r="E186" t="s">
         <v>94</v>
       </c>
-      <c r="F186" s="4">
+      <c r="F186" s="2">
         <v>141060507.61000001</v>
       </c>
-      <c r="G186" s="4">
+      <c r="G186" s="2">
         <v>12300737.640000001</v>
       </c>
-      <c r="H186" s="4">
+      <c r="H186" s="2">
         <v>110573098.25</v>
       </c>
-      <c r="I186" s="4">
+      <c r="I186" s="2">
         <v>9526519.1799999997</v>
       </c>
-      <c r="J186">
+      <c r="J186" s="3">
         <v>4400.8490000000002</v>
       </c>
-      <c r="K186">
+      <c r="K186" s="3">
         <v>126</v>
       </c>
     </row>
@@ -85679,7 +85765,7 @@
       <c r="A187" t="s">
         <v>115</v>
       </c>
-      <c r="B187" s="5">
+      <c r="B187" s="1">
         <v>46297</v>
       </c>
       <c r="C187" t="s">
@@ -85691,22 +85777,22 @@
       <c r="E187" t="s">
         <v>95</v>
       </c>
-      <c r="F187" s="4">
+      <c r="F187" s="2">
         <v>113598022.52</v>
       </c>
-      <c r="G187" s="4">
+      <c r="G187" s="2">
         <v>8066974.7699999996</v>
       </c>
-      <c r="H187" s="4">
+      <c r="H187" s="2">
         <v>89125673.650000006</v>
       </c>
-      <c r="I187" s="4">
+      <c r="I187" s="2">
         <v>6218628.2300000004</v>
       </c>
-      <c r="J187">
+      <c r="J187" s="3">
         <v>2483.0520000000001</v>
       </c>
-      <c r="K187">
+      <c r="K187" s="3">
         <v>90</v>
       </c>
     </row>
@@ -85714,7 +85800,7 @@
       <c r="A188" t="s">
         <v>115</v>
       </c>
-      <c r="B188" s="5">
+      <c r="B188" s="1">
         <v>46297</v>
       </c>
       <c r="C188" t="s">
@@ -85726,22 +85812,22 @@
       <c r="E188" t="s">
         <v>96</v>
       </c>
-      <c r="F188" s="4">
+      <c r="F188" s="2">
         <v>100425179.03</v>
       </c>
-      <c r="G188" s="4">
+      <c r="G188" s="2">
         <v>6847051.6500000004</v>
       </c>
-      <c r="H188" s="4">
+      <c r="H188" s="2">
         <v>78561913.780000001</v>
       </c>
-      <c r="I188" s="4">
+      <c r="I188" s="2">
         <v>5328112.6100000003</v>
       </c>
-      <c r="J188">
+      <c r="J188" s="3">
         <v>2588.8159999999998</v>
       </c>
-      <c r="K188">
+      <c r="K188" s="3">
         <v>78</v>
       </c>
     </row>
@@ -85749,7 +85835,7 @@
       <c r="A189" t="s">
         <v>115</v>
       </c>
-      <c r="B189" s="5">
+      <c r="B189" s="1">
         <v>46297</v>
       </c>
       <c r="C189" t="s">
@@ -85761,22 +85847,22 @@
       <c r="E189" t="s">
         <v>97</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="2">
         <v>83091966.090000004</v>
       </c>
-      <c r="G189" s="4">
+      <c r="G189" s="2">
         <v>6190735.6900000004</v>
       </c>
-      <c r="H189" s="4">
+      <c r="H189" s="2">
         <v>64872877.090000004</v>
       </c>
-      <c r="I189" s="4">
+      <c r="I189" s="2">
         <v>4813133.1399999997</v>
       </c>
-      <c r="J189">
+      <c r="J189" s="3">
         <v>2233.212</v>
       </c>
-      <c r="K189">
+      <c r="K189" s="3">
         <v>69</v>
       </c>
     </row>
@@ -85784,7 +85870,7 @@
       <c r="A190" t="s">
         <v>115</v>
       </c>
-      <c r="B190" s="5">
+      <c r="B190" s="1">
         <v>46297</v>
       </c>
       <c r="C190" t="s">
@@ -85796,22 +85882,22 @@
       <c r="E190" t="s">
         <v>98</v>
       </c>
-      <c r="F190" s="4">
+      <c r="F190" s="2">
         <v>184765498.13</v>
       </c>
-      <c r="G190" s="4">
+      <c r="G190" s="2">
         <v>18764954.460000001</v>
       </c>
-      <c r="H190" s="4">
+      <c r="H190" s="2">
         <v>145734274.81</v>
       </c>
-      <c r="I190" s="4">
+      <c r="I190" s="2">
         <v>14434716.119999999</v>
       </c>
-      <c r="J190">
+      <c r="J190" s="3">
         <v>6498.3919999999998</v>
       </c>
-      <c r="K190">
+      <c r="K190" s="3">
         <v>166</v>
       </c>
     </row>
@@ -85819,7 +85905,7 @@
       <c r="A191" t="s">
         <v>115</v>
       </c>
-      <c r="B191" s="5">
+      <c r="B191" s="1">
         <v>46297</v>
       </c>
       <c r="C191" t="s">
@@ -85831,18 +85917,20 @@
       <c r="E191" t="s">
         <v>99</v>
       </c>
-      <c r="F191" s="4">
+      <c r="F191" s="2">
         <v>90240340.560000002</v>
       </c>
-      <c r="H191" s="4">
+      <c r="G191"/>
+      <c r="H191" s="2">
         <v>71285402.450000003</v>
       </c>
+      <c r="I191"/>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>115</v>
       </c>
-      <c r="B192" s="5">
+      <c r="B192" s="1">
         <v>46297</v>
       </c>
       <c r="C192" t="s">
@@ -85854,22 +85942,22 @@
       <c r="E192" t="s">
         <v>100</v>
       </c>
-      <c r="F192" s="4">
+      <c r="F192" s="2">
         <v>169053025.63</v>
       </c>
-      <c r="G192" s="4">
+      <c r="G192" s="2">
         <v>5436091.5700000003</v>
       </c>
-      <c r="H192" s="4">
+      <c r="H192" s="2">
         <v>132344451.47</v>
       </c>
-      <c r="I192" s="4">
+      <c r="I192" s="2">
         <v>4263240.99</v>
       </c>
-      <c r="J192">
+      <c r="J192" s="3">
         <v>1727.2529999999999</v>
       </c>
-      <c r="K192">
+      <c r="K192" s="3">
         <v>42</v>
       </c>
     </row>
@@ -85877,7 +85965,7 @@
       <c r="A193" t="s">
         <v>115</v>
       </c>
-      <c r="B193" s="5">
+      <c r="B193" s="1">
         <v>46297</v>
       </c>
       <c r="C193" t="s">
@@ -85889,22 +85977,22 @@
       <c r="E193" t="s">
         <v>101</v>
       </c>
-      <c r="F193" s="4">
+      <c r="F193" s="2">
         <v>107094064.84</v>
       </c>
-      <c r="G193" s="4">
+      <c r="G193" s="2">
         <v>12664309.32</v>
       </c>
-      <c r="H193" s="4">
+      <c r="H193" s="2">
         <v>84234991.840000004</v>
       </c>
-      <c r="I193" s="4">
+      <c r="I193" s="2">
         <v>9845512.2300000004</v>
       </c>
-      <c r="J193">
+      <c r="J193" s="3">
         <v>3785.9740000000002</v>
       </c>
-      <c r="K193">
+      <c r="K193" s="3">
         <v>137</v>
       </c>
     </row>
@@ -85912,7 +86000,7 @@
       <c r="A194" t="s">
         <v>115</v>
       </c>
-      <c r="B194" s="5">
+      <c r="B194" s="1">
         <v>46297</v>
       </c>
       <c r="C194" t="s">
@@ -85924,22 +86012,22 @@
       <c r="E194" t="s">
         <v>102</v>
       </c>
-      <c r="F194" s="4">
+      <c r="F194" s="2">
         <v>25925001.440000001</v>
       </c>
-      <c r="G194" s="4">
+      <c r="G194" s="2">
         <v>177624.1</v>
       </c>
-      <c r="H194" s="4">
+      <c r="H194" s="2">
         <v>20484626.879999999</v>
       </c>
-      <c r="I194" s="4">
+      <c r="I194" s="2">
         <v>140369.88</v>
       </c>
-      <c r="J194">
+      <c r="J194" s="3">
         <v>95</v>
       </c>
-      <c r="K194">
+      <c r="K194" s="3">
         <v>4</v>
       </c>
     </row>
@@ -85947,7 +86035,7 @@
       <c r="A195" t="s">
         <v>115</v>
       </c>
-      <c r="B195" s="5">
+      <c r="B195" s="1">
         <v>46298</v>
       </c>
       <c r="C195" t="s">
@@ -85959,22 +86047,22 @@
       <c r="E195" t="s">
         <v>10</v>
       </c>
-      <c r="F195" s="4">
+      <c r="F195" s="2">
         <v>117022483.81</v>
       </c>
-      <c r="G195" s="4">
+      <c r="G195" s="2">
         <v>2778675.66</v>
       </c>
-      <c r="H195" s="4">
+      <c r="H195" s="2">
         <v>91771671.090000004</v>
       </c>
-      <c r="I195" s="4">
+      <c r="I195" s="2">
         <v>2178761.6800000002</v>
       </c>
-      <c r="J195">
+      <c r="J195" s="3">
         <v>775.30200000000002</v>
       </c>
-      <c r="K195">
+      <c r="K195" s="3">
         <v>23</v>
       </c>
     </row>
@@ -85982,7 +86070,7 @@
       <c r="A196" t="s">
         <v>115</v>
       </c>
-      <c r="B196" s="5">
+      <c r="B196" s="1">
         <v>46298</v>
       </c>
       <c r="C196" t="s">
@@ -85994,22 +86082,22 @@
       <c r="E196" t="s">
         <v>11</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="2">
         <v>123148648.3</v>
       </c>
-      <c r="G196" s="4">
+      <c r="G196" s="2">
         <v>2888958.22</v>
       </c>
-      <c r="H196" s="4">
+      <c r="H196" s="2">
         <v>96857112.920000002</v>
       </c>
-      <c r="I196" s="4">
+      <c r="I196" s="2">
         <v>2238165.7799999998</v>
       </c>
-      <c r="J196">
+      <c r="J196" s="3">
         <v>1277.9480000000001</v>
       </c>
-      <c r="K196">
+      <c r="K196" s="3">
         <v>34</v>
       </c>
     </row>
@@ -86017,7 +86105,7 @@
       <c r="A197" t="s">
         <v>115</v>
       </c>
-      <c r="B197" s="5">
+      <c r="B197" s="1">
         <v>46298</v>
       </c>
       <c r="C197" t="s">
@@ -86029,22 +86117,22 @@
       <c r="E197" t="s">
         <v>12</v>
       </c>
-      <c r="F197" s="4">
+      <c r="F197" s="2">
         <v>128519593.09999999</v>
       </c>
-      <c r="G197" s="4">
+      <c r="G197" s="2">
         <v>3860110.11</v>
       </c>
-      <c r="H197" s="4">
+      <c r="H197" s="2">
         <v>101540193.81</v>
       </c>
-      <c r="I197" s="4">
+      <c r="I197" s="2">
         <v>3043001.78</v>
       </c>
-      <c r="J197">
+      <c r="J197" s="3">
         <v>1091.8</v>
       </c>
-      <c r="K197">
+      <c r="K197" s="3">
         <v>32</v>
       </c>
     </row>
@@ -86052,7 +86140,7 @@
       <c r="A198" t="s">
         <v>115</v>
       </c>
-      <c r="B198" s="5">
+      <c r="B198" s="1">
         <v>46298</v>
       </c>
       <c r="C198" t="s">
@@ -86064,18 +86152,20 @@
       <c r="E198" t="s">
         <v>13</v>
       </c>
-      <c r="F198" s="4">
+      <c r="F198" s="2">
         <v>78192430.780000001</v>
       </c>
-      <c r="H198" s="4">
+      <c r="G198"/>
+      <c r="H198" s="2">
         <v>61542679.609999999</v>
       </c>
+      <c r="I198"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>115</v>
       </c>
-      <c r="B199" s="5">
+      <c r="B199" s="1">
         <v>46298</v>
       </c>
       <c r="C199" t="s">
@@ -86087,22 +86177,22 @@
       <c r="E199" t="s">
         <v>14</v>
       </c>
-      <c r="F199" s="4">
+      <c r="F199" s="2">
         <v>99010834.640000001</v>
       </c>
-      <c r="G199" s="4">
+      <c r="G199" s="2">
         <v>5135827.63</v>
       </c>
-      <c r="H199" s="4">
+      <c r="H199" s="2">
         <v>77523154.670000002</v>
       </c>
-      <c r="I199" s="4">
+      <c r="I199" s="2">
         <v>3983575.64</v>
       </c>
-      <c r="J199">
+      <c r="J199" s="3">
         <v>1457.423</v>
       </c>
-      <c r="K199">
+      <c r="K199" s="3">
         <v>40</v>
       </c>
     </row>
@@ -86110,7 +86200,7 @@
       <c r="A200" t="s">
         <v>115</v>
       </c>
-      <c r="B200" s="5">
+      <c r="B200" s="1">
         <v>46298</v>
       </c>
       <c r="C200" t="s">
@@ -86122,22 +86212,22 @@
       <c r="E200" t="s">
         <v>15</v>
       </c>
-      <c r="F200" s="4">
+      <c r="F200" s="2">
         <v>158357424.62</v>
       </c>
-      <c r="G200" s="4">
+      <c r="G200" s="2">
         <v>318449.36</v>
       </c>
-      <c r="H200" s="4">
+      <c r="H200" s="2">
         <v>124707259.59</v>
       </c>
-      <c r="I200" s="4">
+      <c r="I200" s="2">
         <v>246819.07</v>
       </c>
-      <c r="J200">
+      <c r="J200" s="3">
         <v>70</v>
       </c>
-      <c r="K200">
+      <c r="K200" s="3">
         <v>5</v>
       </c>
     </row>
@@ -86145,7 +86235,7 @@
       <c r="A201" t="s">
         <v>115</v>
       </c>
-      <c r="B201" s="5">
+      <c r="B201" s="1">
         <v>46298</v>
       </c>
       <c r="C201" t="s">
@@ -86157,22 +86247,22 @@
       <c r="E201" t="s">
         <v>16</v>
       </c>
-      <c r="F201" s="4">
+      <c r="F201" s="2">
         <v>105266296.97</v>
       </c>
-      <c r="G201" s="4">
+      <c r="G201" s="2">
         <v>3645312.74</v>
       </c>
-      <c r="H201" s="4">
+      <c r="H201" s="2">
         <v>82520526.879999995</v>
       </c>
-      <c r="I201" s="4">
+      <c r="I201" s="2">
         <v>2864642.12</v>
       </c>
-      <c r="J201">
+      <c r="J201" s="3">
         <v>651.74300000000005</v>
       </c>
-      <c r="K201">
+      <c r="K201" s="3">
         <v>31</v>
       </c>
     </row>
@@ -86180,7 +86270,7 @@
       <c r="A202" t="s">
         <v>115</v>
       </c>
-      <c r="B202" s="5">
+      <c r="B202" s="1">
         <v>46298</v>
       </c>
       <c r="C202" t="s">
@@ -86192,18 +86282,20 @@
       <c r="E202" t="s">
         <v>17</v>
       </c>
-      <c r="F202" s="4">
+      <c r="F202" s="2">
         <v>67101639.579999998</v>
       </c>
-      <c r="H202" s="4">
+      <c r="G202"/>
+      <c r="H202" s="2">
         <v>53003719.810000002</v>
       </c>
+      <c r="I202"/>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>115</v>
       </c>
-      <c r="B203" s="5">
+      <c r="B203" s="1">
         <v>46298</v>
       </c>
       <c r="C203" t="s">
@@ -86215,22 +86307,22 @@
       <c r="E203" t="s">
         <v>18</v>
       </c>
-      <c r="F203" s="4">
+      <c r="F203" s="2">
         <v>80485252.290000007</v>
       </c>
-      <c r="G203" s="4">
+      <c r="G203" s="2">
         <v>1751121</v>
       </c>
-      <c r="H203" s="4">
+      <c r="H203" s="2">
         <v>63517074.439999998</v>
       </c>
-      <c r="I203" s="4">
+      <c r="I203" s="2">
         <v>1367804.05</v>
       </c>
-      <c r="J203">
+      <c r="J203" s="3">
         <v>593.23699999999997</v>
       </c>
-      <c r="K203">
+      <c r="K203" s="3">
         <v>19</v>
       </c>
     </row>
@@ -86238,7 +86330,7 @@
       <c r="A204" t="s">
         <v>115</v>
       </c>
-      <c r="B204" s="5">
+      <c r="B204" s="1">
         <v>46298</v>
       </c>
       <c r="C204" t="s">
@@ -86250,22 +86342,22 @@
       <c r="E204" t="s">
         <v>19</v>
       </c>
-      <c r="F204" s="4">
+      <c r="F204" s="2">
         <v>83157880.079999998</v>
       </c>
-      <c r="G204" s="4">
+      <c r="G204" s="2">
         <v>334253.40999999997</v>
       </c>
-      <c r="H204" s="4">
+      <c r="H204" s="2">
         <v>64970756.049999997</v>
       </c>
-      <c r="I204" s="4">
+      <c r="I204" s="2">
         <v>263243.98</v>
       </c>
-      <c r="J204">
+      <c r="J204" s="3">
         <v>85.185000000000002</v>
       </c>
-      <c r="K204">
+      <c r="K204" s="3">
         <v>4</v>
       </c>
     </row>
@@ -86273,7 +86365,7 @@
       <c r="A205" t="s">
         <v>115</v>
       </c>
-      <c r="B205" s="5">
+      <c r="B205" s="1">
         <v>46298</v>
       </c>
       <c r="C205" t="s">
@@ -86285,18 +86377,20 @@
       <c r="E205" t="s">
         <v>20</v>
       </c>
-      <c r="F205" s="4">
+      <c r="F205" s="2">
         <v>88509004.290000007</v>
       </c>
-      <c r="H205" s="4">
+      <c r="G205"/>
+      <c r="H205" s="2">
         <v>69588557.609999999</v>
       </c>
+      <c r="I205"/>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>115</v>
       </c>
-      <c r="B206" s="5">
+      <c r="B206" s="1">
         <v>46298</v>
       </c>
       <c r="C206" t="s">
@@ -86308,22 +86402,22 @@
       <c r="E206" t="s">
         <v>21</v>
       </c>
-      <c r="F206" s="4">
+      <c r="F206" s="2">
         <v>55966259.280000001</v>
       </c>
-      <c r="G206" s="4">
+      <c r="G206" s="2">
         <v>314991</v>
       </c>
-      <c r="H206" s="4">
+      <c r="H206" s="2">
         <v>43748963.090000004</v>
       </c>
-      <c r="I206" s="4">
+      <c r="I206" s="2">
         <v>244052.95</v>
       </c>
-      <c r="J206">
+      <c r="J206" s="3">
         <v>1</v>
       </c>
-      <c r="K206">
+      <c r="K206" s="3">
         <v>1</v>
       </c>
     </row>
@@ -86331,7 +86425,7 @@
       <c r="A207" t="s">
         <v>115</v>
       </c>
-      <c r="B207" s="5">
+      <c r="B207" s="1">
         <v>46298</v>
       </c>
       <c r="C207" t="s">
@@ -86343,18 +86437,20 @@
       <c r="E207" t="s">
         <v>22</v>
       </c>
-      <c r="F207" s="4">
+      <c r="F207" s="2">
         <v>67153205.769999996</v>
       </c>
-      <c r="H207" s="4">
+      <c r="G207"/>
+      <c r="H207" s="2">
         <v>52635385</v>
       </c>
+      <c r="I207"/>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>115</v>
       </c>
-      <c r="B208" s="5">
+      <c r="B208" s="1">
         <v>46298</v>
       </c>
       <c r="C208" t="s">
@@ -86366,18 +86462,20 @@
       <c r="E208" t="s">
         <v>23</v>
       </c>
-      <c r="F208" s="4">
+      <c r="F208" s="2">
         <v>138390183.13999999</v>
       </c>
-      <c r="H208" s="4">
+      <c r="G208"/>
+      <c r="H208" s="2">
         <v>108315470.05</v>
       </c>
+      <c r="I208"/>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>115</v>
       </c>
-      <c r="B209" s="5">
+      <c r="B209" s="1">
         <v>46298</v>
       </c>
       <c r="C209" t="s">
@@ -86389,18 +86487,20 @@
       <c r="E209" t="s">
         <v>24</v>
       </c>
-      <c r="F209" s="4">
+      <c r="F209" s="2">
         <v>102977617.45999999</v>
       </c>
-      <c r="H209" s="4">
+      <c r="G209"/>
+      <c r="H209" s="2">
         <v>80820745.069999993</v>
       </c>
+      <c r="I209"/>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>115</v>
       </c>
-      <c r="B210" s="5">
+      <c r="B210" s="1">
         <v>46298</v>
       </c>
       <c r="C210" t="s">
@@ -86412,22 +86512,22 @@
       <c r="E210" t="s">
         <v>25</v>
       </c>
-      <c r="F210" s="4">
+      <c r="F210" s="2">
         <v>69293942.189999998</v>
       </c>
-      <c r="G210" s="4">
+      <c r="G210" s="2">
         <v>114370.65</v>
       </c>
-      <c r="H210" s="4">
+      <c r="H210" s="2">
         <v>54367635.619999997</v>
       </c>
-      <c r="I210" s="4">
+      <c r="I210" s="2">
         <v>92399.61</v>
       </c>
-      <c r="J210">
+      <c r="J210" s="3">
         <v>37</v>
       </c>
-      <c r="K210">
+      <c r="K210" s="3">
         <v>3</v>
       </c>
     </row>
@@ -86435,7 +86535,7 @@
       <c r="A211" t="s">
         <v>115</v>
       </c>
-      <c r="B211" s="5">
+      <c r="B211" s="1">
         <v>46298</v>
       </c>
       <c r="C211" t="s">
@@ -86447,22 +86547,22 @@
       <c r="E211" t="s">
         <v>26</v>
       </c>
-      <c r="F211" s="4">
+      <c r="F211" s="2">
         <v>71033912.319999993</v>
       </c>
-      <c r="G211" s="4">
+      <c r="G211" s="2">
         <v>2722164.53</v>
       </c>
-      <c r="H211" s="4">
+      <c r="H211" s="2">
         <v>56063152.409999996</v>
       </c>
-      <c r="I211" s="4">
+      <c r="I211" s="2">
         <v>2133238.73</v>
       </c>
-      <c r="J211">
+      <c r="J211" s="3">
         <v>778.58100000000002</v>
       </c>
-      <c r="K211">
+      <c r="K211" s="3">
         <v>31</v>
       </c>
     </row>
@@ -86470,7 +86570,7 @@
       <c r="A212" t="s">
         <v>115</v>
       </c>
-      <c r="B212" s="5">
+      <c r="B212" s="1">
         <v>46298</v>
       </c>
       <c r="C212" t="s">
@@ -86482,18 +86582,20 @@
       <c r="E212" t="s">
         <v>27</v>
       </c>
-      <c r="F212" s="4">
+      <c r="F212" s="2">
         <v>94883784.069999993</v>
       </c>
-      <c r="H212" s="4">
+      <c r="G212"/>
+      <c r="H212" s="2">
         <v>74726373.25</v>
       </c>
+      <c r="I212"/>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>115</v>
       </c>
-      <c r="B213" s="5">
+      <c r="B213" s="1">
         <v>46298</v>
       </c>
       <c r="C213" t="s">
@@ -86505,22 +86607,22 @@
       <c r="E213" t="s">
         <v>28</v>
       </c>
-      <c r="F213" s="4">
+      <c r="F213" s="2">
         <v>138782677.53</v>
       </c>
-      <c r="G213" s="4">
+      <c r="G213" s="2">
         <v>1280315.5900000001</v>
       </c>
-      <c r="H213" s="4">
+      <c r="H213" s="2">
         <v>110063525.11</v>
       </c>
-      <c r="I213" s="4">
+      <c r="I213" s="2">
         <v>1002695.52</v>
       </c>
-      <c r="J213">
+      <c r="J213" s="3">
         <v>296.88</v>
       </c>
-      <c r="K213">
+      <c r="K213" s="3">
         <v>12</v>
       </c>
     </row>
@@ -86528,7 +86630,7 @@
       <c r="A214" t="s">
         <v>115</v>
       </c>
-      <c r="B214" s="5">
+      <c r="B214" s="1">
         <v>46298</v>
       </c>
       <c r="C214" t="s">
@@ -86540,18 +86642,20 @@
       <c r="E214" t="s">
         <v>29</v>
       </c>
-      <c r="F214" s="4">
+      <c r="F214" s="2">
         <v>121367462.18000001</v>
       </c>
-      <c r="H214" s="4">
+      <c r="G214"/>
+      <c r="H214" s="2">
         <v>95455898.040000007</v>
       </c>
+      <c r="I214"/>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>115</v>
       </c>
-      <c r="B215" s="5">
+      <c r="B215" s="1">
         <v>46298</v>
       </c>
       <c r="C215" t="s">
@@ -86563,22 +86667,22 @@
       <c r="E215" t="s">
         <v>30</v>
       </c>
-      <c r="F215" s="4">
+      <c r="F215" s="2">
         <v>109184581.19</v>
       </c>
-      <c r="G215" s="4">
+      <c r="G215" s="2">
         <v>5641979.0199999996</v>
       </c>
-      <c r="H215" s="4">
+      <c r="H215" s="2">
         <v>85532969.939999998</v>
       </c>
-      <c r="I215" s="4">
+      <c r="I215" s="2">
         <v>4448399.41</v>
       </c>
-      <c r="J215">
+      <c r="J215" s="3">
         <v>2085.7820000000002</v>
       </c>
-      <c r="K215">
+      <c r="K215" s="3">
         <v>62</v>
       </c>
     </row>
@@ -86586,7 +86690,7 @@
       <c r="A216" t="s">
         <v>115</v>
       </c>
-      <c r="B216" s="5">
+      <c r="B216" s="1">
         <v>46298</v>
       </c>
       <c r="C216" t="s">
@@ -86598,18 +86702,20 @@
       <c r="E216" t="s">
         <v>31</v>
       </c>
-      <c r="F216" s="4">
+      <c r="F216" s="2">
         <v>82025578.689999998</v>
       </c>
-      <c r="H216" s="4">
+      <c r="G216"/>
+      <c r="H216" s="2">
         <v>64263162.649999999</v>
       </c>
+      <c r="I216"/>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>115</v>
       </c>
-      <c r="B217" s="5">
+      <c r="B217" s="1">
         <v>46298</v>
       </c>
       <c r="C217" t="s">
@@ -86621,18 +86727,20 @@
       <c r="E217" t="s">
         <v>32</v>
       </c>
-      <c r="F217" s="4">
+      <c r="F217" s="2">
         <v>23356118.800000001</v>
       </c>
-      <c r="H217" s="4">
+      <c r="G217"/>
+      <c r="H217" s="2">
         <v>18489201.469999999</v>
       </c>
+      <c r="I217"/>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>115</v>
       </c>
-      <c r="B218" s="5">
+      <c r="B218" s="1">
         <v>46298</v>
       </c>
       <c r="C218" t="s">
@@ -86644,22 +86752,22 @@
       <c r="E218" t="s">
         <v>33</v>
       </c>
-      <c r="F218" s="4">
+      <c r="F218" s="2">
         <v>71622323.280000001</v>
       </c>
-      <c r="G218" s="4">
+      <c r="G218" s="2">
         <v>38849.25</v>
       </c>
-      <c r="H218" s="4">
+      <c r="H218" s="2">
         <v>56392511.5</v>
       </c>
-      <c r="I218" s="4">
+      <c r="I218" s="2">
         <v>30100.14</v>
       </c>
-      <c r="J218">
+      <c r="J218" s="3">
         <v>1</v>
       </c>
-      <c r="K218">
+      <c r="K218" s="3">
         <v>1</v>
       </c>
     </row>
@@ -86667,7 +86775,7 @@
       <c r="A219" t="s">
         <v>115</v>
       </c>
-      <c r="B219" s="5">
+      <c r="B219" s="1">
         <v>46298</v>
       </c>
       <c r="C219" t="s">
@@ -86679,18 +86787,20 @@
       <c r="E219" t="s">
         <v>34</v>
       </c>
-      <c r="F219" s="4">
+      <c r="F219" s="2">
         <v>65690813.5</v>
       </c>
-      <c r="H219" s="4">
+      <c r="G219"/>
+      <c r="H219" s="2">
         <v>51763497.969999999</v>
       </c>
+      <c r="I219"/>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>115</v>
       </c>
-      <c r="B220" s="5">
+      <c r="B220" s="1">
         <v>46298</v>
       </c>
       <c r="C220" t="s">
@@ -86702,18 +86812,20 @@
       <c r="E220" t="s">
         <v>35</v>
       </c>
-      <c r="F220" s="4">
+      <c r="F220" s="2">
         <v>27032072.77</v>
       </c>
-      <c r="H220" s="4">
+      <c r="G220"/>
+      <c r="H220" s="2">
         <v>21390453.120000001</v>
       </c>
+      <c r="I220"/>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>115</v>
       </c>
-      <c r="B221" s="5">
+      <c r="B221" s="1">
         <v>46298</v>
       </c>
       <c r="C221" t="s">
@@ -86725,22 +86837,22 @@
       <c r="E221" t="s">
         <v>36</v>
       </c>
-      <c r="F221" s="4">
+      <c r="F221" s="2">
         <v>118383356.8</v>
       </c>
-      <c r="G221" s="4">
+      <c r="G221" s="2">
         <v>920704.65</v>
       </c>
-      <c r="H221" s="4">
+      <c r="H221" s="2">
         <v>93731603.140000001</v>
       </c>
-      <c r="I221" s="4">
+      <c r="I221" s="2">
         <v>733699.85</v>
       </c>
-      <c r="J221">
+      <c r="J221" s="3">
         <v>186.11500000000001</v>
       </c>
-      <c r="K221">
+      <c r="K221" s="3">
         <v>10</v>
       </c>
     </row>
@@ -86748,7 +86860,7 @@
       <c r="A222" t="s">
         <v>115</v>
       </c>
-      <c r="B222" s="5">
+      <c r="B222" s="1">
         <v>46298</v>
       </c>
       <c r="C222" t="s">
@@ -86760,18 +86872,20 @@
       <c r="E222" t="s">
         <v>37</v>
       </c>
-      <c r="F222" s="4">
+      <c r="F222" s="2">
         <v>88353724.75</v>
       </c>
-      <c r="H222" s="4">
+      <c r="G222"/>
+      <c r="H222" s="2">
         <v>69325625.310000002</v>
       </c>
+      <c r="I222"/>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>115</v>
       </c>
-      <c r="B223" s="5">
+      <c r="B223" s="1">
         <v>46298</v>
       </c>
       <c r="C223" t="s">
@@ -86783,22 +86897,22 @@
       <c r="E223" t="s">
         <v>38</v>
       </c>
-      <c r="F223" s="4">
+      <c r="F223" s="2">
         <v>50694639.439999998</v>
       </c>
-      <c r="G223" s="4">
+      <c r="G223" s="2">
         <v>126352.21</v>
       </c>
-      <c r="H223" s="4">
+      <c r="H223" s="2">
         <v>40098761.700000003</v>
       </c>
-      <c r="I223" s="4">
+      <c r="I223" s="2">
         <v>98583.1</v>
       </c>
-      <c r="J223">
+      <c r="J223" s="3">
         <v>45</v>
       </c>
-      <c r="K223">
+      <c r="K223" s="3">
         <v>1</v>
       </c>
     </row>
@@ -86806,7 +86920,7 @@
       <c r="A224" t="s">
         <v>115</v>
       </c>
-      <c r="B224" s="5">
+      <c r="B224" s="1">
         <v>46298</v>
       </c>
       <c r="C224" t="s">
@@ -86818,22 +86932,22 @@
       <c r="E224" t="s">
         <v>39</v>
       </c>
-      <c r="F224" s="4">
+      <c r="F224" s="2">
         <v>57281261.170000002</v>
       </c>
-      <c r="G224" s="4">
+      <c r="G224" s="2">
         <v>91413.75</v>
       </c>
-      <c r="H224" s="4">
+      <c r="H224" s="2">
         <v>45011539.619999997</v>
       </c>
-      <c r="I224" s="4">
+      <c r="I224" s="2">
         <v>76951.820000000007</v>
       </c>
-      <c r="J224">
+      <c r="J224" s="3">
         <v>7.2039999999999997</v>
       </c>
-      <c r="K224">
+      <c r="K224" s="3">
         <v>2</v>
       </c>
     </row>
@@ -86841,7 +86955,7 @@
       <c r="A225" t="s">
         <v>115</v>
       </c>
-      <c r="B225" s="5">
+      <c r="B225" s="1">
         <v>46298</v>
       </c>
       <c r="C225" t="s">
@@ -86853,18 +86967,20 @@
       <c r="E225" t="s">
         <v>40</v>
       </c>
-      <c r="F225" s="4">
+      <c r="F225" s="2">
         <v>23441428.149999999</v>
       </c>
-      <c r="H225" s="4">
+      <c r="G225"/>
+      <c r="H225" s="2">
         <v>18362832.02</v>
       </c>
+      <c r="I225"/>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>115</v>
       </c>
-      <c r="B226" s="5">
+      <c r="B226" s="1">
         <v>46298</v>
       </c>
       <c r="C226" t="s">
@@ -86876,22 +86992,22 @@
       <c r="E226" t="s">
         <v>42</v>
       </c>
-      <c r="F226" s="4">
+      <c r="F226" s="2">
         <v>113063444.08</v>
       </c>
-      <c r="G226" s="4">
+      <c r="G226" s="2">
         <v>1372332.63</v>
       </c>
-      <c r="H226" s="4">
+      <c r="H226" s="2">
         <v>88669626.450000003</v>
       </c>
-      <c r="I226" s="4">
+      <c r="I226" s="2">
         <v>1090560.47</v>
       </c>
-      <c r="J226">
+      <c r="J226" s="3">
         <v>456.149</v>
       </c>
-      <c r="K226">
+      <c r="K226" s="3">
         <v>17</v>
       </c>
     </row>
@@ -86899,7 +87015,7 @@
       <c r="A227" t="s">
         <v>115</v>
       </c>
-      <c r="B227" s="5">
+      <c r="B227" s="1">
         <v>46298</v>
       </c>
       <c r="C227" t="s">
@@ -86911,22 +87027,22 @@
       <c r="E227" t="s">
         <v>43</v>
       </c>
-      <c r="F227" s="4">
+      <c r="F227" s="2">
         <v>93331073.579999998</v>
       </c>
-      <c r="G227" s="4">
+      <c r="G227" s="2">
         <v>1119999.25</v>
       </c>
-      <c r="H227" s="4">
+      <c r="H227" s="2">
         <v>73045671.590000004</v>
       </c>
-      <c r="I227" s="4">
+      <c r="I227" s="2">
         <v>867768.04</v>
       </c>
-      <c r="J227">
+      <c r="J227" s="3">
         <v>1</v>
       </c>
-      <c r="K227">
+      <c r="K227" s="3">
         <v>1</v>
       </c>
     </row>
@@ -86934,7 +87050,7 @@
       <c r="A228" t="s">
         <v>115</v>
       </c>
-      <c r="B228" s="5">
+      <c r="B228" s="1">
         <v>46298</v>
       </c>
       <c r="C228" t="s">
@@ -86946,22 +87062,22 @@
       <c r="E228" t="s">
         <v>44</v>
       </c>
-      <c r="F228" s="4">
+      <c r="F228" s="2">
         <v>82474426.769999996</v>
       </c>
-      <c r="G228" s="4">
+      <c r="G228" s="2">
         <v>335784.57</v>
       </c>
-      <c r="H228" s="4">
+      <c r="H228" s="2">
         <v>65096569.829999998</v>
       </c>
-      <c r="I228" s="4">
+      <c r="I228" s="2">
         <v>273439.26</v>
       </c>
-      <c r="J228">
+      <c r="J228" s="3">
         <v>89.805999999999997</v>
       </c>
-      <c r="K228">
+      <c r="K228" s="3">
         <v>2</v>
       </c>
     </row>
@@ -86969,7 +87085,7 @@
       <c r="A229" t="s">
         <v>115</v>
       </c>
-      <c r="B229" s="5">
+      <c r="B229" s="1">
         <v>46298</v>
       </c>
       <c r="C229" t="s">
@@ -86981,18 +87097,20 @@
       <c r="E229" t="s">
         <v>45</v>
       </c>
-      <c r="F229" s="4">
+      <c r="F229" s="2">
         <v>75446146</v>
       </c>
-      <c r="H229" s="4">
+      <c r="G229"/>
+      <c r="H229" s="2">
         <v>58881296.909999996</v>
       </c>
+      <c r="I229"/>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>115</v>
       </c>
-      <c r="B230" s="5">
+      <c r="B230" s="1">
         <v>46298</v>
       </c>
       <c r="C230" t="s">
@@ -87004,18 +87122,20 @@
       <c r="E230" t="s">
         <v>46</v>
       </c>
-      <c r="F230" s="4">
+      <c r="F230" s="2">
         <v>21249287.760000002</v>
       </c>
-      <c r="H230" s="4">
+      <c r="G230"/>
+      <c r="H230" s="2">
         <v>16713321.41</v>
       </c>
+      <c r="I230"/>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>115</v>
       </c>
-      <c r="B231" s="5">
+      <c r="B231" s="1">
         <v>46298</v>
       </c>
       <c r="C231" t="s">
@@ -87027,22 +87147,22 @@
       <c r="E231" t="s">
         <v>47</v>
       </c>
-      <c r="F231" s="4">
+      <c r="F231" s="2">
         <v>19956082.989999998</v>
       </c>
-      <c r="G231" s="4">
+      <c r="G231" s="2">
         <v>159999.20000000001</v>
       </c>
-      <c r="H231" s="4">
+      <c r="H231" s="2">
         <v>15727114.58</v>
       </c>
-      <c r="I231" s="4">
+      <c r="I231" s="2">
         <v>123966.32</v>
       </c>
-      <c r="J231">
+      <c r="J231" s="3">
         <v>1</v>
       </c>
-      <c r="K231">
+      <c r="K231" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87050,7 +87170,7 @@
       <c r="A232" t="s">
         <v>115</v>
       </c>
-      <c r="B232" s="5">
+      <c r="B232" s="1">
         <v>46298</v>
       </c>
       <c r="C232" t="s">
@@ -87062,18 +87182,20 @@
       <c r="E232" t="s">
         <v>48</v>
       </c>
-      <c r="F232" s="4">
+      <c r="F232" s="2">
         <v>36343293.280000001</v>
       </c>
-      <c r="H232" s="4">
+      <c r="G232"/>
+      <c r="H232" s="2">
         <v>28523704.989999998</v>
       </c>
+      <c r="I232"/>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>115</v>
       </c>
-      <c r="B233" s="5">
+      <c r="B233" s="1">
         <v>46298</v>
       </c>
       <c r="C233" t="s">
@@ -87085,22 +87207,22 @@
       <c r="E233" t="s">
         <v>49</v>
       </c>
-      <c r="F233" s="4">
+      <c r="F233" s="2">
         <v>54172345.640000001</v>
       </c>
-      <c r="G233" s="4">
+      <c r="G233" s="2">
         <v>594999.31000000006</v>
       </c>
-      <c r="H233" s="4">
+      <c r="H233" s="2">
         <v>42640894.159999996</v>
       </c>
-      <c r="I233" s="4">
+      <c r="I233" s="2">
         <v>461001.54</v>
       </c>
-      <c r="J233">
+      <c r="J233" s="3">
         <v>1</v>
       </c>
-      <c r="K233">
+      <c r="K233" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87108,7 +87230,7 @@
       <c r="A234" t="s">
         <v>115</v>
       </c>
-      <c r="B234" s="5">
+      <c r="B234" s="1">
         <v>46298</v>
       </c>
       <c r="C234" t="s">
@@ -87120,22 +87242,22 @@
       <c r="E234" t="s">
         <v>50</v>
       </c>
-      <c r="F234" s="4">
+      <c r="F234" s="2">
         <v>82293298.159999996</v>
       </c>
-      <c r="G234" s="4">
+      <c r="G234" s="2">
         <v>27640.400000000001</v>
       </c>
-      <c r="H234" s="4">
+      <c r="H234" s="2">
         <v>65710692.049999997</v>
       </c>
-      <c r="I234" s="4">
+      <c r="I234" s="2">
         <v>17541.66</v>
       </c>
-      <c r="J234">
+      <c r="J234" s="3">
         <v>6</v>
       </c>
-      <c r="K234">
+      <c r="K234" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87143,7 +87265,7 @@
       <c r="A235" t="s">
         <v>115</v>
       </c>
-      <c r="B235" s="5">
+      <c r="B235" s="1">
         <v>46298</v>
       </c>
       <c r="C235" t="s">
@@ -87155,22 +87277,22 @@
       <c r="E235" t="s">
         <v>51</v>
       </c>
-      <c r="F235" s="4">
+      <c r="F235" s="2">
         <v>63713535.57</v>
       </c>
-      <c r="G235" s="4">
+      <c r="G235" s="2">
         <v>1587996.19</v>
       </c>
-      <c r="H235" s="4">
+      <c r="H235" s="2">
         <v>50545631.689999998</v>
       </c>
-      <c r="I235" s="4">
+      <c r="I235" s="2">
         <v>1214873.1000000001</v>
       </c>
-      <c r="J235">
+      <c r="J235" s="3">
         <v>4</v>
       </c>
-      <c r="K235">
+      <c r="K235" s="3">
         <v>3</v>
       </c>
     </row>
@@ -87178,7 +87300,7 @@
       <c r="A236" t="s">
         <v>115</v>
       </c>
-      <c r="B236" s="5">
+      <c r="B236" s="1">
         <v>46298</v>
       </c>
       <c r="C236" t="s">
@@ -87190,22 +87312,22 @@
       <c r="E236" t="s">
         <v>52</v>
       </c>
-      <c r="F236" s="4">
+      <c r="F236" s="2">
         <v>72907562.590000004</v>
       </c>
-      <c r="G236" s="4">
+      <c r="G236" s="2">
         <v>51242.02</v>
       </c>
-      <c r="H236" s="4">
+      <c r="H236" s="2">
         <v>57282892.990000002</v>
       </c>
-      <c r="I236" s="4">
+      <c r="I236" s="2">
         <v>39764.85</v>
       </c>
-      <c r="J236">
+      <c r="J236" s="3">
         <v>21</v>
       </c>
-      <c r="K236">
+      <c r="K236" s="3">
         <v>2</v>
       </c>
     </row>
@@ -87213,7 +87335,7 @@
       <c r="A237" t="s">
         <v>115</v>
       </c>
-      <c r="B237" s="5">
+      <c r="B237" s="1">
         <v>46298</v>
       </c>
       <c r="C237" t="s">
@@ -87225,22 +87347,22 @@
       <c r="E237" t="s">
         <v>53</v>
       </c>
-      <c r="F237" s="4">
+      <c r="F237" s="2">
         <v>97988399.969999999</v>
       </c>
-      <c r="G237" s="4">
+      <c r="G237" s="2">
         <v>2193814.04</v>
       </c>
-      <c r="H237" s="4">
+      <c r="H237" s="2">
         <v>76467859.370000005</v>
       </c>
-      <c r="I237" s="4">
+      <c r="I237" s="2">
         <v>1709206.75</v>
       </c>
-      <c r="J237">
+      <c r="J237" s="3">
         <v>873.89800000000002</v>
       </c>
-      <c r="K237">
+      <c r="K237" s="3">
         <v>23</v>
       </c>
     </row>
@@ -87248,7 +87370,7 @@
       <c r="A238" t="s">
         <v>115</v>
       </c>
-      <c r="B238" s="5">
+      <c r="B238" s="1">
         <v>46298</v>
       </c>
       <c r="C238" t="s">
@@ -87260,22 +87382,22 @@
       <c r="E238" t="s">
         <v>54</v>
       </c>
-      <c r="F238" s="4">
+      <c r="F238" s="2">
         <v>70775870.599999994</v>
       </c>
-      <c r="G238" s="4">
+      <c r="G238" s="2">
         <v>1392103.49</v>
       </c>
-      <c r="H238" s="4">
+      <c r="H238" s="2">
         <v>55759042.57</v>
       </c>
-      <c r="I238" s="4">
+      <c r="I238" s="2">
         <v>1099557.1299999999</v>
       </c>
-      <c r="J238">
+      <c r="J238" s="3">
         <v>317.02</v>
       </c>
-      <c r="K238">
+      <c r="K238" s="3">
         <v>14</v>
       </c>
     </row>
@@ -87283,7 +87405,7 @@
       <c r="A239" t="s">
         <v>115</v>
       </c>
-      <c r="B239" s="5">
+      <c r="B239" s="1">
         <v>46298</v>
       </c>
       <c r="C239" t="s">
@@ -87295,22 +87417,22 @@
       <c r="E239" t="s">
         <v>55</v>
       </c>
-      <c r="F239" s="4">
+      <c r="F239" s="2">
         <v>47277557.100000001</v>
       </c>
-      <c r="G239" s="4">
+      <c r="G239" s="2">
         <v>686508.39</v>
       </c>
-      <c r="H239" s="4">
+      <c r="H239" s="2">
         <v>37024510.159999996</v>
       </c>
-      <c r="I239" s="4">
+      <c r="I239" s="2">
         <v>531902.14</v>
       </c>
-      <c r="J239">
+      <c r="J239" s="3">
         <v>26</v>
       </c>
-      <c r="K239">
+      <c r="K239" s="3">
         <v>2</v>
       </c>
     </row>
@@ -87318,7 +87440,7 @@
       <c r="A240" t="s">
         <v>115</v>
       </c>
-      <c r="B240" s="5">
+      <c r="B240" s="1">
         <v>46298</v>
       </c>
       <c r="C240" t="s">
@@ -87330,22 +87452,22 @@
       <c r="E240" t="s">
         <v>56</v>
       </c>
-      <c r="F240" s="4">
+      <c r="F240" s="2">
         <v>139674044.00999999</v>
       </c>
-      <c r="G240" s="4">
+      <c r="G240" s="2">
         <v>4284403.6399999997</v>
       </c>
-      <c r="H240" s="4">
+      <c r="H240" s="2">
         <v>109486280.79000001</v>
       </c>
-      <c r="I240" s="4">
+      <c r="I240" s="2">
         <v>3336225.41</v>
       </c>
-      <c r="J240">
+      <c r="J240" s="3">
         <v>1361.3689999999999</v>
       </c>
-      <c r="K240">
+      <c r="K240" s="3">
         <v>38</v>
       </c>
     </row>
@@ -87353,7 +87475,7 @@
       <c r="A241" t="s">
         <v>115</v>
       </c>
-      <c r="B241" s="5">
+      <c r="B241" s="1">
         <v>46298</v>
       </c>
       <c r="C241" t="s">
@@ -87365,22 +87487,22 @@
       <c r="E241" t="s">
         <v>57</v>
       </c>
-      <c r="F241" s="4">
+      <c r="F241" s="2">
         <v>66549019.189999998</v>
       </c>
-      <c r="G241" s="4">
+      <c r="G241" s="2">
         <v>6833029.1500000004</v>
       </c>
-      <c r="H241" s="4">
+      <c r="H241" s="2">
         <v>52219749.07</v>
       </c>
-      <c r="I241" s="4">
+      <c r="I241" s="2">
         <v>5259550.25</v>
       </c>
-      <c r="J241">
+      <c r="J241" s="3">
         <v>2027.9860000000001</v>
       </c>
-      <c r="K241">
+      <c r="K241" s="3">
         <v>78</v>
       </c>
     </row>
@@ -87388,7 +87510,7 @@
       <c r="A242" t="s">
         <v>115</v>
       </c>
-      <c r="B242" s="5">
+      <c r="B242" s="1">
         <v>46298</v>
       </c>
       <c r="C242" t="s">
@@ -87400,18 +87522,20 @@
       <c r="E242" t="s">
         <v>58</v>
       </c>
-      <c r="F242" s="4">
+      <c r="F242" s="2">
         <v>73163430.25</v>
       </c>
-      <c r="H242" s="4">
+      <c r="G242"/>
+      <c r="H242" s="2">
         <v>57192773.509999998</v>
       </c>
+      <c r="I242"/>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>115</v>
       </c>
-      <c r="B243" s="5">
+      <c r="B243" s="1">
         <v>46298</v>
       </c>
       <c r="C243" t="s">
@@ -87423,18 +87547,20 @@
       <c r="E243" t="s">
         <v>59</v>
       </c>
-      <c r="F243" s="4">
+      <c r="F243" s="2">
         <v>45941503.619999997</v>
       </c>
-      <c r="H243" s="4">
+      <c r="G243"/>
+      <c r="H243" s="2">
         <v>36246783.310000002</v>
       </c>
+      <c r="I243"/>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>115</v>
       </c>
-      <c r="B244" s="5">
+      <c r="B244" s="1">
         <v>46298</v>
       </c>
       <c r="C244" t="s">
@@ -87446,22 +87572,22 @@
       <c r="E244" t="s">
         <v>60</v>
       </c>
-      <c r="F244" s="4">
+      <c r="F244" s="2">
         <v>103501054.84</v>
       </c>
-      <c r="G244" s="4">
+      <c r="G244" s="2">
         <v>216399.1</v>
       </c>
-      <c r="H244" s="4">
+      <c r="H244" s="2">
         <v>80693563.349999994</v>
       </c>
-      <c r="I244" s="4">
+      <c r="I244" s="2">
         <v>164952.92000000001</v>
       </c>
-      <c r="J244">
+      <c r="J244" s="3">
         <v>73</v>
       </c>
-      <c r="K244">
+      <c r="K244" s="3">
         <v>6</v>
       </c>
     </row>
@@ -87469,7 +87595,7 @@
       <c r="A245" t="s">
         <v>115</v>
       </c>
-      <c r="B245" s="5">
+      <c r="B245" s="1">
         <v>46298</v>
       </c>
       <c r="C245" t="s">
@@ -87481,18 +87607,20 @@
       <c r="E245" t="s">
         <v>111</v>
       </c>
-      <c r="F245" s="4">
+      <c r="F245" s="2">
         <v>2051651.18</v>
       </c>
-      <c r="H245" s="4">
+      <c r="G245"/>
+      <c r="H245" s="2">
         <v>1595585.86</v>
       </c>
+      <c r="I245"/>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>115</v>
       </c>
-      <c r="B246" s="5">
+      <c r="B246" s="1">
         <v>46298</v>
       </c>
       <c r="C246" t="s">
@@ -87504,22 +87632,22 @@
       <c r="E246" t="s">
         <v>61</v>
       </c>
-      <c r="F246" s="4">
+      <c r="F246" s="2">
         <v>41708740.450000003</v>
       </c>
-      <c r="G246" s="4">
+      <c r="G246" s="2">
         <v>122608.54</v>
       </c>
-      <c r="H246" s="4">
+      <c r="H246" s="2">
         <v>32887117.48</v>
       </c>
-      <c r="I246" s="4">
+      <c r="I246" s="2">
         <v>99293.9</v>
       </c>
-      <c r="J246">
+      <c r="J246" s="3">
         <v>58.097000000000001</v>
       </c>
-      <c r="K246">
+      <c r="K246" s="3">
         <v>3</v>
       </c>
     </row>
@@ -87527,7 +87655,7 @@
       <c r="A247" t="s">
         <v>115</v>
       </c>
-      <c r="B247" s="5">
+      <c r="B247" s="1">
         <v>46298</v>
       </c>
       <c r="C247" t="s">
@@ -87539,18 +87667,20 @@
       <c r="E247" t="s">
         <v>62</v>
       </c>
-      <c r="F247" s="4">
+      <c r="F247" s="2">
         <v>83018412.5</v>
       </c>
-      <c r="H247" s="4">
+      <c r="G247"/>
+      <c r="H247" s="2">
         <v>65373006.689999998</v>
       </c>
+      <c r="I247"/>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>115</v>
       </c>
-      <c r="B248" s="5">
+      <c r="B248" s="1">
         <v>46298</v>
       </c>
       <c r="C248" t="s">
@@ -87562,22 +87692,22 @@
       <c r="E248" t="s">
         <v>63</v>
       </c>
-      <c r="F248" s="4">
+      <c r="F248" s="2">
         <v>27625436.469999999</v>
       </c>
-      <c r="G248" s="4">
+      <c r="G248" s="2">
         <v>140497.15</v>
       </c>
-      <c r="H248" s="4">
+      <c r="H248" s="2">
         <v>21678603.870000001</v>
       </c>
-      <c r="I248" s="4">
+      <c r="I248" s="2">
         <v>109489.73</v>
       </c>
-      <c r="J248">
+      <c r="J248" s="3">
         <v>29.442</v>
       </c>
-      <c r="K248">
+      <c r="K248" s="3">
         <v>2</v>
       </c>
     </row>
@@ -87585,7 +87715,7 @@
       <c r="A249" t="s">
         <v>115</v>
       </c>
-      <c r="B249" s="5">
+      <c r="B249" s="1">
         <v>46298</v>
       </c>
       <c r="C249" t="s">
@@ -87597,22 +87727,22 @@
       <c r="E249" t="s">
         <v>64</v>
       </c>
-      <c r="F249" s="4">
+      <c r="F249" s="2">
         <v>72517027.519999996</v>
       </c>
-      <c r="G249" s="4">
+      <c r="G249" s="2">
         <v>269999.09000000003</v>
       </c>
-      <c r="H249" s="4">
+      <c r="H249" s="2">
         <v>57839172.240000002</v>
       </c>
-      <c r="I249" s="4">
+      <c r="I249" s="2">
         <v>209193.5</v>
       </c>
-      <c r="J249">
+      <c r="J249" s="3">
         <v>1</v>
       </c>
-      <c r="K249">
+      <c r="K249" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87620,7 +87750,7 @@
       <c r="A250" t="s">
         <v>115</v>
       </c>
-      <c r="B250" s="5">
+      <c r="B250" s="1">
         <v>46298</v>
       </c>
       <c r="C250" t="s">
@@ -87632,22 +87762,22 @@
       <c r="E250" t="s">
         <v>65</v>
       </c>
-      <c r="F250" s="4">
+      <c r="F250" s="2">
         <v>70181635.799999997</v>
       </c>
-      <c r="G250" s="4">
+      <c r="G250" s="2">
         <v>25799.25</v>
       </c>
-      <c r="H250" s="4">
+      <c r="H250" s="2">
         <v>55345411.259999998</v>
       </c>
-      <c r="I250" s="4">
+      <c r="I250" s="2">
         <v>21888.5</v>
       </c>
-      <c r="J250">
+      <c r="J250" s="3">
         <v>1</v>
       </c>
-      <c r="K250">
+      <c r="K250" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87655,7 +87785,7 @@
       <c r="A251" t="s">
         <v>115</v>
       </c>
-      <c r="B251" s="5">
+      <c r="B251" s="1">
         <v>46298</v>
       </c>
       <c r="C251" t="s">
@@ -87667,22 +87797,22 @@
       <c r="E251" t="s">
         <v>66</v>
       </c>
-      <c r="F251" s="4">
+      <c r="F251" s="2">
         <v>129933190.87</v>
       </c>
-      <c r="G251" s="4">
+      <c r="G251" s="2">
         <v>2817730.85</v>
       </c>
-      <c r="H251" s="4">
+      <c r="H251" s="2">
         <v>102627399.45999999</v>
       </c>
-      <c r="I251" s="4">
+      <c r="I251" s="2">
         <v>2067294.33</v>
       </c>
-      <c r="J251">
+      <c r="J251" s="3">
         <v>64.173000000000002</v>
       </c>
-      <c r="K251">
+      <c r="K251" s="3">
         <v>6</v>
       </c>
     </row>
@@ -87690,7 +87820,7 @@
       <c r="A252" t="s">
         <v>115</v>
       </c>
-      <c r="B252" s="5">
+      <c r="B252" s="1">
         <v>46298</v>
       </c>
       <c r="C252" t="s">
@@ -87702,22 +87832,22 @@
       <c r="E252" t="s">
         <v>67</v>
       </c>
-      <c r="F252" s="4">
+      <c r="F252" s="2">
         <v>79154904.900000006</v>
       </c>
-      <c r="G252" s="4">
+      <c r="G252" s="2">
         <v>631999.19999999995</v>
       </c>
-      <c r="H252" s="4">
+      <c r="H252" s="2">
         <v>62695708.450000003</v>
       </c>
-      <c r="I252" s="4">
+      <c r="I252" s="2">
         <v>489668.8</v>
       </c>
-      <c r="J252">
+      <c r="J252" s="3">
         <v>1</v>
       </c>
-      <c r="K252">
+      <c r="K252" s="3">
         <v>1</v>
       </c>
     </row>
@@ -87725,7 +87855,7 @@
       <c r="A253" t="s">
         <v>115</v>
       </c>
-      <c r="B253" s="5">
+      <c r="B253" s="1">
         <v>46298</v>
       </c>
       <c r="C253" t="s">
@@ -87737,22 +87867,22 @@
       <c r="E253" t="s">
         <v>68</v>
       </c>
-      <c r="F253" s="4">
+      <c r="F253" s="2">
         <v>58283979.159999996</v>
       </c>
-      <c r="G253" s="4">
+      <c r="G253" s="2">
         <v>4461558.9800000004</v>
       </c>
-      <c r="H253" s="4">
+      <c r="H253" s="2">
         <v>45513863.399999999</v>
       </c>
-      <c r="I253" s="4">
+      <c r="I253" s="2">
         <v>3455341.69</v>
       </c>
-      <c r="J253">
+      <c r="J253" s="3">
         <v>1033.3530000000001</v>
       </c>
-      <c r="K253">
+      <c r="K253" s="3">
         <v>26</v>
       </c>
     </row>
@@ -87760,7 +87890,7 @@
       <c r="A254" t="s">
         <v>115</v>
       </c>
-      <c r="B254" s="5">
+      <c r="B254" s="1">
         <v>46298</v>
       </c>
       <c r="C254" t="s">
@@ -87772,18 +87902,20 @@
       <c r="E254" t="s">
         <v>69</v>
       </c>
-      <c r="F254" s="4">
+      <c r="F254" s="2">
         <v>54254723.32</v>
       </c>
-      <c r="H254" s="4">
+      <c r="G254"/>
+      <c r="H254" s="2">
         <v>42915281.100000001</v>
       </c>
+      <c r="I254"/>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>115</v>
       </c>
-      <c r="B255" s="5">
+      <c r="B255" s="1">
         <v>46298</v>
       </c>
       <c r="C255" t="s">
@@ -87795,18 +87927,20 @@
       <c r="E255" t="s">
         <v>70</v>
       </c>
-      <c r="F255" s="4">
+      <c r="F255" s="2">
         <v>26379268.489999998</v>
       </c>
-      <c r="H255" s="4">
+      <c r="G255"/>
+      <c r="H255" s="2">
         <v>20991361.559999999</v>
       </c>
+      <c r="I255"/>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>115</v>
       </c>
-      <c r="B256" s="5">
+      <c r="B256" s="1">
         <v>46298</v>
       </c>
       <c r="C256" t="s">
@@ -87818,22 +87952,22 @@
       <c r="E256" t="s">
         <v>71</v>
       </c>
-      <c r="F256" s="4">
+      <c r="F256" s="2">
         <v>24173965.789999999</v>
       </c>
-      <c r="G256" s="4">
+      <c r="G256" s="2">
         <v>420518.41</v>
       </c>
-      <c r="H256" s="4">
+      <c r="H256" s="2">
         <v>19117222.530000001</v>
       </c>
-      <c r="I256" s="4">
+      <c r="I256" s="2">
         <v>329296.34000000003</v>
       </c>
-      <c r="J256">
+      <c r="J256" s="3">
         <v>100.334</v>
       </c>
-      <c r="K256">
+      <c r="K256" s="3">
         <v>3</v>
       </c>
     </row>
@@ -87841,7 +87975,7 @@
       <c r="A257" t="s">
         <v>115</v>
       </c>
-      <c r="B257" s="5">
+      <c r="B257" s="1">
         <v>46298</v>
       </c>
       <c r="C257" t="s">
@@ -87853,18 +87987,20 @@
       <c r="E257" t="s">
         <v>72</v>
       </c>
-      <c r="F257" s="4">
+      <c r="F257" s="2">
         <v>24419111.239999998</v>
       </c>
-      <c r="H257" s="4">
+      <c r="G257"/>
+      <c r="H257" s="2">
         <v>19313316.719999999</v>
       </c>
+      <c r="I257"/>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>115</v>
       </c>
-      <c r="B258" s="5">
+      <c r="B258" s="1">
         <v>46298</v>
       </c>
       <c r="C258" t="s">
@@ -87876,18 +88012,20 @@
       <c r="E258" t="s">
         <v>73</v>
       </c>
-      <c r="F258" s="4">
+      <c r="F258" s="2">
         <v>72160689.099999994</v>
       </c>
-      <c r="H258" s="4">
+      <c r="G258"/>
+      <c r="H258" s="2">
         <v>56472075.159999996</v>
       </c>
+      <c r="I258"/>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>115</v>
       </c>
-      <c r="B259" s="5">
+      <c r="B259" s="1">
         <v>46298</v>
       </c>
       <c r="C259" t="s">
@@ -87899,22 +88037,22 @@
       <c r="E259" t="s">
         <v>74</v>
       </c>
-      <c r="F259" s="4">
+      <c r="F259" s="2">
         <v>109331542.63</v>
       </c>
-      <c r="G259" s="4">
+      <c r="G259" s="2">
         <v>4322736.96</v>
       </c>
-      <c r="H259" s="4">
+      <c r="H259" s="2">
         <v>86136464.780000001</v>
       </c>
-      <c r="I259" s="4">
+      <c r="I259" s="2">
         <v>3326064.94</v>
       </c>
-      <c r="J259">
+      <c r="J259" s="3">
         <v>1354.6110000000001</v>
       </c>
-      <c r="K259">
+      <c r="K259" s="3">
         <v>41</v>
       </c>
     </row>
@@ -87922,7 +88060,7 @@
       <c r="A260" t="s">
         <v>115</v>
       </c>
-      <c r="B260" s="5">
+      <c r="B260" s="1">
         <v>46298</v>
       </c>
       <c r="C260" t="s">
@@ -87934,22 +88072,22 @@
       <c r="E260" t="s">
         <v>75</v>
       </c>
-      <c r="F260" s="4">
+      <c r="F260" s="2">
         <v>49617386.689999998</v>
       </c>
-      <c r="G260" s="4">
+      <c r="G260" s="2">
         <v>1375141.1</v>
       </c>
-      <c r="H260" s="4">
+      <c r="H260" s="2">
         <v>39465632.060000002</v>
       </c>
-      <c r="I260" s="4">
+      <c r="I260" s="2">
         <v>1071952.02</v>
       </c>
-      <c r="J260">
+      <c r="J260" s="3">
         <v>26</v>
       </c>
-      <c r="K260">
+      <c r="K260" s="3">
         <v>3</v>
       </c>
     </row>
@@ -87957,7 +88095,7 @@
       <c r="A261" t="s">
         <v>115</v>
       </c>
-      <c r="B261" s="5">
+      <c r="B261" s="1">
         <v>46298</v>
       </c>
       <c r="C261" t="s">
@@ -87969,18 +88107,20 @@
       <c r="E261" t="s">
         <v>76</v>
       </c>
-      <c r="F261" s="4">
+      <c r="F261" s="2">
         <v>63880097.310000002</v>
       </c>
-      <c r="H261" s="4">
+      <c r="G261"/>
+      <c r="H261" s="2">
         <v>49878651.159999996</v>
       </c>
+      <c r="I261"/>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>115</v>
       </c>
-      <c r="B262" s="5">
+      <c r="B262" s="1">
         <v>46298</v>
       </c>
       <c r="C262" t="s">
@@ -87992,18 +88132,20 @@
       <c r="E262" t="s">
         <v>77</v>
       </c>
-      <c r="F262" s="4">
+      <c r="F262" s="2">
         <v>98158981.129999995</v>
       </c>
-      <c r="H262" s="4">
+      <c r="G262"/>
+      <c r="H262" s="2">
         <v>77395224.75</v>
       </c>
+      <c r="I262"/>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>115</v>
       </c>
-      <c r="B263" s="5">
+      <c r="B263" s="1">
         <v>46298</v>
       </c>
       <c r="C263" t="s">
@@ -88015,18 +88157,20 @@
       <c r="E263" t="s">
         <v>78</v>
       </c>
-      <c r="F263" s="4">
+      <c r="F263" s="2">
         <v>78817118.450000003</v>
       </c>
-      <c r="H263" s="4">
+      <c r="G263"/>
+      <c r="H263" s="2">
         <v>61975747.439999998</v>
       </c>
+      <c r="I263"/>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>115</v>
       </c>
-      <c r="B264" s="5">
+      <c r="B264" s="1">
         <v>46298</v>
       </c>
       <c r="C264" t="s">
@@ -88038,18 +88182,20 @@
       <c r="E264" t="s">
         <v>79</v>
       </c>
-      <c r="F264" s="4">
+      <c r="F264" s="2">
         <v>61704554.340000004</v>
       </c>
-      <c r="H264" s="4">
+      <c r="G264"/>
+      <c r="H264" s="2">
         <v>48461231.640000001</v>
       </c>
+      <c r="I264"/>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>115</v>
       </c>
-      <c r="B265" s="5">
+      <c r="B265" s="1">
         <v>46298</v>
       </c>
       <c r="C265" t="s">
@@ -88061,18 +88207,20 @@
       <c r="E265" t="s">
         <v>80</v>
       </c>
-      <c r="F265" s="4">
+      <c r="F265" s="2">
         <v>48783819.68</v>
       </c>
-      <c r="H265" s="4">
+      <c r="G265"/>
+      <c r="H265" s="2">
         <v>38148522.369999997</v>
       </c>
+      <c r="I265"/>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>115</v>
       </c>
-      <c r="B266" s="5">
+      <c r="B266" s="1">
         <v>46298</v>
       </c>
       <c r="C266" t="s">
@@ -88084,18 +88232,20 @@
       <c r="E266" t="s">
         <v>81</v>
       </c>
-      <c r="F266" s="4">
+      <c r="F266" s="2">
         <v>62811915.5</v>
       </c>
-      <c r="H266" s="4">
+      <c r="G266"/>
+      <c r="H266" s="2">
         <v>50106366.450000003</v>
       </c>
+      <c r="I266"/>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>115</v>
       </c>
-      <c r="B267" s="5">
+      <c r="B267" s="1">
         <v>46298</v>
       </c>
       <c r="C267" t="s">
@@ -88107,18 +88257,20 @@
       <c r="E267" t="s">
         <v>82</v>
       </c>
-      <c r="F267" s="4">
+      <c r="F267" s="2">
         <v>80819039.560000002</v>
       </c>
-      <c r="H267" s="4">
+      <c r="G267"/>
+      <c r="H267" s="2">
         <v>63611948.32</v>
       </c>
+      <c r="I267"/>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>115</v>
       </c>
-      <c r="B268" s="5">
+      <c r="B268" s="1">
         <v>46298</v>
       </c>
       <c r="C268" t="s">
@@ -88130,18 +88282,20 @@
       <c r="E268" t="s">
         <v>112</v>
       </c>
-      <c r="F268" s="4">
+      <c r="F268" s="2">
         <v>2729253.36</v>
       </c>
-      <c r="H268" s="4">
+      <c r="G268"/>
+      <c r="H268" s="2">
         <v>2133667.2799999998</v>
       </c>
+      <c r="I268"/>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>115</v>
       </c>
-      <c r="B269" s="5">
+      <c r="B269" s="1">
         <v>46298</v>
       </c>
       <c r="C269" t="s">
@@ -88153,18 +88307,20 @@
       <c r="E269" t="s">
         <v>113</v>
       </c>
-      <c r="F269" s="4">
+      <c r="F269" s="2">
         <v>674576.11</v>
       </c>
-      <c r="H269" s="4">
+      <c r="G269"/>
+      <c r="H269" s="2">
         <v>522500.7</v>
       </c>
+      <c r="I269"/>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>115</v>
       </c>
-      <c r="B270" s="5">
+      <c r="B270" s="1">
         <v>46298</v>
       </c>
       <c r="C270" t="s">
@@ -88176,18 +88332,20 @@
       <c r="E270" t="s">
         <v>83</v>
       </c>
-      <c r="F270" s="4">
+      <c r="F270" s="2">
         <v>29420053.670000002</v>
       </c>
-      <c r="H270" s="4">
+      <c r="G270"/>
+      <c r="H270" s="2">
         <v>23273080.420000002</v>
       </c>
+      <c r="I270"/>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>115</v>
       </c>
-      <c r="B271" s="5">
+      <c r="B271" s="1">
         <v>46298</v>
       </c>
       <c r="C271" t="s">
@@ -88199,22 +88357,22 @@
       <c r="E271" t="s">
         <v>84</v>
       </c>
-      <c r="F271" s="4">
+      <c r="F271" s="2">
         <v>76619212.650000006</v>
       </c>
-      <c r="G271" s="4">
+      <c r="G271" s="2">
         <v>539997</v>
       </c>
-      <c r="H271" s="4">
+      <c r="H271" s="2">
         <v>60315946.909999996</v>
       </c>
-      <c r="I271" s="4">
+      <c r="I271" s="2">
         <v>418386.12</v>
       </c>
-      <c r="J271">
+      <c r="J271" s="3">
         <v>4</v>
       </c>
-      <c r="K271">
+      <c r="K271" s="3">
         <v>1</v>
       </c>
     </row>
@@ -88222,7 +88380,7 @@
       <c r="A272" t="s">
         <v>115</v>
       </c>
-      <c r="B272" s="5">
+      <c r="B272" s="1">
         <v>46298</v>
       </c>
       <c r="C272" t="s">
@@ -88234,18 +88392,20 @@
       <c r="E272" t="s">
         <v>114</v>
       </c>
-      <c r="F272" s="4">
+      <c r="F272" s="2">
         <v>4867406.8</v>
       </c>
-      <c r="H272" s="4">
+      <c r="G272"/>
+      <c r="H272" s="2">
         <v>3815783.44</v>
       </c>
+      <c r="I272"/>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>115</v>
       </c>
-      <c r="B273" s="5">
+      <c r="B273" s="1">
         <v>46298</v>
       </c>
       <c r="C273" t="s">
@@ -88257,18 +88417,20 @@
       <c r="E273" t="s">
         <v>85</v>
       </c>
-      <c r="F273" s="4">
+      <c r="F273" s="2">
         <v>49707128.170000002</v>
       </c>
-      <c r="H273" s="4">
+      <c r="G273"/>
+      <c r="H273" s="2">
         <v>39065736.380000003</v>
       </c>
+      <c r="I273"/>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>115</v>
       </c>
-      <c r="B274" s="5">
+      <c r="B274" s="1">
         <v>46298</v>
       </c>
       <c r="C274" t="s">
@@ -88280,18 +88442,20 @@
       <c r="E274" t="s">
         <v>86</v>
       </c>
-      <c r="F274" s="4">
+      <c r="F274" s="2">
         <v>47685017.810000002</v>
       </c>
-      <c r="H274" s="4">
+      <c r="G274"/>
+      <c r="H274" s="2">
         <v>37893586.270000003</v>
       </c>
+      <c r="I274"/>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>115</v>
       </c>
-      <c r="B275" s="5">
+      <c r="B275" s="1">
         <v>46298</v>
       </c>
       <c r="C275" t="s">
@@ -88303,18 +88467,20 @@
       <c r="E275" t="s">
         <v>87</v>
       </c>
-      <c r="F275" s="4">
+      <c r="F275" s="2">
         <v>34808096.560000002</v>
       </c>
-      <c r="H275" s="4">
+      <c r="G275"/>
+      <c r="H275" s="2">
         <v>27385850.120000001</v>
       </c>
+      <c r="I275"/>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>115</v>
       </c>
-      <c r="B276" s="5">
+      <c r="B276" s="1">
         <v>46298</v>
       </c>
       <c r="C276" t="s">
@@ -88326,22 +88492,22 @@
       <c r="E276" t="s">
         <v>88</v>
       </c>
-      <c r="F276" s="4">
+      <c r="F276" s="2">
         <v>68054935.319999993</v>
       </c>
-      <c r="G276" s="4">
+      <c r="G276" s="2">
         <v>903872.64</v>
       </c>
-      <c r="H276" s="4">
+      <c r="H276" s="2">
         <v>53830409.960000001</v>
       </c>
-      <c r="I276" s="4">
+      <c r="I276" s="2">
         <v>721580.21</v>
       </c>
-      <c r="J276">
+      <c r="J276" s="3">
         <v>322.637</v>
       </c>
-      <c r="K276">
+      <c r="K276" s="3">
         <v>11</v>
       </c>
     </row>
@@ -88349,7 +88515,7 @@
       <c r="A277" t="s">
         <v>115</v>
       </c>
-      <c r="B277" s="5">
+      <c r="B277" s="1">
         <v>46298</v>
       </c>
       <c r="C277" t="s">
@@ -88361,18 +88527,20 @@
       <c r="E277" t="s">
         <v>89</v>
       </c>
-      <c r="F277" s="4">
+      <c r="F277" s="2">
         <v>59694482.350000001</v>
       </c>
-      <c r="H277" s="4">
+      <c r="G277"/>
+      <c r="H277" s="2">
         <v>46722720.159999996</v>
       </c>
+      <c r="I277"/>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>115</v>
       </c>
-      <c r="B278" s="5">
+      <c r="B278" s="1">
         <v>46298</v>
       </c>
       <c r="C278" t="s">
@@ -88384,18 +88552,20 @@
       <c r="E278" t="s">
         <v>90</v>
       </c>
-      <c r="F278" s="4">
+      <c r="F278" s="2">
         <v>48102459.920000002</v>
       </c>
-      <c r="H278" s="4">
+      <c r="G278"/>
+      <c r="H278" s="2">
         <v>37829384.869999997</v>
       </c>
+      <c r="I278"/>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>115</v>
       </c>
-      <c r="B279" s="5">
+      <c r="B279" s="1">
         <v>46298</v>
       </c>
       <c r="C279" t="s">
@@ -88407,22 +88577,22 @@
       <c r="E279" t="s">
         <v>91</v>
       </c>
-      <c r="F279" s="4">
+      <c r="F279" s="2">
         <v>353739521.47000003</v>
       </c>
-      <c r="G279" s="4">
+      <c r="G279" s="2">
         <v>25107902.460000001</v>
       </c>
-      <c r="H279" s="4">
+      <c r="H279" s="2">
         <v>280895183.18000001</v>
       </c>
-      <c r="I279" s="4">
+      <c r="I279" s="2">
         <v>19327704.710000001</v>
       </c>
-      <c r="J279">
+      <c r="J279" s="3">
         <v>6137.5129999999999</v>
       </c>
-      <c r="K279">
+      <c r="K279" s="3">
         <v>187</v>
       </c>
     </row>
@@ -88430,7 +88600,7 @@
       <c r="A280" t="s">
         <v>115</v>
       </c>
-      <c r="B280" s="5">
+      <c r="B280" s="1">
         <v>46298</v>
       </c>
       <c r="C280" t="s">
@@ -88442,22 +88612,22 @@
       <c r="E280" t="s">
         <v>92</v>
       </c>
-      <c r="F280" s="4">
+      <c r="F280" s="2">
         <v>194319692.40000001</v>
       </c>
-      <c r="G280" s="4">
+      <c r="G280" s="2">
         <v>13141775.5</v>
       </c>
-      <c r="H280" s="4">
+      <c r="H280" s="2">
         <v>152287467.65000001</v>
       </c>
-      <c r="I280" s="4">
+      <c r="I280" s="2">
         <v>10161305.84</v>
       </c>
-      <c r="J280">
+      <c r="J280" s="3">
         <v>3929.6860000000001</v>
       </c>
-      <c r="K280">
+      <c r="K280" s="3">
         <v>126</v>
       </c>
     </row>
@@ -88465,7 +88635,7 @@
       <c r="A281" t="s">
         <v>115</v>
       </c>
-      <c r="B281" s="5">
+      <c r="B281" s="1">
         <v>46298</v>
       </c>
       <c r="C281" t="s">
@@ -88477,22 +88647,22 @@
       <c r="E281" t="s">
         <v>93</v>
       </c>
-      <c r="F281" s="4">
+      <c r="F281" s="2">
         <v>203213620.56</v>
       </c>
-      <c r="G281" s="4">
+      <c r="G281" s="2">
         <v>12796960.52</v>
       </c>
-      <c r="H281" s="4">
+      <c r="H281" s="2">
         <v>159499309.84999999</v>
       </c>
-      <c r="I281" s="4">
+      <c r="I281" s="2">
         <v>9901876.9000000004</v>
       </c>
-      <c r="J281">
+      <c r="J281" s="3">
         <v>4485.768</v>
       </c>
-      <c r="K281">
+      <c r="K281" s="3">
         <v>124</v>
       </c>
     </row>
@@ -88500,7 +88670,7 @@
       <c r="A282" t="s">
         <v>115</v>
       </c>
-      <c r="B282" s="5">
+      <c r="B282" s="1">
         <v>46298</v>
       </c>
       <c r="C282" t="s">
@@ -88512,22 +88682,22 @@
       <c r="E282" t="s">
         <v>94</v>
       </c>
-      <c r="F282" s="4">
+      <c r="F282" s="2">
         <v>228107555.47999999</v>
       </c>
-      <c r="G282" s="4">
+      <c r="G282" s="2">
         <v>16481393.560000001</v>
       </c>
-      <c r="H282" s="4">
+      <c r="H282" s="2">
         <v>178986473.02000001</v>
       </c>
-      <c r="I282" s="4">
+      <c r="I282" s="2">
         <v>12808322.25</v>
       </c>
-      <c r="J282">
+      <c r="J282" s="3">
         <v>4986.8370000000004</v>
       </c>
-      <c r="K282">
+      <c r="K282" s="3">
         <v>116</v>
       </c>
     </row>
@@ -88535,7 +88705,7 @@
       <c r="A283" t="s">
         <v>115</v>
       </c>
-      <c r="B283" s="5">
+      <c r="B283" s="1">
         <v>46298</v>
       </c>
       <c r="C283" t="s">
@@ -88547,22 +88717,22 @@
       <c r="E283" t="s">
         <v>95</v>
       </c>
-      <c r="F283" s="4">
+      <c r="F283" s="2">
         <v>181050733.09</v>
       </c>
-      <c r="G283" s="4">
+      <c r="G283" s="2">
         <v>8790635.5899999999</v>
       </c>
-      <c r="H283" s="4">
+      <c r="H283" s="2">
         <v>141990761.08000001</v>
       </c>
-      <c r="I283" s="4">
+      <c r="I283" s="2">
         <v>6864352.7199999997</v>
       </c>
-      <c r="J283">
+      <c r="J283" s="3">
         <v>1798.6780000000001</v>
       </c>
-      <c r="K283">
+      <c r="K283" s="3">
         <v>67</v>
       </c>
     </row>
@@ -88570,7 +88740,7 @@
       <c r="A284" t="s">
         <v>115</v>
       </c>
-      <c r="B284" s="5">
+      <c r="B284" s="1">
         <v>46298</v>
       </c>
       <c r="C284" t="s">
@@ -88582,22 +88752,22 @@
       <c r="E284" t="s">
         <v>96</v>
       </c>
-      <c r="F284" s="4">
+      <c r="F284" s="2">
         <v>196180236.13</v>
       </c>
-      <c r="G284" s="4">
+      <c r="G284" s="2">
         <v>6542335.4400000004</v>
       </c>
-      <c r="H284" s="4">
+      <c r="H284" s="2">
         <v>153354560.59</v>
       </c>
-      <c r="I284" s="4">
+      <c r="I284" s="2">
         <v>5047170.9000000004</v>
       </c>
-      <c r="J284">
+      <c r="J284" s="3">
         <v>2315.5920000000001</v>
       </c>
-      <c r="K284">
+      <c r="K284" s="3">
         <v>55</v>
       </c>
     </row>
@@ -88605,7 +88775,7 @@
       <c r="A285" t="s">
         <v>115</v>
       </c>
-      <c r="B285" s="5">
+      <c r="B285" s="1">
         <v>46298</v>
       </c>
       <c r="C285" t="s">
@@ -88617,22 +88787,22 @@
       <c r="E285" t="s">
         <v>97</v>
       </c>
-      <c r="F285" s="4">
+      <c r="F285" s="2">
         <v>141846980.34</v>
       </c>
-      <c r="G285" s="4">
+      <c r="G285" s="2">
         <v>9012860.0399999991</v>
       </c>
-      <c r="H285" s="4">
+      <c r="H285" s="2">
         <v>111184671.02</v>
       </c>
-      <c r="I285" s="4">
+      <c r="I285" s="2">
         <v>6994437.5999999996</v>
       </c>
-      <c r="J285">
+      <c r="J285" s="3">
         <v>2804.308</v>
       </c>
-      <c r="K285">
+      <c r="K285" s="3">
         <v>59</v>
       </c>
     </row>
@@ -88640,7 +88810,7 @@
       <c r="A286" t="s">
         <v>115</v>
       </c>
-      <c r="B286" s="5">
+      <c r="B286" s="1">
         <v>46298</v>
       </c>
       <c r="C286" t="s">
@@ -88652,22 +88822,22 @@
       <c r="E286" t="s">
         <v>98</v>
       </c>
-      <c r="F286" s="4">
+      <c r="F286" s="2">
         <v>233984670.03999999</v>
       </c>
-      <c r="G286" s="4">
+      <c r="G286" s="2">
         <v>17459201.600000001</v>
       </c>
-      <c r="H286" s="4">
+      <c r="H286" s="2">
         <v>184671372.44</v>
       </c>
-      <c r="I286" s="4">
+      <c r="I286" s="2">
         <v>13379512.16</v>
       </c>
-      <c r="J286">
+      <c r="J286" s="3">
         <v>4908.2929999999997</v>
       </c>
-      <c r="K286">
+      <c r="K286" s="3">
         <v>150</v>
       </c>
     </row>
@@ -88675,7 +88845,7 @@
       <c r="A287" t="s">
         <v>115</v>
       </c>
-      <c r="B287" s="5">
+      <c r="B287" s="1">
         <v>46298</v>
       </c>
       <c r="C287" t="s">
@@ -88687,18 +88857,20 @@
       <c r="E287" t="s">
         <v>99</v>
       </c>
-      <c r="F287" s="4">
+      <c r="F287" s="2">
         <v>135889890.13999999</v>
       </c>
-      <c r="H287" s="4">
+      <c r="G287"/>
+      <c r="H287" s="2">
         <v>106934006.65000001</v>
       </c>
+      <c r="I287"/>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>115</v>
       </c>
-      <c r="B288" s="5">
+      <c r="B288" s="1">
         <v>46298</v>
       </c>
       <c r="C288" t="s">
@@ -88710,22 +88882,22 @@
       <c r="E288" t="s">
         <v>100</v>
       </c>
-      <c r="F288" s="4">
+      <c r="F288" s="2">
         <v>233744805.13</v>
       </c>
-      <c r="G288" s="4">
+      <c r="G288" s="2">
         <v>5450659.0199999996</v>
       </c>
-      <c r="H288" s="4">
+      <c r="H288" s="2">
         <v>183670667.77000001</v>
       </c>
-      <c r="I288" s="4">
+      <c r="I288" s="2">
         <v>4238773.6500000004</v>
       </c>
-      <c r="J288">
+      <c r="J288" s="3">
         <v>1759.5889999999999</v>
       </c>
-      <c r="K288">
+      <c r="K288" s="3">
         <v>46</v>
       </c>
     </row>
@@ -88733,7 +88905,7 @@
       <c r="A289" t="s">
         <v>115</v>
       </c>
-      <c r="B289" s="5">
+      <c r="B289" s="1">
         <v>46298</v>
       </c>
       <c r="C289" t="s">
@@ -88745,22 +88917,22 @@
       <c r="E289" t="s">
         <v>101</v>
       </c>
-      <c r="F289" s="4">
+      <c r="F289" s="2">
         <v>129217578.8</v>
       </c>
-      <c r="G289" s="4">
+      <c r="G289" s="2">
         <v>5192261.37</v>
       </c>
-      <c r="H289" s="4">
+      <c r="H289" s="2">
         <v>101878363.3</v>
       </c>
-      <c r="I289" s="4">
+      <c r="I289" s="2">
         <v>4064361.73</v>
       </c>
-      <c r="J289">
+      <c r="J289" s="3">
         <v>1662.87</v>
       </c>
-      <c r="K289">
+      <c r="K289" s="3">
         <v>57</v>
       </c>
     </row>
@@ -88768,7 +88940,7 @@
       <c r="A290" t="s">
         <v>115</v>
       </c>
-      <c r="B290" s="5">
+      <c r="B290" s="1">
         <v>46298</v>
       </c>
       <c r="C290" t="s">
@@ -88780,22 +88952,22 @@
       <c r="E290" t="s">
         <v>102</v>
       </c>
-      <c r="F290" s="4">
+      <c r="F290" s="2">
         <v>33060838.350000001</v>
       </c>
-      <c r="G290" s="4">
+      <c r="G290" s="2">
         <v>143820.39000000001</v>
       </c>
-      <c r="H290" s="4">
+      <c r="H290" s="2">
         <v>26094183.940000001</v>
       </c>
-      <c r="I290" s="4">
+      <c r="I290" s="2">
         <v>119639.92</v>
       </c>
-      <c r="J290">
+      <c r="J290" s="3">
         <v>21.222000000000001</v>
       </c>
-      <c r="K290">
+      <c r="K290" s="3">
         <v>2</v>
       </c>
     </row>
@@ -88803,7 +88975,7 @@
       <c r="A291" t="s">
         <v>115</v>
       </c>
-      <c r="B291" s="5">
+      <c r="B291" s="1">
         <v>46299</v>
       </c>
       <c r="C291" t="s">
@@ -88815,22 +88987,22 @@
       <c r="E291" t="s">
         <v>10</v>
       </c>
-      <c r="F291" s="4">
+      <c r="F291" s="2">
         <v>56814105.280000001</v>
       </c>
-      <c r="G291" s="4">
+      <c r="G291" s="2">
         <v>838783.9</v>
       </c>
-      <c r="H291" s="4">
+      <c r="H291" s="2">
         <v>44412514.939999998</v>
       </c>
-      <c r="I291" s="4">
+      <c r="I291" s="2">
         <v>636325.31000000006</v>
       </c>
-      <c r="J291">
+      <c r="J291" s="3">
         <v>114</v>
       </c>
-      <c r="K291">
+      <c r="K291" s="3">
         <v>8</v>
       </c>
     </row>
@@ -88838,7 +89010,7 @@
       <c r="A292" t="s">
         <v>115</v>
       </c>
-      <c r="B292" s="5">
+      <c r="B292" s="1">
         <v>46299</v>
       </c>
       <c r="C292" t="s">
@@ -88850,18 +89022,20 @@
       <c r="E292" t="s">
         <v>11</v>
       </c>
-      <c r="F292" s="4">
+      <c r="F292" s="2">
         <v>51309425.82</v>
       </c>
-      <c r="H292" s="4">
+      <c r="G292"/>
+      <c r="H292" s="2">
         <v>40167811.240000002</v>
       </c>
+      <c r="I292"/>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>115</v>
       </c>
-      <c r="B293" s="5">
+      <c r="B293" s="1">
         <v>46299</v>
       </c>
       <c r="C293" t="s">
@@ -88873,22 +89047,22 @@
       <c r="E293" t="s">
         <v>12</v>
       </c>
-      <c r="F293" s="4">
+      <c r="F293" s="2">
         <v>53587224.149999999</v>
       </c>
-      <c r="G293" s="4">
+      <c r="G293" s="2">
         <v>1169657.06</v>
       </c>
-      <c r="H293" s="4">
+      <c r="H293" s="2">
         <v>42277267.229999997</v>
       </c>
-      <c r="I293" s="4">
+      <c r="I293" s="2">
         <v>918904.47</v>
       </c>
-      <c r="J293">
+      <c r="J293" s="3">
         <v>305.53199999999998</v>
       </c>
-      <c r="K293">
+      <c r="K293" s="3">
         <v>12</v>
       </c>
     </row>
@@ -88896,7 +89070,7 @@
       <c r="A294" t="s">
         <v>115</v>
       </c>
-      <c r="B294" s="5">
+      <c r="B294" s="1">
         <v>46299</v>
       </c>
       <c r="C294" t="s">
@@ -88908,18 +89082,20 @@
       <c r="E294" t="s">
         <v>13</v>
       </c>
-      <c r="F294" s="4">
+      <c r="F294" s="2">
         <v>44794424.859999999</v>
       </c>
-      <c r="H294" s="4">
+      <c r="G294"/>
+      <c r="H294" s="2">
         <v>35352710.649999999</v>
       </c>
+      <c r="I294"/>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>115</v>
       </c>
-      <c r="B295" s="5">
+      <c r="B295" s="1">
         <v>46299</v>
       </c>
       <c r="C295" t="s">
@@ -88931,18 +89107,20 @@
       <c r="E295" t="s">
         <v>14</v>
       </c>
-      <c r="F295" s="4">
+      <c r="F295" s="2">
         <v>48738620.170000002</v>
       </c>
-      <c r="H295" s="4">
+      <c r="G295"/>
+      <c r="H295" s="2">
         <v>38150513.380000003</v>
       </c>
+      <c r="I295"/>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>115</v>
       </c>
-      <c r="B296" s="5">
+      <c r="B296" s="1">
         <v>46299</v>
       </c>
       <c r="C296" t="s">
@@ -88954,18 +89132,20 @@
       <c r="E296" t="s">
         <v>16</v>
       </c>
-      <c r="F296" s="4">
+      <c r="F296" s="2">
         <v>69158414.689999998</v>
       </c>
-      <c r="H296" s="4">
+      <c r="G296"/>
+      <c r="H296" s="2">
         <v>54343172.049999997</v>
       </c>
+      <c r="I296"/>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>115</v>
       </c>
-      <c r="B297" s="5">
+      <c r="B297" s="1">
         <v>46299</v>
       </c>
       <c r="C297" t="s">
@@ -88977,18 +89157,20 @@
       <c r="E297" t="s">
         <v>17</v>
       </c>
-      <c r="F297" s="4">
+      <c r="F297" s="2">
         <v>34705327.340000004</v>
       </c>
-      <c r="H297" s="4">
+      <c r="G297"/>
+      <c r="H297" s="2">
         <v>27212043.440000001</v>
       </c>
+      <c r="I297"/>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>115</v>
       </c>
-      <c r="B298" s="5">
+      <c r="B298" s="1">
         <v>46299</v>
       </c>
       <c r="C298" t="s">
@@ -89000,18 +89182,20 @@
       <c r="E298" t="s">
         <v>18</v>
       </c>
-      <c r="F298" s="4">
+      <c r="F298" s="2">
         <v>45716472.630000003</v>
       </c>
-      <c r="H298" s="4">
+      <c r="G298"/>
+      <c r="H298" s="2">
         <v>36555814.740000002</v>
       </c>
+      <c r="I298"/>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>115</v>
       </c>
-      <c r="B299" s="5">
+      <c r="B299" s="1">
         <v>46299</v>
       </c>
       <c r="C299" t="s">
@@ -89023,18 +89207,20 @@
       <c r="E299" t="s">
         <v>19</v>
       </c>
-      <c r="F299" s="4">
+      <c r="F299" s="2">
         <v>35131909.030000001</v>
       </c>
-      <c r="H299" s="4">
+      <c r="G299"/>
+      <c r="H299" s="2">
         <v>27533147.629999999</v>
       </c>
+      <c r="I299"/>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>115</v>
       </c>
-      <c r="B300" s="5">
+      <c r="B300" s="1">
         <v>46299</v>
       </c>
       <c r="C300" t="s">
@@ -89046,18 +89232,20 @@
       <c r="E300" t="s">
         <v>20</v>
       </c>
-      <c r="F300" s="4">
+      <c r="F300" s="2">
         <v>42923910.039999999</v>
       </c>
-      <c r="H300" s="4">
+      <c r="G300"/>
+      <c r="H300" s="2">
         <v>33838330.719999999</v>
       </c>
+      <c r="I300"/>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>115</v>
       </c>
-      <c r="B301" s="5">
+      <c r="B301" s="1">
         <v>46299</v>
       </c>
       <c r="C301" t="s">
@@ -89069,18 +89257,20 @@
       <c r="E301" t="s">
         <v>21</v>
       </c>
-      <c r="F301" s="4">
+      <c r="F301" s="2">
         <v>37800498.270000003</v>
       </c>
-      <c r="H301" s="4">
+      <c r="G301"/>
+      <c r="H301" s="2">
         <v>29650561.350000001</v>
       </c>
+      <c r="I301"/>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>115</v>
       </c>
-      <c r="B302" s="5">
+      <c r="B302" s="1">
         <v>46299</v>
       </c>
       <c r="C302" t="s">
@@ -89092,18 +89282,20 @@
       <c r="E302" t="s">
         <v>22</v>
       </c>
-      <c r="F302" s="4">
+      <c r="F302" s="2">
         <v>35087569.219999999</v>
       </c>
-      <c r="H302" s="4">
+      <c r="G302"/>
+      <c r="H302" s="2">
         <v>27570687.260000002</v>
       </c>
+      <c r="I302"/>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>115</v>
       </c>
-      <c r="B303" s="5">
+      <c r="B303" s="1">
         <v>46299</v>
       </c>
       <c r="C303" t="s">
@@ -89115,18 +89307,20 @@
       <c r="E303" t="s">
         <v>23</v>
       </c>
-      <c r="F303" s="4">
+      <c r="F303" s="2">
         <v>61908259.509999998</v>
       </c>
-      <c r="H303" s="4">
+      <c r="G303"/>
+      <c r="H303" s="2">
         <v>48501538.939999998</v>
       </c>
+      <c r="I303"/>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>115</v>
       </c>
-      <c r="B304" s="5">
+      <c r="B304" s="1">
         <v>46299</v>
       </c>
       <c r="C304" t="s">
@@ -89138,22 +89332,22 @@
       <c r="E304" t="s">
         <v>24</v>
       </c>
-      <c r="F304" s="4">
+      <c r="F304" s="2">
         <v>57380799.770000003</v>
       </c>
-      <c r="G304" s="4">
+      <c r="G304" s="2">
         <v>699999</v>
       </c>
-      <c r="H304" s="4">
+      <c r="H304" s="2">
         <v>44827338.140000001</v>
       </c>
-      <c r="I304" s="4">
+      <c r="I304" s="2">
         <v>542354.63</v>
       </c>
-      <c r="J304">
+      <c r="J304" s="3">
         <v>1</v>
       </c>
-      <c r="K304">
+      <c r="K304" s="3">
         <v>1</v>
       </c>
     </row>
@@ -89161,7 +89355,7 @@
       <c r="A305" t="s">
         <v>115</v>
       </c>
-      <c r="B305" s="5">
+      <c r="B305" s="1">
         <v>46299</v>
       </c>
       <c r="C305" t="s">
@@ -89173,22 +89367,22 @@
       <c r="E305" t="s">
         <v>25</v>
       </c>
-      <c r="F305" s="4">
+      <c r="F305" s="2">
         <v>29992610.789999999</v>
       </c>
-      <c r="G305" s="4">
+      <c r="G305" s="2">
         <v>104105.05</v>
       </c>
-      <c r="H305" s="4">
+      <c r="H305" s="2">
         <v>23574669.57</v>
       </c>
-      <c r="I305" s="4">
+      <c r="I305" s="2">
         <v>80887.320000000007</v>
       </c>
-      <c r="J305">
+      <c r="J305" s="3">
         <v>77</v>
       </c>
-      <c r="K305">
+      <c r="K305" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89196,7 +89390,7 @@
       <c r="A306" t="s">
         <v>115</v>
       </c>
-      <c r="B306" s="5">
+      <c r="B306" s="1">
         <v>46299</v>
       </c>
       <c r="C306" t="s">
@@ -89208,18 +89402,20 @@
       <c r="E306" t="s">
         <v>26</v>
       </c>
-      <c r="F306" s="4">
+      <c r="F306" s="2">
         <v>41685684.840000004</v>
       </c>
-      <c r="H306" s="4">
+      <c r="G306"/>
+      <c r="H306" s="2">
         <v>32874598.09</v>
       </c>
+      <c r="I306"/>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>115</v>
       </c>
-      <c r="B307" s="5">
+      <c r="B307" s="1">
         <v>46299</v>
       </c>
       <c r="C307" t="s">
@@ -89231,18 +89427,20 @@
       <c r="E307" t="s">
         <v>27</v>
       </c>
-      <c r="F307" s="4">
+      <c r="F307" s="2">
         <v>33124046.25</v>
       </c>
-      <c r="H307" s="4">
+      <c r="G307"/>
+      <c r="H307" s="2">
         <v>26085163.050000001</v>
       </c>
+      <c r="I307"/>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>115</v>
       </c>
-      <c r="B308" s="5">
+      <c r="B308" s="1">
         <v>46299</v>
       </c>
       <c r="C308" t="s">
@@ -89254,22 +89452,22 @@
       <c r="E308" t="s">
         <v>28</v>
       </c>
-      <c r="F308" s="4">
+      <c r="F308" s="2">
         <v>65247870.490000002</v>
       </c>
-      <c r="G308" s="4">
+      <c r="G308" s="2">
         <v>91668.5</v>
       </c>
-      <c r="H308" s="4">
+      <c r="H308" s="2">
         <v>51623501.490000002</v>
       </c>
-      <c r="I308" s="4">
+      <c r="I308" s="2">
         <v>77773.06</v>
       </c>
-      <c r="J308">
+      <c r="J308" s="3">
         <v>5.6479999999999997</v>
       </c>
-      <c r="K308">
+      <c r="K308" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89277,7 +89475,7 @@
       <c r="A309" t="s">
         <v>115</v>
       </c>
-      <c r="B309" s="5">
+      <c r="B309" s="1">
         <v>46299</v>
       </c>
       <c r="C309" t="s">
@@ -89289,22 +89487,22 @@
       <c r="E309" t="s">
         <v>30</v>
       </c>
-      <c r="F309" s="4">
+      <c r="F309" s="2">
         <v>64622392.539999999</v>
       </c>
-      <c r="G309" s="4">
+      <c r="G309" s="2">
         <v>559301.42000000004</v>
       </c>
-      <c r="H309" s="4">
+      <c r="H309" s="2">
         <v>50636690.57</v>
       </c>
-      <c r="I309" s="4">
+      <c r="I309" s="2">
         <v>433825.97</v>
       </c>
-      <c r="J309">
+      <c r="J309" s="3">
         <v>156</v>
       </c>
-      <c r="K309">
+      <c r="K309" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89312,7 +89510,7 @@
       <c r="A310" t="s">
         <v>115</v>
       </c>
-      <c r="B310" s="5">
+      <c r="B310" s="1">
         <v>46299</v>
       </c>
       <c r="C310" t="s">
@@ -89324,18 +89522,20 @@
       <c r="E310" t="s">
         <v>31</v>
       </c>
-      <c r="F310" s="4">
+      <c r="F310" s="2">
         <v>41591563.649999999</v>
       </c>
-      <c r="H310" s="4">
+      <c r="G310"/>
+      <c r="H310" s="2">
         <v>32859983.609999999</v>
       </c>
+      <c r="I310"/>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>115</v>
       </c>
-      <c r="B311" s="5">
+      <c r="B311" s="1">
         <v>46299</v>
       </c>
       <c r="C311" t="s">
@@ -89347,18 +89547,20 @@
       <c r="E311" t="s">
         <v>32</v>
       </c>
-      <c r="F311" s="4">
+      <c r="F311" s="2">
         <v>12369537.91</v>
       </c>
-      <c r="H311" s="4">
+      <c r="G311"/>
+      <c r="H311" s="2">
         <v>9823496</v>
       </c>
+      <c r="I311"/>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>115</v>
       </c>
-      <c r="B312" s="5">
+      <c r="B312" s="1">
         <v>46299</v>
       </c>
       <c r="C312" t="s">
@@ -89370,18 +89572,20 @@
       <c r="E312" t="s">
         <v>33</v>
       </c>
-      <c r="F312" s="4">
+      <c r="F312" s="2">
         <v>35378530.020000003</v>
       </c>
-      <c r="H312" s="4">
+      <c r="G312"/>
+      <c r="H312" s="2">
         <v>27862050.66</v>
       </c>
+      <c r="I312"/>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>115</v>
       </c>
-      <c r="B313" s="5">
+      <c r="B313" s="1">
         <v>46299</v>
       </c>
       <c r="C313" t="s">
@@ -89393,18 +89597,20 @@
       <c r="E313" t="s">
         <v>34</v>
       </c>
-      <c r="F313" s="4">
+      <c r="F313" s="2">
         <v>30459227.34</v>
       </c>
-      <c r="H313" s="4">
+      <c r="G313"/>
+      <c r="H313" s="2">
         <v>24066289.16</v>
       </c>
+      <c r="I313"/>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>115</v>
       </c>
-      <c r="B314" s="5">
+      <c r="B314" s="1">
         <v>46299</v>
       </c>
       <c r="C314" t="s">
@@ -89416,18 +89622,20 @@
       <c r="E314" t="s">
         <v>35</v>
       </c>
-      <c r="F314" s="4">
+      <c r="F314" s="2">
         <v>14788412.9</v>
       </c>
-      <c r="H314" s="4">
+      <c r="G314"/>
+      <c r="H314" s="2">
         <v>11752156.380000001</v>
       </c>
+      <c r="I314"/>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>115</v>
       </c>
-      <c r="B315" s="5">
+      <c r="B315" s="1">
         <v>46299</v>
       </c>
       <c r="C315" t="s">
@@ -89439,18 +89647,20 @@
       <c r="E315" t="s">
         <v>36</v>
       </c>
-      <c r="F315" s="4">
+      <c r="F315" s="2">
         <v>60911503.920000002</v>
       </c>
-      <c r="H315" s="4">
+      <c r="G315"/>
+      <c r="H315" s="2">
         <v>48608347.170000002</v>
       </c>
+      <c r="I315"/>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>115</v>
       </c>
-      <c r="B316" s="5">
+      <c r="B316" s="1">
         <v>46299</v>
       </c>
       <c r="C316" t="s">
@@ -89462,18 +89672,20 @@
       <c r="E316" t="s">
         <v>37</v>
       </c>
-      <c r="F316" s="4">
+      <c r="F316" s="2">
         <v>42173516.729999997</v>
       </c>
-      <c r="H316" s="4">
+      <c r="G316"/>
+      <c r="H316" s="2">
         <v>33203102.640000001</v>
       </c>
+      <c r="I316"/>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>115</v>
       </c>
-      <c r="B317" s="5">
+      <c r="B317" s="1">
         <v>46299</v>
       </c>
       <c r="C317" t="s">
@@ -89485,22 +89697,22 @@
       <c r="E317" t="s">
         <v>38</v>
       </c>
-      <c r="F317" s="4">
+      <c r="F317" s="2">
         <v>37427368.789999999</v>
       </c>
-      <c r="G317" s="4">
+      <c r="G317" s="2">
         <v>1064539.1499999999</v>
       </c>
-      <c r="H317" s="4">
+      <c r="H317" s="2">
         <v>29545466.859999999</v>
       </c>
-      <c r="I317" s="4">
+      <c r="I317" s="2">
         <v>827490.12</v>
       </c>
-      <c r="J317">
+      <c r="J317" s="3">
         <v>24</v>
       </c>
-      <c r="K317">
+      <c r="K317" s="3">
         <v>6</v>
       </c>
     </row>
@@ -89508,7 +89720,7 @@
       <c r="A318" t="s">
         <v>115</v>
       </c>
-      <c r="B318" s="5">
+      <c r="B318" s="1">
         <v>46299</v>
       </c>
       <c r="C318" t="s">
@@ -89520,22 +89732,22 @@
       <c r="E318" t="s">
         <v>39</v>
       </c>
-      <c r="F318" s="4">
+      <c r="F318" s="2">
         <v>25514009.050000001</v>
       </c>
-      <c r="G318" s="4">
+      <c r="G318" s="2">
         <v>-91413.75</v>
       </c>
-      <c r="H318" s="4">
+      <c r="H318" s="2">
         <v>20067749.219999999</v>
       </c>
-      <c r="I318" s="4">
+      <c r="I318" s="2">
         <v>-76951.820000000007</v>
       </c>
-      <c r="J318">
+      <c r="J318" s="3">
         <v>-7.2039999999999997</v>
       </c>
-      <c r="K318">
+      <c r="K318" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89543,7 +89755,7 @@
       <c r="A319" t="s">
         <v>115</v>
       </c>
-      <c r="B319" s="5">
+      <c r="B319" s="1">
         <v>46299</v>
       </c>
       <c r="C319" t="s">
@@ -89555,18 +89767,20 @@
       <c r="E319" t="s">
         <v>40</v>
       </c>
-      <c r="F319" s="4">
+      <c r="F319" s="2">
         <v>7037528.0899999999</v>
       </c>
-      <c r="H319" s="4">
+      <c r="G319"/>
+      <c r="H319" s="2">
         <v>5541309</v>
       </c>
+      <c r="I319"/>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>115</v>
       </c>
-      <c r="B320" s="5">
+      <c r="B320" s="1">
         <v>46299</v>
       </c>
       <c r="C320" t="s">
@@ -89578,22 +89792,22 @@
       <c r="E320" t="s">
         <v>43</v>
       </c>
-      <c r="F320" s="4">
+      <c r="F320" s="2">
         <v>45248968.32</v>
       </c>
-      <c r="G320" s="4">
+      <c r="G320" s="2">
         <v>2349998.19</v>
       </c>
-      <c r="H320" s="4">
+      <c r="H320" s="2">
         <v>35353148.369999997</v>
       </c>
-      <c r="I320" s="4">
+      <c r="I320" s="2">
         <v>1820763.07</v>
       </c>
-      <c r="J320">
+      <c r="J320" s="3">
         <v>2</v>
       </c>
-      <c r="K320">
+      <c r="K320" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89601,7 +89815,7 @@
       <c r="A321" t="s">
         <v>115</v>
       </c>
-      <c r="B321" s="5">
+      <c r="B321" s="1">
         <v>46299</v>
       </c>
       <c r="C321" t="s">
@@ -89613,22 +89827,22 @@
       <c r="E321" t="s">
         <v>44</v>
       </c>
-      <c r="F321" s="4">
+      <c r="F321" s="2">
         <v>35231703.619999997</v>
       </c>
-      <c r="G321" s="4">
+      <c r="G321" s="2">
         <v>350483.85</v>
       </c>
-      <c r="H321" s="4">
+      <c r="H321" s="2">
         <v>27873864.949999999</v>
       </c>
-      <c r="I321" s="4">
+      <c r="I321" s="2">
         <v>272899.42</v>
       </c>
-      <c r="J321">
+      <c r="J321" s="3">
         <v>26</v>
       </c>
-      <c r="K321">
+      <c r="K321" s="3">
         <v>3</v>
       </c>
     </row>
@@ -89636,7 +89850,7 @@
       <c r="A322" t="s">
         <v>115</v>
       </c>
-      <c r="B322" s="5">
+      <c r="B322" s="1">
         <v>46299</v>
       </c>
       <c r="C322" t="s">
@@ -89648,18 +89862,20 @@
       <c r="E322" t="s">
         <v>45</v>
       </c>
-      <c r="F322" s="4">
+      <c r="F322" s="2">
         <v>35830746</v>
       </c>
-      <c r="H322" s="4">
+      <c r="G322"/>
+      <c r="H322" s="2">
         <v>28124638.07</v>
       </c>
+      <c r="I322"/>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>115</v>
       </c>
-      <c r="B323" s="5">
+      <c r="B323" s="1">
         <v>46299</v>
       </c>
       <c r="C323" t="s">
@@ -89671,18 +89887,20 @@
       <c r="E323" t="s">
         <v>46</v>
       </c>
-      <c r="F323" s="4">
+      <c r="F323" s="2">
         <v>11122852.09</v>
       </c>
-      <c r="H323" s="4">
+      <c r="G323"/>
+      <c r="H323" s="2">
         <v>8747218.1799999997</v>
       </c>
+      <c r="I323"/>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>115</v>
       </c>
-      <c r="B324" s="5">
+      <c r="B324" s="1">
         <v>46299</v>
       </c>
       <c r="C324" t="s">
@@ -89694,18 +89912,20 @@
       <c r="E324" t="s">
         <v>47</v>
       </c>
-      <c r="F324" s="4">
+      <c r="F324" s="2">
         <v>10040423.449999999</v>
       </c>
-      <c r="H324" s="4">
+      <c r="G324"/>
+      <c r="H324" s="2">
         <v>7943015.4100000001</v>
       </c>
+      <c r="I324"/>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>115</v>
       </c>
-      <c r="B325" s="5">
+      <c r="B325" s="1">
         <v>46299</v>
       </c>
       <c r="C325" t="s">
@@ -89717,22 +89937,22 @@
       <c r="E325" t="s">
         <v>48</v>
       </c>
-      <c r="F325" s="4">
+      <c r="F325" s="2">
         <v>11010337.869999999</v>
       </c>
-      <c r="G325" s="4">
+      <c r="G325" s="2">
         <v>17760</v>
       </c>
-      <c r="H325" s="4">
+      <c r="H325" s="2">
         <v>8636093.3399999999</v>
       </c>
-      <c r="I325" s="4">
+      <c r="I325" s="2">
         <v>13760.32</v>
       </c>
-      <c r="J325">
+      <c r="J325" s="3">
         <v>8</v>
       </c>
-      <c r="K325">
+      <c r="K325" s="3">
         <v>1</v>
       </c>
     </row>
@@ -89740,7 +89960,7 @@
       <c r="A326" t="s">
         <v>115</v>
       </c>
-      <c r="B326" s="5">
+      <c r="B326" s="1">
         <v>46299</v>
       </c>
       <c r="C326" t="s">
@@ -89752,18 +89972,20 @@
       <c r="E326" t="s">
         <v>49</v>
       </c>
-      <c r="F326" s="4">
+      <c r="F326" s="2">
         <v>27527320.640000001</v>
       </c>
-      <c r="H326" s="4">
+      <c r="G326"/>
+      <c r="H326" s="2">
         <v>21481914.579999998</v>
       </c>
+      <c r="I326"/>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>115</v>
       </c>
-      <c r="B327" s="5">
+      <c r="B327" s="1">
         <v>46299</v>
       </c>
       <c r="C327" t="s">
@@ -89775,18 +89997,20 @@
       <c r="E327" t="s">
         <v>50</v>
       </c>
-      <c r="F327" s="4">
+      <c r="F327" s="2">
         <v>52388130.969999999</v>
       </c>
-      <c r="H327" s="4">
+      <c r="G327"/>
+      <c r="H327" s="2">
         <v>41749547.799999997</v>
       </c>
+      <c r="I327"/>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>115</v>
       </c>
-      <c r="B328" s="5">
+      <c r="B328" s="1">
         <v>46299</v>
       </c>
       <c r="C328" t="s">
@@ -89798,22 +90022,22 @@
       <c r="E328" t="s">
         <v>51</v>
       </c>
-      <c r="F328" s="4">
+      <c r="F328" s="2">
         <v>38850188.340000004</v>
       </c>
-      <c r="G328" s="4">
+      <c r="G328" s="2">
         <v>80790.5</v>
       </c>
-      <c r="H328" s="4">
+      <c r="H328" s="2">
         <v>31084626.989999998</v>
       </c>
-      <c r="I328" s="4">
+      <c r="I328" s="2">
         <v>68543.97</v>
       </c>
-      <c r="J328">
+      <c r="J328" s="3">
         <v>5.39</v>
       </c>
-      <c r="K328">
+      <c r="K328" s="3">
         <v>2</v>
       </c>
     </row>
@@ -89821,7 +90045,7 @@
       <c r="A329" t="s">
         <v>115</v>
       </c>
-      <c r="B329" s="5">
+      <c r="B329" s="1">
         <v>46299</v>
       </c>
       <c r="C329" t="s">
@@ -89833,18 +90057,20 @@
       <c r="E329" t="s">
         <v>52</v>
       </c>
-      <c r="F329" s="4">
+      <c r="F329" s="2">
         <v>31005651.460000001</v>
       </c>
-      <c r="H329" s="4">
+      <c r="G329"/>
+      <c r="H329" s="2">
         <v>24312870.510000002</v>
       </c>
+      <c r="I329"/>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>115</v>
       </c>
-      <c r="B330" s="5">
+      <c r="B330" s="1">
         <v>46299</v>
       </c>
       <c r="C330" t="s">
@@ -89856,18 +90082,20 @@
       <c r="E330" t="s">
         <v>53</v>
       </c>
-      <c r="F330" s="4">
+      <c r="F330" s="2">
         <v>32820384.309999999</v>
       </c>
-      <c r="H330" s="4">
+      <c r="G330"/>
+      <c r="H330" s="2">
         <v>25697133.859999999</v>
       </c>
+      <c r="I330"/>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>115</v>
       </c>
-      <c r="B331" s="5">
+      <c r="B331" s="1">
         <v>46299</v>
       </c>
       <c r="C331" t="s">
@@ -89879,18 +90107,20 @@
       <c r="E331" t="s">
         <v>54</v>
       </c>
-      <c r="F331" s="4">
+      <c r="F331" s="2">
         <v>28037072.550000001</v>
       </c>
-      <c r="H331" s="4">
+      <c r="G331"/>
+      <c r="H331" s="2">
         <v>22159882.57</v>
       </c>
+      <c r="I331"/>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>115</v>
       </c>
-      <c r="B332" s="5">
+      <c r="B332" s="1">
         <v>46299</v>
       </c>
       <c r="C332" t="s">
@@ -89902,18 +90132,20 @@
       <c r="E332" t="s">
         <v>55</v>
       </c>
-      <c r="F332" s="4">
+      <c r="F332" s="2">
         <v>25255417.02</v>
       </c>
-      <c r="H332" s="4">
+      <c r="G332"/>
+      <c r="H332" s="2">
         <v>19906621.489999998</v>
       </c>
+      <c r="I332"/>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>115</v>
       </c>
-      <c r="B333" s="5">
+      <c r="B333" s="1">
         <v>46299</v>
       </c>
       <c r="C333" t="s">
@@ -89925,18 +90157,20 @@
       <c r="E333" t="s">
         <v>56</v>
       </c>
-      <c r="F333" s="4">
+      <c r="F333" s="2">
         <v>59028340.719999999</v>
       </c>
-      <c r="H333" s="4">
+      <c r="G333"/>
+      <c r="H333" s="2">
         <v>46276457.460000001</v>
       </c>
+      <c r="I333"/>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>115</v>
       </c>
-      <c r="B334" s="5">
+      <c r="B334" s="1">
         <v>46299</v>
       </c>
       <c r="C334" t="s">
@@ -89948,18 +90182,20 @@
       <c r="E334" t="s">
         <v>57</v>
       </c>
-      <c r="F334" s="4">
+      <c r="F334" s="2">
         <v>42515591.869999997</v>
       </c>
-      <c r="H334" s="4">
+      <c r="G334"/>
+      <c r="H334" s="2">
         <v>33450122.280000001</v>
       </c>
+      <c r="I334"/>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>115</v>
       </c>
-      <c r="B335" s="5">
+      <c r="B335" s="1">
         <v>46299</v>
       </c>
       <c r="C335" t="s">
@@ -89971,18 +90207,20 @@
       <c r="E335" t="s">
         <v>58</v>
       </c>
-      <c r="F335" s="4">
+      <c r="F335" s="2">
         <v>35393171.619999997</v>
       </c>
-      <c r="H335" s="4">
+      <c r="G335"/>
+      <c r="H335" s="2">
         <v>27738379.699999999</v>
       </c>
+      <c r="I335"/>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>115</v>
       </c>
-      <c r="B336" s="5">
+      <c r="B336" s="1">
         <v>46299</v>
       </c>
       <c r="C336" t="s">
@@ -89994,18 +90232,20 @@
       <c r="E336" t="s">
         <v>59</v>
       </c>
-      <c r="F336" s="4">
+      <c r="F336" s="2">
         <v>26836684.539999999</v>
       </c>
-      <c r="H336" s="4">
+      <c r="G336"/>
+      <c r="H336" s="2">
         <v>21387515.27</v>
       </c>
+      <c r="I336"/>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>115</v>
       </c>
-      <c r="B337" s="5">
+      <c r="B337" s="1">
         <v>46299</v>
       </c>
       <c r="C337" t="s">
@@ -90017,18 +90257,20 @@
       <c r="E337" t="s">
         <v>60</v>
       </c>
-      <c r="F337" s="4">
+      <c r="F337" s="2">
         <v>31680730.289999999</v>
       </c>
-      <c r="H337" s="4">
+      <c r="G337"/>
+      <c r="H337" s="2">
         <v>24686024.780000001</v>
       </c>
+      <c r="I337"/>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>115</v>
       </c>
-      <c r="B338" s="5">
+      <c r="B338" s="1">
         <v>46299</v>
       </c>
       <c r="C338" t="s">
@@ -90040,18 +90282,20 @@
       <c r="E338" t="s">
         <v>111</v>
       </c>
-      <c r="F338" s="4">
+      <c r="F338" s="2">
         <v>2188836.2599999998</v>
       </c>
-      <c r="H338" s="4">
+      <c r="G338"/>
+      <c r="H338" s="2">
         <v>1706732.36</v>
       </c>
+      <c r="I338"/>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>115</v>
       </c>
-      <c r="B339" s="5">
+      <c r="B339" s="1">
         <v>46299</v>
       </c>
       <c r="C339" t="s">
@@ -90063,22 +90307,22 @@
       <c r="E339" t="s">
         <v>61</v>
       </c>
-      <c r="F339" s="4">
+      <c r="F339" s="2">
         <v>26443154.73</v>
       </c>
-      <c r="G339" s="4">
+      <c r="G339" s="2">
         <v>141823.20000000001</v>
       </c>
-      <c r="H339" s="4">
+      <c r="H339" s="2">
         <v>20763552</v>
       </c>
-      <c r="I339" s="4">
+      <c r="I339" s="2">
         <v>109883.52</v>
       </c>
-      <c r="J339">
+      <c r="J339" s="3">
         <v>48</v>
       </c>
-      <c r="K339">
+      <c r="K339" s="3">
         <v>2</v>
       </c>
     </row>
@@ -90086,7 +90330,7 @@
       <c r="A340" t="s">
         <v>115</v>
       </c>
-      <c r="B340" s="5">
+      <c r="B340" s="1">
         <v>46299</v>
       </c>
       <c r="C340" t="s">
@@ -90098,18 +90342,20 @@
       <c r="E340" t="s">
         <v>62</v>
       </c>
-      <c r="F340" s="4">
+      <c r="F340" s="2">
         <v>49461759.57</v>
       </c>
-      <c r="H340" s="4">
+      <c r="G340"/>
+      <c r="H340" s="2">
         <v>38915429.170000002</v>
       </c>
+      <c r="I340"/>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>115</v>
       </c>
-      <c r="B341" s="5">
+      <c r="B341" s="1">
         <v>46299</v>
       </c>
       <c r="C341" t="s">
@@ -90121,18 +90367,20 @@
       <c r="E341" t="s">
         <v>63</v>
       </c>
-      <c r="F341" s="4">
+      <c r="F341" s="2">
         <v>19877881.280000001</v>
       </c>
-      <c r="H341" s="4">
+      <c r="G341"/>
+      <c r="H341" s="2">
         <v>15555791.380000001</v>
       </c>
+      <c r="I341"/>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>115</v>
       </c>
-      <c r="B342" s="5">
+      <c r="B342" s="1">
         <v>46299</v>
       </c>
       <c r="C342" t="s">
@@ -90144,18 +90392,20 @@
       <c r="E342" t="s">
         <v>64</v>
       </c>
-      <c r="F342" s="4">
+      <c r="F342" s="2">
         <v>40937563.829999998</v>
       </c>
-      <c r="H342" s="4">
+      <c r="G342"/>
+      <c r="H342" s="2">
         <v>32592393.859999999</v>
       </c>
+      <c r="I342"/>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>115</v>
       </c>
-      <c r="B343" s="5">
+      <c r="B343" s="1">
         <v>46299</v>
       </c>
       <c r="C343" t="s">
@@ -90167,18 +90417,20 @@
       <c r="E343" t="s">
         <v>65</v>
       </c>
-      <c r="F343" s="4">
+      <c r="F343" s="2">
         <v>36486712.670000002</v>
       </c>
-      <c r="H343" s="4">
+      <c r="G343"/>
+      <c r="H343" s="2">
         <v>28766577.93</v>
       </c>
+      <c r="I343"/>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>115</v>
       </c>
-      <c r="B344" s="5">
+      <c r="B344" s="1">
         <v>46299</v>
       </c>
       <c r="C344" t="s">
@@ -90190,22 +90442,22 @@
       <c r="E344" t="s">
         <v>67</v>
       </c>
-      <c r="F344" s="4">
+      <c r="F344" s="2">
         <v>44401623.740000002</v>
       </c>
-      <c r="G344" s="4">
+      <c r="G344" s="2">
         <v>129382.78</v>
       </c>
-      <c r="H344" s="4">
+      <c r="H344" s="2">
         <v>35335077.259999998</v>
       </c>
-      <c r="I344" s="4">
+      <c r="I344" s="2">
         <v>96370.84</v>
       </c>
-      <c r="J344">
+      <c r="J344" s="3">
         <v>70</v>
       </c>
-      <c r="K344">
+      <c r="K344" s="3">
         <v>1</v>
       </c>
     </row>
@@ -90213,7 +90465,7 @@
       <c r="A345" t="s">
         <v>115</v>
       </c>
-      <c r="B345" s="5">
+      <c r="B345" s="1">
         <v>46299</v>
       </c>
       <c r="C345" t="s">
@@ -90225,18 +90477,20 @@
       <c r="E345" t="s">
         <v>68</v>
       </c>
-      <c r="F345" s="4">
+      <c r="F345" s="2">
         <v>37740036.829999998</v>
       </c>
-      <c r="H345" s="4">
+      <c r="G345"/>
+      <c r="H345" s="2">
         <v>29560958.120000001</v>
       </c>
+      <c r="I345"/>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>115</v>
       </c>
-      <c r="B346" s="5">
+      <c r="B346" s="1">
         <v>46299</v>
       </c>
       <c r="C346" t="s">
@@ -90248,18 +90502,20 @@
       <c r="E346" t="s">
         <v>69</v>
       </c>
-      <c r="F346" s="4">
+      <c r="F346" s="2">
         <v>26374265.920000002</v>
       </c>
-      <c r="H346" s="4">
+      <c r="G346"/>
+      <c r="H346" s="2">
         <v>20616714.949999999</v>
       </c>
+      <c r="I346"/>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>115</v>
       </c>
-      <c r="B347" s="5">
+      <c r="B347" s="1">
         <v>46299</v>
       </c>
       <c r="C347" t="s">
@@ -90271,18 +90527,20 @@
       <c r="E347" t="s">
         <v>70</v>
       </c>
-      <c r="F347" s="4">
+      <c r="F347" s="2">
         <v>16240307.5</v>
       </c>
-      <c r="H347" s="4">
+      <c r="G347"/>
+      <c r="H347" s="2">
         <v>12906928.85</v>
       </c>
+      <c r="I347"/>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>115</v>
       </c>
-      <c r="B348" s="5">
+      <c r="B348" s="1">
         <v>46299</v>
       </c>
       <c r="C348" t="s">
@@ -90294,22 +90552,22 @@
       <c r="E348" t="s">
         <v>71</v>
       </c>
-      <c r="F348" s="4">
+      <c r="F348" s="2">
         <v>11798441.529999999</v>
       </c>
-      <c r="G348" s="4">
+      <c r="G348" s="2">
         <v>348895.52</v>
       </c>
-      <c r="H348" s="4">
+      <c r="H348" s="2">
         <v>9375503.3900000006</v>
       </c>
-      <c r="I348" s="4">
+      <c r="I348" s="2">
         <v>271878.39</v>
       </c>
-      <c r="J348">
+      <c r="J348" s="3">
         <v>109.006</v>
       </c>
-      <c r="K348">
+      <c r="K348" s="3">
         <v>2</v>
       </c>
     </row>
@@ -90317,7 +90575,7 @@
       <c r="A349" t="s">
         <v>115</v>
       </c>
-      <c r="B349" s="5">
+      <c r="B349" s="1">
         <v>46299</v>
       </c>
       <c r="C349" t="s">
@@ -90329,18 +90587,20 @@
       <c r="E349" t="s">
         <v>72</v>
       </c>
-      <c r="F349" s="4">
+      <c r="F349" s="2">
         <v>24959945.800000001</v>
       </c>
-      <c r="H349" s="4">
+      <c r="G349"/>
+      <c r="H349" s="2">
         <v>19746182.57</v>
       </c>
+      <c r="I349"/>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>115</v>
       </c>
-      <c r="B350" s="5">
+      <c r="B350" s="1">
         <v>46299</v>
       </c>
       <c r="C350" t="s">
@@ -90352,18 +90612,20 @@
       <c r="E350" t="s">
         <v>73</v>
       </c>
-      <c r="F350" s="4">
+      <c r="F350" s="2">
         <v>43502093.960000001</v>
       </c>
-      <c r="H350" s="4">
+      <c r="G350"/>
+      <c r="H350" s="2">
         <v>34040828.579999998</v>
       </c>
+      <c r="I350"/>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>115</v>
       </c>
-      <c r="B351" s="5">
+      <c r="B351" s="1">
         <v>46299</v>
       </c>
       <c r="C351" t="s">
@@ -90375,22 +90637,22 @@
       <c r="E351" t="s">
         <v>74</v>
       </c>
-      <c r="F351" s="4">
+      <c r="F351" s="2">
         <v>39019238.280000001</v>
       </c>
-      <c r="G351" s="4">
+      <c r="G351" s="2">
         <v>-270736.64000000001</v>
       </c>
-      <c r="H351" s="4">
+      <c r="H351" s="2">
         <v>30807632.109999999</v>
       </c>
-      <c r="I351" s="4">
+      <c r="I351" s="2">
         <v>-212350.8</v>
       </c>
-      <c r="J351">
+      <c r="J351" s="3">
         <v>-113.946</v>
       </c>
-      <c r="K351">
+      <c r="K351" s="3">
         <v>2</v>
       </c>
     </row>
@@ -90398,7 +90660,7 @@
       <c r="A352" t="s">
         <v>115</v>
       </c>
-      <c r="B352" s="5">
+      <c r="B352" s="1">
         <v>46299</v>
       </c>
       <c r="C352" t="s">
@@ -90410,18 +90672,20 @@
       <c r="E352" t="s">
         <v>75</v>
       </c>
-      <c r="F352" s="4">
+      <c r="F352" s="2">
         <v>30834044.75</v>
       </c>
-      <c r="H352" s="4">
+      <c r="G352"/>
+      <c r="H352" s="2">
         <v>24094777.57</v>
       </c>
+      <c r="I352"/>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>115</v>
       </c>
-      <c r="B353" s="5">
+      <c r="B353" s="1">
         <v>46299</v>
       </c>
       <c r="C353" t="s">
@@ -90433,18 +90697,20 @@
       <c r="E353" t="s">
         <v>76</v>
       </c>
-      <c r="F353" s="4">
+      <c r="F353" s="2">
         <v>35853797.229999997</v>
       </c>
-      <c r="H353" s="4">
+      <c r="G353"/>
+      <c r="H353" s="2">
         <v>28147303.640000001</v>
       </c>
+      <c r="I353"/>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>115</v>
       </c>
-      <c r="B354" s="5">
+      <c r="B354" s="1">
         <v>46299</v>
       </c>
       <c r="C354" t="s">
@@ -90456,18 +90722,20 @@
       <c r="E354" t="s">
         <v>77</v>
       </c>
-      <c r="F354" s="4">
+      <c r="F354" s="2">
         <v>41159709.689999998</v>
       </c>
-      <c r="H354" s="4">
+      <c r="G354"/>
+      <c r="H354" s="2">
         <v>32381413.329999998</v>
       </c>
+      <c r="I354"/>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>115</v>
       </c>
-      <c r="B355" s="5">
+      <c r="B355" s="1">
         <v>46299</v>
       </c>
       <c r="C355" t="s">
@@ -90479,18 +90747,20 @@
       <c r="E355" t="s">
         <v>78</v>
       </c>
-      <c r="F355" s="4">
+      <c r="F355" s="2">
         <v>42170899.229999997</v>
       </c>
-      <c r="H355" s="4">
+      <c r="G355"/>
+      <c r="H355" s="2">
         <v>33082289.34</v>
       </c>
+      <c r="I355"/>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>115</v>
       </c>
-      <c r="B356" s="5">
+      <c r="B356" s="1">
         <v>46299</v>
       </c>
       <c r="C356" t="s">
@@ -90502,18 +90772,20 @@
       <c r="E356" t="s">
         <v>79</v>
       </c>
-      <c r="F356" s="4">
+      <c r="F356" s="2">
         <v>29832267.43</v>
       </c>
-      <c r="H356" s="4">
+      <c r="G356"/>
+      <c r="H356" s="2">
         <v>23495781.199999999</v>
       </c>
+      <c r="I356"/>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>115</v>
       </c>
-      <c r="B357" s="5">
+      <c r="B357" s="1">
         <v>46299</v>
       </c>
       <c r="C357" t="s">
@@ -90525,18 +90797,20 @@
       <c r="E357" t="s">
         <v>81</v>
       </c>
-      <c r="F357" s="4">
+      <c r="F357" s="2">
         <v>55080034.060000002</v>
       </c>
-      <c r="H357" s="4">
+      <c r="G357"/>
+      <c r="H357" s="2">
         <v>43934659.759999998</v>
       </c>
+      <c r="I357"/>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>115</v>
       </c>
-      <c r="B358" s="5">
+      <c r="B358" s="1">
         <v>46299</v>
       </c>
       <c r="C358" t="s">
@@ -90548,18 +90822,20 @@
       <c r="E358" t="s">
         <v>112</v>
       </c>
-      <c r="F358" s="4">
+      <c r="F358" s="2">
         <v>2225052.1</v>
       </c>
-      <c r="H358" s="4">
+      <c r="G358"/>
+      <c r="H358" s="2">
         <v>1746479.75</v>
       </c>
+      <c r="I358"/>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>115</v>
       </c>
-      <c r="B359" s="5">
+      <c r="B359" s="1">
         <v>46299</v>
       </c>
       <c r="C359" t="s">
@@ -90571,18 +90847,20 @@
       <c r="E359" t="s">
         <v>83</v>
       </c>
-      <c r="F359" s="4">
+      <c r="F359" s="2">
         <v>21686687.32</v>
       </c>
-      <c r="H359" s="4">
+      <c r="G359"/>
+      <c r="H359" s="2">
         <v>17207597.199999999</v>
       </c>
+      <c r="I359"/>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>115</v>
       </c>
-      <c r="B360" s="5">
+      <c r="B360" s="1">
         <v>46299</v>
       </c>
       <c r="C360" t="s">
@@ -90594,18 +90872,20 @@
       <c r="E360" t="s">
         <v>84</v>
       </c>
-      <c r="F360" s="4">
+      <c r="F360" s="2">
         <v>38512381.509999998</v>
       </c>
-      <c r="H360" s="4">
+      <c r="G360"/>
+      <c r="H360" s="2">
         <v>30229136.350000001</v>
       </c>
+      <c r="I360"/>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>115</v>
       </c>
-      <c r="B361" s="5">
+      <c r="B361" s="1">
         <v>46299</v>
       </c>
       <c r="C361" t="s">
@@ -90617,18 +90897,20 @@
       <c r="E361" t="s">
         <v>114</v>
       </c>
-      <c r="F361" s="4">
+      <c r="F361" s="2">
         <v>3244168.22</v>
       </c>
-      <c r="H361" s="4">
+      <c r="G361"/>
+      <c r="H361" s="2">
         <v>2548086.41</v>
       </c>
+      <c r="I361"/>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>115</v>
       </c>
-      <c r="B362" s="5">
+      <c r="B362" s="1">
         <v>46299</v>
       </c>
       <c r="C362" t="s">
@@ -90640,18 +90922,20 @@
       <c r="E362" t="s">
         <v>85</v>
       </c>
-      <c r="F362" s="4">
+      <c r="F362" s="2">
         <v>23524673.309999999</v>
       </c>
-      <c r="H362" s="4">
+      <c r="G362"/>
+      <c r="H362" s="2">
         <v>18553267.75</v>
       </c>
+      <c r="I362"/>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>115</v>
       </c>
-      <c r="B363" s="5">
+      <c r="B363" s="1">
         <v>46299</v>
       </c>
       <c r="C363" t="s">
@@ -90663,22 +90947,22 @@
       <c r="E363" t="s">
         <v>86</v>
       </c>
-      <c r="F363" s="4">
+      <c r="F363" s="2">
         <v>29154198.280000001</v>
       </c>
-      <c r="G363" s="4">
+      <c r="G363" s="2">
         <v>1909997.38</v>
       </c>
-      <c r="H363" s="4">
+      <c r="H363" s="2">
         <v>23169010.52</v>
       </c>
-      <c r="I363" s="4">
+      <c r="I363" s="2">
         <v>1479853.35</v>
       </c>
-      <c r="J363">
+      <c r="J363" s="3">
         <v>3</v>
       </c>
-      <c r="K363">
+      <c r="K363" s="3">
         <v>3</v>
       </c>
     </row>
@@ -90686,7 +90970,7 @@
       <c r="A364" t="s">
         <v>115</v>
       </c>
-      <c r="B364" s="5">
+      <c r="B364" s="1">
         <v>46299</v>
       </c>
       <c r="C364" t="s">
@@ -90698,18 +90982,20 @@
       <c r="E364" t="s">
         <v>87</v>
       </c>
-      <c r="F364" s="4">
+      <c r="F364" s="2">
         <v>21747983.059999999</v>
       </c>
-      <c r="H364" s="4">
+      <c r="G364"/>
+      <c r="H364" s="2">
         <v>17118912.050000001</v>
       </c>
+      <c r="I364"/>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>115</v>
       </c>
-      <c r="B365" s="5">
+      <c r="B365" s="1">
         <v>46299</v>
       </c>
       <c r="C365" t="s">
@@ -90721,18 +91007,20 @@
       <c r="E365" t="s">
         <v>88</v>
       </c>
-      <c r="F365" s="4">
+      <c r="F365" s="2">
         <v>30771703.93</v>
       </c>
-      <c r="H365" s="4">
+      <c r="G365"/>
+      <c r="H365" s="2">
         <v>24362370.09</v>
       </c>
+      <c r="I365"/>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>115</v>
       </c>
-      <c r="B366" s="5">
+      <c r="B366" s="1">
         <v>46299</v>
       </c>
       <c r="C366" t="s">
@@ -90744,18 +91032,20 @@
       <c r="E366" t="s">
         <v>89</v>
       </c>
-      <c r="F366" s="4">
+      <c r="F366" s="2">
         <v>31659307.289999999</v>
       </c>
-      <c r="H366" s="4">
+      <c r="G366"/>
+      <c r="H366" s="2">
         <v>24922705.489999998</v>
       </c>
+      <c r="I366"/>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>115</v>
       </c>
-      <c r="B367" s="5">
+      <c r="B367" s="1">
         <v>46299</v>
       </c>
       <c r="C367" t="s">
@@ -90767,18 +91057,20 @@
       <c r="E367" t="s">
         <v>90</v>
       </c>
-      <c r="F367" s="4">
+      <c r="F367" s="2">
         <v>30806777.260000002</v>
       </c>
-      <c r="H367" s="4">
+      <c r="G367"/>
+      <c r="H367" s="2">
         <v>24195790.579999998</v>
       </c>
+      <c r="I367"/>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>115</v>
       </c>
-      <c r="B368" s="5">
+      <c r="B368" s="1">
         <v>46299</v>
       </c>
       <c r="C368" t="s">
@@ -90790,22 +91082,22 @@
       <c r="E368" t="s">
         <v>91</v>
       </c>
-      <c r="F368" s="4">
+      <c r="F368" s="2">
         <v>167121641.97</v>
       </c>
-      <c r="G368" s="4">
+      <c r="G368" s="2">
         <v>4623692.3</v>
       </c>
-      <c r="H368" s="4">
+      <c r="H368" s="2">
         <v>132927864.36</v>
       </c>
-      <c r="I368" s="4">
+      <c r="I368" s="2">
         <v>3595846.91</v>
       </c>
-      <c r="J368">
+      <c r="J368" s="3">
         <v>1674.242</v>
       </c>
-      <c r="K368">
+      <c r="K368" s="3">
         <v>54</v>
       </c>
     </row>
@@ -90813,7 +91105,7 @@
       <c r="A369" t="s">
         <v>115</v>
       </c>
-      <c r="B369" s="5">
+      <c r="B369" s="1">
         <v>46299</v>
       </c>
       <c r="C369" t="s">
@@ -90825,22 +91117,22 @@
       <c r="E369" t="s">
         <v>92</v>
       </c>
-      <c r="F369" s="4">
+      <c r="F369" s="2">
         <v>89086672.769999996</v>
       </c>
-      <c r="G369" s="4">
+      <c r="G369" s="2">
         <v>4549077.72</v>
       </c>
-      <c r="H369" s="4">
+      <c r="H369" s="2">
         <v>69796426.730000004</v>
       </c>
-      <c r="I369" s="4">
+      <c r="I369" s="2">
         <v>3495796.8</v>
       </c>
-      <c r="J369">
+      <c r="J369" s="3">
         <v>1680.7460000000001</v>
       </c>
-      <c r="K369">
+      <c r="K369" s="3">
         <v>39</v>
       </c>
     </row>
@@ -90848,7 +91140,7 @@
       <c r="A370" t="s">
         <v>115</v>
       </c>
-      <c r="B370" s="5">
+      <c r="B370" s="1">
         <v>46299</v>
       </c>
       <c r="C370" t="s">
@@ -90860,22 +91152,22 @@
       <c r="E370" t="s">
         <v>93</v>
       </c>
-      <c r="F370" s="4">
+      <c r="F370" s="2">
         <v>82927643.439999998</v>
       </c>
-      <c r="G370" s="4">
+      <c r="G370" s="2">
         <v>-62311.4</v>
       </c>
-      <c r="H370" s="4">
+      <c r="H370" s="2">
         <v>65118422.829999998</v>
       </c>
-      <c r="I370" s="4">
+      <c r="I370" s="2">
         <v>-48278.47</v>
       </c>
-      <c r="J370">
+      <c r="J370" s="3">
         <v>-12</v>
       </c>
-      <c r="K370">
+      <c r="K370" s="3">
         <v>2</v>
       </c>
     </row>
@@ -90883,7 +91175,7 @@
       <c r="A371" t="s">
         <v>115</v>
       </c>
-      <c r="B371" s="5">
+      <c r="B371" s="1">
         <v>46299</v>
       </c>
       <c r="C371" t="s">
@@ -90895,22 +91187,22 @@
       <c r="E371" t="s">
         <v>94</v>
       </c>
-      <c r="F371" s="4">
+      <c r="F371" s="2">
         <v>82409222.659999996</v>
       </c>
-      <c r="G371" s="4">
+      <c r="G371" s="2">
         <v>2314932.9900000002</v>
       </c>
-      <c r="H371" s="4">
+      <c r="H371" s="2">
         <v>64350092.729999997</v>
       </c>
-      <c r="I371" s="4">
+      <c r="I371" s="2">
         <v>1789502.88</v>
       </c>
-      <c r="J371">
+      <c r="J371" s="3">
         <v>826.303</v>
       </c>
-      <c r="K371">
+      <c r="K371" s="3">
         <v>28</v>
       </c>
     </row>
@@ -90918,7 +91210,7 @@
       <c r="A372" t="s">
         <v>115</v>
       </c>
-      <c r="B372" s="5">
+      <c r="B372" s="1">
         <v>46299</v>
       </c>
       <c r="C372" t="s">
@@ -90930,18 +91222,20 @@
       <c r="E372" t="s">
         <v>95</v>
       </c>
-      <c r="F372" s="4">
+      <c r="F372" s="2">
         <v>66582009.799999997</v>
       </c>
-      <c r="H372" s="4">
+      <c r="G372"/>
+      <c r="H372" s="2">
         <v>52318261.649999999</v>
       </c>
+      <c r="I372"/>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>115</v>
       </c>
-      <c r="B373" s="5">
+      <c r="B373" s="1">
         <v>46299</v>
       </c>
       <c r="C373" t="s">
@@ -90953,18 +91247,20 @@
       <c r="E373" t="s">
         <v>96</v>
       </c>
-      <c r="F373" s="4">
+      <c r="F373" s="2">
         <v>89083836.430000007</v>
       </c>
-      <c r="H373" s="4">
+      <c r="G373"/>
+      <c r="H373" s="2">
         <v>69683934.329999998</v>
       </c>
+      <c r="I373"/>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>115</v>
       </c>
-      <c r="B374" s="5">
+      <c r="B374" s="1">
         <v>46299</v>
       </c>
       <c r="C374" t="s">
@@ -90976,18 +91272,20 @@
       <c r="E374" t="s">
         <v>97</v>
       </c>
-      <c r="F374" s="4">
+      <c r="F374" s="2">
         <v>61991084.530000001</v>
       </c>
-      <c r="H374" s="4">
+      <c r="G374"/>
+      <c r="H374" s="2">
         <v>48628458.939999998</v>
       </c>
+      <c r="I374"/>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>115</v>
       </c>
-      <c r="B375" s="5">
+      <c r="B375" s="1">
         <v>46299</v>
       </c>
       <c r="C375" t="s">
@@ -90999,18 +91297,20 @@
       <c r="E375" t="s">
         <v>98</v>
       </c>
-      <c r="F375" s="4">
+      <c r="F375" s="2">
         <v>108259870.11</v>
       </c>
-      <c r="H375" s="4">
+      <c r="G375"/>
+      <c r="H375" s="2">
         <v>85499091.989999995</v>
       </c>
+      <c r="I375"/>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>115</v>
       </c>
-      <c r="B376" s="5">
+      <c r="B376" s="1">
         <v>46299</v>
       </c>
       <c r="C376" t="s">
@@ -91022,18 +91322,20 @@
       <c r="E376" t="s">
         <v>99</v>
       </c>
-      <c r="F376" s="4">
+      <c r="F376" s="2">
         <v>75660184.219999999</v>
       </c>
-      <c r="H376" s="4">
+      <c r="G376"/>
+      <c r="H376" s="2">
         <v>59621704.700000003</v>
       </c>
+      <c r="I376"/>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>115</v>
       </c>
-      <c r="B377" s="5">
+      <c r="B377" s="1">
         <v>46299</v>
       </c>
       <c r="C377" t="s">
@@ -91045,22 +91347,22 @@
       <c r="E377" t="s">
         <v>100</v>
       </c>
-      <c r="F377" s="4">
+      <c r="F377" s="2">
         <v>96443670.099999994</v>
       </c>
-      <c r="G377" s="4">
+      <c r="G377" s="2">
         <v>1016637.9</v>
       </c>
-      <c r="H377" s="4">
+      <c r="H377" s="2">
         <v>75691404.650000006</v>
       </c>
-      <c r="I377" s="4">
+      <c r="I377" s="2">
         <v>791361.49</v>
       </c>
-      <c r="J377">
+      <c r="J377" s="3">
         <v>363.69799999999998</v>
       </c>
-      <c r="K377">
+      <c r="K377" s="3">
         <v>14</v>
       </c>
     </row>
@@ -91068,7 +91370,7 @@
       <c r="A378" t="s">
         <v>115</v>
       </c>
-      <c r="B378" s="5">
+      <c r="B378" s="1">
         <v>46299</v>
       </c>
       <c r="C378" t="s">
@@ -91080,18 +91382,20 @@
       <c r="E378" t="s">
         <v>101</v>
       </c>
-      <c r="F378" s="4">
+      <c r="F378" s="2">
         <v>53152539.5</v>
       </c>
-      <c r="H378" s="4">
+      <c r="G378"/>
+      <c r="H378" s="2">
         <v>41882872.640000001</v>
       </c>
+      <c r="I378"/>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>115</v>
       </c>
-      <c r="B379" s="5">
+      <c r="B379" s="1">
         <v>46299</v>
       </c>
       <c r="C379" t="s">
@@ -91103,12 +91407,14 @@
       <c r="E379" t="s">
         <v>102</v>
       </c>
-      <c r="F379" s="4">
+      <c r="F379" s="2">
         <v>13226017.810000001</v>
       </c>
-      <c r="H379" s="4">
+      <c r="G379"/>
+      <c r="H379" s="2">
         <v>10473150.32</v>
       </c>
+      <c r="I379"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{FE92DB44-9108-48C0-9E4D-CDD7D4A1EECC}"/>

--- a/shared_uploads/vsventas.xlsx
+++ b/shared_uploads/vsventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C960806\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EF19B9-2793-4DA3-9924-3EBE88E6EE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA705CFD-5D7A-4DD6-8449-C116939289A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9727" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10015" uniqueCount="117">
   <si>
     <t># Mes</t>
   </si>
@@ -80130,7 +80130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE92DB44-9108-48C0-9E4D-CDD7D4A1EECC}">
-  <dimension ref="A1:K379"/>
+  <dimension ref="A1:K475"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.90625" style="5"/>
@@ -88988,22 +88988,22 @@
         <v>10</v>
       </c>
       <c r="F291" s="2">
-        <v>56814105.280000001</v>
+        <v>118726877.58</v>
       </c>
       <c r="G291" s="2">
-        <v>838783.9</v>
+        <v>1521118.2</v>
       </c>
       <c r="H291" s="2">
-        <v>44412514.939999998</v>
+        <v>92685126.030000001</v>
       </c>
       <c r="I291" s="2">
-        <v>636325.31000000006</v>
+        <v>1168629.3799999999</v>
       </c>
       <c r="J291" s="3">
-        <v>114</v>
+        <v>349</v>
       </c>
       <c r="K291" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -89023,11 +89023,11 @@
         <v>11</v>
       </c>
       <c r="F292" s="2">
-        <v>51309425.82</v>
+        <v>111150122.16</v>
       </c>
       <c r="G292"/>
       <c r="H292" s="2">
-        <v>40167811.240000002</v>
+        <v>86923231.939999998</v>
       </c>
       <c r="I292"/>
     </row>
@@ -89048,22 +89048,22 @@
         <v>12</v>
       </c>
       <c r="F293" s="2">
-        <v>53587224.149999999</v>
+        <v>94763689.629999995</v>
       </c>
       <c r="G293" s="2">
-        <v>1169657.06</v>
+        <v>629660.06000000006</v>
       </c>
       <c r="H293" s="2">
-        <v>42277267.229999997</v>
+        <v>74609062.469999999</v>
       </c>
       <c r="I293" s="2">
-        <v>918904.47</v>
+        <v>500518.35</v>
       </c>
       <c r="J293" s="3">
-        <v>305.53199999999998</v>
+        <v>301.53199999999998</v>
       </c>
       <c r="K293" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -89083,11 +89083,11 @@
         <v>13</v>
       </c>
       <c r="F294" s="2">
-        <v>44794424.859999999</v>
+        <v>83541223.540000007</v>
       </c>
       <c r="G294"/>
       <c r="H294" s="2">
-        <v>35352710.649999999</v>
+        <v>65612183.329999998</v>
       </c>
       <c r="I294"/>
     </row>
@@ -89108,11 +89108,11 @@
         <v>14</v>
       </c>
       <c r="F295" s="2">
-        <v>48738620.170000002</v>
+        <v>93414161.099999994</v>
       </c>
       <c r="G295"/>
       <c r="H295" s="2">
-        <v>38150513.380000003</v>
+        <v>73065540.049999997</v>
       </c>
       <c r="I295"/>
     </row>
@@ -89133,11 +89133,11 @@
         <v>16</v>
       </c>
       <c r="F296" s="2">
-        <v>69158414.689999998</v>
+        <v>138201218.75</v>
       </c>
       <c r="G296"/>
       <c r="H296" s="2">
-        <v>54343172.049999997</v>
+        <v>108273701.16</v>
       </c>
       <c r="I296"/>
     </row>
@@ -89158,11 +89158,11 @@
         <v>17</v>
       </c>
       <c r="F297" s="2">
-        <v>34705327.340000004</v>
+        <v>57417149.240000002</v>
       </c>
       <c r="G297"/>
       <c r="H297" s="2">
-        <v>27212043.440000001</v>
+        <v>45045172.229999997</v>
       </c>
       <c r="I297"/>
     </row>
@@ -89183,11 +89183,11 @@
         <v>18</v>
       </c>
       <c r="F298" s="2">
-        <v>45716472.630000003</v>
+        <v>73691626.819999993</v>
       </c>
       <c r="G298"/>
       <c r="H298" s="2">
-        <v>36555814.740000002</v>
+        <v>58555557.990000002</v>
       </c>
       <c r="I298"/>
     </row>
@@ -89208,11 +89208,11 @@
         <v>19</v>
       </c>
       <c r="F299" s="2">
-        <v>35131909.030000001</v>
+        <v>73364071.069999993</v>
       </c>
       <c r="G299"/>
       <c r="H299" s="2">
-        <v>27533147.629999999</v>
+        <v>57407689.549999997</v>
       </c>
       <c r="I299"/>
     </row>
@@ -89233,11 +89233,11 @@
         <v>20</v>
       </c>
       <c r="F300" s="2">
-        <v>42923910.039999999</v>
+        <v>72802202.319999993</v>
       </c>
       <c r="G300"/>
       <c r="H300" s="2">
-        <v>33838330.719999999</v>
+        <v>57331206.090000004</v>
       </c>
       <c r="I300"/>
     </row>
@@ -89258,11 +89258,11 @@
         <v>21</v>
       </c>
       <c r="F301" s="2">
-        <v>37800498.270000003</v>
+        <v>72259010.530000001</v>
       </c>
       <c r="G301"/>
       <c r="H301" s="2">
-        <v>29650561.350000001</v>
+        <v>56595522.509999998</v>
       </c>
       <c r="I301"/>
     </row>
@@ -89283,11 +89283,11 @@
         <v>22</v>
       </c>
       <c r="F302" s="2">
-        <v>35087569.219999999</v>
+        <v>68405062.510000005</v>
       </c>
       <c r="G302"/>
       <c r="H302" s="2">
-        <v>27570687.260000002</v>
+        <v>53778765.969999999</v>
       </c>
       <c r="I302"/>
     </row>
@@ -89308,11 +89308,11 @@
         <v>23</v>
       </c>
       <c r="F303" s="2">
-        <v>61908259.509999998</v>
+        <v>118779902.66</v>
       </c>
       <c r="G303"/>
       <c r="H303" s="2">
-        <v>48501538.939999998</v>
+        <v>92946858.579999998</v>
       </c>
       <c r="I303"/>
     </row>
@@ -89333,13 +89333,13 @@
         <v>24</v>
       </c>
       <c r="F304" s="2">
-        <v>57380799.770000003</v>
+        <v>101771190.23</v>
       </c>
       <c r="G304" s="2">
         <v>699999</v>
       </c>
       <c r="H304" s="2">
-        <v>44827338.140000001</v>
+        <v>79652500.260000005</v>
       </c>
       <c r="I304" s="2">
         <v>542354.63</v>
@@ -89368,13 +89368,13 @@
         <v>25</v>
       </c>
       <c r="F305" s="2">
-        <v>29992610.789999999</v>
+        <v>48471306.420000002</v>
       </c>
       <c r="G305" s="2">
         <v>104105.05</v>
       </c>
       <c r="H305" s="2">
-        <v>23574669.57</v>
+        <v>38072373.130000003</v>
       </c>
       <c r="I305" s="2">
         <v>80887.320000000007</v>
@@ -89403,11 +89403,11 @@
         <v>26</v>
       </c>
       <c r="F306" s="2">
-        <v>41685684.840000004</v>
+        <v>79583941.840000004</v>
       </c>
       <c r="G306"/>
       <c r="H306" s="2">
-        <v>32874598.09</v>
+        <v>62456281.920000002</v>
       </c>
       <c r="I306"/>
     </row>
@@ -89428,11 +89428,11 @@
         <v>27</v>
       </c>
       <c r="F307" s="2">
-        <v>33124046.25</v>
+        <v>64513349.060000002</v>
       </c>
       <c r="G307"/>
       <c r="H307" s="2">
-        <v>26085163.050000001</v>
+        <v>50489975.939999998</v>
       </c>
       <c r="I307"/>
     </row>
@@ -89453,13 +89453,13 @@
         <v>28</v>
       </c>
       <c r="F308" s="2">
-        <v>65247870.490000002</v>
+        <v>117796011.15000001</v>
       </c>
       <c r="G308" s="2">
         <v>91668.5</v>
       </c>
       <c r="H308" s="2">
-        <v>51623501.490000002</v>
+        <v>93167711.340000004</v>
       </c>
       <c r="I308" s="2">
         <v>77773.06</v>
@@ -89488,13 +89488,13 @@
         <v>30</v>
       </c>
       <c r="F309" s="2">
-        <v>64622392.539999999</v>
+        <v>117266827.05</v>
       </c>
       <c r="G309" s="2">
         <v>559301.42000000004</v>
       </c>
       <c r="H309" s="2">
-        <v>50636690.57</v>
+        <v>91732089.5</v>
       </c>
       <c r="I309" s="2">
         <v>433825.97</v>
@@ -89523,11 +89523,11 @@
         <v>31</v>
       </c>
       <c r="F310" s="2">
-        <v>41591563.649999999</v>
+        <v>76798351.090000004</v>
       </c>
       <c r="G310"/>
       <c r="H310" s="2">
-        <v>32859983.609999999</v>
+        <v>60462892</v>
       </c>
       <c r="I310"/>
     </row>
@@ -89548,11 +89548,11 @@
         <v>32</v>
       </c>
       <c r="F311" s="2">
-        <v>12369537.91</v>
+        <v>19439096.559999999</v>
       </c>
       <c r="G311"/>
       <c r="H311" s="2">
-        <v>9823496</v>
+        <v>15396886.949999999</v>
       </c>
       <c r="I311"/>
     </row>
@@ -89573,11 +89573,11 @@
         <v>33</v>
       </c>
       <c r="F312" s="2">
-        <v>35378530.020000003</v>
+        <v>55949713.020000003</v>
       </c>
       <c r="G312"/>
       <c r="H312" s="2">
-        <v>27862050.66</v>
+        <v>44014945.5</v>
       </c>
       <c r="I312"/>
     </row>
@@ -89598,11 +89598,11 @@
         <v>34</v>
       </c>
       <c r="F313" s="2">
-        <v>30459227.34</v>
+        <v>56223519.640000001</v>
       </c>
       <c r="G313"/>
       <c r="H313" s="2">
-        <v>24066289.16</v>
+        <v>44303238.240000002</v>
       </c>
       <c r="I313"/>
     </row>
@@ -89623,11 +89623,11 @@
         <v>35</v>
       </c>
       <c r="F314" s="2">
-        <v>14788412.9</v>
+        <v>24928004.879999999</v>
       </c>
       <c r="G314"/>
       <c r="H314" s="2">
-        <v>11752156.380000001</v>
+        <v>19778846.420000002</v>
       </c>
       <c r="I314"/>
     </row>
@@ -89648,11 +89648,11 @@
         <v>36</v>
       </c>
       <c r="F315" s="2">
-        <v>60911503.920000002</v>
+        <v>61364373.060000002</v>
       </c>
       <c r="G315"/>
       <c r="H315" s="2">
-        <v>48608347.170000002</v>
+        <v>48971795.340000004</v>
       </c>
       <c r="I315"/>
     </row>
@@ -89673,11 +89673,11 @@
         <v>37</v>
       </c>
       <c r="F316" s="2">
-        <v>42173516.729999997</v>
+        <v>70906267.519999996</v>
       </c>
       <c r="G316"/>
       <c r="H316" s="2">
-        <v>33203102.640000001</v>
+        <v>55715973.399999999</v>
       </c>
       <c r="I316"/>
     </row>
@@ -89698,22 +89698,22 @@
         <v>38</v>
       </c>
       <c r="F317" s="2">
-        <v>37427368.789999999</v>
+        <v>64174373.590000004</v>
       </c>
       <c r="G317" s="2">
-        <v>1064539.1499999999</v>
+        <v>2014409.35</v>
       </c>
       <c r="H317" s="2">
-        <v>29545466.859999999</v>
+        <v>50586661.299999997</v>
       </c>
       <c r="I317" s="2">
-        <v>827490.12</v>
+        <v>1563443.33</v>
       </c>
       <c r="J317" s="3">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K317" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
@@ -89733,13 +89733,13 @@
         <v>39</v>
       </c>
       <c r="F318" s="2">
-        <v>25514009.050000001</v>
+        <v>45669484.539999999</v>
       </c>
       <c r="G318" s="2">
         <v>-91413.75</v>
       </c>
       <c r="H318" s="2">
-        <v>20067749.219999999</v>
+        <v>35903073.640000001</v>
       </c>
       <c r="I318" s="2">
         <v>-76951.820000000007</v>
@@ -89768,11 +89768,11 @@
         <v>40</v>
       </c>
       <c r="F319" s="2">
-        <v>7037528.0899999999</v>
+        <v>7386000.7999999998</v>
       </c>
       <c r="G319"/>
       <c r="H319" s="2">
-        <v>5541309</v>
+        <v>5819696.8099999996</v>
       </c>
       <c r="I319"/>
     </row>
@@ -89793,13 +89793,13 @@
         <v>43</v>
       </c>
       <c r="F320" s="2">
-        <v>45248968.32</v>
+        <v>89089111.549999997</v>
       </c>
       <c r="G320" s="2">
         <v>2349998.19</v>
       </c>
       <c r="H320" s="2">
-        <v>35353148.369999997</v>
+        <v>69402407.099999994</v>
       </c>
       <c r="I320" s="2">
         <v>1820763.07</v>
@@ -89828,13 +89828,13 @@
         <v>44</v>
       </c>
       <c r="F321" s="2">
-        <v>35231703.619999997</v>
+        <v>67603087.439999998</v>
       </c>
       <c r="G321" s="2">
         <v>350483.85</v>
       </c>
       <c r="H321" s="2">
-        <v>27873864.949999999</v>
+        <v>53269959.079999998</v>
       </c>
       <c r="I321" s="2">
         <v>272899.42</v>
@@ -89863,11 +89863,11 @@
         <v>45</v>
       </c>
       <c r="F322" s="2">
-        <v>35830746</v>
+        <v>68039540.900000006</v>
       </c>
       <c r="G322"/>
       <c r="H322" s="2">
-        <v>28124638.07</v>
+        <v>53389375.109999999</v>
       </c>
       <c r="I322"/>
     </row>
@@ -89888,11 +89888,11 @@
         <v>46</v>
       </c>
       <c r="F323" s="2">
-        <v>11122852.09</v>
+        <v>19329765.57</v>
       </c>
       <c r="G323"/>
       <c r="H323" s="2">
-        <v>8747218.1799999997</v>
+        <v>15193316.33</v>
       </c>
       <c r="I323"/>
     </row>
@@ -89913,11 +89913,11 @@
         <v>47</v>
       </c>
       <c r="F324" s="2">
-        <v>10040423.449999999</v>
+        <v>15181122.609999999</v>
       </c>
       <c r="G324"/>
       <c r="H324" s="2">
-        <v>7943015.4100000001</v>
+        <v>11987023.869999999</v>
       </c>
       <c r="I324"/>
     </row>
@@ -89938,13 +89938,13 @@
         <v>48</v>
       </c>
       <c r="F325" s="2">
-        <v>11010337.869999999</v>
+        <v>19167614.100000001</v>
       </c>
       <c r="G325" s="2">
         <v>17760</v>
       </c>
       <c r="H325" s="2">
-        <v>8636093.3399999999</v>
+        <v>15036189.43</v>
       </c>
       <c r="I325" s="2">
         <v>13760.32</v>
@@ -89973,11 +89973,11 @@
         <v>49</v>
       </c>
       <c r="F326" s="2">
-        <v>27527320.640000001</v>
+        <v>46560201.509999998</v>
       </c>
       <c r="G326"/>
       <c r="H326" s="2">
-        <v>21481914.579999998</v>
+        <v>36509994.109999999</v>
       </c>
       <c r="I326"/>
     </row>
@@ -89998,13 +89998,23 @@
         <v>50</v>
       </c>
       <c r="F327" s="2">
-        <v>52388130.969999999</v>
-      </c>
-      <c r="G327"/>
+        <v>92895827.349999994</v>
+      </c>
+      <c r="G327">
+        <v>69901.100000000006</v>
+      </c>
       <c r="H327" s="2">
-        <v>41749547.799999997</v>
-      </c>
-      <c r="I327"/>
+        <v>73547274.019999996</v>
+      </c>
+      <c r="I327">
+        <v>54158.94</v>
+      </c>
+      <c r="J327">
+        <v>10</v>
+      </c>
+      <c r="K327">
+        <v>2</v>
+      </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
@@ -90023,13 +90033,13 @@
         <v>51</v>
       </c>
       <c r="F328" s="2">
-        <v>38850188.340000004</v>
+        <v>64322688.090000004</v>
       </c>
       <c r="G328" s="2">
         <v>80790.5</v>
       </c>
       <c r="H328" s="2">
-        <v>31084626.989999998</v>
+        <v>51032299.420000002</v>
       </c>
       <c r="I328" s="2">
         <v>68543.97</v>
@@ -90058,11 +90068,11 @@
         <v>52</v>
       </c>
       <c r="F329" s="2">
-        <v>31005651.460000001</v>
+        <v>68194640.859999999</v>
       </c>
       <c r="G329"/>
       <c r="H329" s="2">
-        <v>24312870.510000002</v>
+        <v>53512092.549999997</v>
       </c>
       <c r="I329"/>
     </row>
@@ -90083,11 +90093,11 @@
         <v>53</v>
       </c>
       <c r="F330" s="2">
-        <v>32820384.309999999</v>
+        <v>71183622.629999995</v>
       </c>
       <c r="G330"/>
       <c r="H330" s="2">
-        <v>25697133.859999999</v>
+        <v>55677954.649999999</v>
       </c>
       <c r="I330"/>
     </row>
@@ -90108,11 +90118,11 @@
         <v>54</v>
       </c>
       <c r="F331" s="2">
-        <v>28037072.550000001</v>
+        <v>54343883.729999997</v>
       </c>
       <c r="G331"/>
       <c r="H331" s="2">
-        <v>22159882.57</v>
+        <v>42794445.810000002</v>
       </c>
       <c r="I331"/>
     </row>
@@ -90133,11 +90143,11 @@
         <v>55</v>
       </c>
       <c r="F332" s="2">
-        <v>25255417.02</v>
+        <v>47210907.909999996</v>
       </c>
       <c r="G332"/>
       <c r="H332" s="2">
-        <v>19906621.489999998</v>
+        <v>37161048.479999997</v>
       </c>
       <c r="I332"/>
     </row>
@@ -90158,11 +90168,11 @@
         <v>56</v>
       </c>
       <c r="F333" s="2">
-        <v>59028340.719999999</v>
+        <v>124576567.90000001</v>
       </c>
       <c r="G333"/>
       <c r="H333" s="2">
-        <v>46276457.460000001</v>
+        <v>97533818.010000005</v>
       </c>
       <c r="I333"/>
     </row>
@@ -90183,11 +90193,11 @@
         <v>57</v>
       </c>
       <c r="F334" s="2">
-        <v>42515591.869999997</v>
+        <v>74204320.099999994</v>
       </c>
       <c r="G334"/>
       <c r="H334" s="2">
-        <v>33450122.280000001</v>
+        <v>58076161.130000003</v>
       </c>
       <c r="I334"/>
     </row>
@@ -90208,11 +90218,11 @@
         <v>58</v>
       </c>
       <c r="F335" s="2">
-        <v>35393171.619999997</v>
+        <v>62440647.060000002</v>
       </c>
       <c r="G335"/>
       <c r="H335" s="2">
-        <v>27738379.699999999</v>
+        <v>48938952</v>
       </c>
       <c r="I335"/>
     </row>
@@ -90233,11 +90243,11 @@
         <v>59</v>
       </c>
       <c r="F336" s="2">
-        <v>26836684.539999999</v>
+        <v>40216782.479999997</v>
       </c>
       <c r="G336"/>
       <c r="H336" s="2">
-        <v>21387515.27</v>
+        <v>31848878.530000001</v>
       </c>
       <c r="I336"/>
     </row>
@@ -90258,11 +90268,11 @@
         <v>60</v>
       </c>
       <c r="F337" s="2">
-        <v>31680730.289999999</v>
+        <v>69629398.280000001</v>
       </c>
       <c r="G337"/>
       <c r="H337" s="2">
-        <v>24686024.780000001</v>
+        <v>54255233.100000001</v>
       </c>
       <c r="I337"/>
     </row>
@@ -90283,11 +90293,11 @@
         <v>111</v>
       </c>
       <c r="F338" s="2">
-        <v>2188836.2599999998</v>
+        <v>4325526.8099999996</v>
       </c>
       <c r="G338"/>
       <c r="H338" s="2">
-        <v>1706732.36</v>
+        <v>3386241.17</v>
       </c>
       <c r="I338"/>
     </row>
@@ -90308,13 +90318,13 @@
         <v>61</v>
       </c>
       <c r="F339" s="2">
-        <v>26443154.73</v>
+        <v>47184114.289999999</v>
       </c>
       <c r="G339" s="2">
         <v>141823.20000000001</v>
       </c>
       <c r="H339" s="2">
-        <v>20763552</v>
+        <v>36951804.219999999</v>
       </c>
       <c r="I339" s="2">
         <v>109883.52</v>
@@ -90343,11 +90353,11 @@
         <v>62</v>
       </c>
       <c r="F340" s="2">
-        <v>49461759.57</v>
+        <v>85312045.349999994</v>
       </c>
       <c r="G340"/>
       <c r="H340" s="2">
-        <v>38915429.170000002</v>
+        <v>67130046.700000003</v>
       </c>
       <c r="I340"/>
     </row>
@@ -90368,11 +90378,11 @@
         <v>63</v>
       </c>
       <c r="F341" s="2">
-        <v>19877881.280000001</v>
+        <v>31431825.43</v>
       </c>
       <c r="G341"/>
       <c r="H341" s="2">
-        <v>15555791.380000001</v>
+        <v>24590813.43</v>
       </c>
       <c r="I341"/>
     </row>
@@ -90393,11 +90403,11 @@
         <v>64</v>
       </c>
       <c r="F342" s="2">
-        <v>40937563.829999998</v>
+        <v>68761711.209999993</v>
       </c>
       <c r="G342"/>
       <c r="H342" s="2">
-        <v>32592393.859999999</v>
+        <v>54575115.469999999</v>
       </c>
       <c r="I342"/>
     </row>
@@ -90418,11 +90428,11 @@
         <v>65</v>
       </c>
       <c r="F343" s="2">
-        <v>36486712.670000002</v>
+        <v>64137821.170000002</v>
       </c>
       <c r="G343"/>
       <c r="H343" s="2">
-        <v>28766577.93</v>
+        <v>50489816.049999997</v>
       </c>
       <c r="I343"/>
     </row>
@@ -90443,13 +90453,13 @@
         <v>67</v>
       </c>
       <c r="F344" s="2">
-        <v>44401623.740000002</v>
+        <v>75919953.510000005</v>
       </c>
       <c r="G344" s="2">
         <v>129382.78</v>
       </c>
       <c r="H344" s="2">
-        <v>35335077.259999998</v>
+        <v>60049123.460000001</v>
       </c>
       <c r="I344" s="2">
         <v>96370.84</v>
@@ -90478,11 +90488,11 @@
         <v>68</v>
       </c>
       <c r="F345" s="2">
-        <v>37740036.829999998</v>
+        <v>66709045.520000003</v>
       </c>
       <c r="G345"/>
       <c r="H345" s="2">
-        <v>29560958.120000001</v>
+        <v>52155867.079999998</v>
       </c>
       <c r="I345"/>
     </row>
@@ -90503,11 +90513,11 @@
         <v>69</v>
       </c>
       <c r="F346" s="2">
-        <v>26374265.920000002</v>
+        <v>46783420.539999999</v>
       </c>
       <c r="G346"/>
       <c r="H346" s="2">
-        <v>20616714.949999999</v>
+        <v>36606518.450000003</v>
       </c>
       <c r="I346"/>
     </row>
@@ -90528,11 +90538,11 @@
         <v>70</v>
       </c>
       <c r="F347" s="2">
-        <v>16240307.5</v>
+        <v>24744860.949999999</v>
       </c>
       <c r="G347"/>
       <c r="H347" s="2">
-        <v>12906928.85</v>
+        <v>19568588.460000001</v>
       </c>
       <c r="I347"/>
     </row>
@@ -90553,13 +90563,13 @@
         <v>71</v>
       </c>
       <c r="F348" s="2">
-        <v>11798441.529999999</v>
+        <v>18500461.07</v>
       </c>
       <c r="G348" s="2">
         <v>348895.52</v>
       </c>
       <c r="H348" s="2">
-        <v>9375503.3900000006</v>
+        <v>14629547.470000001</v>
       </c>
       <c r="I348" s="2">
         <v>271878.39</v>
@@ -90588,11 +90598,11 @@
         <v>72</v>
       </c>
       <c r="F349" s="2">
-        <v>24959945.800000001</v>
+        <v>39508993.640000001</v>
       </c>
       <c r="G349"/>
       <c r="H349" s="2">
-        <v>19746182.57</v>
+        <v>31069593.640000001</v>
       </c>
       <c r="I349"/>
     </row>
@@ -90613,11 +90623,11 @@
         <v>73</v>
       </c>
       <c r="F350" s="2">
-        <v>43502093.960000001</v>
+        <v>76508520.25</v>
       </c>
       <c r="G350"/>
       <c r="H350" s="2">
-        <v>34040828.579999998</v>
+        <v>59820508.280000001</v>
       </c>
       <c r="I350"/>
     </row>
@@ -90638,22 +90648,22 @@
         <v>74</v>
       </c>
       <c r="F351" s="2">
-        <v>39019238.280000001</v>
+        <v>66398052.020000003</v>
       </c>
       <c r="G351" s="2">
-        <v>-270736.64000000001</v>
+        <v>2109104.3199999998</v>
       </c>
       <c r="H351" s="2">
-        <v>30807632.109999999</v>
+        <v>52477381.689999998</v>
       </c>
       <c r="I351" s="2">
-        <v>-212350.8</v>
+        <v>1652667.02</v>
       </c>
       <c r="J351" s="3">
-        <v>-113.946</v>
+        <v>535.72799999999995</v>
       </c>
       <c r="K351" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
@@ -90673,13 +90683,23 @@
         <v>75</v>
       </c>
       <c r="F352" s="2">
-        <v>30834044.75</v>
-      </c>
-      <c r="G352"/>
+        <v>52444877.840000004</v>
+      </c>
+      <c r="G352">
+        <v>319999.2</v>
+      </c>
       <c r="H352" s="2">
-        <v>24094777.57</v>
-      </c>
-      <c r="I352"/>
+        <v>40981619.549999997</v>
+      </c>
+      <c r="I352">
+        <v>247933.26</v>
+      </c>
+      <c r="J352">
+        <v>1</v>
+      </c>
+      <c r="K352">
+        <v>1</v>
+      </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
@@ -90698,11 +90718,11 @@
         <v>76</v>
       </c>
       <c r="F353" s="2">
-        <v>35853797.229999997</v>
+        <v>59697635.5</v>
       </c>
       <c r="G353"/>
       <c r="H353" s="2">
-        <v>28147303.640000001</v>
+        <v>46771871.57</v>
       </c>
       <c r="I353"/>
     </row>
@@ -90723,11 +90743,11 @@
         <v>77</v>
       </c>
       <c r="F354" s="2">
-        <v>41159709.689999998</v>
+        <v>80092944.290000007</v>
       </c>
       <c r="G354"/>
       <c r="H354" s="2">
-        <v>32381413.329999998</v>
+        <v>62958212.920000002</v>
       </c>
       <c r="I354"/>
     </row>
@@ -90748,11 +90768,11 @@
         <v>78</v>
       </c>
       <c r="F355" s="2">
-        <v>42170899.229999997</v>
+        <v>65828887.609999999</v>
       </c>
       <c r="G355"/>
       <c r="H355" s="2">
-        <v>33082289.34</v>
+        <v>51651148.82</v>
       </c>
       <c r="I355"/>
     </row>
@@ -90773,11 +90793,11 @@
         <v>79</v>
       </c>
       <c r="F356" s="2">
-        <v>29832267.43</v>
+        <v>46893210.119999997</v>
       </c>
       <c r="G356"/>
       <c r="H356" s="2">
-        <v>23495781.199999999</v>
+        <v>36826435.590000004</v>
       </c>
       <c r="I356"/>
     </row>
@@ -90798,11 +90818,11 @@
         <v>81</v>
       </c>
       <c r="F357" s="2">
-        <v>55080034.060000002</v>
+        <v>84441532.870000005</v>
       </c>
       <c r="G357"/>
       <c r="H357" s="2">
-        <v>43934659.759999998</v>
+        <v>66949320.100000001</v>
       </c>
       <c r="I357"/>
     </row>
@@ -90823,11 +90843,11 @@
         <v>112</v>
       </c>
       <c r="F358" s="2">
-        <v>2225052.1</v>
+        <v>3980156.96</v>
       </c>
       <c r="G358"/>
       <c r="H358" s="2">
-        <v>1746479.75</v>
+        <v>3119580.84</v>
       </c>
       <c r="I358"/>
     </row>
@@ -90848,11 +90868,11 @@
         <v>83</v>
       </c>
       <c r="F359" s="2">
-        <v>21686687.32</v>
+        <v>37548564.670000002</v>
       </c>
       <c r="G359"/>
       <c r="H359" s="2">
-        <v>17207597.199999999</v>
+        <v>29575899.559999999</v>
       </c>
       <c r="I359"/>
     </row>
@@ -90873,13 +90893,23 @@
         <v>84</v>
       </c>
       <c r="F360" s="2">
-        <v>38512381.509999998</v>
-      </c>
-      <c r="G360"/>
+        <v>74492089.650000006</v>
+      </c>
+      <c r="G360">
+        <v>294054.40000000002</v>
+      </c>
       <c r="H360" s="2">
-        <v>30229136.350000001</v>
-      </c>
-      <c r="I360"/>
+        <v>58539586.670000002</v>
+      </c>
+      <c r="I360">
+        <v>226614.69</v>
+      </c>
+      <c r="J360">
+        <v>42.91</v>
+      </c>
+      <c r="K360">
+        <v>3</v>
+      </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
@@ -90898,11 +90928,11 @@
         <v>114</v>
       </c>
       <c r="F361" s="2">
-        <v>3244168.22</v>
+        <v>6719084.0199999996</v>
       </c>
       <c r="G361"/>
       <c r="H361" s="2">
-        <v>2548086.41</v>
+        <v>5214741.6399999997</v>
       </c>
       <c r="I361"/>
     </row>
@@ -90923,11 +90953,11 @@
         <v>85</v>
       </c>
       <c r="F362" s="2">
-        <v>23524673.309999999</v>
+        <v>40149230.219999999</v>
       </c>
       <c r="G362"/>
       <c r="H362" s="2">
-        <v>18553267.75</v>
+        <v>31578061.66</v>
       </c>
       <c r="I362"/>
     </row>
@@ -90948,13 +90978,13 @@
         <v>86</v>
       </c>
       <c r="F363" s="2">
-        <v>29154198.280000001</v>
+        <v>29232914.859999999</v>
       </c>
       <c r="G363" s="2">
         <v>1909997.38</v>
       </c>
       <c r="H363" s="2">
-        <v>23169010.52</v>
+        <v>23233772.579999998</v>
       </c>
       <c r="I363" s="2">
         <v>1479853.35</v>
@@ -90983,11 +91013,11 @@
         <v>87</v>
       </c>
       <c r="F364" s="2">
-        <v>21747983.059999999</v>
+        <v>38960602.670000002</v>
       </c>
       <c r="G364"/>
       <c r="H364" s="2">
-        <v>17118912.050000001</v>
+        <v>30635766.760000002</v>
       </c>
       <c r="I364"/>
     </row>
@@ -91008,11 +91038,11 @@
         <v>88</v>
       </c>
       <c r="F365" s="2">
-        <v>30771703.93</v>
+        <v>58078314.5</v>
       </c>
       <c r="G365"/>
       <c r="H365" s="2">
-        <v>24362370.09</v>
+        <v>45917569.329999998</v>
       </c>
       <c r="I365"/>
     </row>
@@ -91033,11 +91063,11 @@
         <v>89</v>
       </c>
       <c r="F366" s="2">
-        <v>31659307.289999999</v>
+        <v>51795539.829999998</v>
       </c>
       <c r="G366"/>
       <c r="H366" s="2">
-        <v>24922705.489999998</v>
+        <v>40765022.82</v>
       </c>
       <c r="I366"/>
     </row>
@@ -91058,11 +91088,11 @@
         <v>90</v>
       </c>
       <c r="F367" s="2">
-        <v>30806777.260000002</v>
+        <v>46932654.869999997</v>
       </c>
       <c r="G367"/>
       <c r="H367" s="2">
-        <v>24195790.579999998</v>
+        <v>36840850.310000002</v>
       </c>
       <c r="I367"/>
     </row>
@@ -91083,22 +91113,22 @@
         <v>91</v>
       </c>
       <c r="F368" s="2">
-        <v>167121641.97</v>
+        <v>286785298.66000003</v>
       </c>
       <c r="G368" s="2">
-        <v>4623692.3</v>
+        <v>6220219.3700000001</v>
       </c>
       <c r="H368" s="2">
-        <v>132927864.36</v>
+        <v>227448713.49000001</v>
       </c>
       <c r="I368" s="2">
-        <v>3595846.91</v>
+        <v>4837298.2699999996</v>
       </c>
       <c r="J368" s="3">
-        <v>1674.242</v>
+        <v>2159.8739999999998</v>
       </c>
       <c r="K368" s="3">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
@@ -91118,13 +91148,13 @@
         <v>92</v>
       </c>
       <c r="F369" s="2">
-        <v>89086672.769999996</v>
+        <v>160993214.16999999</v>
       </c>
       <c r="G369" s="2">
         <v>4549077.72</v>
       </c>
       <c r="H369" s="2">
-        <v>69796426.730000004</v>
+        <v>125928765.91</v>
       </c>
       <c r="I369" s="2">
         <v>3495796.8</v>
@@ -91153,13 +91183,13 @@
         <v>93</v>
       </c>
       <c r="F370" s="2">
-        <v>82927643.439999998</v>
+        <v>167864342.31999999</v>
       </c>
       <c r="G370" s="2">
         <v>-62311.4</v>
       </c>
       <c r="H370" s="2">
-        <v>65118422.829999998</v>
+        <v>131707110.56</v>
       </c>
       <c r="I370" s="2">
         <v>-48278.47</v>
@@ -91188,22 +91218,22 @@
         <v>94</v>
       </c>
       <c r="F371" s="2">
-        <v>82409222.659999996</v>
+        <v>157918268.19999999</v>
       </c>
       <c r="G371" s="2">
-        <v>2314932.9900000002</v>
+        <v>3000653.86</v>
       </c>
       <c r="H371" s="2">
-        <v>64350092.729999997</v>
+        <v>123699521.52</v>
       </c>
       <c r="I371" s="2">
-        <v>1789502.88</v>
+        <v>2318835.4500000002</v>
       </c>
       <c r="J371" s="3">
-        <v>826.303</v>
+        <v>1032.462</v>
       </c>
       <c r="K371" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
@@ -91223,11 +91253,11 @@
         <v>95</v>
       </c>
       <c r="F372" s="2">
-        <v>66582009.799999997</v>
+        <v>120776033.84</v>
       </c>
       <c r="G372"/>
       <c r="H372" s="2">
-        <v>52318261.649999999</v>
+        <v>94696480.640000001</v>
       </c>
       <c r="I372"/>
     </row>
@@ -91248,11 +91278,11 @@
         <v>96</v>
       </c>
       <c r="F373" s="2">
-        <v>89083836.430000007</v>
+        <v>205004352.74000001</v>
       </c>
       <c r="G373"/>
       <c r="H373" s="2">
-        <v>69683934.329999998</v>
+        <v>160089797.72999999</v>
       </c>
       <c r="I373"/>
     </row>
@@ -91273,11 +91303,11 @@
         <v>97</v>
       </c>
       <c r="F374" s="2">
-        <v>61991084.530000001</v>
+        <v>126763000.73</v>
       </c>
       <c r="G374"/>
       <c r="H374" s="2">
-        <v>48628458.939999998</v>
+        <v>99310339.120000005</v>
       </c>
       <c r="I374"/>
     </row>
@@ -91298,13 +91328,23 @@
         <v>98</v>
       </c>
       <c r="F375" s="2">
-        <v>108259870.11</v>
-      </c>
-      <c r="G375"/>
+        <v>186953093.02000001</v>
+      </c>
+      <c r="G375">
+        <v>4475833.83</v>
+      </c>
       <c r="H375" s="2">
-        <v>85499091.989999995</v>
-      </c>
-      <c r="I375"/>
+        <v>147308690.05000001</v>
+      </c>
+      <c r="I375">
+        <v>3457793.8</v>
+      </c>
+      <c r="J375">
+        <v>1326.921</v>
+      </c>
+      <c r="K375">
+        <v>36</v>
+      </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
@@ -91323,11 +91363,11 @@
         <v>99</v>
       </c>
       <c r="F376" s="2">
-        <v>75660184.219999999</v>
+        <v>137435044.59</v>
       </c>
       <c r="G376"/>
       <c r="H376" s="2">
-        <v>59621704.700000003</v>
+        <v>107956994.45</v>
       </c>
       <c r="I376"/>
     </row>
@@ -91348,13 +91388,13 @@
         <v>100</v>
       </c>
       <c r="F377" s="2">
-        <v>96443670.099999994</v>
+        <v>210955920.28999999</v>
       </c>
       <c r="G377" s="2">
         <v>1016637.9</v>
       </c>
       <c r="H377" s="2">
-        <v>75691404.650000006</v>
+        <v>164925455.52000001</v>
       </c>
       <c r="I377" s="2">
         <v>791361.49</v>
@@ -91383,13 +91423,23 @@
         <v>101</v>
       </c>
       <c r="F378" s="2">
-        <v>53152539.5</v>
-      </c>
-      <c r="G378"/>
+        <v>126811359.93000001</v>
+      </c>
+      <c r="G378">
+        <v>2262668.48</v>
+      </c>
       <c r="H378" s="2">
-        <v>41882872.640000001</v>
-      </c>
-      <c r="I378"/>
+        <v>99877139.640000001</v>
+      </c>
+      <c r="I378">
+        <v>1756773.73</v>
+      </c>
+      <c r="J378">
+        <v>754.11</v>
+      </c>
+      <c r="K378">
+        <v>12</v>
+      </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
@@ -91408,13 +91458,2749 @@
         <v>102</v>
       </c>
       <c r="F379" s="2">
-        <v>13226017.810000001</v>
+        <v>23687657.699999999</v>
       </c>
       <c r="G379"/>
       <c r="H379" s="2">
-        <v>10473150.32</v>
+        <v>18724006.18</v>
       </c>
       <c r="I379"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>115</v>
+      </c>
+      <c r="B380" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C380" t="s">
+        <v>9</v>
+      </c>
+      <c r="D380">
+        <v>1002</v>
+      </c>
+      <c r="E380" t="s">
+        <v>10</v>
+      </c>
+      <c r="F380" s="4">
+        <v>67448514.370000005</v>
+      </c>
+      <c r="G380" s="4">
+        <v>2857806.22</v>
+      </c>
+      <c r="H380" s="4">
+        <v>52811215.170000002</v>
+      </c>
+      <c r="I380" s="4">
+        <v>2236997.11</v>
+      </c>
+      <c r="J380">
+        <v>918.48900000000003</v>
+      </c>
+      <c r="K380">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>115</v>
+      </c>
+      <c r="B381" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C381" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381">
+        <v>1003</v>
+      </c>
+      <c r="E381" t="s">
+        <v>11</v>
+      </c>
+      <c r="F381" s="4">
+        <v>79190757.900000006</v>
+      </c>
+      <c r="G381" s="4">
+        <v>3174549.67</v>
+      </c>
+      <c r="H381" s="4">
+        <v>63156855.460000001</v>
+      </c>
+      <c r="I381" s="4">
+        <v>2490286.73</v>
+      </c>
+      <c r="J381">
+        <v>953.60900000000004</v>
+      </c>
+      <c r="K381">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>115</v>
+      </c>
+      <c r="B382" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C382" t="s">
+        <v>9</v>
+      </c>
+      <c r="D382">
+        <v>1004</v>
+      </c>
+      <c r="E382" t="s">
+        <v>12</v>
+      </c>
+      <c r="F382" s="4">
+        <v>104224072.16</v>
+      </c>
+      <c r="G382" s="4">
+        <v>4987541.5999999996</v>
+      </c>
+      <c r="H382" s="4">
+        <v>82288122.790000007</v>
+      </c>
+      <c r="I382" s="4">
+        <v>3949705.06</v>
+      </c>
+      <c r="J382">
+        <v>1333.298</v>
+      </c>
+      <c r="K382">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>115</v>
+      </c>
+      <c r="B383" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C383" t="s">
+        <v>9</v>
+      </c>
+      <c r="D383">
+        <v>1005</v>
+      </c>
+      <c r="E383" t="s">
+        <v>13</v>
+      </c>
+      <c r="F383" s="4">
+        <v>72624996.920000002</v>
+      </c>
+      <c r="H383" s="4">
+        <v>57769957.340000004</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>115</v>
+      </c>
+      <c r="B384" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C384" t="s">
+        <v>9</v>
+      </c>
+      <c r="D384">
+        <v>1006</v>
+      </c>
+      <c r="E384" t="s">
+        <v>14</v>
+      </c>
+      <c r="F384" s="4">
+        <v>68493789.620000005</v>
+      </c>
+      <c r="G384" s="4">
+        <v>1916424.73</v>
+      </c>
+      <c r="H384" s="4">
+        <v>54521346.140000001</v>
+      </c>
+      <c r="I384" s="4">
+        <v>1499413.42</v>
+      </c>
+      <c r="J384">
+        <v>648.41700000000003</v>
+      </c>
+      <c r="K384">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>115</v>
+      </c>
+      <c r="B385" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C385" t="s">
+        <v>9</v>
+      </c>
+      <c r="D385">
+        <v>1007</v>
+      </c>
+      <c r="E385" t="s">
+        <v>15</v>
+      </c>
+      <c r="F385" s="4">
+        <v>88335522.900000006</v>
+      </c>
+      <c r="G385" s="4">
+        <v>523964.79</v>
+      </c>
+      <c r="H385" s="4">
+        <v>69765807.930000007</v>
+      </c>
+      <c r="I385" s="4">
+        <v>416806.3</v>
+      </c>
+      <c r="J385">
+        <v>156.77500000000001</v>
+      </c>
+      <c r="K385">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>115</v>
+      </c>
+      <c r="B386" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C386" t="s">
+        <v>9</v>
+      </c>
+      <c r="D386">
+        <v>1008</v>
+      </c>
+      <c r="E386" t="s">
+        <v>16</v>
+      </c>
+      <c r="F386" s="4">
+        <v>75976580.459999993</v>
+      </c>
+      <c r="G386" s="4">
+        <v>2310777.9700000002</v>
+      </c>
+      <c r="H386" s="4">
+        <v>59488191.560000002</v>
+      </c>
+      <c r="I386" s="4">
+        <v>1815231.77</v>
+      </c>
+      <c r="J386">
+        <v>483.05700000000002</v>
+      </c>
+      <c r="K386">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>115</v>
+      </c>
+      <c r="B387" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C387" t="s">
+        <v>9</v>
+      </c>
+      <c r="D387">
+        <v>1010</v>
+      </c>
+      <c r="E387" t="s">
+        <v>17</v>
+      </c>
+      <c r="F387" s="4">
+        <v>53028828.310000002</v>
+      </c>
+      <c r="H387" s="4">
+        <v>41781154.509999998</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>115</v>
+      </c>
+      <c r="B388" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C388" t="s">
+        <v>9</v>
+      </c>
+      <c r="D388">
+        <v>1011</v>
+      </c>
+      <c r="E388" t="s">
+        <v>18</v>
+      </c>
+      <c r="F388" s="4">
+        <v>61759936.729999997</v>
+      </c>
+      <c r="G388" s="4">
+        <v>1334112.1000000001</v>
+      </c>
+      <c r="H388" s="4">
+        <v>48484704.939999998</v>
+      </c>
+      <c r="I388" s="4">
+        <v>1048114.14</v>
+      </c>
+      <c r="J388">
+        <v>294.25700000000001</v>
+      </c>
+      <c r="K388">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>115</v>
+      </c>
+      <c r="B389" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C389" t="s">
+        <v>9</v>
+      </c>
+      <c r="D389">
+        <v>1012</v>
+      </c>
+      <c r="E389" t="s">
+        <v>19</v>
+      </c>
+      <c r="F389" s="4">
+        <v>68780505.340000004</v>
+      </c>
+      <c r="G389" s="4">
+        <v>455724.46</v>
+      </c>
+      <c r="H389" s="4">
+        <v>53736947.640000001</v>
+      </c>
+      <c r="I389" s="4">
+        <v>355834.25</v>
+      </c>
+      <c r="J389">
+        <v>33.17</v>
+      </c>
+      <c r="K389">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>115</v>
+      </c>
+      <c r="B390" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390">
+        <v>1013</v>
+      </c>
+      <c r="E390" t="s">
+        <v>20</v>
+      </c>
+      <c r="F390" s="4">
+        <v>49259715.109999999</v>
+      </c>
+      <c r="H390" s="4">
+        <v>38707955.020000003</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>115</v>
+      </c>
+      <c r="B391" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C391" t="s">
+        <v>9</v>
+      </c>
+      <c r="D391">
+        <v>1014</v>
+      </c>
+      <c r="E391" t="s">
+        <v>21</v>
+      </c>
+      <c r="F391" s="4">
+        <v>47426307.490000002</v>
+      </c>
+      <c r="H391" s="4">
+        <v>37039971.07</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>115</v>
+      </c>
+      <c r="B392" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C392" t="s">
+        <v>9</v>
+      </c>
+      <c r="D392">
+        <v>1015</v>
+      </c>
+      <c r="E392" t="s">
+        <v>22</v>
+      </c>
+      <c r="F392" s="4">
+        <v>59129754.270000003</v>
+      </c>
+      <c r="H392" s="4">
+        <v>46452717.200000003</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>115</v>
+      </c>
+      <c r="B393" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C393" t="s">
+        <v>9</v>
+      </c>
+      <c r="D393">
+        <v>1016</v>
+      </c>
+      <c r="E393" t="s">
+        <v>23</v>
+      </c>
+      <c r="F393" s="4">
+        <v>63293643.789999999</v>
+      </c>
+      <c r="H393" s="4">
+        <v>49595684.100000001</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>115</v>
+      </c>
+      <c r="B394" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C394" t="s">
+        <v>9</v>
+      </c>
+      <c r="D394">
+        <v>1017</v>
+      </c>
+      <c r="E394" t="s">
+        <v>24</v>
+      </c>
+      <c r="F394" s="4">
+        <v>52361107.979999997</v>
+      </c>
+      <c r="H394" s="4">
+        <v>40940129.289999999</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>115</v>
+      </c>
+      <c r="B395" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395">
+        <v>1018</v>
+      </c>
+      <c r="E395" t="s">
+        <v>25</v>
+      </c>
+      <c r="F395" s="4">
+        <v>51920440.079999998</v>
+      </c>
+      <c r="H395" s="4">
+        <v>40593190.920000002</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>115</v>
+      </c>
+      <c r="B396" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C396" t="s">
+        <v>9</v>
+      </c>
+      <c r="D396">
+        <v>1020</v>
+      </c>
+      <c r="E396" t="s">
+        <v>26</v>
+      </c>
+      <c r="F396" s="4">
+        <v>73455731.040000007</v>
+      </c>
+      <c r="G396" s="4">
+        <v>4606344.3600000003</v>
+      </c>
+      <c r="H396" s="4">
+        <v>57986546.25</v>
+      </c>
+      <c r="I396" s="4">
+        <v>3589477.45</v>
+      </c>
+      <c r="J396">
+        <v>1306.2940000000001</v>
+      </c>
+      <c r="K396">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>115</v>
+      </c>
+      <c r="B397" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C397" t="s">
+        <v>9</v>
+      </c>
+      <c r="D397">
+        <v>1021</v>
+      </c>
+      <c r="E397" t="s">
+        <v>27</v>
+      </c>
+      <c r="F397" s="4">
+        <v>68191907.090000004</v>
+      </c>
+      <c r="H397" s="4">
+        <v>53306905.640000001</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>115</v>
+      </c>
+      <c r="B398" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C398" t="s">
+        <v>9</v>
+      </c>
+      <c r="D398">
+        <v>1022</v>
+      </c>
+      <c r="E398" t="s">
+        <v>28</v>
+      </c>
+      <c r="F398" s="4">
+        <v>60538087.920000002</v>
+      </c>
+      <c r="G398" s="4">
+        <v>371175.74</v>
+      </c>
+      <c r="H398" s="4">
+        <v>48003233.390000001</v>
+      </c>
+      <c r="I398" s="4">
+        <v>289415.44</v>
+      </c>
+      <c r="J398">
+        <v>131.68700000000001</v>
+      </c>
+      <c r="K398">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>115</v>
+      </c>
+      <c r="B399" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C399" t="s">
+        <v>9</v>
+      </c>
+      <c r="D399">
+        <v>1023</v>
+      </c>
+      <c r="E399" t="s">
+        <v>29</v>
+      </c>
+      <c r="F399" s="4">
+        <v>45750857.530000001</v>
+      </c>
+      <c r="H399" s="4">
+        <v>35801412.840000004</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>115</v>
+      </c>
+      <c r="B400" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C400" t="s">
+        <v>9</v>
+      </c>
+      <c r="D400">
+        <v>1024</v>
+      </c>
+      <c r="E400" t="s">
+        <v>30</v>
+      </c>
+      <c r="F400" s="4">
+        <v>65278697.590000004</v>
+      </c>
+      <c r="G400" s="4">
+        <v>3467853.76</v>
+      </c>
+      <c r="H400" s="4">
+        <v>51106512.990000002</v>
+      </c>
+      <c r="I400" s="4">
+        <v>2752727.74</v>
+      </c>
+      <c r="J400">
+        <v>1401.0989999999999</v>
+      </c>
+      <c r="K400">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>115</v>
+      </c>
+      <c r="B401" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C401" t="s">
+        <v>9</v>
+      </c>
+      <c r="D401">
+        <v>1026</v>
+      </c>
+      <c r="E401" t="s">
+        <v>31</v>
+      </c>
+      <c r="F401" s="4">
+        <v>46724190.710000001</v>
+      </c>
+      <c r="H401" s="4">
+        <v>36891138.619999997</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>115</v>
+      </c>
+      <c r="B402" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C402" t="s">
+        <v>9</v>
+      </c>
+      <c r="D402">
+        <v>1027</v>
+      </c>
+      <c r="E402" t="s">
+        <v>32</v>
+      </c>
+      <c r="F402" s="4">
+        <v>17331507.079999998</v>
+      </c>
+      <c r="H402" s="4">
+        <v>13728883.91</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>115</v>
+      </c>
+      <c r="B403" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C403" t="s">
+        <v>9</v>
+      </c>
+      <c r="D403">
+        <v>1028</v>
+      </c>
+      <c r="E403" t="s">
+        <v>33</v>
+      </c>
+      <c r="F403" s="4">
+        <v>41159435.259999998</v>
+      </c>
+      <c r="H403" s="4">
+        <v>32255111.190000001</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>115</v>
+      </c>
+      <c r="B404" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C404" t="s">
+        <v>9</v>
+      </c>
+      <c r="D404">
+        <v>1029</v>
+      </c>
+      <c r="E404" t="s">
+        <v>34</v>
+      </c>
+      <c r="F404" s="4">
+        <v>34929469.159999996</v>
+      </c>
+      <c r="H404" s="4">
+        <v>27405082.010000002</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>115</v>
+      </c>
+      <c r="B405" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C405" t="s">
+        <v>9</v>
+      </c>
+      <c r="D405">
+        <v>1030</v>
+      </c>
+      <c r="E405" t="s">
+        <v>35</v>
+      </c>
+      <c r="F405" s="4">
+        <v>15638475.49</v>
+      </c>
+      <c r="H405" s="4">
+        <v>12321787.029999999</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>115</v>
+      </c>
+      <c r="B406" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C406" t="s">
+        <v>9</v>
+      </c>
+      <c r="D406">
+        <v>1031</v>
+      </c>
+      <c r="E406" t="s">
+        <v>36</v>
+      </c>
+      <c r="F406" s="4">
+        <v>72247304.689999998</v>
+      </c>
+      <c r="G406" s="4">
+        <v>1497303.52</v>
+      </c>
+      <c r="H406" s="4">
+        <v>56928508.450000003</v>
+      </c>
+      <c r="I406" s="4">
+        <v>1214833.24</v>
+      </c>
+      <c r="J406">
+        <v>439.35399999999998</v>
+      </c>
+      <c r="K406">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>115</v>
+      </c>
+      <c r="B407" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C407" t="s">
+        <v>9</v>
+      </c>
+      <c r="D407">
+        <v>1032</v>
+      </c>
+      <c r="E407" t="s">
+        <v>37</v>
+      </c>
+      <c r="F407" s="4">
+        <v>47667556.600000001</v>
+      </c>
+      <c r="H407" s="4">
+        <v>37394621.009999998</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>115</v>
+      </c>
+      <c r="B408" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C408" t="s">
+        <v>9</v>
+      </c>
+      <c r="D408">
+        <v>1033</v>
+      </c>
+      <c r="E408" t="s">
+        <v>38</v>
+      </c>
+      <c r="F408" s="4">
+        <v>33330247.760000002</v>
+      </c>
+      <c r="G408" s="4">
+        <v>1688857.96</v>
+      </c>
+      <c r="H408" s="4">
+        <v>26378999.84</v>
+      </c>
+      <c r="I408" s="4">
+        <v>1309907.1399999999</v>
+      </c>
+      <c r="J408">
+        <v>18.065999999999999</v>
+      </c>
+      <c r="K408">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>115</v>
+      </c>
+      <c r="B409" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C409" t="s">
+        <v>9</v>
+      </c>
+      <c r="D409">
+        <v>1035</v>
+      </c>
+      <c r="E409" t="s">
+        <v>39</v>
+      </c>
+      <c r="F409" s="4">
+        <v>31003395.5</v>
+      </c>
+      <c r="H409" s="4">
+        <v>24332336.329999998</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>115</v>
+      </c>
+      <c r="B410" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C410" t="s">
+        <v>9</v>
+      </c>
+      <c r="D410">
+        <v>1036</v>
+      </c>
+      <c r="E410" t="s">
+        <v>40</v>
+      </c>
+      <c r="F410" s="4">
+        <v>14949155.640000001</v>
+      </c>
+      <c r="H410" s="4">
+        <v>11715735.189999999</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>115</v>
+      </c>
+      <c r="B411" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C411" t="s">
+        <v>9</v>
+      </c>
+      <c r="D411">
+        <v>1038</v>
+      </c>
+      <c r="E411" t="s">
+        <v>42</v>
+      </c>
+      <c r="F411" s="4">
+        <v>69445227.329999998</v>
+      </c>
+      <c r="G411" s="4">
+        <v>1959046.56</v>
+      </c>
+      <c r="H411" s="4">
+        <v>54352119.909999996</v>
+      </c>
+      <c r="I411" s="4">
+        <v>1551592.34</v>
+      </c>
+      <c r="J411">
+        <v>547.01</v>
+      </c>
+      <c r="K411">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>115</v>
+      </c>
+      <c r="B412" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C412" t="s">
+        <v>9</v>
+      </c>
+      <c r="D412">
+        <v>1039</v>
+      </c>
+      <c r="E412" t="s">
+        <v>43</v>
+      </c>
+      <c r="F412" s="4">
+        <v>58173783.700000003</v>
+      </c>
+      <c r="H412" s="4">
+        <v>45602357.539999999</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>115</v>
+      </c>
+      <c r="B413" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C413" t="s">
+        <v>9</v>
+      </c>
+      <c r="D413">
+        <v>1042</v>
+      </c>
+      <c r="E413" t="s">
+        <v>44</v>
+      </c>
+      <c r="F413" s="4">
+        <v>42577555.740000002</v>
+      </c>
+      <c r="G413" s="4">
+        <v>2381555</v>
+      </c>
+      <c r="H413" s="4">
+        <v>33473280.289999999</v>
+      </c>
+      <c r="I413" s="4">
+        <v>1828474.43</v>
+      </c>
+      <c r="J413">
+        <v>186.131</v>
+      </c>
+      <c r="K413">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>115</v>
+      </c>
+      <c r="B414" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C414" t="s">
+        <v>9</v>
+      </c>
+      <c r="D414">
+        <v>1043</v>
+      </c>
+      <c r="E414" t="s">
+        <v>45</v>
+      </c>
+      <c r="F414" s="4">
+        <v>38352554.640000001</v>
+      </c>
+      <c r="H414" s="4">
+        <v>30047049.620000001</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>115</v>
+      </c>
+      <c r="B415" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C415" t="s">
+        <v>9</v>
+      </c>
+      <c r="D415">
+        <v>1044</v>
+      </c>
+      <c r="E415" t="s">
+        <v>46</v>
+      </c>
+      <c r="F415" s="4">
+        <v>14212862.5</v>
+      </c>
+      <c r="H415" s="4">
+        <v>11146325.449999999</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>115</v>
+      </c>
+      <c r="B416" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C416" t="s">
+        <v>9</v>
+      </c>
+      <c r="D416">
+        <v>1045</v>
+      </c>
+      <c r="E416" t="s">
+        <v>47</v>
+      </c>
+      <c r="F416" s="4">
+        <v>13572968.390000001</v>
+      </c>
+      <c r="H416" s="4">
+        <v>10698985.73</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>115</v>
+      </c>
+      <c r="B417" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C417" t="s">
+        <v>9</v>
+      </c>
+      <c r="D417">
+        <v>1046</v>
+      </c>
+      <c r="E417" t="s">
+        <v>48</v>
+      </c>
+      <c r="F417" s="4">
+        <v>19906801.18</v>
+      </c>
+      <c r="H417" s="4">
+        <v>15607871.029999999</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>115</v>
+      </c>
+      <c r="B418" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C418" t="s">
+        <v>9</v>
+      </c>
+      <c r="D418">
+        <v>1050</v>
+      </c>
+      <c r="E418" t="s">
+        <v>49</v>
+      </c>
+      <c r="F418" s="4">
+        <v>35914664.009999998</v>
+      </c>
+      <c r="H418" s="4">
+        <v>28125391.300000001</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>115</v>
+      </c>
+      <c r="B419" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C419" t="s">
+        <v>9</v>
+      </c>
+      <c r="D419">
+        <v>1051</v>
+      </c>
+      <c r="E419" t="s">
+        <v>50</v>
+      </c>
+      <c r="F419" s="4">
+        <v>79750599.299999997</v>
+      </c>
+      <c r="G419" s="4">
+        <v>195462.9</v>
+      </c>
+      <c r="H419" s="4">
+        <v>63519372.219999999</v>
+      </c>
+      <c r="I419" s="4">
+        <v>149625.07</v>
+      </c>
+      <c r="J419">
+        <v>59.56</v>
+      </c>
+      <c r="K419">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>115</v>
+      </c>
+      <c r="B420" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C420" t="s">
+        <v>9</v>
+      </c>
+      <c r="D420">
+        <v>1052</v>
+      </c>
+      <c r="E420" t="s">
+        <v>51</v>
+      </c>
+      <c r="F420" s="4">
+        <v>35392656.880000003</v>
+      </c>
+      <c r="G420" s="4">
+        <v>105600.75</v>
+      </c>
+      <c r="H420" s="4">
+        <v>27854534.66</v>
+      </c>
+      <c r="I420" s="4">
+        <v>77944.84</v>
+      </c>
+      <c r="J420">
+        <v>17</v>
+      </c>
+      <c r="K420">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>115</v>
+      </c>
+      <c r="B421" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C421" t="s">
+        <v>9</v>
+      </c>
+      <c r="D421">
+        <v>1053</v>
+      </c>
+      <c r="E421" t="s">
+        <v>52</v>
+      </c>
+      <c r="F421" s="4">
+        <v>34443165.789999999</v>
+      </c>
+      <c r="H421" s="4">
+        <v>27029245</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>115</v>
+      </c>
+      <c r="B422" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C422" t="s">
+        <v>9</v>
+      </c>
+      <c r="D422">
+        <v>1054</v>
+      </c>
+      <c r="E422" t="s">
+        <v>53</v>
+      </c>
+      <c r="F422" s="4">
+        <v>47403736.880000003</v>
+      </c>
+      <c r="G422" s="4">
+        <v>1635846.74</v>
+      </c>
+      <c r="H422" s="4">
+        <v>37095098.219999999</v>
+      </c>
+      <c r="I422" s="4">
+        <v>1300696.1499999999</v>
+      </c>
+      <c r="J422">
+        <v>419.62</v>
+      </c>
+      <c r="K422">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>115</v>
+      </c>
+      <c r="B423" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C423" t="s">
+        <v>9</v>
+      </c>
+      <c r="D423">
+        <v>1055</v>
+      </c>
+      <c r="E423" t="s">
+        <v>54</v>
+      </c>
+      <c r="F423" s="4">
+        <v>41169094.390000001</v>
+      </c>
+      <c r="G423" s="4">
+        <v>942482.11</v>
+      </c>
+      <c r="H423" s="4">
+        <v>32464285.640000001</v>
+      </c>
+      <c r="I423" s="4">
+        <v>739013.51</v>
+      </c>
+      <c r="J423">
+        <v>415.80599999999998</v>
+      </c>
+      <c r="K423">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>115</v>
+      </c>
+      <c r="B424" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C424" t="s">
+        <v>9</v>
+      </c>
+      <c r="D424">
+        <v>1056</v>
+      </c>
+      <c r="E424" t="s">
+        <v>55</v>
+      </c>
+      <c r="F424" s="4">
+        <v>41305335.460000001</v>
+      </c>
+      <c r="G424" s="4">
+        <v>44134.9</v>
+      </c>
+      <c r="H424" s="4">
+        <v>32440686.82</v>
+      </c>
+      <c r="I424" s="4">
+        <v>34195.43</v>
+      </c>
+      <c r="J424">
+        <v>24</v>
+      </c>
+      <c r="K424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>115</v>
+      </c>
+      <c r="B425" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C425" t="s">
+        <v>9</v>
+      </c>
+      <c r="D425">
+        <v>1057</v>
+      </c>
+      <c r="E425" t="s">
+        <v>56</v>
+      </c>
+      <c r="F425" s="4">
+        <v>73237128.420000002</v>
+      </c>
+      <c r="G425" s="4">
+        <v>3828738.3</v>
+      </c>
+      <c r="H425" s="4">
+        <v>57615765.310000002</v>
+      </c>
+      <c r="I425" s="4">
+        <v>3059499.01</v>
+      </c>
+      <c r="J425">
+        <v>1167.039</v>
+      </c>
+      <c r="K425">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>115</v>
+      </c>
+      <c r="B426" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C426" t="s">
+        <v>9</v>
+      </c>
+      <c r="D426">
+        <v>1058</v>
+      </c>
+      <c r="E426" t="s">
+        <v>57</v>
+      </c>
+      <c r="F426" s="4">
+        <v>42966636.369999997</v>
+      </c>
+      <c r="G426" s="4">
+        <v>3679697.71</v>
+      </c>
+      <c r="H426" s="4">
+        <v>33394476.030000001</v>
+      </c>
+      <c r="I426" s="4">
+        <v>2851006.16</v>
+      </c>
+      <c r="J426">
+        <v>1160</v>
+      </c>
+      <c r="K426">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>115</v>
+      </c>
+      <c r="B427" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C427" t="s">
+        <v>9</v>
+      </c>
+      <c r="D427">
+        <v>1059</v>
+      </c>
+      <c r="E427" t="s">
+        <v>58</v>
+      </c>
+      <c r="F427" s="4">
+        <v>32265253.960000001</v>
+      </c>
+      <c r="H427" s="4">
+        <v>25243969.190000001</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>115</v>
+      </c>
+      <c r="B428" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C428" t="s">
+        <v>9</v>
+      </c>
+      <c r="D428">
+        <v>1060</v>
+      </c>
+      <c r="E428" t="s">
+        <v>59</v>
+      </c>
+      <c r="F428" s="4">
+        <v>35547999.460000001</v>
+      </c>
+      <c r="H428" s="4">
+        <v>28326779.449999999</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>115</v>
+      </c>
+      <c r="B429" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C429" t="s">
+        <v>9</v>
+      </c>
+      <c r="D429">
+        <v>1061</v>
+      </c>
+      <c r="E429" t="s">
+        <v>60</v>
+      </c>
+      <c r="F429" s="4">
+        <v>56910439.799999997</v>
+      </c>
+      <c r="G429" s="4">
+        <v>738526.35</v>
+      </c>
+      <c r="H429" s="4">
+        <v>44499893.460000001</v>
+      </c>
+      <c r="I429" s="4">
+        <v>569493.63</v>
+      </c>
+      <c r="J429">
+        <v>66</v>
+      </c>
+      <c r="K429">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>115</v>
+      </c>
+      <c r="B430" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C430" t="s">
+        <v>9</v>
+      </c>
+      <c r="D430">
+        <v>1066</v>
+      </c>
+      <c r="E430" t="s">
+        <v>111</v>
+      </c>
+      <c r="F430" s="4">
+        <v>2178929.0099999998</v>
+      </c>
+      <c r="H430" s="4">
+        <v>1696347.31</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>115</v>
+      </c>
+      <c r="B431" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C431" t="s">
+        <v>9</v>
+      </c>
+      <c r="D431">
+        <v>1067</v>
+      </c>
+      <c r="E431" t="s">
+        <v>61</v>
+      </c>
+      <c r="F431" s="4">
+        <v>32151783.530000001</v>
+      </c>
+      <c r="G431" s="4">
+        <v>187200.61</v>
+      </c>
+      <c r="H431" s="4">
+        <v>25271770.600000001</v>
+      </c>
+      <c r="I431" s="4">
+        <v>145576.92000000001</v>
+      </c>
+      <c r="J431">
+        <v>60</v>
+      </c>
+      <c r="K431">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>115</v>
+      </c>
+      <c r="B432" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C432" t="s">
+        <v>9</v>
+      </c>
+      <c r="D432">
+        <v>1068</v>
+      </c>
+      <c r="E432" t="s">
+        <v>62</v>
+      </c>
+      <c r="F432" s="4">
+        <v>91753051.219999999</v>
+      </c>
+      <c r="H432" s="4">
+        <v>71959454.25</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>115</v>
+      </c>
+      <c r="B433" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C433" t="s">
+        <v>9</v>
+      </c>
+      <c r="D433">
+        <v>1074</v>
+      </c>
+      <c r="E433" t="s">
+        <v>63</v>
+      </c>
+      <c r="F433" s="4">
+        <v>15393467.220000001</v>
+      </c>
+      <c r="G433" s="4">
+        <v>69000</v>
+      </c>
+      <c r="H433" s="4">
+        <v>12073634.369999999</v>
+      </c>
+      <c r="I433" s="4">
+        <v>49586.78</v>
+      </c>
+      <c r="J433">
+        <v>30</v>
+      </c>
+      <c r="K433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>115</v>
+      </c>
+      <c r="B434" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C434" t="s">
+        <v>9</v>
+      </c>
+      <c r="D434">
+        <v>1075</v>
+      </c>
+      <c r="E434" t="s">
+        <v>64</v>
+      </c>
+      <c r="F434" s="4">
+        <v>47437845.329999998</v>
+      </c>
+      <c r="H434" s="4">
+        <v>37538153.850000001</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>115</v>
+      </c>
+      <c r="B435" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C435" t="s">
+        <v>9</v>
+      </c>
+      <c r="D435">
+        <v>1076</v>
+      </c>
+      <c r="E435" t="s">
+        <v>65</v>
+      </c>
+      <c r="F435" s="4">
+        <v>43087893.049999997</v>
+      </c>
+      <c r="H435" s="4">
+        <v>33960383.57</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>115</v>
+      </c>
+      <c r="B436" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C436" t="s">
+        <v>9</v>
+      </c>
+      <c r="D436">
+        <v>1077</v>
+      </c>
+      <c r="E436" t="s">
+        <v>66</v>
+      </c>
+      <c r="F436" s="4">
+        <v>52028513.020000003</v>
+      </c>
+      <c r="G436" s="4">
+        <v>635540.43000000005</v>
+      </c>
+      <c r="H436" s="4">
+        <v>40742834.200000003</v>
+      </c>
+      <c r="I436" s="4">
+        <v>496497.06</v>
+      </c>
+      <c r="J436">
+        <v>120.59099999999999</v>
+      </c>
+      <c r="K436">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>115</v>
+      </c>
+      <c r="B437" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C437" t="s">
+        <v>9</v>
+      </c>
+      <c r="D437">
+        <v>1078</v>
+      </c>
+      <c r="E437" t="s">
+        <v>67</v>
+      </c>
+      <c r="F437" s="4">
+        <v>43903735.109999999</v>
+      </c>
+      <c r="G437" s="4">
+        <v>784999.12</v>
+      </c>
+      <c r="H437" s="4">
+        <v>34242153.619999997</v>
+      </c>
+      <c r="I437" s="4">
+        <v>592716.26</v>
+      </c>
+      <c r="J437">
+        <v>1</v>
+      </c>
+      <c r="K437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>115</v>
+      </c>
+      <c r="B438" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C438" t="s">
+        <v>9</v>
+      </c>
+      <c r="D438">
+        <v>1080</v>
+      </c>
+      <c r="E438" t="s">
+        <v>68</v>
+      </c>
+      <c r="F438" s="4">
+        <v>38886774.640000001</v>
+      </c>
+      <c r="G438" s="4">
+        <v>1623368.54</v>
+      </c>
+      <c r="H438" s="4">
+        <v>30316530.23</v>
+      </c>
+      <c r="I438" s="4">
+        <v>1292091.53</v>
+      </c>
+      <c r="J438">
+        <v>491.27</v>
+      </c>
+      <c r="K438">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>115</v>
+      </c>
+      <c r="B439" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C439" t="s">
+        <v>9</v>
+      </c>
+      <c r="D439">
+        <v>1081</v>
+      </c>
+      <c r="E439" t="s">
+        <v>69</v>
+      </c>
+      <c r="F439" s="4">
+        <v>34380699.439999998</v>
+      </c>
+      <c r="H439" s="4">
+        <v>27176756.629999999</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>115</v>
+      </c>
+      <c r="B440" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C440" t="s">
+        <v>9</v>
+      </c>
+      <c r="D440">
+        <v>1082</v>
+      </c>
+      <c r="E440" t="s">
+        <v>70</v>
+      </c>
+      <c r="F440" s="4">
+        <v>15100898.42</v>
+      </c>
+      <c r="H440" s="4">
+        <v>11947943.4</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>115</v>
+      </c>
+      <c r="B441" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C441" t="s">
+        <v>9</v>
+      </c>
+      <c r="D441">
+        <v>1084</v>
+      </c>
+      <c r="E441" t="s">
+        <v>71</v>
+      </c>
+      <c r="F441" s="4">
+        <v>12358456.99</v>
+      </c>
+      <c r="H441" s="4">
+        <v>9700556.8800000008</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>115</v>
+      </c>
+      <c r="B442" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C442" t="s">
+        <v>9</v>
+      </c>
+      <c r="D442">
+        <v>1085</v>
+      </c>
+      <c r="E442" t="s">
+        <v>72</v>
+      </c>
+      <c r="F442" s="4">
+        <v>19827623.5</v>
+      </c>
+      <c r="H442" s="4">
+        <v>15491710.66</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>115</v>
+      </c>
+      <c r="B443" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C443" t="s">
+        <v>9</v>
+      </c>
+      <c r="D443">
+        <v>1086</v>
+      </c>
+      <c r="E443" t="s">
+        <v>73</v>
+      </c>
+      <c r="F443" s="4">
+        <v>36928255.649999999</v>
+      </c>
+      <c r="H443" s="4">
+        <v>28818448.350000001</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>115</v>
+      </c>
+      <c r="B444" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C444" t="s">
+        <v>9</v>
+      </c>
+      <c r="D444">
+        <v>1087</v>
+      </c>
+      <c r="E444" t="s">
+        <v>74</v>
+      </c>
+      <c r="F444" s="4">
+        <v>71187131.269999996</v>
+      </c>
+      <c r="G444" s="4">
+        <v>4748492.82</v>
+      </c>
+      <c r="H444" s="4">
+        <v>55977482.960000001</v>
+      </c>
+      <c r="I444" s="4">
+        <v>3714698.86</v>
+      </c>
+      <c r="J444">
+        <v>1407.2850000000001</v>
+      </c>
+      <c r="K444">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>115</v>
+      </c>
+      <c r="B445" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C445" t="s">
+        <v>9</v>
+      </c>
+      <c r="D445">
+        <v>1088</v>
+      </c>
+      <c r="E445" t="s">
+        <v>75</v>
+      </c>
+      <c r="F445" s="4">
+        <v>37897777.57</v>
+      </c>
+      <c r="H445" s="4">
+        <v>30561161.550000001</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>115</v>
+      </c>
+      <c r="B446" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C446" t="s">
+        <v>9</v>
+      </c>
+      <c r="D446">
+        <v>1092</v>
+      </c>
+      <c r="E446" t="s">
+        <v>76</v>
+      </c>
+      <c r="F446" s="4">
+        <v>43702376.329999998</v>
+      </c>
+      <c r="G446" s="4">
+        <v>1199999.25</v>
+      </c>
+      <c r="H446" s="4">
+        <v>34076997.710000001</v>
+      </c>
+      <c r="I446" s="4">
+        <v>929751.51</v>
+      </c>
+      <c r="J446">
+        <v>1</v>
+      </c>
+      <c r="K446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>115</v>
+      </c>
+      <c r="B447" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C447" t="s">
+        <v>9</v>
+      </c>
+      <c r="D447">
+        <v>1093</v>
+      </c>
+      <c r="E447" t="s">
+        <v>77</v>
+      </c>
+      <c r="F447" s="4">
+        <v>59219789.719999999</v>
+      </c>
+      <c r="H447" s="4">
+        <v>46620339.280000001</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>115</v>
+      </c>
+      <c r="B448" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C448" t="s">
+        <v>9</v>
+      </c>
+      <c r="D448">
+        <v>1096</v>
+      </c>
+      <c r="E448" t="s">
+        <v>78</v>
+      </c>
+      <c r="F448" s="4">
+        <v>44977363.57</v>
+      </c>
+      <c r="H448" s="4">
+        <v>35362712.409999996</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>115</v>
+      </c>
+      <c r="B449" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C449" t="s">
+        <v>9</v>
+      </c>
+      <c r="D449">
+        <v>1097</v>
+      </c>
+      <c r="E449" t="s">
+        <v>79</v>
+      </c>
+      <c r="F449" s="4">
+        <v>33183236.73</v>
+      </c>
+      <c r="H449" s="4">
+        <v>26173017.879999999</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>115</v>
+      </c>
+      <c r="B450" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C450" t="s">
+        <v>9</v>
+      </c>
+      <c r="D450">
+        <v>1098</v>
+      </c>
+      <c r="E450" t="s">
+        <v>80</v>
+      </c>
+      <c r="F450" s="4">
+        <v>22248946.969999999</v>
+      </c>
+      <c r="H450" s="4">
+        <v>17362240.5</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>115</v>
+      </c>
+      <c r="B451" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C451" t="s">
+        <v>9</v>
+      </c>
+      <c r="D451">
+        <v>1099</v>
+      </c>
+      <c r="E451" t="s">
+        <v>81</v>
+      </c>
+      <c r="F451" s="4">
+        <v>34732898.229999997</v>
+      </c>
+      <c r="G451" s="4">
+        <v>204999</v>
+      </c>
+      <c r="H451" s="4">
+        <v>27832238.059999999</v>
+      </c>
+      <c r="I451" s="4">
+        <v>158831.87</v>
+      </c>
+      <c r="J451">
+        <v>1</v>
+      </c>
+      <c r="K451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>115</v>
+      </c>
+      <c r="B452" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C452" t="s">
+        <v>9</v>
+      </c>
+      <c r="D452">
+        <v>1100</v>
+      </c>
+      <c r="E452" t="s">
+        <v>82</v>
+      </c>
+      <c r="F452" s="4">
+        <v>37049536.359999999</v>
+      </c>
+      <c r="H452" s="4">
+        <v>29124376.210000001</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>115</v>
+      </c>
+      <c r="B453" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C453" t="s">
+        <v>9</v>
+      </c>
+      <c r="D453">
+        <v>1102</v>
+      </c>
+      <c r="E453" t="s">
+        <v>112</v>
+      </c>
+      <c r="F453" s="4">
+        <v>2484491.86</v>
+      </c>
+      <c r="H453" s="4">
+        <v>1939097.03</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>115</v>
+      </c>
+      <c r="B454" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C454" t="s">
+        <v>9</v>
+      </c>
+      <c r="D454">
+        <v>1103</v>
+      </c>
+      <c r="E454" t="s">
+        <v>113</v>
+      </c>
+      <c r="F454" s="4">
+        <v>3431028.75</v>
+      </c>
+      <c r="H454" s="4">
+        <v>2674351.2000000002</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>115</v>
+      </c>
+      <c r="B455" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C455" t="s">
+        <v>9</v>
+      </c>
+      <c r="D455">
+        <v>1106</v>
+      </c>
+      <c r="E455" t="s">
+        <v>83</v>
+      </c>
+      <c r="F455" s="4">
+        <v>18822712.5</v>
+      </c>
+      <c r="H455" s="4">
+        <v>14778846.23</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>115</v>
+      </c>
+      <c r="B456" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C456" t="s">
+        <v>9</v>
+      </c>
+      <c r="D456">
+        <v>1108</v>
+      </c>
+      <c r="E456" t="s">
+        <v>84</v>
+      </c>
+      <c r="F456" s="4">
+        <v>44955894.310000002</v>
+      </c>
+      <c r="G456" s="4">
+        <v>192953</v>
+      </c>
+      <c r="H456" s="4">
+        <v>35389225.32</v>
+      </c>
+      <c r="I456" s="4">
+        <v>155989.37</v>
+      </c>
+      <c r="J456">
+        <v>61.701999999999998</v>
+      </c>
+      <c r="K456">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>115</v>
+      </c>
+      <c r="B457" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C457" t="s">
+        <v>9</v>
+      </c>
+      <c r="D457">
+        <v>1109</v>
+      </c>
+      <c r="E457" t="s">
+        <v>114</v>
+      </c>
+      <c r="F457" s="4">
+        <v>2920548.05</v>
+      </c>
+      <c r="H457" s="4">
+        <v>2281325.66</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>115</v>
+      </c>
+      <c r="B458" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C458" t="s">
+        <v>9</v>
+      </c>
+      <c r="D458">
+        <v>1110</v>
+      </c>
+      <c r="E458" t="s">
+        <v>85</v>
+      </c>
+      <c r="F458" s="4">
+        <v>21798931.739999998</v>
+      </c>
+      <c r="H458" s="4">
+        <v>17108826.670000002</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>115</v>
+      </c>
+      <c r="B459" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C459" t="s">
+        <v>9</v>
+      </c>
+      <c r="D459">
+        <v>1111</v>
+      </c>
+      <c r="E459" t="s">
+        <v>86</v>
+      </c>
+      <c r="F459" s="4">
+        <v>23865124.760000002</v>
+      </c>
+      <c r="H459" s="4">
+        <v>18769817.079999998</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>115</v>
+      </c>
+      <c r="B460" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C460" t="s">
+        <v>9</v>
+      </c>
+      <c r="D460">
+        <v>1114</v>
+      </c>
+      <c r="E460" t="s">
+        <v>87</v>
+      </c>
+      <c r="F460" s="4">
+        <v>23682976.84</v>
+      </c>
+      <c r="H460" s="4">
+        <v>18538557.07</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>115</v>
+      </c>
+      <c r="B461" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C461" t="s">
+        <v>9</v>
+      </c>
+      <c r="D461">
+        <v>1115</v>
+      </c>
+      <c r="E461" t="s">
+        <v>88</v>
+      </c>
+      <c r="F461" s="4">
+        <v>39932253.32</v>
+      </c>
+      <c r="G461" s="4">
+        <v>775691.04</v>
+      </c>
+      <c r="H461" s="4">
+        <v>31488483.34</v>
+      </c>
+      <c r="I461" s="4">
+        <v>612857.23</v>
+      </c>
+      <c r="J461">
+        <v>266.73</v>
+      </c>
+      <c r="K461">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>115</v>
+      </c>
+      <c r="B462" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C462" t="s">
+        <v>9</v>
+      </c>
+      <c r="D462">
+        <v>1116</v>
+      </c>
+      <c r="E462" t="s">
+        <v>89</v>
+      </c>
+      <c r="F462" s="4">
+        <v>31502965.699999999</v>
+      </c>
+      <c r="H462" s="4">
+        <v>24727677.82</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>115</v>
+      </c>
+      <c r="B463" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C463" t="s">
+        <v>9</v>
+      </c>
+      <c r="D463">
+        <v>1119</v>
+      </c>
+      <c r="E463" t="s">
+        <v>90</v>
+      </c>
+      <c r="F463" s="4">
+        <v>20544057.140000001</v>
+      </c>
+      <c r="H463" s="4">
+        <v>16085366.130000001</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>115</v>
+      </c>
+      <c r="B464" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C464" t="s">
+        <v>9</v>
+      </c>
+      <c r="D464">
+        <v>2997</v>
+      </c>
+      <c r="E464" t="s">
+        <v>91</v>
+      </c>
+      <c r="F464" s="4">
+        <v>241889697.61000001</v>
+      </c>
+      <c r="G464" s="4">
+        <v>22493405.199999999</v>
+      </c>
+      <c r="H464" s="4">
+        <v>192761532.61000001</v>
+      </c>
+      <c r="I464" s="4">
+        <v>17495564.300000001</v>
+      </c>
+      <c r="J464">
+        <v>6577.8130000000001</v>
+      </c>
+      <c r="K464">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>115</v>
+      </c>
+      <c r="B465" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C465" t="s">
+        <v>9</v>
+      </c>
+      <c r="D465">
+        <v>2998</v>
+      </c>
+      <c r="E465" t="s">
+        <v>92</v>
+      </c>
+      <c r="F465" s="4">
+        <v>100340877.77</v>
+      </c>
+      <c r="G465" s="4">
+        <v>12071621.35</v>
+      </c>
+      <c r="H465" s="4">
+        <v>78371793.510000005</v>
+      </c>
+      <c r="I465" s="4">
+        <v>9381145.9900000002</v>
+      </c>
+      <c r="J465">
+        <v>4094</v>
+      </c>
+      <c r="K465">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>115</v>
+      </c>
+      <c r="B466" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C466" t="s">
+        <v>9</v>
+      </c>
+      <c r="D466">
+        <v>2999</v>
+      </c>
+      <c r="E466" t="s">
+        <v>93</v>
+      </c>
+      <c r="F466" s="4">
+        <v>109477974.09999999</v>
+      </c>
+      <c r="G466" s="4">
+        <v>10933837.640000001</v>
+      </c>
+      <c r="H466" s="4">
+        <v>85602512.510000005</v>
+      </c>
+      <c r="I466" s="4">
+        <v>8494776.7400000002</v>
+      </c>
+      <c r="J466">
+        <v>3419.3229999999999</v>
+      </c>
+      <c r="K466">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>115</v>
+      </c>
+      <c r="B467" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C467" t="s">
+        <v>9</v>
+      </c>
+      <c r="D467">
+        <v>3601</v>
+      </c>
+      <c r="E467" t="s">
+        <v>94</v>
+      </c>
+      <c r="F467" s="4">
+        <v>136002132.87</v>
+      </c>
+      <c r="G467" s="4">
+        <v>11599242.380000001</v>
+      </c>
+      <c r="H467" s="4">
+        <v>106478260.76000001</v>
+      </c>
+      <c r="I467" s="4">
+        <v>9013348.0800000001</v>
+      </c>
+      <c r="J467">
+        <v>3823.4110000000001</v>
+      </c>
+      <c r="K467">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>115</v>
+      </c>
+      <c r="B468" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C468" t="s">
+        <v>9</v>
+      </c>
+      <c r="D468">
+        <v>3602</v>
+      </c>
+      <c r="E468" t="s">
+        <v>95</v>
+      </c>
+      <c r="F468" s="4">
+        <v>120412076.77</v>
+      </c>
+      <c r="G468" s="4">
+        <v>7361323.9900000002</v>
+      </c>
+      <c r="H468" s="4">
+        <v>94344890.980000004</v>
+      </c>
+      <c r="I468" s="4">
+        <v>5702035.4800000004</v>
+      </c>
+      <c r="J468">
+        <v>1803.644</v>
+      </c>
+      <c r="K468">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>115</v>
+      </c>
+      <c r="B469" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C469" t="s">
+        <v>9</v>
+      </c>
+      <c r="D469">
+        <v>3603</v>
+      </c>
+      <c r="E469" t="s">
+        <v>96</v>
+      </c>
+      <c r="F469" s="4">
+        <v>115237654.79000001</v>
+      </c>
+      <c r="G469" s="4">
+        <v>4938615.1399999997</v>
+      </c>
+      <c r="H469" s="4">
+        <v>90254124.469999999</v>
+      </c>
+      <c r="I469" s="4">
+        <v>3826863.1</v>
+      </c>
+      <c r="J469">
+        <v>1528.4469999999999</v>
+      </c>
+      <c r="K469">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>115</v>
+      </c>
+      <c r="B470" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C470" t="s">
+        <v>9</v>
+      </c>
+      <c r="D470">
+        <v>3604</v>
+      </c>
+      <c r="E470" t="s">
+        <v>97</v>
+      </c>
+      <c r="F470" s="4">
+        <v>69573379.040000007</v>
+      </c>
+      <c r="G470" s="4">
+        <v>8806264.4800000004</v>
+      </c>
+      <c r="H470" s="4">
+        <v>54623082.850000001</v>
+      </c>
+      <c r="I470" s="4">
+        <v>6793807.0599999996</v>
+      </c>
+      <c r="J470">
+        <v>1784.588</v>
+      </c>
+      <c r="K470">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>115</v>
+      </c>
+      <c r="B471" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C471" t="s">
+        <v>9</v>
+      </c>
+      <c r="D471">
+        <v>3605</v>
+      </c>
+      <c r="E471" t="s">
+        <v>98</v>
+      </c>
+      <c r="F471" s="4">
+        <v>173556013.97999999</v>
+      </c>
+      <c r="G471" s="4">
+        <v>15394914.59</v>
+      </c>
+      <c r="H471" s="4">
+        <v>136990140.88999999</v>
+      </c>
+      <c r="I471" s="4">
+        <v>11949824.25</v>
+      </c>
+      <c r="J471">
+        <v>4216.2920000000004</v>
+      </c>
+      <c r="K471">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>115</v>
+      </c>
+      <c r="B472" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C472" t="s">
+        <v>9</v>
+      </c>
+      <c r="D472">
+        <v>3606</v>
+      </c>
+      <c r="E472" t="s">
+        <v>99</v>
+      </c>
+      <c r="F472" s="4">
+        <v>86054597.590000004</v>
+      </c>
+      <c r="H472" s="4">
+        <v>67725247.239999995</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>115</v>
+      </c>
+      <c r="B473" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C473" t="s">
+        <v>9</v>
+      </c>
+      <c r="D473">
+        <v>3608</v>
+      </c>
+      <c r="E473" t="s">
+        <v>100</v>
+      </c>
+      <c r="F473" s="4">
+        <v>125246388.63</v>
+      </c>
+      <c r="G473" s="4">
+        <v>4237502.97</v>
+      </c>
+      <c r="H473" s="4">
+        <v>97578594.370000005</v>
+      </c>
+      <c r="I473" s="4">
+        <v>3333050.55</v>
+      </c>
+      <c r="J473">
+        <v>1175.903</v>
+      </c>
+      <c r="K473">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>115</v>
+      </c>
+      <c r="B474" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C474" t="s">
+        <v>9</v>
+      </c>
+      <c r="D474">
+        <v>3613</v>
+      </c>
+      <c r="E474" t="s">
+        <v>101</v>
+      </c>
+      <c r="F474" s="4">
+        <v>121393592.06999999</v>
+      </c>
+      <c r="G474" s="4">
+        <v>9000407.8800000008</v>
+      </c>
+      <c r="H474" s="4">
+        <v>95800738.920000002</v>
+      </c>
+      <c r="I474" s="4">
+        <v>7029934.8200000003</v>
+      </c>
+      <c r="J474">
+        <v>2833.3890000000001</v>
+      </c>
+      <c r="K474">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>115</v>
+      </c>
+      <c r="B475" s="5">
+        <v>46300</v>
+      </c>
+      <c r="C475" t="s">
+        <v>9</v>
+      </c>
+      <c r="D475">
+        <v>4001</v>
+      </c>
+      <c r="E475" t="s">
+        <v>102</v>
+      </c>
+      <c r="F475" s="4">
+        <v>20166128.890000001</v>
+      </c>
+      <c r="G475" s="4">
+        <v>31242.75</v>
+      </c>
+      <c r="H475" s="4">
+        <v>15877252.41</v>
+      </c>
+      <c r="I475" s="4">
+        <v>26236.26</v>
+      </c>
+      <c r="J475">
+        <v>13</v>
+      </c>
+      <c r="K475">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{FE92DB44-9108-48C0-9E4D-CDD7D4A1EECC}"/>
